--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC19" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Germany_Bu" displayName="AveragesTable_Germany_Bu" ref="A1:EC19" headerRowCount="1">
   <autoFilter ref="A1:EC19"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -4994,13 +4994,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5084,139 +5084,139 @@
         <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>98.8</v>
+        <v>105</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>43</v>
+        <v>45.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AP11" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15.6</v>
+        <v>15.17</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.33</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.2</v>
+        <v>6.33</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>51.6</v>
+        <v>52.17</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>11.6</v>
+        <v>12.83</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.4</v>
+        <v>7.67</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.2</v>
+        <v>5.17</v>
       </c>
       <c r="BD11" t="n">
-        <v>19.4</v>
+        <v>19.67</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BH11" t="n">
-        <v>11.3</v>
+        <v>11.27</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BK11" t="n">
         <v>1</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BN11" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.9</v>
+        <v>4.73</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.4</v>
+        <v>6.55</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BT11" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BU11" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BV11" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BW11" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX11" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BY11" t="n">
         <v>3.35</v>
@@ -5225,28 +5225,28 @@
         <v>3.35</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.01</v>
+        <v>3.96</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.03</v>
+        <v>2.96</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="CE11" t="n">
         <v>1.23</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.84</v>
+        <v>3.79</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CI11" t="n">
         <v>2.48</v>
@@ -5255,10 +5255,10 @@
         <v>1.53</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CM11" t="n">
         <v>2.68</v>
@@ -5267,43 +5267,43 @@
         <v>2.08</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="CT11" t="n">
         <v>3.32</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CV11" t="n">
         <v>2.62</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CX11" t="n">
         <v>1.5</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="DB11" t="n">
         <v>1.26</v>
@@ -5312,82 +5312,82 @@
         <v>1.63</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="DE11" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="DH11" t="n">
-        <v>104.9</v>
+        <v>107.73</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.5</v>
+        <v>5.36</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="DM11" t="n">
-        <v>47.5</v>
+        <v>48.45</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="DP11" t="n">
-        <v>15.1</v>
+        <v>14.91</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.1</v>
+        <v>6.18</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>52.4</v>
+        <v>52.64</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.9</v>
+        <v>13.45</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.9</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ11" t="n">
         <v>5</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.3</v>
+        <v>21.27</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="12">
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="n">
         <v>5</v>
@@ -5812,82 +5812,82 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4</v>
+        <v>3.17</v>
       </c>
       <c r="H13" t="n">
-        <v>125.6</v>
+        <v>122.33</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="K13" t="n">
-        <v>4.4</v>
+        <v>4.83</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M13" t="n">
-        <v>59.6</v>
+        <v>57.83</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="P13" t="n">
-        <v>13.8</v>
+        <v>13.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="R13" t="n">
-        <v>7.6</v>
+        <v>7.83</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>49</v>
+        <v>48.33</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.4</v>
+        <v>13.17</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.4</v>
+        <v>10.17</v>
       </c>
       <c r="AB13" t="n">
         <v>3</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.6</v>
+        <v>23</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5971,70 +5971,70 @@
         <v>3.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.699999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.4</v>
+        <v>5.64</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT13" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BU13" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV13" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW13" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="BZ13" t="n">
         <v>2.51</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CC13" t="n">
         <v>3.14</v>
@@ -6049,28 +6049,28 @@
         <v>2.41</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="CH13" t="n">
         <v>1.56</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="CM13" t="n">
         <v>2.6</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CO13" t="n">
         <v>1.2</v>
@@ -6079,7 +6079,7 @@
         <v>1.65</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
@@ -6100,16 +6100,16 @@
         <v>1.56</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY13" t="n">
         <v>1.8</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DB13" t="n">
         <v>1.26</v>
@@ -6118,82 +6118,82 @@
         <v>1.67</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="DH13" t="n">
-        <v>114</v>
+        <v>113.27</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="DK13" t="n">
-        <v>5</v>
+        <v>5.18</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DM13" t="n">
-        <v>61.4</v>
+        <v>60.27</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.2</v>
+        <v>13.18</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.5</v>
+        <v>11.64</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.3</v>
+        <v>7.45</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.8</v>
+        <v>12.27</v>
       </c>
       <c r="DY13" t="n">
-        <v>9</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="EA13" t="n">
-        <v>23.7</v>
+        <v>23.82</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="14">

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="H2" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>47.17</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="P2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="R2" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>49.17</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>22.33</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.4</v>
       </c>
-      <c r="G2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H2" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M2" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P2" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="R2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE2" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AF2" t="n">
         <v>0.2</v>
@@ -1550,70 +1550,70 @@
         <v>3.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.5</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>90</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BU2" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BV2" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX2" t="n">
-        <v>80</v>
+        <v>72.73</v>
       </c>
       <c r="BY2" t="n">
-        <v>4.21</v>
+        <v>3.9</v>
       </c>
       <c r="BZ2" t="n">
-        <v>4.82</v>
+        <v>4.44</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.07</v>
+        <v>4.01</v>
       </c>
       <c r="CC2" t="n">
         <v>3.83</v>
@@ -1628,7 +1628,7 @@
         <v>2.42</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="CH2" t="n">
         <v>1.54</v>
@@ -1640,16 +1640,16 @@
         <v>1.63</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL2" t="n">
         <v>1.93</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CO2" t="n">
         <v>1.2</v>
@@ -1658,16 +1658,16 @@
         <v>1.72</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CR2" t="n">
         <v>1.35</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CU2" t="n">
         <v>1.59</v>
@@ -1682,10 +1682,10 @@
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="DA2" t="n">
         <v>2</v>
@@ -1694,85 +1694,85 @@
         <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="DH2" t="n">
-        <v>107.9</v>
+        <v>105.09</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="DM2" t="n">
-        <v>39.7</v>
+        <v>40.55</v>
       </c>
       <c r="DN2" t="n">
         <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.6</v>
+        <v>13.55</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.6</v>
+        <v>11.46</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.5</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>46.4</v>
+        <v>46.55</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.1</v>
+        <v>12.18</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.8</v>
+        <v>20.09</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="EC2" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>0.5</v>
@@ -1872,118 +1872,118 @@
         <v>1.67</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AI3" t="n">
-        <v>89.5</v>
+        <v>90.2</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AN3" t="n">
-        <v>35.75</v>
+        <v>39</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.75</v>
+        <v>8.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>51.25</v>
+        <v>53.4</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
-        <v>15</v>
+        <v>15.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.6</v>
+        <v>5.45</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,19 +1992,19 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BU3" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BV3" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BW3" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BX3" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BY3" t="n">
         <v>1.74</v>
@@ -2013,31 +2013,31 @@
         <v>1.78</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.22</v>
+        <v>4.18</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="CC3" t="n">
-        <v>4.01</v>
+        <v>3.61</v>
       </c>
       <c r="CD3" t="n">
-        <v>4.48</v>
+        <v>3.99</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.6</v>
@@ -2046,13 +2046,13 @@
         <v>1.48</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO3" t="n">
         <v>1.16</v>
@@ -2076,10 +2076,10 @@
         <v>1.65</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CX3" t="n">
         <v>1.56</v>
@@ -2097,85 +2097,85 @@
         <v>1.27</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DG3" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="DH3" t="n">
-        <v>109.3</v>
+        <v>107.82</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.5</v>
+        <v>4.18</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DM3" t="n">
-        <v>43.6</v>
+        <v>44.36</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="DP3" t="n">
-        <v>9.1</v>
+        <v>8.91</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.1</v>
+        <v>12.09</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>58.3</v>
+        <v>58.64</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.4</v>
+        <v>13.73</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.1</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.3</v>
+        <v>5.09</v>
       </c>
       <c r="EA3" t="n">
-        <v>15.2</v>
+        <v>15.36</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="H4" t="n">
-        <v>121.2</v>
+        <v>117.83</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="K4" t="n">
-        <v>6.2</v>
+        <v>5.67</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>63.8</v>
+        <v>63.17</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3.8</v>
+        <v>3.33</v>
       </c>
       <c r="P4" t="n">
-        <v>11.2</v>
+        <v>10.83</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>62.6</v>
+        <v>64.17</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>20</v>
+        <v>20.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>10.8</v>
+        <v>11.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AD4" t="n">
         <v>2.37</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AF4" t="n">
         <v>0.2</v>
@@ -2356,37 +2356,37 @@
         <v>3</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.1</v>
+        <v>4.45</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.1</v>
+        <v>9.91</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.1</v>
+        <v>4.45</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="BM4" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="BO4" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.2</v>
+        <v>5.18</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.9</v>
+        <v>4.73</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2398,16 +2398,16 @@
         <v>100</v>
       </c>
       <c r="BU4" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BV4" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BW4" t="n">
-        <v>10</v>
+        <v>18.18</v>
       </c>
       <c r="BX4" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BY4" t="n">
         <v>1.19</v>
@@ -2416,10 +2416,10 @@
         <v>1.21</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.16</v>
+        <v>7.2</v>
       </c>
       <c r="CB4" t="n">
-        <v>8.16</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="CC4" t="n">
         <v>1.31</v>
@@ -2428,151 +2428,151 @@
         <v>1.3</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CG4" t="n">
-        <v>5.07</v>
+        <v>5.02</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CL4" t="n">
         <v>1.91</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CQ4" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CR4" t="inlineStr"/>
       <c r="CS4" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="DA4" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="DB4" t="inlineStr"/>
       <c r="DC4" t="n">
         <v>1.37</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="DH4" t="n">
-        <v>127.9</v>
+        <v>125.45</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.7</v>
+        <v>5.46</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DM4" t="n">
-        <v>67.8</v>
+        <v>67.09</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DO4" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.4</v>
+        <v>10.27</v>
       </c>
       <c r="DQ4" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.3</v>
+        <v>5.27</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>65</v>
+        <v>65.64</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>18.9</v>
+        <v>19.18</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.5</v>
+        <v>10.82</v>
       </c>
       <c r="DZ4" t="n">
-        <v>8.4</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.2</v>
+        <v>18.82</v>
       </c>
       <c r="EB4" t="n">
         <v>2.28</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="5">
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
@@ -2594,79 +2594,79 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G5" t="n">
-        <v>6.75</v>
+        <v>5.6</v>
       </c>
       <c r="H5" t="n">
-        <v>126.25</v>
+        <v>119</v>
       </c>
       <c r="I5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>9.25</v>
+        <v>7.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M5" t="n">
-        <v>67.75</v>
+        <v>64</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O5" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>11.75</v>
+        <v>11.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="R5" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="S5" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>60.25</v>
+        <v>57.4</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>16.25</v>
+        <v>15.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.75</v>
+        <v>10.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.25</v>
+        <v>18</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -2753,70 +2753,70 @@
         <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.5</v>
+        <v>10.09</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.4</v>
+        <v>0.64</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.3</v>
+        <v>6.91</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT5" t="n">
-        <v>30</v>
+        <v>36.36</v>
       </c>
       <c r="BU5" t="n">
-        <v>10</v>
+        <v>18.18</v>
       </c>
       <c r="BV5" t="n">
-        <v>10</v>
+        <v>18.18</v>
       </c>
       <c r="BW5" t="n">
-        <v>10</v>
+        <v>18.18</v>
       </c>
       <c r="BX5" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="CC5" t="n">
         <v>2.66</v>
@@ -2828,31 +2828,31 @@
         <v>1.24</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CG5" t="n">
         <v>3.8</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.56</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO5" t="n">
         <v>1.13</v>
@@ -2861,25 +2861,25 @@
         <v>1.52</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CR5" t="n">
         <v>1.34</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CT5" t="n">
         <v>3.36</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CV5" t="n">
         <v>2.49</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CX5" t="n">
         <v>1.55</v>
@@ -2897,85 +2897,85 @@
         <v>1.26</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DG5" t="n">
-        <v>4.4</v>
+        <v>4.09</v>
       </c>
       <c r="DH5" t="n">
-        <v>114.7</v>
+        <v>112.45</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="DK5" t="n">
-        <v>6</v>
+        <v>5.63</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DM5" t="n">
-        <v>59.5</v>
+        <v>58.55</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.3</v>
+        <v>12.27</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.7</v>
+        <v>10.55</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.7</v>
+        <v>6.09</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>56.3</v>
+        <v>55.37</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX5" t="n">
-        <v>13</v>
+        <v>13.09</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.6</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.4</v>
+        <v>19.36</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="6">
@@ -2985,13 +2985,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3078,136 +3078,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
         <v>2</v>
       </c>
       <c r="AI6" t="n">
-        <v>85.75</v>
+        <v>82.2</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.75</v>
+        <v>12.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.25</v>
+        <v>12.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.25</v>
+        <v>6.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>48.5</v>
+        <v>49</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.75</v>
+        <v>13.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.25</v>
+        <v>7.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="BD6" t="n">
-        <v>14.5</v>
+        <v>15.8</v>
       </c>
       <c r="BE6" t="n">
         <v>1.53</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.2</v>
+        <v>10.09</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BK6" t="n">
         <v>1</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BM6" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BP6" t="n">
         <v>5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.2</v>
+        <v>5.09</v>
       </c>
       <c r="BR6" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT6" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BU6" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BV6" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW6" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX6" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BY6" t="n">
         <v>3.76</v>
@@ -3216,55 +3216,55 @@
         <v>3.71</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.18</v>
+        <v>4.14</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.17</v>
+        <v>3.79</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.43</v>
+        <v>3.97</v>
       </c>
       <c r="CE6" t="n">
         <v>1.25</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.55</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CO6" t="n">
         <v>1.15</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
@@ -3309,76 +3309,76 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DH6" t="n">
-        <v>89</v>
+        <v>87.09</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.7</v>
+        <v>37.91</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.9</v>
+        <v>11.91</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.2</v>
+        <v>10.36</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.7</v>
+        <v>7.27</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.7</v>
+        <v>12.09</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.7</v>
+        <v>7.18</v>
       </c>
       <c r="DZ6" t="n">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="EA6" t="n">
-        <v>15.3</v>
+        <v>15.82</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="7">
@@ -3388,13 +3388,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3481,49 +3481,49 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="AI7" t="n">
-        <v>107.2</v>
+        <v>109.33</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.6</v>
+        <v>5.17</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>54.4</v>
+        <v>51.67</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP7" t="n">
         <v>2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.6</v>
+        <v>9.67</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.2</v>
+        <v>9.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>9</v>
+        <v>8.17</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3535,82 +3535,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>57</v>
+        <v>56.33</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>13.4</v>
+        <v>13</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.2</v>
+        <v>4.67</v>
       </c>
       <c r="BD7" t="n">
-        <v>22.4</v>
+        <v>21.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.7</v>
+        <v>7.55</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="BO7" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BT7" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BU7" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BV7" t="n">
-        <v>30</v>
+        <v>36.36</v>
       </c>
       <c r="BW7" t="n">
-        <v>20</v>
+        <v>27.27</v>
       </c>
       <c r="BX7" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BY7" t="n">
         <v>2.46</v>
@@ -3619,28 +3619,28 @@
         <v>2.92</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.09</v>
+        <v>4.03</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.24</v>
+        <v>4.19</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CI7" t="n">
         <v>2.55</v>
@@ -3652,30 +3652,30 @@
         <v>1.47</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CM7" t="n">
         <v>2.51</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CR7" t="inlineStr"/>
       <c r="CS7" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CT7" t="inlineStr"/>
       <c r="CU7" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CV7" t="n">
         <v>2.68</v>
@@ -3697,85 +3697,85 @@
       </c>
       <c r="DB7" t="inlineStr"/>
       <c r="DC7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="DH7" t="n">
-        <v>101.8</v>
+        <v>103.45</v>
       </c>
       <c r="DI7" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.9</v>
+        <v>4.73</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DM7" t="n">
-        <v>50.9</v>
+        <v>49.73</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.2</v>
+        <v>9.73</v>
       </c>
       <c r="DQ7" t="n">
-        <v>10.1</v>
+        <v>9.73</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.8</v>
+        <v>7.46</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>56.3</v>
+        <v>56</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>13.4</v>
+        <v>13.18</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.699999999999999</v>
+        <v>8.27</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.7</v>
+        <v>4.91</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.5</v>
+        <v>21.09</v>
       </c>
       <c r="EB7" t="n">
         <v>1.54</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="8">
@@ -3785,13 +3785,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
         <v>0.4</v>
@@ -3878,136 +3878,136 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI8" t="n">
-        <v>87.8</v>
+        <v>83.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.8</v>
+        <v>3.17</v>
       </c>
       <c r="AM8" t="n">
         <v>1</v>
       </c>
       <c r="AN8" t="n">
-        <v>42</v>
+        <v>39.33</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>13.6</v>
+        <v>12.83</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.6</v>
+        <v>8.67</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>48</v>
+        <v>44.67</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.4</v>
+        <v>10.83</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.6</v>
+        <v>18.17</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="BH8" t="n">
-        <v>7.8</v>
+        <v>7.82</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="BL8" t="n">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="BR8" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BU8" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BV8" t="n">
-        <v>10</v>
+        <v>18.18</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="BX8" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BY8" t="n">
         <v>2.2</v>
@@ -4016,73 +4016,73 @@
         <v>2.25</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.49</v>
+        <v>3.88</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.99</v>
+        <v>4.66</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.04</v>
+        <v>5.04</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.28</v>
+        <v>3.39</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="CT8" t="n">
         <v>3.17</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="CX8" t="n">
         <v>1.69</v>
@@ -4091,7 +4091,7 @@
         <v>2.14</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA8" t="n">
         <v>1.74</v>
@@ -4100,85 +4100,85 @@
         <v>1.3</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.04</v>
+        <v>2.94</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DH8" t="n">
-        <v>95.90000000000001</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.4</v>
+        <v>4.46</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="DM8" t="n">
-        <v>44.8</v>
+        <v>43.09</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="DP8" t="n">
-        <v>8.9</v>
+        <v>8.73</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.9</v>
+        <v>13.45</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.2</v>
+        <v>6.46</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.8</v>
+        <v>7.64</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.7</v>
+        <v>20.27</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="9">
@@ -4188,13 +4188,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>0.4</v>
@@ -4281,136 +4281,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>88.8</v>
+        <v>86</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AL9" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>32.33</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="BC9" t="n">
         <v>4</v>
       </c>
-      <c r="AM9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>31</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BD9" t="n">
-        <v>17</v>
+        <v>18.17</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="BF9" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.699999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BR9" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BU9" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV9" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BY9" t="n">
         <v>2.7</v>
@@ -4419,28 +4419,28 @@
         <v>2.77</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.49</v>
+        <v>4.39</v>
       </c>
       <c r="CB9" t="n">
-        <v>5.34</v>
+        <v>5.17</v>
       </c>
       <c r="CC9" t="n">
-        <v>7.93</v>
+        <v>7.12</v>
       </c>
       <c r="CD9" t="n">
-        <v>8.52</v>
+        <v>7.58</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.6</v>
+        <v>3.56</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CI9" t="n">
         <v>2.25</v>
@@ -4449,106 +4449,106 @@
         <v>1.61</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CN9" t="n">
         <v>1.99</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.47</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DB9" t="n">
         <v>1.32</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="DG9" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DH9" t="n">
-        <v>89.90000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.7</v>
+        <v>3.63</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DM9" t="n">
-        <v>37</v>
+        <v>37.18</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.5</v>
+        <v>13.18</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.7</v>
+        <v>12.73</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.300000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4560,28 +4560,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47.7</v>
+        <v>48.09</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.6</v>
+        <v>13.73</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.6</v>
+        <v>19.09</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="10">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
         <v>5</v>
@@ -4603,49 +4603,49 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="H10" t="n">
-        <v>87.8</v>
+        <v>87.67</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="K10" t="n">
-        <v>4.8</v>
+        <v>4.67</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>41.2</v>
+        <v>37.33</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O10" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="P10" t="n">
-        <v>9.800000000000001</v>
+        <v>10.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="R10" t="n">
-        <v>8.4</v>
+        <v>8.17</v>
       </c>
       <c r="S10" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4657,28 +4657,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>41</v>
+        <v>42.33</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.8</v>
+        <v>11.83</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.67</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.6</v>
+        <v>4.17</v>
       </c>
       <c r="AC10" t="n">
-        <v>16.2</v>
+        <v>15.17</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4762,70 +4762,70 @@
         <v>1.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="BL10" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.3</v>
+        <v>5.18</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BT10" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BU10" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BV10" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW10" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.43</v>
+        <v>3.37</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.08</v>
+        <v>4.02</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
       <c r="CC10" t="n">
         <v>5.75</v>
@@ -4837,10 +4837,10 @@
         <v>1.27</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CH10" t="n">
         <v>1.61</v>
@@ -4852,25 +4852,25 @@
         <v>1.61</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL10" t="n">
         <v>2.01</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CO10" t="n">
         <v>1.17</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
@@ -4885,10 +4885,10 @@
         <v>1.66</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CX10" t="n">
         <v>1.57</v>
@@ -4906,10 +4906,10 @@
         <v>1.27</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
@@ -4918,40 +4918,40 @@
         <v>1</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="DH10" t="n">
-        <v>81</v>
+        <v>81.55</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="DL10" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DM10" t="n">
-        <v>36.7</v>
+        <v>35</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.4</v>
+        <v>10.63</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.5</v>
+        <v>11.55</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.5</v>
+        <v>9.27</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4963,28 +4963,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>39.2</v>
+        <v>40.09</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.7</v>
+        <v>10.36</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.9</v>
+        <v>6.73</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.2</v>
+        <v>15.64</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="11">
@@ -5397,61 +5397,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="H12" t="n">
-        <v>91</v>
+        <v>93.8</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="J12" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>40.5</v>
+        <v>42</v>
       </c>
       <c r="N12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="P12" t="n">
-        <v>10.25</v>
+        <v>9.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>14</v>
+        <v>12.2</v>
       </c>
       <c r="R12" t="n">
-        <v>7.75</v>
+        <v>7.2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5463,28 +5463,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>16.25</v>
+        <v>15.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AC12" t="n">
-        <v>17</v>
+        <v>18.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AF12" t="n">
         <v>0.17</v>
@@ -5568,70 +5568,70 @@
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BH12" t="n">
-        <v>11.6</v>
+        <v>11.09</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="BN12" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.7</v>
+        <v>5.36</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT12" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BU12" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BV12" t="n">
-        <v>30</v>
+        <v>36.36</v>
       </c>
       <c r="BW12" t="n">
-        <v>10</v>
+        <v>18.18</v>
       </c>
       <c r="BX12" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.81</v>
+        <v>3.77</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="CC12" t="n">
         <v>4.3</v>
@@ -5646,28 +5646,28 @@
         <v>2.36</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="CH12" t="n">
         <v>1.57</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.56</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.87</v>
+        <v>2.84</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CO12" t="n">
         <v>1.17</v>
@@ -5682,7 +5682,7 @@
         <v>1.35</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CT12" t="n">
         <v>3.24</v>
@@ -5691,10 +5691,10 @@
         <v>1.63</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CX12" t="n">
         <v>1.53</v>
@@ -5712,85 +5712,85 @@
         <v>1.27</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="DH12" t="n">
-        <v>89.3</v>
+        <v>90.73</v>
       </c>
       <c r="DI12" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.4</v>
+        <v>4.27</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DM12" t="n">
-        <v>40.8</v>
+        <v>41.45</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.6</v>
+        <v>0.54</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="DP12" t="n">
-        <v>9.6</v>
+        <v>9.27</v>
       </c>
       <c r="DQ12" t="n">
-        <v>12.3</v>
+        <v>11.64</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.5</v>
+        <v>9.09</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.5</v>
+        <v>46.55</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.8</v>
+        <v>13.55</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.6</v>
+        <v>4.64</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.3</v>
+        <v>19.63</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="13">
@@ -6203,10 +6203,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
@@ -6215,49 +6215,49 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G14" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>88.75</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="K14" t="n">
-        <v>5.25</v>
+        <v>6.8</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="M14" t="n">
-        <v>37.25</v>
+        <v>40.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="P14" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>10.75</v>
+        <v>10</v>
       </c>
       <c r="R14" t="n">
-        <v>7.75</v>
+        <v>7.6</v>
       </c>
       <c r="S14" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6269,28 +6269,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.75</v>
+        <v>17</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>20.75</v>
+        <v>20</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
         <v>0.67</v>
@@ -6374,70 +6374,70 @@
         <v>1.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.3</v>
+        <v>11.18</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BO14" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.2</v>
+        <v>5.45</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.1</v>
+        <v>5.73</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BU14" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BV14" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW14" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.3</v>
+        <v>4.36</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.48</v>
+        <v>4.51</v>
       </c>
       <c r="CC14" t="n">
         <v>4.1</v>
@@ -6446,19 +6446,19 @@
         <v>4.09</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.17</v>
+        <v>4.19</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.48</v>
@@ -6467,7 +6467,7 @@
         <v>1.4</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CM14" t="n">
         <v>2.76</v>
@@ -6479,10 +6479,10 @@
         <v>1.1</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="n">
@@ -6496,7 +6496,7 @@
         <v>2.88</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CX14" t="n">
         <v>1.44</v>
@@ -6512,52 +6512,52 @@
       </c>
       <c r="DB14" t="inlineStr"/>
       <c r="DC14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="DH14" t="n">
-        <v>85.5</v>
+        <v>89.27</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.7</v>
+        <v>6.36</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DM14" t="n">
-        <v>40.1</v>
+        <v>41.45</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.9</v>
+        <v>3.37</v>
       </c>
       <c r="DP14" t="n">
-        <v>10</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.9</v>
+        <v>10.55</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6569,28 +6569,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.3</v>
+        <v>48.63</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>15.9</v>
+        <v>16.45</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.7</v>
+        <v>10.55</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.2</v>
+        <v>5.91</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.5</v>
+        <v>16.55</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="15">
@@ -6600,10 +6600,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>5</v>
@@ -6612,82 +6612,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="H15" t="n">
-        <v>107.6</v>
+        <v>112</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6</v>
+        <v>7.67</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M15" t="n">
-        <v>54.8</v>
+        <v>56.17</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O15" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>11.4</v>
+        <v>11.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="R15" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>52.4</v>
+        <v>53.5</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.4</v>
+        <v>7.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.2</v>
+        <v>4.83</v>
       </c>
       <c r="AC15" t="n">
-        <v>24.2</v>
+        <v>23.83</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6771,70 +6771,70 @@
         <v>1.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BM15" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.4</v>
+        <v>4.18</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.5</v>
+        <v>4.82</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>90</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BU15" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV15" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW15" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX15" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.94</v>
+        <v>2.91</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.61</v>
+        <v>3.56</v>
       </c>
       <c r="CC15" t="n">
         <v>3.87</v>
@@ -6843,28 +6843,28 @@
         <v>4.07</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CK15" t="n">
         <v>1.64</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CM15" t="n">
         <v>2.21</v>
@@ -6873,31 +6873,31 @@
         <v>1.75</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.09</v>
+        <v>3.22</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="CX15" t="n">
         <v>1.65</v>
@@ -6912,10 +6912,10 @@
         <v>1.78</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="DD15" t="n">
         <v>2.95</v>
@@ -6924,76 +6924,76 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.7</v>
+        <v>3.09</v>
       </c>
       <c r="DH15" t="n">
-        <v>108.4</v>
+        <v>110.73</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.3</v>
+        <v>5.55</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM15" t="n">
-        <v>51.5</v>
+        <v>52.55</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.8</v>
+        <v>11.64</v>
       </c>
       <c r="DQ15" t="n">
-        <v>11.1</v>
+        <v>10.82</v>
       </c>
       <c r="DR15" t="n">
-        <v>5.2</v>
+        <v>5.36</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>50.8</v>
+        <v>51.55</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.8</v>
+        <v>11.82</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.8</v>
+        <v>7.91</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="EA15" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="16">
@@ -7003,13 +7003,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7096,136 +7096,136 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="AI16" t="n">
-        <v>142.8</v>
+        <v>137.33</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AL16" t="n">
-        <v>6.6</v>
+        <v>6.17</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>83.2</v>
+        <v>78</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="AR16" t="n">
         <v>12</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>60.6</v>
+        <v>59.5</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>14.4</v>
+        <v>14.67</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.6</v>
+        <v>9.67</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.2</v>
+        <v>17.83</v>
       </c>
       <c r="BE16" t="n">
         <v>1.85</v>
       </c>
       <c r="BF16" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="BH16" t="n">
-        <v>11.1</v>
+        <v>10.64</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BL16" t="n">
         <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BP16" t="n">
-        <v>5</v>
+        <v>4.82</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6.1</v>
+        <v>5.82</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BU16" t="n">
-        <v>30</v>
+        <v>36.36</v>
       </c>
       <c r="BV16" t="n">
-        <v>10</v>
+        <v>18.18</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="BX16" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BY16" t="n">
         <v>1.58</v>
@@ -7237,25 +7237,25 @@
         <v>4.1</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.51</v>
+        <v>2.81</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.61</v>
+        <v>2.9</v>
       </c>
       <c r="CE16" t="n">
         <v>1.25</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CI16" t="n">
         <v>2.43</v>
@@ -7264,16 +7264,16 @@
         <v>1.55</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CN16" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CO16" t="n">
         <v>1.15</v>
@@ -7282,22 +7282,22 @@
         <v>1.56</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CR16" t="n">
         <v>1.33</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CT16" t="n">
         <v>3.35</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CW16" t="n">
         <v>1.55</v>
@@ -7325,76 +7325,76 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="DH16" t="n">
-        <v>129.2</v>
+        <v>127.45</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.9</v>
+        <v>5.73</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="DM16" t="n">
-        <v>63.9</v>
+        <v>62.82</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.9</v>
+        <v>10.82</v>
       </c>
       <c r="DQ16" t="n">
         <v>12</v>
       </c>
       <c r="DR16" t="n">
-        <v>6</v>
+        <v>5.91</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>59.3</v>
+        <v>58.82</v>
       </c>
       <c r="DW16" t="n">
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.6</v>
+        <v>15.64</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.9</v>
+        <v>9.91</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.7</v>
+        <v>5.73</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.3</v>
+        <v>18.54</v>
       </c>
       <c r="EB16" t="n">
         <v>1.85</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="17">
@@ -7404,13 +7404,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
         <v>0.17</v>
@@ -7494,49 +7494,49 @@
         <v>3.17</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI17" t="n">
-        <v>78.25</v>
+        <v>84.2</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AN17" t="n">
-        <v>31.25</v>
+        <v>31.2</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.25</v>
+        <v>10.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>11.25</v>
+        <v>10.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AU17" t="n">
         <v>1</v>
@@ -7551,82 +7551,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>31.25</v>
+        <v>33.2</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.25</v>
+        <v>10.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>15.5</v>
+        <v>16.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.3</v>
+        <v>10.27</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="BL17" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.5</v>
+        <v>5.18</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.6</v>
+        <v>4.91</v>
       </c>
       <c r="BR17" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
       <c r="BT17" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BU17" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BV17" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW17" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY17" t="n">
         <v>3.49</v>
@@ -7635,73 +7635,73 @@
         <v>4.54</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.12</v>
+        <v>4.02</v>
       </c>
       <c r="CC17" t="n">
-        <v>5.32</v>
+        <v>4.83</v>
       </c>
       <c r="CD17" t="n">
-        <v>5.13</v>
+        <v>4.7</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.37</v>
+        <v>3.29</v>
       </c>
       <c r="CH17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="CU17" t="n">
         <v>1.53</v>
       </c>
-      <c r="CI17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CJ17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CK17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CL17" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CM17" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="CN17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="CO17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="CP17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="CQ17" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CS17" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="CT17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="CU17" t="n">
-        <v>1.55</v>
-      </c>
       <c r="CV17" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CX17" t="n">
         <v>1.59</v>
@@ -7716,55 +7716,55 @@
         <v>1.92</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="DD17" t="n">
         <v>2.88</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF17" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="DH17" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="DL17" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="DM17" t="n">
-        <v>37</v>
+        <v>36.45</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="DP17" t="n">
-        <v>14.5</v>
+        <v>13.91</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.8</v>
+        <v>11.63</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7776,28 +7776,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>32.6</v>
+        <v>33.36</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.3</v>
+        <v>11.82</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="EA17" t="n">
-        <v>17.9</v>
+        <v>18.27</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="18">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
         <v>0.2</v>
@@ -7903,133 +7903,133 @@
         <v>1</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.8</v>
+        <v>2.67</v>
       </c>
       <c r="AI18" t="n">
-        <v>80.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.6</v>
+        <v>3.33</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>30.8</v>
+        <v>32.67</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>11.4</v>
+        <v>10.33</v>
       </c>
       <c r="AS18" t="n">
-        <v>11</v>
+        <v>10.17</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>46.2</v>
+        <v>46.5</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.4</v>
+        <v>10.33</v>
       </c>
       <c r="BB18" t="n">
-        <v>5</v>
+        <v>5.67</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.4</v>
+        <v>4.67</v>
       </c>
       <c r="BD18" t="n">
-        <v>19.8</v>
+        <v>18.83</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.300000000000001</v>
+        <v>10.27</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BN18" t="n">
         <v>2</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.5</v>
+        <v>4.82</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.8</v>
+        <v>5.45</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
       <c r="BU18" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BV18" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW18" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX18" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY18" t="n">
         <v>2.46</v>
@@ -8038,55 +8038,55 @@
         <v>2.64</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.61</v>
+        <v>4.64</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="CC18" t="n">
-        <v>6.72</v>
+        <v>6.48</v>
       </c>
       <c r="CD18" t="n">
-        <v>8.300000000000001</v>
+        <v>7.85</v>
       </c>
       <c r="CE18" t="n">
         <v>1.25</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL18" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="CR18" t="n">
         <v>1.34</v>
@@ -8101,10 +8101,10 @@
         <v>1.75</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CX18" t="n">
         <v>1.54</v>
@@ -8122,85 +8122,85 @@
         <v>1.26</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="DH18" t="n">
-        <v>94.90000000000001</v>
+        <v>93.36</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="DK18" t="n">
-        <v>4</v>
+        <v>4.27</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.4</v>
+        <v>41.46</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="DP18" t="n">
-        <v>9.5</v>
+        <v>9.27</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.2</v>
+        <v>9.73</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>49.7</v>
+        <v>49.55</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.2</v>
+        <v>12.45</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.5</v>
+        <v>7.64</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.8</v>
+        <v>19.27</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="19">
@@ -8210,61 +8210,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
         <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>107</v>
+        <v>98.83</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>53</v>
+        <v>55.33</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="P19" t="n">
-        <v>11.8</v>
+        <v>11.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="R19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8276,28 +8276,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>47.2</v>
+        <v>45.67</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z19" t="n">
-        <v>14</v>
+        <v>15.17</v>
       </c>
       <c r="AA19" t="n">
-        <v>9.6</v>
+        <v>9.83</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.4</v>
+        <v>5.33</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.8</v>
+        <v>17.67</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8381,70 +8381,70 @@
         <v>1.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.8</v>
+        <v>11.64</v>
       </c>
       <c r="BI19" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.7</v>
+        <v>0.91</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BM19" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.7</v>
+        <v>4.82</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.8</v>
+        <v>5.64</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT19" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BU19" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BV19" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BW19" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BX19" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="CC19" t="n">
         <v>3.3</v>
@@ -8471,25 +8471,25 @@
         <v>1.55</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CO19" t="n">
         <v>1.18</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
@@ -8504,10 +8504,10 @@
         <v>1.6</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CX19" t="n">
         <v>1.48</v>
@@ -8525,85 +8525,85 @@
         <v>1.27</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF19" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="DH19" t="n">
-        <v>92.2</v>
+        <v>89.09</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.8</v>
+        <v>4.27</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
       </c>
       <c r="DM19" t="n">
-        <v>43.7</v>
+        <v>45.82</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.3</v>
+        <v>11.36</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11</v>
+        <v>10.64</v>
       </c>
       <c r="DR19" t="n">
-        <v>10</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>46.3</v>
+        <v>45.55</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.1</v>
+        <v>12.91</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.4</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DZ19" t="n">
-        <v>3.7</v>
+        <v>4.27</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.9</v>
+        <v>16.91</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -2997,82 +2997,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="H6" t="n">
+        <v>88.29000000000001</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M6" t="n">
+        <v>37.71</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="P6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="R6" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="H6" t="n">
-        <v>91.17</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M6" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="P6" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>8.83</v>
-      </c>
-      <c r="R6" t="n">
-        <v>8</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.17</v>
-      </c>
       <c r="U6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>43.5</v>
+        <v>43.14</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z6" t="n">
-        <v>11</v>
+        <v>10.43</v>
       </c>
       <c r="AA6" t="n">
         <v>7</v>
       </c>
       <c r="AB6" t="n">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="AC6" t="n">
-        <v>15.83</v>
+        <v>16.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3156,70 +3156,70 @@
         <v>1.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.09</v>
+        <v>10.17</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BK6" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM6" t="n">
         <v>1</v>
       </c>
-      <c r="BL6" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.09</v>
-      </c>
       <c r="BN6" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="BP6" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.09</v>
+        <v>5.42</v>
       </c>
       <c r="BR6" t="n">
-        <v>81.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="BS6" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX6" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.76</v>
+        <v>3.63</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.71</v>
+        <v>3.6</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="CC6" t="n">
         <v>3.79</v>
@@ -3231,46 +3231,46 @@
         <v>1.25</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CI6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CQ6" t="n">
         <v>2.42</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>2.45</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CT6" t="n">
         <v>3.19</v>
@@ -3279,106 +3279,106 @@
         <v>1.69</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CX6" t="n">
         <v>1.53</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.45</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="DB6" t="n">
         <v>1.3</v>
       </c>
       <c r="DC6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>85.75</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DJ6" t="n">
         <v>1.67</v>
       </c>
-      <c r="DD6" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="DE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="DG6" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>1.82</v>
-      </c>
       <c r="DK6" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM6" t="n">
-        <v>37.91</v>
+        <v>37</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.91</v>
+        <v>11.67</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.36</v>
+        <v>10.25</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.27</v>
+        <v>7.58</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46</v>
+        <v>45.58</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.09</v>
+        <v>11.67</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.91</v>
+        <v>4.5</v>
       </c>
       <c r="EA6" t="n">
-        <v>15.82</v>
+        <v>16</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7">
@@ -6203,13 +6203,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6293,139 +6293,139 @@
         <v>1.6</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.83</v>
+        <v>4.14</v>
       </c>
       <c r="AI14" t="n">
-        <v>83.33</v>
+        <v>91</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AL14" t="n">
         <v>6</v>
       </c>
       <c r="AM14" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>11.17</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BM14" t="n">
         <v>0.33</v>
       </c>
-      <c r="AN14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="AT14" t="n">
+      <c r="BN14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BO14" t="n">
         <v>1.67</v>
       </c>
-      <c r="AU14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>46.83</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>16</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>11.18</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>1.82</v>
-      </c>
       <c r="BP14" t="n">
-        <v>5.45</v>
+        <v>5.17</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.73</v>
+        <v>6</v>
       </c>
       <c r="BR14" t="n">
-        <v>100</v>
+        <v>91.67</v>
       </c>
       <c r="BS14" t="n">
-        <v>81.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT14" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BV14" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW14" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BX14" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BY14" t="n">
         <v>1.6</v>
@@ -6434,31 +6434,31 @@
         <v>1.72</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.36</v>
+        <v>4.32</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.51</v>
+        <v>4.45</v>
       </c>
       <c r="CC14" t="n">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.09</v>
+        <v>3.84</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CF14" t="n">
         <v>2.03</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.48</v>
@@ -6467,13 +6467,13 @@
         <v>1.4</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CO14" t="n">
         <v>1.1</v>
@@ -6486,23 +6486,23 @@
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CV14" t="n">
         <v>2.88</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CX14" t="n">
         <v>1.44</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.65</v>
@@ -6512,52 +6512,52 @@
       </c>
       <c r="DB14" t="inlineStr"/>
       <c r="DC14" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="DG14" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="DH14" t="n">
-        <v>89.27</v>
+        <v>93.25</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.36</v>
+        <v>6.33</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DM14" t="n">
-        <v>41.45</v>
+        <v>42.67</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.37</v>
+        <v>3.09</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.539999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.55</v>
+        <v>10.41</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.550000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6569,28 +6569,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.63</v>
+        <v>49.5</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>16.45</v>
+        <v>16.75</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.55</v>
+        <v>11</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.91</v>
+        <v>5.75</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.55</v>
+        <v>16.75</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>0.17</v>
@@ -1469,139 +1469,139 @@
         <v>2.33</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG2" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>101</v>
+        <v>99.83</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.8</v>
+        <v>3.17</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN2" t="n">
-        <v>32.6</v>
+        <v>32.17</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15.4</v>
+        <v>14.33</v>
       </c>
       <c r="AR2" t="n">
-        <v>12.4</v>
+        <v>13.17</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.6</v>
+        <v>9.67</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>43.4</v>
+        <v>42.83</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>11.8</v>
+        <v>12.17</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.4</v>
+        <v>7.83</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="BD2" t="n">
-        <v>17.4</v>
+        <v>17.17</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.8</v>
+        <v>3.17</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.359999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.36</v>
+        <v>0.58</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.82</v>
+        <v>3.92</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT2" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BU2" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BV2" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX2" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BY2" t="n">
         <v>3.9</v>
@@ -1610,61 +1610,61 @@
         <v>4.44</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.83</v>
+        <v>3.91</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.92</v>
+        <v>4.02</v>
       </c>
       <c r="CE2" t="n">
         <v>1.3</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="CN2" t="n">
         <v>1.93</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>1.92</v>
       </c>
       <c r="CO2" t="n">
         <v>1.2</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="CR2" t="n">
         <v>1.35</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CT2" t="n">
         <v>3.24</v>
@@ -1673,7 +1673,7 @@
         <v>1.59</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CW2" t="n">
         <v>1.64</v>
@@ -1682,13 +1682,13 @@
         <v>1.51</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.45</v>
       </c>
       <c r="DA2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DB2" t="n">
         <v>1.28</v>
@@ -1697,82 +1697,82 @@
         <v>1.69</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DH2" t="n">
-        <v>105.09</v>
+        <v>104.16</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.27</v>
+        <v>4.08</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="DM2" t="n">
-        <v>40.55</v>
+        <v>39.67</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.55</v>
+        <v>13.16</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.46</v>
+        <v>11.92</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.359999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>46.55</v>
+        <v>46</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.18</v>
+        <v>12.34</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.18</v>
+        <v>8.33</v>
       </c>
       <c r="DZ2" t="n">
         <v>4</v>
       </c>
       <c r="EA2" t="n">
-        <v>20.09</v>
+        <v>19.75</v>
       </c>
       <c r="EB2" t="n">
         <v>1.35</v>
       </c>
       <c r="EC2" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="3">
@@ -1782,67 +1782,67 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="F3" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="H3" t="n">
-        <v>122.5</v>
+        <v>120.29</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>5.71</v>
       </c>
       <c r="L3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M3" t="n">
-        <v>48.83</v>
+        <v>49.29</v>
       </c>
       <c r="N3" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="P3" t="n">
-        <v>9.33</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.33</v>
+        <v>11</v>
       </c>
       <c r="R3" t="n">
-        <v>6.33</v>
+        <v>6.14</v>
       </c>
       <c r="S3" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="U3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -1851,25 +1851,25 @@
         <v>63</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>16.57</v>
       </c>
       <c r="AA3" t="n">
-        <v>11</v>
+        <v>10.86</v>
       </c>
       <c r="AB3" t="n">
-        <v>6</v>
+        <v>5.71</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.33</v>
+        <v>15.71</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AF3" t="n">
         <v>0.4</v>
@@ -1953,37 +1953,37 @@
         <v>2.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.73</v>
+        <v>10</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.27</v>
+        <v>4.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,31 +1992,31 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BU3" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BW3" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BX3" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.18</v>
+        <v>4.12</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="CC3" t="n">
         <v>3.61</v>
@@ -2031,43 +2031,43 @@
         <v>2.31</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CI3" t="n">
         <v>2.33</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="CO3" t="n">
         <v>1.16</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CR3" t="n">
         <v>1.34</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CT3" t="n">
         <v>3.3</v>
@@ -2076,22 +2076,22 @@
         <v>1.65</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="DB3" t="n">
         <v>1.27</v>
@@ -2103,79 +2103,79 @@
         <v>2.54</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="DH3" t="n">
-        <v>107.82</v>
+        <v>107.75</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.18</v>
+        <v>4.66</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="DM3" t="n">
-        <v>44.36</v>
+        <v>45</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.54</v>
+        <v>0.67</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="DP3" t="n">
-        <v>8.91</v>
+        <v>8.75</v>
       </c>
       <c r="DQ3" t="n">
-        <v>12.09</v>
+        <v>11.83</v>
       </c>
       <c r="DR3" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>58.64</v>
+        <v>59</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.73</v>
+        <v>13.75</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.640000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.09</v>
+        <v>5</v>
       </c>
       <c r="EA3" t="n">
-        <v>15.36</v>
+        <v>15.58</v>
       </c>
       <c r="EB3" t="n">
         <v>1.55</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="G4" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H4" t="n">
+        <v>130.29</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M4" t="n">
+        <v>66.86</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P4" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="R4" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>66.43000000000001</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>19.86</v>
+      </c>
+      <c r="AD4" t="n">
         <v>2.33</v>
       </c>
-      <c r="H4" t="n">
-        <v>117.83</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M4" t="n">
-        <v>63.17</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="P4" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="R4" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>64.17</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>20.33</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AE4" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AF4" t="n">
         <v>0.2</v>
@@ -2356,37 +2356,37 @@
         <v>3</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.91</v>
+        <v>10.08</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.18</v>
+        <v>4.92</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.73</v>
+        <v>5.17</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2398,28 +2398,28 @@
         <v>100</v>
       </c>
       <c r="BU4" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BV4" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BW4" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BX4" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.2</v>
+        <v>7.52</v>
       </c>
       <c r="CB4" t="n">
-        <v>8.130000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="CC4" t="n">
         <v>1.31</v>
@@ -2431,19 +2431,19 @@
         <v>1.15</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CG4" t="n">
-        <v>5.02</v>
+        <v>4.96</v>
       </c>
       <c r="CH4" t="n">
         <v>1.96</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="CK4" t="n">
         <v>1.52</v>
@@ -2452,10 +2452,10 @@
         <v>1.91</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CO4" t="n">
         <v>1.06</v>
@@ -2468,111 +2468,111 @@
       </c>
       <c r="CR4" t="inlineStr"/>
       <c r="CS4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="CX4" t="n">
         <v>1.52</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.47</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB4" t="inlineStr"/>
       <c r="DC4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="DD4" t="n">
         <v>1.79</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="DH4" t="n">
-        <v>125.45</v>
+        <v>132.09</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.46</v>
+        <v>5.84</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="DM4" t="n">
-        <v>67.09</v>
+        <v>68.92</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="DP4" t="n">
-        <v>10.27</v>
+        <v>9.83</v>
       </c>
       <c r="DQ4" t="n">
-        <v>10</v>
+        <v>9.83</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>65.64</v>
+        <v>66.83</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>19.18</v>
+        <v>19.17</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.82</v>
+        <v>11.17</v>
       </c>
       <c r="DZ4" t="n">
-        <v>8.359999999999999</v>
+        <v>8</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.82</v>
+        <v>20.08</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="5">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" t="n">
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2675,49 +2675,49 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="AI5" t="n">
-        <v>107</v>
+        <v>103.86</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AN5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AO5" t="n">
         <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.67</v>
+        <v>12.14</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.5</v>
+        <v>10.86</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.5</v>
+        <v>6.29</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2729,82 +2729,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>53.67</v>
+        <v>51.29</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.83</v>
+        <v>10.29</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.17</v>
+        <v>6.57</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="BD5" t="n">
-        <v>20.5</v>
+        <v>19.71</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.09</v>
+        <v>10.33</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.91</v>
+        <v>6.83</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT5" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BU5" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BV5" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW5" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BX5" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>1.57</v>
@@ -2813,28 +2813,28 @@
         <v>1.58</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.37</v>
+        <v>4.29</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.5</v>
+        <v>4.42</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="CE5" t="n">
         <v>1.24</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CI5" t="n">
         <v>2.35</v>
@@ -2843,25 +2843,25 @@
         <v>1.56</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="CR5" t="n">
         <v>1.34</v>
@@ -2873,109 +2873,109 @@
         <v>3.36</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="DB5" t="n">
         <v>1.26</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="DG5" t="n">
-        <v>4.09</v>
+        <v>3.75</v>
       </c>
       <c r="DH5" t="n">
-        <v>112.45</v>
+        <v>110.17</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.63</v>
+        <v>5.41</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="DM5" t="n">
-        <v>58.55</v>
+        <v>57.58</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.27</v>
+        <v>12</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.55</v>
+        <v>10.25</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.09</v>
+        <v>6.5</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>55.37</v>
+        <v>53.84</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.09</v>
+        <v>12.59</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.550000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.36</v>
+        <v>19</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="6">
@@ -3051,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>43.14</v>
+        <v>43.29</v>
       </c>
       <c r="Y6" t="n">
         <v>0.14</v>
@@ -3357,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.58</v>
+        <v>45.67</v>
       </c>
       <c r="DW6" t="n">
         <v>0.08</v>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
@@ -3400,13 +3400,13 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>96.40000000000001</v>
+        <v>97.83</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3415,64 +3415,64 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>5.83</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>47.4</v>
+        <v>52</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>3.67</v>
       </c>
       <c r="P7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="R7" t="n">
-        <v>6.6</v>
+        <v>6.67</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>55.6</v>
+        <v>55.33</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.4</v>
+        <v>13.67</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.2</v>
+        <v>4.83</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.6</v>
+        <v>21.83</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -3559,70 +3559,70 @@
         <v>2.17</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.55</v>
+        <v>8.17</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BO7" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.45</v>
+        <v>3.92</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>72.73</v>
+        <v>66.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BW7" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BX7" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="CC7" t="n">
         <v>2.4</v>
@@ -3637,7 +3637,7 @@
         <v>2.19</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CH7" t="n">
         <v>1.68</v>
@@ -3646,19 +3646,19 @@
         <v>2.55</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CO7" t="n">
         <v>1.14</v>
@@ -3671,33 +3671,33 @@
       </c>
       <c r="CR7" t="inlineStr"/>
       <c r="CS7" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CT7" t="inlineStr"/>
       <c r="CU7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CX7" t="n">
         <v>1.57</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.38</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="DB7" t="inlineStr"/>
       <c r="DC7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="DD7" t="n">
         <v>2.32</v>
@@ -3706,76 +3706,76 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.37</v>
+        <v>2.58</v>
       </c>
       <c r="DH7" t="n">
-        <v>103.45</v>
+        <v>103.58</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.73</v>
+        <v>5.5</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DM7" t="n">
-        <v>49.73</v>
+        <v>51.84</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.27</v>
+        <v>2.83</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.73</v>
+        <v>9.5</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.73</v>
+        <v>9.58</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.46</v>
+        <v>7.42</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>56</v>
+        <v>55.83</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>13.18</v>
+        <v>13.34</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.27</v>
+        <v>8.58</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.91</v>
+        <v>4.75</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.09</v>
+        <v>21.67</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="8">
@@ -3785,94 +3785,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="H8" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M8" t="n">
-        <v>47.6</v>
+        <v>48.83</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>3.67</v>
       </c>
       <c r="P8" t="n">
         <v>9</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.2</v>
+        <v>13.83</v>
       </c>
       <c r="R8" t="n">
-        <v>3.8</v>
+        <v>3.17</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>52</v>
+        <v>55.83</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.2</v>
+        <v>13.17</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.2</v>
+        <v>8.17</v>
       </c>
       <c r="AB8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC8" t="n">
-        <v>22.8</v>
+        <v>23.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3956,67 +3956,67 @@
         <v>1</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="BH8" t="n">
-        <v>7.82</v>
+        <v>7.83</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="BP8" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="BR8" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS8" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BV8" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX8" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
       <c r="CB8" t="n">
         <v>3.88</v>
@@ -4031,19 +4031,19 @@
         <v>1.32</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CK8" t="n">
         <v>1.63</v>
@@ -4052,28 +4052,28 @@
         <v>2.1</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="CU8" t="n">
         <v>1.51</v>
@@ -4091,94 +4091,94 @@
         <v>2.14</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="DH8" t="n">
-        <v>92.81999999999999</v>
+        <v>95.75</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.46</v>
+        <v>4.58</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="DM8" t="n">
-        <v>43.09</v>
+        <v>44.08</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="DP8" t="n">
-        <v>8.73</v>
+        <v>8.75</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.45</v>
+        <v>13.33</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.46</v>
+        <v>5.92</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48</v>
+        <v>50.25</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.64</v>
+        <v>8.08</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.36</v>
+        <v>3.92</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.27</v>
+        <v>20.75</v>
       </c>
       <c r="EB8" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="EC8" t="n">
         <v>1.25</v>
-      </c>
-      <c r="EC8" t="n">
-        <v>1.36</v>
       </c>
     </row>
     <row r="9">
@@ -4188,61 +4188,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="H9" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M9" t="n">
-        <v>43</v>
+        <v>39.17</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="P9" t="n">
-        <v>12.8</v>
+        <v>13.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.4</v>
+        <v>13.17</v>
       </c>
       <c r="R9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4254,28 +4254,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>47.6</v>
+        <v>45.33</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>15.6</v>
+        <v>14.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.8</v>
+        <v>5.17</v>
       </c>
       <c r="AC9" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4359,70 +4359,70 @@
         <v>2.17</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.550000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BO9" t="n">
         <v>1</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="BR9" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS9" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV9" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.39</v>
+        <v>4.33</v>
       </c>
       <c r="CB9" t="n">
-        <v>5.17</v>
+        <v>5.03</v>
       </c>
       <c r="CC9" t="n">
         <v>7.12</v>
@@ -4437,16 +4437,16 @@
         <v>2.31</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CH9" t="n">
         <v>1.64</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CK9" t="n">
         <v>1.45</v>
@@ -4461,13 +4461,13 @@
         <v>1.99</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP9" t="n">
         <v>1.62</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
@@ -4485,19 +4485,19 @@
         <v>2.46</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY9" t="n">
         <v>1.78</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DB9" t="n">
         <v>1.32</v>
@@ -4506,49 +4506,49 @@
         <v>1.68</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="DH9" t="n">
-        <v>88.27</v>
+        <v>86</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DM9" t="n">
-        <v>37.18</v>
+        <v>35.75</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.18</v>
+        <v>13.42</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.73</v>
+        <v>12.67</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.359999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4560,28 +4560,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>48.09</v>
+        <v>46.92</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.73</v>
+        <v>13.34</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.91</v>
+        <v>8.75</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.82</v>
+        <v>4.58</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.09</v>
+        <v>19.08</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="10">
@@ -4591,13 +4591,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4684,49 +4684,49 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="AI10" t="n">
-        <v>74.2</v>
+        <v>79</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="AN10" t="n">
-        <v>32.2</v>
+        <v>32.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>10.83</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.4</v>
+        <v>10.83</v>
       </c>
       <c r="AS10" t="n">
-        <v>10.6</v>
+        <v>10.17</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4738,82 +4738,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>37.4</v>
+        <v>40.67</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.6</v>
+        <v>8.83</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC10" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="BD10" t="n">
-        <v>16.2</v>
+        <v>18.33</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.09</v>
+        <v>9.17</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.18</v>
+        <v>5.25</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BU10" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX10" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BY10" t="n">
         <v>3.37</v>
@@ -4825,37 +4825,37 @@
         <v>4.02</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.75</v>
+        <v>5.66</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.17</v>
+        <v>6.21</v>
       </c>
       <c r="CE10" t="n">
         <v>1.27</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK10" t="n">
         <v>1.52</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CM10" t="n">
         <v>2.4</v>
@@ -4867,28 +4867,28 @@
         <v>1.17</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="CX10" t="n">
         <v>1.57</v>
@@ -4897,61 +4897,61 @@
         <v>1.91</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="DA10" t="n">
         <v>1.91</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.53</v>
+        <v>2.63</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="DH10" t="n">
-        <v>81.55</v>
+        <v>83.34</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.55</v>
+        <v>4.58</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="DM10" t="n">
-        <v>35</v>
+        <v>34.92</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.63</v>
+        <v>10.58</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.55</v>
+        <v>11.66</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.27</v>
+        <v>9.17</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4963,28 +4963,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>40.09</v>
+        <v>41.5</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.36</v>
+        <v>10.33</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.73</v>
+        <v>6.84</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="EA10" t="n">
-        <v>15.64</v>
+        <v>16.75</v>
       </c>
       <c r="EB10" t="n">
         <v>1.16</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="11">
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
@@ -5006,49 +5006,49 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="G11" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>111</v>
+        <v>111.17</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="K11" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="M11" t="n">
-        <v>52</v>
+        <v>53.83</v>
       </c>
       <c r="N11" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.6</v>
+        <v>8.67</v>
       </c>
       <c r="R11" t="n">
-        <v>6</v>
+        <v>6.17</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5060,28 +5060,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>53.2</v>
+        <v>54.33</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.2</v>
+        <v>14.67</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.4</v>
+        <v>10.17</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>23.2</v>
+        <v>21.67</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
         <v>0.17</v>
@@ -5165,70 +5165,70 @@
         <v>2.17</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>11.27</v>
+        <v>11.08</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="BK11" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.73</v>
+        <v>4.75</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.55</v>
+        <v>6.33</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>90.91</v>
+        <v>91.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BU11" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BV11" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX11" t="n">
-        <v>81.81999999999999</v>
+        <v>75</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.35</v>
+        <v>3.07</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.35</v>
+        <v>3.08</v>
       </c>
       <c r="CA11" t="n">
         <v>3.96</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="CC11" t="n">
         <v>2.96</v>
@@ -5237,19 +5237,19 @@
         <v>3.02</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.53</v>
@@ -5258,7 +5258,7 @@
         <v>1.41</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CM11" t="n">
         <v>2.68</v>
@@ -5270,7 +5270,7 @@
         <v>1.15</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CQ11" t="n">
         <v>2.35</v>
@@ -5279,7 +5279,7 @@
         <v>1.35</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CT11" t="n">
         <v>3.32</v>
@@ -5288,7 +5288,7 @@
         <v>1.65</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CW11" t="n">
         <v>1.55</v>
@@ -5312,82 +5312,82 @@
         <v>1.63</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="DH11" t="n">
-        <v>107.73</v>
+        <v>108.08</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.36</v>
+        <v>5.5</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="DM11" t="n">
-        <v>48.45</v>
+        <v>49.66</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.91</v>
+        <v>15.08</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.539999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.18</v>
+        <v>6.25</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>52.64</v>
+        <v>53.25</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.45</v>
+        <v>13.75</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.460000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.27</v>
+        <v>20.67</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5397,13 +5397,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>0.4</v>
@@ -5487,139 +5487,139 @@
         <v>1.4</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>91.29000000000001</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>40.29</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>47.14</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL12" t="n">
         <v>1.17</v>
       </c>
-      <c r="AH12" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>88.17</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>41</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>20.83</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>11.09</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1.27</v>
-      </c>
       <c r="BM12" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.36</v>
+        <v>4.92</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BU12" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BV12" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BW12" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BX12" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BY12" t="n">
         <v>2.36</v>
@@ -5628,34 +5628,34 @@
         <v>2.53</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="CB12" t="n">
         <v>3.87</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.47</v>
+        <v>4.29</v>
       </c>
       <c r="CE12" t="n">
         <v>1.28</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.47</v>
+        <v>3.49</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CK12" t="n">
         <v>1.38</v>
@@ -5664,19 +5664,19 @@
         <v>1.65</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
@@ -5691,10 +5691,10 @@
         <v>1.63</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CX12" t="n">
         <v>1.53</v>
@@ -5706,7 +5706,7 @@
         <v>2.43</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DB12" t="n">
         <v>1.27</v>
@@ -5715,82 +5715,82 @@
         <v>1.63</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="DH12" t="n">
-        <v>90.73</v>
+        <v>92.34</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.27</v>
+        <v>3.91</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM12" t="n">
-        <v>41.45</v>
+        <v>41</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="DP12" t="n">
-        <v>9.27</v>
+        <v>9.42</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.64</v>
+        <v>11.58</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.09</v>
+        <v>9.33</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.55</v>
+        <v>46.92</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.55</v>
+        <v>13.25</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.91</v>
+        <v>8.83</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.64</v>
+        <v>4.42</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.63</v>
+        <v>19.08</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="13">
@@ -5800,13 +5800,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5893,136 +5893,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="AI13" t="n">
-        <v>102.4</v>
+        <v>95.33</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="AL13" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AN13" t="n">
-        <v>63.2</v>
+        <v>53.83</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>11.8</v>
+        <v>11.33</v>
       </c>
       <c r="AS13" t="n">
-        <v>7</v>
+        <v>7.17</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>49.8</v>
+        <v>45.67</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.2</v>
+        <v>9.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.6</v>
+        <v>7.17</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="BD13" t="n">
-        <v>24.8</v>
+        <v>23.5</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.91</v>
+        <v>8.83</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.18</v>
+        <v>3.33</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.64</v>
+        <v>5.42</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT13" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BU13" t="n">
-        <v>27.27</v>
+        <v>33.33</v>
       </c>
       <c r="BV13" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW13" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX13" t="n">
-        <v>54.55</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>2.43</v>
@@ -6031,169 +6031,169 @@
         <v>2.51</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.14</v>
+        <v>3.32</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.15</v>
+        <v>3.46</v>
       </c>
       <c r="CE13" t="n">
         <v>1.29</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="CR13" t="n">
         <v>1.35</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.29</v>
+        <v>3.31</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="DB13" t="n">
         <v>1.26</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="DH13" t="n">
-        <v>113.27</v>
+        <v>108.83</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.18</v>
+        <v>4.92</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM13" t="n">
-        <v>60.27</v>
+        <v>55.83</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.18</v>
+        <v>13.08</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.64</v>
+        <v>11.42</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.45</v>
+        <v>7.5</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.27</v>
+        <v>11.34</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.460000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="EA13" t="n">
-        <v>23.82</v>
+        <v>23.25</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -6350,7 +6350,7 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>48.57</v>
+        <v>48.43</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -6569,7 +6569,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.5</v>
+        <v>49.42</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
@@ -6600,13 +6600,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6690,52 +6690,52 @@
         <v>2</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>109.2</v>
+        <v>96.17</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL15" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>48.2</v>
+        <v>42.83</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.2</v>
+        <v>11.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>10.6</v>
+        <v>9.67</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.6</v>
+        <v>5.17</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6747,82 +6747,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>49.2</v>
+        <v>44.33</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>11</v>
+        <v>10.83</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>24.2</v>
+        <v>22.33</v>
       </c>
       <c r="BE15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO15" t="n">
         <v>1.25</v>
       </c>
-      <c r="BF15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>9</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BP15" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.82</v>
+        <v>5.25</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT15" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BU15" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BW15" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX15" t="n">
-        <v>36.36</v>
+        <v>41.67</v>
       </c>
       <c r="BY15" t="n">
         <v>2.86</v>
@@ -6831,40 +6831,40 @@
         <v>2.91</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.49</v>
+        <v>4.12</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.56</v>
+        <v>4.18</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.87</v>
+        <v>7.22</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.07</v>
+        <v>7.22</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.07</v>
+        <v>3.17</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CM15" t="n">
         <v>2.21</v>
@@ -6873,127 +6873,127 @@
         <v>1.75</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="CT15" t="n">
         <v>3.1</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DB15" t="n">
         <v>1.32</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="DE15" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="DH15" t="n">
-        <v>110.73</v>
+        <v>104.08</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.55</v>
+        <v>5.25</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DM15" t="n">
-        <v>52.55</v>
+        <v>49.5</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.64</v>
+        <v>11.34</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.82</v>
+        <v>10.34</v>
       </c>
       <c r="DR15" t="n">
-        <v>5.36</v>
+        <v>5.58</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>51.55</v>
+        <v>48.92</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.82</v>
+        <v>11.66</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.91</v>
+        <v>8</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.91</v>
+        <v>3.67</v>
       </c>
       <c r="EA15" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="16">
@@ -7003,13 +7003,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7096,136 +7096,136 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
       <c r="AI16" t="n">
-        <v>137.33</v>
+        <v>134.71</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AL16" t="n">
-        <v>6.17</v>
+        <v>6.14</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AN16" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AP16" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>11.14</v>
       </c>
       <c r="AR16" t="n">
-        <v>12</v>
+        <v>12.57</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>5.71</v>
       </c>
       <c r="AT16" t="n">
         <v>2</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>59.5</v>
+        <v>60.43</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>14.67</v>
+        <v>14.57</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.67</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BC16" t="n">
-        <v>5</v>
+        <v>4.71</v>
       </c>
       <c r="BD16" t="n">
-        <v>17.83</v>
+        <v>18.57</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.64</v>
+        <v>10.58</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BL16" t="n">
         <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.82</v>
+        <v>4.58</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.82</v>
+        <v>6</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT16" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BU16" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BV16" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW16" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX16" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BY16" t="n">
         <v>1.58</v>
@@ -7234,49 +7234,49 @@
         <v>1.72</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.1</v>
+        <v>4.06</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.09</v>
+        <v>4.04</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.81</v>
+        <v>2.71</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="CE16" t="n">
         <v>1.25</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CH16" t="n">
         <v>1.66</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CP16" t="n">
         <v>1.56</v>
@@ -7303,98 +7303,98 @@
         <v>1.55</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="CY16" t="n">
         <v>1.78</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DB16" t="inlineStr"/>
       <c r="DC16" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="DG16" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="DH16" t="n">
-        <v>127.45</v>
+        <v>126.75</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ16" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>62.92</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>59.42</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>10</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="EB16" t="n">
         <v>1.82</v>
       </c>
-      <c r="DK16" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="DL16" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="DM16" t="n">
-        <v>62.82</v>
-      </c>
-      <c r="DN16" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="DO16" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="DP16" t="n">
-        <v>10.82</v>
-      </c>
-      <c r="DQ16" t="n">
-        <v>12</v>
-      </c>
-      <c r="DR16" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="DS16" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DT16" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV16" t="n">
-        <v>58.82</v>
-      </c>
-      <c r="DW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX16" t="n">
-        <v>15.64</v>
-      </c>
-      <c r="DY16" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="DZ16" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="EA16" t="n">
-        <v>18.54</v>
-      </c>
-      <c r="EB16" t="n">
-        <v>1.85</v>
-      </c>
       <c r="EC16" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -7404,94 +7404,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="G17" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>91.17</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>5.86</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="M17" t="n">
-        <v>40.83</v>
+        <v>41.29</v>
       </c>
       <c r="N17" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="O17" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="P17" t="n">
-        <v>16.83</v>
+        <v>16.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.83</v>
+        <v>12.43</v>
       </c>
       <c r="R17" t="n">
-        <v>6.17</v>
+        <v>6.71</v>
       </c>
       <c r="S17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>34.86</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.33</v>
       </c>
-      <c r="T17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AE17" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="AF17" t="n">
         <v>0.2</v>
@@ -7575,70 +7575,70 @@
         <v>1.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.27</v>
+        <v>10.25</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.18</v>
+        <v>5.08</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.91</v>
+        <v>5</v>
       </c>
       <c r="BR17" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS17" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BT17" t="n">
-        <v>54.55</v>
+        <v>58.33</v>
       </c>
       <c r="BU17" t="n">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="BV17" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW17" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BX17" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.49</v>
+        <v>3.22</v>
       </c>
       <c r="BZ17" t="n">
-        <v>4.54</v>
+        <v>4.12</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="CC17" t="n">
         <v>4.83</v>
@@ -7650,28 +7650,28 @@
         <v>1.32</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI17" t="n">
         <v>2.07</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CN17" t="n">
         <v>1.93</v>
@@ -7683,34 +7683,34 @@
         <v>1.82</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="DA17" t="n">
         <v>1.92</v>
@@ -7719,52 +7719,52 @@
         <v>1.33</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DH17" t="n">
         <v>88</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="DK17" t="n">
         <v>5</v>
       </c>
       <c r="DL17" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DM17" t="n">
-        <v>36.45</v>
+        <v>37.09</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.91</v>
+        <v>13.84</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.63</v>
+        <v>11.5</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.09</v>
+        <v>8.25</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7776,28 +7776,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>33.36</v>
+        <v>34.17</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.82</v>
+        <v>11.58</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.359999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.46</v>
+        <v>3.33</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.27</v>
+        <v>18.17</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="18">
@@ -7807,94 +7807,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="H18" t="n">
-        <v>109.4</v>
+        <v>107.83</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="K18" t="n">
-        <v>5.4</v>
+        <v>5.17</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="M18" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O18" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="P18" t="n">
-        <v>10.2</v>
+        <v>10.33</v>
       </c>
       <c r="Q18" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="R18" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="S18" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>53.2</v>
+        <v>52.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>15</v>
+        <v>15.33</v>
       </c>
       <c r="AA18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="AC18" t="n">
-        <v>19.8</v>
+        <v>19.5</v>
       </c>
       <c r="AD18" t="n">
         <v>1.68</v>
       </c>
       <c r="AE18" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7978,70 +7978,70 @@
         <v>1.83</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.27</v>
+        <v>9.75</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN18" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.82</v>
+        <v>4.75</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.45</v>
+        <v>5</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>81.81999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT18" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BU18" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BV18" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW18" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX18" t="n">
-        <v>45.45</v>
+        <v>50</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.64</v>
+        <v>4.57</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="CC18" t="n">
         <v>6.48</v>
@@ -8056,28 +8056,28 @@
         <v>2.18</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.86</v>
+        <v>3.85</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CO18" t="n">
         <v>1.13</v>
@@ -8086,7 +8086,7 @@
         <v>1.52</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CR18" t="n">
         <v>1.34</v>
@@ -8101,7 +8101,7 @@
         <v>1.75</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CW18" t="n">
         <v>1.53</v>
@@ -8110,13 +8110,13 @@
         <v>1.54</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.45</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="DB18" t="n">
         <v>1.26</v>
@@ -8125,82 +8125,82 @@
         <v>1.56</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.82</v>
+        <v>2.58</v>
       </c>
       <c r="DH18" t="n">
-        <v>93.36</v>
+        <v>93.92</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.46</v>
+        <v>41.84</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="DP18" t="n">
-        <v>9.27</v>
+        <v>9.42</v>
       </c>
       <c r="DQ18" t="n">
-        <v>9.73</v>
+        <v>9.83</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.550000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>49.55</v>
+        <v>49.5</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.45</v>
+        <v>12.83</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.64</v>
+        <v>8.08</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.82</v>
+        <v>4.75</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.27</v>
+        <v>19.16</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="19">
@@ -8210,13 +8210,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
         <v>0.17</v>
@@ -8303,136 +8303,136 @@
         <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.6</v>
+        <v>1.17</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AI19" t="n">
-        <v>77.40000000000001</v>
+        <v>78.33</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AL19" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AM19" t="n">
         <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>34.4</v>
+        <v>34</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>10.2</v>
+        <v>9.67</v>
       </c>
       <c r="AS19" t="n">
-        <v>11.2</v>
+        <v>11.17</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.2</v>
+        <v>10.17</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.2</v>
+        <v>7.17</v>
       </c>
       <c r="BC19" t="n">
         <v>3</v>
       </c>
       <c r="BD19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.64</v>
+        <v>11.92</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.82</v>
+        <v>5.17</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.64</v>
+        <v>5.67</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT19" t="n">
-        <v>63.64</v>
+        <v>58.33</v>
       </c>
       <c r="BU19" t="n">
-        <v>45.45</v>
+        <v>41.67</v>
       </c>
       <c r="BV19" t="n">
-        <v>18.18</v>
+        <v>16.67</v>
       </c>
       <c r="BW19" t="n">
-        <v>9.09</v>
+        <v>8.33</v>
       </c>
       <c r="BX19" t="n">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="BY19" t="n">
         <v>2.61</v>
@@ -8441,37 +8441,37 @@
         <v>2.7</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL19" t="n">
         <v>1.77</v>
@@ -8483,28 +8483,28 @@
         <v>2.03</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CR19" t="n">
         <v>1.34</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CT19" t="n">
         <v>3.31</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CW19" t="n">
         <v>1.54</v>
@@ -8525,85 +8525,85 @@
         <v>1.27</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF19" t="n">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="DH19" t="n">
-        <v>89.09</v>
+        <v>88.58</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.27</v>
+        <v>4</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
       </c>
       <c r="DM19" t="n">
-        <v>45.82</v>
+        <v>44.66</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.36</v>
+        <v>11.16</v>
       </c>
       <c r="DQ19" t="n">
-        <v>10.64</v>
+        <v>10.34</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.550000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.55</v>
+        <v>45.58</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.91</v>
+        <v>12.67</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.630000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.27</v>
+        <v>4.16</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.91</v>
+        <v>17.34</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -2985,13 +2985,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
         <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3078,136 +3078,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AI6" t="n">
-        <v>82.2</v>
+        <v>87</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.2</v>
+        <v>5.33</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>36</v>
+        <v>35.33</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.6</v>
+        <v>11.17</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.2</v>
+        <v>12.17</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.4</v>
+        <v>6.33</v>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>49</v>
+        <v>48.33</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.4</v>
+        <v>7.67</v>
       </c>
       <c r="BC6" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="BD6" t="n">
-        <v>15.8</v>
+        <v>17.17</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.17</v>
+        <v>10.46</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM6" t="n">
         <v>1</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.42</v>
+        <v>5.85</v>
       </c>
       <c r="BR6" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BT6" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU6" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BV6" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX6" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BY6" t="n">
         <v>3.63</v>
@@ -3216,28 +3216,28 @@
         <v>3.6</v>
       </c>
       <c r="CA6" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="CB6" t="n">
         <v>4.08</v>
       </c>
-      <c r="CB6" t="n">
-        <v>4.12</v>
-      </c>
       <c r="CC6" t="n">
-        <v>3.79</v>
+        <v>3.59</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.97</v>
+        <v>3.74</v>
       </c>
       <c r="CE6" t="n">
         <v>1.25</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.66</v>
+        <v>3.62</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CI6" t="n">
         <v>2.46</v>
@@ -3246,55 +3246,55 @@
         <v>1.54</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL6" t="n">
         <v>1.78</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CN6" t="n">
         <v>2.1</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CT6" t="n">
         <v>3.19</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CW6" t="n">
         <v>1.57</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="DB6" t="n">
         <v>1.3</v>
@@ -3303,82 +3303,82 @@
         <v>1.66</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="DH6" t="n">
-        <v>85.75</v>
+        <v>87.69</v>
       </c>
       <c r="DI6" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.83</v>
+        <v>4.92</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DM6" t="n">
-        <v>37</v>
+        <v>36.61</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.67</v>
+        <v>11.08</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.25</v>
+        <v>10.39</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.58</v>
+        <v>7.46</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.67</v>
+        <v>45.62</v>
       </c>
       <c r="DW6" t="n">
         <v>0.08</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.67</v>
+        <v>11.85</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.17</v>
+        <v>7.31</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="EA6" t="n">
-        <v>16</v>
+        <v>16.62</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="7">
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
@@ -5812,82 +5812,82 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G13" t="n">
-        <v>3.17</v>
+        <v>3.71</v>
       </c>
       <c r="H13" t="n">
-        <v>122.33</v>
+        <v>123</v>
       </c>
       <c r="I13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J13" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="K13" t="n">
-        <v>4.83</v>
+        <v>5.29</v>
       </c>
       <c r="L13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M13" t="n">
-        <v>57.83</v>
+        <v>58.14</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="P13" t="n">
-        <v>13.67</v>
+        <v>13.43</v>
       </c>
       <c r="Q13" t="n">
-        <v>11.5</v>
+        <v>10.43</v>
       </c>
       <c r="R13" t="n">
-        <v>7.83</v>
+        <v>7.29</v>
       </c>
       <c r="S13" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="T13" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="U13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>48.33</v>
+        <v>49.29</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.17</v>
+        <v>12.43</v>
       </c>
       <c r="AA13" t="n">
-        <v>10.17</v>
+        <v>9.57</v>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AC13" t="n">
-        <v>23</v>
+        <v>22.71</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5971,70 +5971,70 @@
         <v>3.17</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.83</v>
+        <v>9.23</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.42</v>
+        <v>5.85</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BT13" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU13" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV13" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW13" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CC13" t="n">
         <v>3.32</v>
@@ -6043,19 +6043,19 @@
         <v>3.46</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.58</v>
@@ -6064,13 +6064,13 @@
         <v>1.45</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CO13" t="n">
         <v>1.21</v>
@@ -6094,7 +6094,7 @@
         <v>1.57</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CW13" t="n">
         <v>1.57</v>
@@ -6106,10 +6106,10 @@
         <v>1.84</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB13" t="n">
         <v>1.26</v>
@@ -6127,73 +6127,73 @@
         <v>2.08</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.42</v>
+        <v>3.69</v>
       </c>
       <c r="DH13" t="n">
-        <v>108.83</v>
+        <v>110.23</v>
       </c>
       <c r="DI13" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.92</v>
+        <v>5.16</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM13" t="n">
-        <v>55.83</v>
+        <v>56.15</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="DP13" t="n">
-        <v>13.08</v>
+        <v>13</v>
       </c>
       <c r="DQ13" t="n">
-        <v>11.42</v>
+        <v>10.85</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.5</v>
+        <v>7.23</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47</v>
+        <v>47.62</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.34</v>
+        <v>11.08</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.67</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="EA13" t="n">
-        <v>23.25</v>
+        <v>23.07</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="14">

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="F2" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="G2" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="H2" t="n">
-        <v>108.5</v>
+        <v>103</v>
       </c>
       <c r="I2" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>5.43</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="M2" t="n">
-        <v>47.17</v>
+        <v>44</v>
       </c>
       <c r="N2" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="O2" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="P2" t="n">
         <v>12</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.67</v>
+        <v>10</v>
       </c>
       <c r="R2" t="n">
-        <v>7.33</v>
+        <v>8.57</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="T2" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>49.17</v>
+        <v>46.71</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.5</v>
+        <v>12.57</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.83</v>
+        <v>8.57</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.33</v>
+        <v>20.86</v>
       </c>
       <c r="AD2" t="n">
         <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="AF2" t="n">
         <v>0.17</v>
@@ -1550,70 +1550,70 @@
         <v>3.17</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.42</v>
+        <v>8.69</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BL2" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.92</v>
+        <v>4.08</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.5</v>
+        <v>4.62</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT2" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BU2" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BV2" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX2" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="BZ2" t="n">
-        <v>4.44</v>
+        <v>4.32</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="CC2" t="n">
         <v>3.91</v>
@@ -1625,7 +1625,7 @@
         <v>1.3</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CG2" t="n">
         <v>3.37</v>
@@ -1634,31 +1634,31 @@
         <v>1.55</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL2" t="n">
         <v>1.91</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CN2" t="n">
         <v>1.93</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CR2" t="n">
         <v>1.35</v>
@@ -1673,22 +1673,22 @@
         <v>1.59</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CW2" t="n">
         <v>1.64</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="DB2" t="n">
         <v>1.28</v>
@@ -1700,46 +1700,46 @@
         <v>2.68</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="DF2" t="n">
         <v>1.92</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DH2" t="n">
-        <v>104.16</v>
+        <v>101.54</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.08</v>
+        <v>4.16</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DM2" t="n">
-        <v>39.67</v>
+        <v>38.54</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="DO2" t="n">
         <v>2</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.16</v>
+        <v>13.08</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.92</v>
+        <v>11.46</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.5</v>
+        <v>9.08</v>
       </c>
       <c r="DS2" t="n">
         <v>0.08</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>46</v>
+        <v>44.92</v>
       </c>
       <c r="DW2" t="n">
         <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.34</v>
+        <v>12.39</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.33</v>
+        <v>8.23</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.75</v>
+        <v>19.16</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
         <v>0.43</v>
@@ -1872,118 +1872,118 @@
         <v>1.86</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AI3" t="n">
-        <v>90.2</v>
+        <v>99</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>3.2</v>
+        <v>3.83</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="AN3" t="n">
-        <v>39</v>
+        <v>43.33</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AR3" t="n">
-        <v>13</v>
+        <v>12.83</v>
       </c>
       <c r="AS3" t="n">
-        <v>10</v>
+        <v>8.83</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>53.4</v>
+        <v>55.83</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.8</v>
+        <v>7.83</v>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="BD3" t="n">
-        <v>15.4</v>
+        <v>15.67</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="BH3" t="n">
-        <v>10</v>
+        <v>10.15</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.5</v>
+        <v>4.62</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.5</v>
+        <v>5.54</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,19 +1992,19 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BU3" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BV3" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW3" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BX3" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BY3" t="n">
         <v>1.85</v>
@@ -2013,16 +2013,16 @@
         <v>1.92</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.19</v>
+        <v>4.14</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.61</v>
+        <v>3.32</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.99</v>
+        <v>3.68</v>
       </c>
       <c r="CE3" t="n">
         <v>1.26</v>
@@ -2031,7 +2031,7 @@
         <v>2.31</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CH3" t="n">
         <v>1.62</v>
@@ -2052,7 +2052,7 @@
         <v>2.46</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO3" t="n">
         <v>1.16</v>
@@ -2061,7 +2061,7 @@
         <v>1.6</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CR3" t="n">
         <v>1.34</v>
@@ -2085,13 +2085,13 @@
         <v>1.57</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB3" t="n">
         <v>1.27</v>
@@ -2103,79 +2103,79 @@
         <v>2.54</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DG3" t="n">
         <v>3</v>
       </c>
       <c r="DH3" t="n">
-        <v>107.75</v>
+        <v>110.46</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.66</v>
+        <v>4.84</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DM3" t="n">
-        <v>45</v>
+        <v>46.54</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="DP3" t="n">
-        <v>8.75</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.83</v>
+        <v>11.84</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.75</v>
+        <v>7.38</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>59</v>
+        <v>59.69</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.75</v>
+        <v>14.23</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.75</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5</v>
+        <v>4.77</v>
       </c>
       <c r="EA3" t="n">
-        <v>15.58</v>
+        <v>15.69</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>0.29</v>
@@ -2275,118 +2275,118 @@
         <v>1.71</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="AI4" t="n">
-        <v>134.6</v>
+        <v>130.83</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>71.8</v>
+        <v>69.67</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.6</v>
+        <v>9.83</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.8</v>
+        <v>9.83</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AU4" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>67.40000000000001</v>
+        <v>66</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="BB4" t="n">
-        <v>10.2</v>
+        <v>9.83</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.6</v>
+        <v>8.17</v>
       </c>
       <c r="BD4" t="n">
-        <v>20.4</v>
+        <v>20.33</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="BF4" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.08</v>
+        <v>9.85</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.83</v>
+        <v>1.08</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.92</v>
+        <v>4.85</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2398,16 +2398,16 @@
         <v>100</v>
       </c>
       <c r="BU4" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BV4" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BW4" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY4" t="n">
         <v>1.18</v>
@@ -2416,46 +2416,46 @@
         <v>1.2</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.52</v>
+        <v>7.32</v>
       </c>
       <c r="CB4" t="n">
-        <v>8.369999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="CC4" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="CE4" t="n">
         <v>1.15</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CG4" t="n">
-        <v>4.96</v>
+        <v>4.91</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL4" t="n">
         <v>1.91</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CO4" t="n">
         <v>1.06</v>
@@ -2468,17 +2468,17 @@
       </c>
       <c r="CR4" t="inlineStr"/>
       <c r="CS4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="CX4" t="n">
         <v>1.52</v>
@@ -2487,10 +2487,10 @@
         <v>1.86</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB4" t="inlineStr"/>
       <c r="DC4" t="n">
@@ -2500,79 +2500,79 @@
         <v>1.79</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="DG4" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="DH4" t="n">
-        <v>132.09</v>
+        <v>130.54</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.84</v>
+        <v>5.69</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DM4" t="n">
-        <v>68.92</v>
+        <v>68.16</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.83</v>
+        <v>9.92</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.83</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.25</v>
+        <v>5.38</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>66.83</v>
+        <v>66.23</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>19.17</v>
+        <v>19.15</v>
       </c>
       <c r="DY4" t="n">
-        <v>11.17</v>
+        <v>10.92</v>
       </c>
       <c r="DZ4" t="n">
-        <v>8</v>
+        <v>8.23</v>
       </c>
       <c r="EA4" t="n">
         <v>20.08</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="5">
@@ -2582,10 +2582,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
@@ -2594,82 +2594,82 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H5" t="n">
-        <v>119</v>
+        <v>114.83</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="K5" t="n">
-        <v>7.8</v>
+        <v>7.67</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="M5" t="n">
-        <v>64</v>
+        <v>60.33</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="P5" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.4</v>
+        <v>9.33</v>
       </c>
       <c r="R5" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>57.4</v>
+        <v>55</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.8</v>
+        <v>14.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>10.2</v>
+        <v>9.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.6</v>
+        <v>5.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>18</v>
+        <v>18.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2753,70 +2753,70 @@
         <v>2.29</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.33</v>
+        <v>10.46</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.83</v>
+        <v>6.92</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT5" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU5" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV5" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW5" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CA5" t="n">
         <v>4.29</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
       <c r="CC5" t="n">
         <v>2.65</v>
@@ -2828,40 +2828,40 @@
         <v>1.24</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL5" t="n">
         <v>1.87</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="CR5" t="n">
         <v>1.34</v>
@@ -2876,7 +2876,7 @@
         <v>1.7</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="CW5" t="n">
         <v>1.58</v>
@@ -2885,64 +2885,64 @@
         <v>1.56</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.42</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="DB5" t="n">
         <v>1.26</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="DH5" t="n">
-        <v>110.17</v>
+        <v>108.92</v>
       </c>
       <c r="DI5" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.41</v>
+        <v>5.54</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="DM5" t="n">
-        <v>57.58</v>
+        <v>56.38</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="DP5" t="n">
-        <v>12</v>
+        <v>11.61</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.25</v>
+        <v>10.15</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.5</v>
+        <v>6.85</v>
       </c>
       <c r="DS5" t="n">
         <v>0.08</v>
@@ -2954,28 +2954,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>53.84</v>
+        <v>53</v>
       </c>
       <c r="DW5" t="n">
         <v>0.08</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.59</v>
+        <v>12.23</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.08</v>
+        <v>7.77</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="EA5" t="n">
-        <v>19</v>
+        <v>19.07</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="6">
@@ -3219,13 +3219,13 @@
         <v>4.03</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="CC6" t="n">
         <v>3.59</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="CE6" t="n">
         <v>1.25</v>
@@ -3267,13 +3267,13 @@
         <v>2.44</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="CU6" t="n">
         <v>1.68</v>
@@ -3300,10 +3300,10 @@
         <v>1.3</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
@@ -3388,13 +3388,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3481,49 +3481,49 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.17</v>
+        <v>2.71</v>
       </c>
       <c r="AI7" t="n">
-        <v>109.33</v>
+        <v>107.29</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AL7" t="n">
-        <v>5.17</v>
+        <v>4.43</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>51.67</v>
+        <v>49.57</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AP7" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.67</v>
+        <v>10.71</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.5</v>
+        <v>9.43</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.17</v>
+        <v>8</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.33</v>
+        <v>2.86</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3535,82 +3535,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>56.33</v>
+        <v>55.14</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>13</v>
+        <v>12.29</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.67</v>
+        <v>4.29</v>
       </c>
       <c r="BD7" t="n">
-        <v>21.5</v>
+        <v>20.71</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.17</v>
+        <v>7.85</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.25</v>
+        <v>4.38</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="BO7" t="n">
         <v>2</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.92</v>
+        <v>3.77</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT7" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU7" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BV7" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BW7" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BX7" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BY7" t="n">
         <v>2.37</v>
@@ -3625,10 +3625,10 @@
         <v>4.17</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.55</v>
+        <v>2.82</v>
       </c>
       <c r="CE7" t="n">
         <v>1.24</v>
@@ -3643,22 +3643,22 @@
         <v>1.68</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.5</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CO7" t="n">
         <v>1.14</v>
@@ -3667,7 +3667,7 @@
         <v>1.54</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CR7" t="inlineStr"/>
       <c r="CS7" t="n">
@@ -3678,10 +3678,10 @@
         <v>1.75</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CX7" t="n">
         <v>1.57</v>
@@ -3706,76 +3706,76 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="DH7" t="n">
-        <v>103.58</v>
+        <v>102.92</v>
       </c>
       <c r="DI7" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.5</v>
+        <v>5.08</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DM7" t="n">
-        <v>51.84</v>
+        <v>50.69</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.83</v>
+        <v>2.61</v>
       </c>
       <c r="DP7" t="n">
-        <v>9.5</v>
+        <v>10.07</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.58</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.42</v>
+        <v>7.39</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>55.83</v>
+        <v>55.23</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>13.34</v>
+        <v>12.93</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.58</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.75</v>
+        <v>4.54</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.67</v>
+        <v>21.23</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="8">
@@ -3785,13 +3785,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>0.33</v>
@@ -3878,43 +3878,43 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AI8" t="n">
-        <v>83.5</v>
+        <v>87</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.17</v>
+        <v>3.57</v>
       </c>
       <c r="AM8" t="n">
         <v>1</v>
       </c>
       <c r="AN8" t="n">
-        <v>39.33</v>
+        <v>43.14</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.5</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.83</v>
+        <v>12.57</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.67</v>
+        <v>8.57</v>
       </c>
       <c r="AT8" t="n">
         <v>2</v>
@@ -3923,91 +3923,91 @@
         <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>44.67</v>
+        <v>47.14</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA8" t="n">
-        <v>10.83</v>
+        <v>11.43</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.17</v>
+        <v>18.71</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="BF8" t="n">
         <v>1</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="BH8" t="n">
-        <v>7.83</v>
+        <v>8.31</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.08</v>
+        <v>4.38</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="BR8" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS8" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT8" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU8" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BV8" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX8" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY8" t="n">
         <v>2.14</v>
@@ -4016,43 +4016,43 @@
         <v>2.17</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.66</v>
+        <v>4.25</v>
       </c>
       <c r="CD8" t="n">
-        <v>5.04</v>
+        <v>4.57</v>
       </c>
       <c r="CE8" t="n">
         <v>1.32</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.35</v>
+        <v>3.32</v>
       </c>
       <c r="CH8" t="n">
         <v>1.51</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.68</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CL8" t="n">
         <v>2.1</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CN8" t="n">
         <v>1.74</v>
@@ -4061,124 +4061,124 @@
         <v>1.23</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DH8" t="n">
-        <v>95.75</v>
+        <v>96.69</v>
       </c>
       <c r="DI8" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.58</v>
+        <v>4.69</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM8" t="n">
-        <v>44.08</v>
+        <v>45.77</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.83</v>
+        <v>2.93</v>
       </c>
       <c r="DP8" t="n">
-        <v>8.75</v>
+        <v>8.84</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.33</v>
+        <v>13.15</v>
       </c>
       <c r="DR8" t="n">
-        <v>5.92</v>
+        <v>6.08</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.25</v>
+        <v>51.15</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX8" t="n">
-        <v>12</v>
+        <v>12.23</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.08</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.92</v>
+        <v>3.77</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.75</v>
+        <v>20.84</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="9">
@@ -4188,61 +4188,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F9" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="G9" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="H9" t="n">
-        <v>86</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="L9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M9" t="n">
-        <v>39.17</v>
+        <v>41.57</v>
       </c>
       <c r="N9" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O9" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="P9" t="n">
-        <v>13.33</v>
+        <v>12.57</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.17</v>
+        <v>13.14</v>
       </c>
       <c r="R9" t="n">
-        <v>9.17</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4254,22 +4254,22 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.33</v>
+        <v>46.57</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.5</v>
+        <v>14.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.33</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.17</v>
+        <v>5.29</v>
       </c>
       <c r="AC9" t="n">
-        <v>20</v>
+        <v>18.86</v>
       </c>
       <c r="AD9" t="n">
         <v>1.56</v>
@@ -4359,70 +4359,70 @@
         <v>2.17</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.67</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="BO9" t="n">
         <v>1</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.25</v>
+        <v>4.31</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.33</v>
+        <v>4.23</v>
       </c>
       <c r="BR9" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS9" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU9" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BV9" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.33</v>
+        <v>4.27</v>
       </c>
       <c r="CB9" t="n">
-        <v>5.03</v>
+        <v>4.92</v>
       </c>
       <c r="CC9" t="n">
         <v>7.12</v>
@@ -4434,16 +4434,16 @@
         <v>1.28</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.6</v>
@@ -4452,7 +4452,7 @@
         <v>1.45</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM9" t="n">
         <v>2.57</v>
@@ -4464,22 +4464,22 @@
         <v>1.16</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="CT9" t="n">
         <v>3.14</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CV9" t="n">
         <v>2.46</v>
@@ -4503,52 +4503,52 @@
         <v>1.32</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="DE9" t="n">
         <v>0.16</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DG9" t="n">
         <v>2.08</v>
       </c>
       <c r="DH9" t="n">
-        <v>86</v>
+        <v>86.77</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.67</v>
+        <v>3.77</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.75</v>
+        <v>37.31</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.42</v>
+        <v>13</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.67</v>
+        <v>12.69</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.58</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4560,25 +4560,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.92</v>
+        <v>47.46</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.34</v>
+        <v>13.23</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.75</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.58</v>
+        <v>4.69</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.08</v>
+        <v>18.54</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="EC9" t="n">
         <v>2.08</v>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
@@ -4603,49 +4603,49 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="G10" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="H10" t="n">
-        <v>87.67</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J10" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="K10" t="n">
-        <v>4.67</v>
+        <v>5.14</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>37.33</v>
+        <v>37.29</v>
       </c>
       <c r="N10" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="P10" t="n">
-        <v>10.33</v>
+        <v>10.43</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.5</v>
+        <v>12.14</v>
       </c>
       <c r="R10" t="n">
-        <v>8.17</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4657,28 +4657,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>42.33</v>
+        <v>41.71</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>11.83</v>
+        <v>12.43</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.67</v>
+        <v>8.43</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="AC10" t="n">
-        <v>15.17</v>
+        <v>15.14</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4765,67 +4765,67 @@
         <v>3.08</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.17</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI10" t="n">
         <v>3.08</v>
       </c>
       <c r="BJ10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BL10" t="n">
         <v>0.92</v>
       </c>
-      <c r="BK10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.83</v>
-      </c>
       <c r="BM10" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.92</v>
+        <v>4.23</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.25</v>
+        <v>5.31</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT10" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU10" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV10" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX10" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.37</v>
+        <v>3.46</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.22</v>
+        <v>4.18</v>
       </c>
       <c r="CC10" t="n">
         <v>5.66</v>
@@ -4834,124 +4834,124 @@
         <v>6.21</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF10" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CM10" t="n">
         <v>2.37</v>
       </c>
-      <c r="CG10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>2.4</v>
-      </c>
       <c r="CN10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DA10" t="n">
         <v>1.88</v>
       </c>
-      <c r="CO10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CQ10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CS10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="CT10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="CU10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CV10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="CW10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CX10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CY10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CZ10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="DA10" t="n">
-        <v>1.91</v>
-      </c>
       <c r="DB10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="DH10" t="n">
-        <v>83.34</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="DI10" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.58</v>
+        <v>4.84</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DM10" t="n">
-        <v>34.92</v>
+        <v>35.08</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.58</v>
+        <v>10.61</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.66</v>
+        <v>11.54</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.17</v>
+        <v>9.16</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4963,28 +4963,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>41.5</v>
+        <v>41.23</v>
       </c>
       <c r="DW10" t="n">
         <v>0.08</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.33</v>
+        <v>10.77</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.84</v>
+        <v>7.31</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.75</v>
+        <v>16.61</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="11">
@@ -4994,13 +4994,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
         <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5084,139 +5084,139 @@
         <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AI11" t="n">
-        <v>105</v>
+        <v>105.57</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN11" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15.17</v>
+        <v>14.29</v>
       </c>
       <c r="AR11" t="n">
-        <v>10.33</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>52.17</v>
+        <v>52.86</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.83</v>
+        <v>12.57</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.67</v>
+        <v>7.71</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.17</v>
+        <v>4.86</v>
       </c>
       <c r="BD11" t="n">
-        <v>19.67</v>
+        <v>20.57</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="BH11" t="n">
-        <v>11.08</v>
+        <v>11.15</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.75</v>
+        <v>4.69</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.33</v>
+        <v>6.46</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT11" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BU11" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BV11" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX11" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BY11" t="n">
         <v>3.07</v>
@@ -5225,34 +5225,34 @@
         <v>3.08</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.96</v>
+        <v>4.01</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CK11" t="n">
         <v>1.41</v>
@@ -5261,19 +5261,19 @@
         <v>1.76</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
@@ -5288,73 +5288,73 @@
         <v>1.65</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CX11" t="n">
         <v>1.5</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.52</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DB11" t="n">
         <v>1.26</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="DE11" t="n">
         <v>0.08</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="DH11" t="n">
-        <v>108.08</v>
+        <v>108.15</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DJ11" t="n">
         <v>2</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM11" t="n">
-        <v>49.66</v>
+        <v>49.61</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="DP11" t="n">
-        <v>15.08</v>
+        <v>14.62</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.5</v>
+        <v>9.31</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.25</v>
+        <v>6.08</v>
       </c>
       <c r="DS11" t="n">
         <v>0.16</v>
@@ -5366,25 +5366,25 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.25</v>
+        <v>53.54</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.75</v>
+        <v>13.54</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.92</v>
+        <v>8.85</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.84</v>
+        <v>4.69</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.67</v>
+        <v>21.08</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="EC11" t="n">
         <v>2</v>
@@ -5397,61 +5397,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="H12" t="n">
-        <v>93.8</v>
+        <v>96.33</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="O12" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="P12" t="n">
-        <v>9.4</v>
+        <v>8.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.2</v>
+        <v>11.17</v>
       </c>
       <c r="R12" t="n">
-        <v>7.2</v>
+        <v>6.83</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="T12" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5463,28 +5463,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>46.6</v>
+        <v>48.5</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.2</v>
+        <v>14.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="AB12" t="n">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>18.2</v>
+        <v>19.83</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AF12" t="n">
         <v>0.14</v>
@@ -5568,22 +5568,22 @@
         <v>2.29</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.5</v>
+        <v>10.38</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BM12" t="n">
         <v>0.92</v>
@@ -5592,10 +5592,10 @@
         <v>2.08</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="BQ12" t="n">
         <v>4.92</v>
@@ -5604,34 +5604,34 @@
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT12" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU12" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BV12" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BW12" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX12" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="CC12" t="n">
         <v>4.1</v>
@@ -5640,124 +5640,124 @@
         <v>4.29</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.49</v>
+        <v>3.45</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CK12" t="n">
         <v>1.38</v>
       </c>
       <c r="CL12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CP12" t="n">
         <v>1.65</v>
       </c>
-      <c r="CM12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="CP12" t="n">
-        <v>1.64</v>
-      </c>
       <c r="CQ12" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS12" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CZ12" t="n">
         <v>2.36</v>
       </c>
-      <c r="CT12" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="CU12" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CV12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="CW12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CX12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CY12" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CZ12" t="n">
-        <v>2.43</v>
-      </c>
       <c r="DA12" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="DB12" t="n">
         <v>1.27</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="DH12" t="n">
-        <v>92.34</v>
+        <v>93.62</v>
       </c>
       <c r="DI12" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM12" t="n">
-        <v>41</v>
+        <v>40.16</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DP12" t="n">
-        <v>9.42</v>
+        <v>9.15</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.58</v>
+        <v>11.15</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.33</v>
+        <v>9</v>
       </c>
       <c r="DS12" t="n">
         <v>0.08</v>
@@ -5769,28 +5769,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.92</v>
+        <v>47.77</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.25</v>
+        <v>13.08</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.83</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.42</v>
+        <v>4.69</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.08</v>
+        <v>19.77</v>
       </c>
       <c r="EB12" t="n">
         <v>1.45</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="13">
@@ -6034,7 +6034,7 @@
         <v>3.61</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CC13" t="n">
         <v>3.32</v>
@@ -6082,22 +6082,22 @@
         <v>2.69</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX13" t="n">
         <v>1.54</v>
@@ -6115,10 +6115,10 @@
         <v>1.26</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
@@ -6203,94 +6203,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
         <v>7</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>96.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="K14" t="n">
-        <v>6.8</v>
+        <v>6.33</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="M14" t="n">
-        <v>40.8</v>
+        <v>41.33</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="O14" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="P14" t="n">
-        <v>8.6</v>
+        <v>8.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R14" t="n">
-        <v>7.6</v>
+        <v>6.67</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>17</v>
+        <v>16.83</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.8</v>
+        <v>7.67</v>
       </c>
       <c r="AC14" t="n">
         <v>20</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AF14" t="n">
         <v>0.57</v>
@@ -6374,70 +6374,70 @@
         <v>1.71</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="BH14" t="n">
-        <v>11.17</v>
+        <v>10.62</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.92</v>
+        <v>1.15</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.17</v>
+        <v>4.92</v>
       </c>
       <c r="BQ14" t="n">
-        <v>6</v>
+        <v>5.69</v>
       </c>
       <c r="BR14" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS14" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT14" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU14" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BV14" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BW14" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BX14" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.32</v>
+        <v>4.3</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="CC14" t="n">
         <v>3.84</v>
@@ -6449,28 +6449,28 @@
         <v>1.21</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.48</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CN14" t="n">
         <v>2.1</v>
@@ -6479,21 +6479,21 @@
         <v>1.1</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CQ14" t="n">
         <v>2.08</v>
       </c>
       <c r="CR14" t="inlineStr"/>
       <c r="CS14" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CT14" t="inlineStr"/>
       <c r="CU14" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CW14" t="n">
         <v>1.46</v>
@@ -6512,85 +6512,85 @@
       </c>
       <c r="DB14" t="inlineStr"/>
       <c r="DC14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="DH14" t="n">
-        <v>93.25</v>
+        <v>94.23</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.33</v>
+        <v>6.15</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DM14" t="n">
-        <v>42.67</v>
+        <v>42.77</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="DO14" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.5</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.41</v>
+        <v>10.84</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.08</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DT14" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.42</v>
+        <v>49.62</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>16.75</v>
+        <v>16.69</v>
       </c>
       <c r="DY14" t="n">
-        <v>11</v>
+        <v>10.85</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.75</v>
+        <v>5.85</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.75</v>
+        <v>17</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="15">
@@ -6600,13 +6600,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6690,52 +6690,52 @@
         <v>2</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AI15" t="n">
-        <v>96.17</v>
+        <v>94</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>42.83</v>
+        <v>41.43</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.5</v>
+        <v>10.71</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.17</v>
+        <v>5.57</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6747,82 +6747,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>44.33</v>
+        <v>44</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.83</v>
+        <v>10</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.33</v>
+        <v>7.71</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="BD15" t="n">
-        <v>22.33</v>
+        <v>20.14</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.25</v>
+        <v>9.23</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BP15" t="n">
         <v>4</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.25</v>
+        <v>5.23</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT15" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BU15" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV15" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX15" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BY15" t="n">
         <v>2.86</v>
@@ -6831,28 +6831,28 @@
         <v>2.91</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.18</v>
+        <v>4.13</v>
       </c>
       <c r="CC15" t="n">
-        <v>7.22</v>
+        <v>6.72</v>
       </c>
       <c r="CD15" t="n">
-        <v>7.22</v>
+        <v>6.74</v>
       </c>
       <c r="CE15" t="n">
         <v>1.34</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI15" t="n">
         <v>2.04</v>
@@ -6861,16 +6861,16 @@
         <v>1.76</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO15" t="n">
         <v>1.24</v>
@@ -6885,13 +6885,13 @@
         <v>1.39</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="CT15" t="n">
         <v>3.1</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV15" t="n">
         <v>2.19</v>
@@ -6900,7 +6900,7 @@
         <v>1.78</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY15" t="n">
         <v>2.06</v>
@@ -6909,16 +6909,16 @@
         <v>2.29</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="DB15" t="n">
         <v>1.32</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="DE15" t="n">
         <v>0.08</v>
@@ -6927,40 +6927,40 @@
         <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="DH15" t="n">
-        <v>104.08</v>
+        <v>102.31</v>
       </c>
       <c r="DI15" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.25</v>
+        <v>5.16</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM15" t="n">
-        <v>49.5</v>
+        <v>48.23</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.34</v>
+        <v>10.92</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.34</v>
+        <v>10</v>
       </c>
       <c r="DR15" t="n">
-        <v>5.58</v>
+        <v>5.77</v>
       </c>
       <c r="DS15" t="n">
         <v>0.08</v>
@@ -6972,28 +6972,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>48.92</v>
+        <v>48.38</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.66</v>
+        <v>11.15</v>
       </c>
       <c r="DY15" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.67</v>
+        <v>3.46</v>
       </c>
       <c r="EA15" t="n">
-        <v>23.08</v>
+        <v>21.84</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="16">
@@ -7003,10 +7003,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -7015,82 +7015,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="H16" t="n">
-        <v>115.6</v>
+        <v>107.17</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2</v>
+        <v>4.83</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M16" t="n">
-        <v>44.6</v>
+        <v>41.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="O16" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="P16" t="n">
-        <v>10.6</v>
+        <v>9.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>11.83</v>
       </c>
       <c r="R16" t="n">
-        <v>5.8</v>
+        <v>5.67</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6</v>
+        <v>1.33</v>
       </c>
       <c r="T16" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>58</v>
+        <v>55.17</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="Z16" t="n">
-        <v>16.8</v>
+        <v>16.17</v>
       </c>
       <c r="AA16" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.6</v>
+        <v>5.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.4</v>
+        <v>17.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7174,70 +7174,70 @@
         <v>2.14</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.58</v>
+        <v>10.31</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.17</v>
+        <v>3.31</v>
       </c>
       <c r="BJ16" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BL16" t="n">
         <v>0.92</v>
       </c>
-      <c r="BK16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BL16" t="n">
+      <c r="BM16" t="n">
         <v>1</v>
       </c>
-      <c r="BM16" t="n">
-        <v>0.75</v>
-      </c>
       <c r="BN16" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="BQ16" t="n">
-        <v>6</v>
+        <v>5.77</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT16" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BU16" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BV16" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX16" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.58</v>
+        <v>2.24</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.72</v>
+        <v>2.23</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.06</v>
+        <v>4.13</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.04</v>
+        <v>4.09</v>
       </c>
       <c r="CC16" t="n">
         <v>2.71</v>
@@ -7249,149 +7249,149 @@
         <v>1.25</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CN16" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CO16" t="n">
         <v>1.14</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="CR16" t="n">
         <v>1.33</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="CT16" t="n">
         <v>3.35</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="DB16" t="inlineStr"/>
       <c r="DC16" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.09</v>
+        <v>2.93</v>
       </c>
       <c r="DH16" t="n">
-        <v>126.75</v>
+        <v>122</v>
       </c>
       <c r="DI16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>60.08</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>10.54</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>58</v>
+      </c>
+      <c r="DW16" t="n">
         <v>0.08</v>
       </c>
-      <c r="DJ16" t="n">
-        <v>2</v>
-      </c>
-      <c r="DK16" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="DL16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DM16" t="n">
-        <v>62.92</v>
-      </c>
-      <c r="DN16" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="DO16" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="DP16" t="n">
-        <v>10.92</v>
-      </c>
-      <c r="DQ16" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="DR16" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="DS16" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DT16" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV16" t="n">
-        <v>59.42</v>
-      </c>
-      <c r="DW16" t="n">
-        <v>0</v>
-      </c>
       <c r="DX16" t="n">
-        <v>15.5</v>
+        <v>15.31</v>
       </c>
       <c r="DY16" t="n">
-        <v>10</v>
+        <v>10.16</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.5</v>
+        <v>5.15</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.92</v>
+        <v>18.08</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="EC16" t="n">
         <v>2</v>
@@ -7404,13 +7404,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>0.14</v>
@@ -7494,49 +7494,49 @@
         <v>3.14</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="AI17" t="n">
-        <v>84.2</v>
+        <v>89.5</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AN17" t="n">
-        <v>31.2</v>
+        <v>39</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10.4</v>
+        <v>10.33</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>10.4</v>
+        <v>9</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="n">
         <v>1</v>
@@ -7551,82 +7551,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>33.2</v>
+        <v>37.17</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>10.4</v>
+        <v>12.17</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.2</v>
+        <v>3.67</v>
       </c>
       <c r="BD17" t="n">
-        <v>16.8</v>
+        <v>18.83</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.25</v>
+        <v>10.31</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.08</v>
+        <v>4.92</v>
       </c>
       <c r="BQ17" t="n">
         <v>5</v>
       </c>
       <c r="BR17" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS17" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT17" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU17" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BV17" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW17" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY17" t="n">
         <v>3.22</v>
@@ -7635,46 +7635,46 @@
         <v>4.12</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.87</v>
+        <v>3.82</v>
       </c>
       <c r="CB17" t="n">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.83</v>
+        <v>4.56</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.7</v>
+        <v>4.57</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="CH17" t="n">
         <v>1.5</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.74</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL17" t="n">
         <v>1.9</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO17" t="n">
         <v>1.24</v>
@@ -7683,19 +7683,19 @@
         <v>1.82</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="CR17" t="n">
         <v>1.4</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV17" t="n">
         <v>2.11</v>
@@ -7707,64 +7707,64 @@
         <v>1.58</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.4</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="DB17" t="n">
         <v>1.33</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="DH17" t="n">
-        <v>88</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="DK17" t="n">
-        <v>5</v>
+        <v>5.46</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DM17" t="n">
-        <v>37.09</v>
+        <v>40.23</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.84</v>
+        <v>13.54</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.5</v>
+        <v>11.54</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.25</v>
+        <v>7.77</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7776,28 +7776,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>34.17</v>
+        <v>35.93</v>
       </c>
       <c r="DW17" t="n">
         <v>0.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.58</v>
+        <v>12.31</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.25</v>
+        <v>8.77</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.33</v>
+        <v>3.54</v>
       </c>
       <c r="EA17" t="n">
-        <v>18.17</v>
+        <v>19</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="18">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
         <v>0.17</v>
@@ -7900,136 +7900,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1</v>
+        <v>1.57</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AI18" t="n">
-        <v>80</v>
+        <v>83.70999999999999</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.83</v>
+        <v>2.43</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AN18" t="n">
-        <v>32.67</v>
+        <v>33.57</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8.5</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AR18" t="n">
-        <v>10.33</v>
+        <v>10</v>
       </c>
       <c r="AS18" t="n">
-        <v>10.17</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>46.5</v>
+        <v>46.43</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.33</v>
+        <v>10.29</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.67</v>
+        <v>5.86</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.67</v>
+        <v>4.43</v>
       </c>
       <c r="BD18" t="n">
-        <v>18.83</v>
+        <v>19.14</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.83</v>
+        <v>2.43</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.08</v>
+        <v>3.23</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.75</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.08</v>
+        <v>3.23</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.75</v>
+        <v>4.77</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT18" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU18" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BV18" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX18" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY18" t="n">
         <v>2.41</v>
@@ -8038,37 +8038,37 @@
         <v>2.57</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.6</v>
+        <v>4.51</v>
       </c>
       <c r="CC18" t="n">
-        <v>6.48</v>
+        <v>5.96</v>
       </c>
       <c r="CD18" t="n">
-        <v>7.85</v>
+        <v>7.16</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL18" t="n">
         <v>1.95</v>
@@ -8080,10 +8080,10 @@
         <v>1.92</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CQ18" t="n">
         <v>2.29</v>
@@ -8092,16 +8092,16 @@
         <v>1.34</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="CT18" t="n">
         <v>3.32</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="CW18" t="n">
         <v>1.53</v>
@@ -8122,85 +8122,85 @@
         <v>1.26</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="DE18" t="n">
         <v>0.08</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="DH18" t="n">
-        <v>93.92</v>
+        <v>94.84</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.58</v>
+        <v>2.85</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.25</v>
+        <v>4.16</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.84</v>
+        <v>41.61</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="DP18" t="n">
-        <v>9.42</v>
+        <v>9.69</v>
       </c>
       <c r="DQ18" t="n">
-        <v>9.83</v>
+        <v>9.69</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.33</v>
+        <v>8.31</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>49.5</v>
+        <v>49.23</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.83</v>
+        <v>12.62</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.08</v>
+        <v>8</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.75</v>
+        <v>4.61</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.16</v>
+        <v>19.31</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.42</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="19">
@@ -8210,94 +8210,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="F19" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="G19" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H19" t="n">
+        <v>96</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
         <v>2</v>
       </c>
-      <c r="H19" t="n">
-        <v>98.83</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.67</v>
-      </c>
       <c r="K19" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="R19" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>45.29</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="AB19" t="n">
         <v>5</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>55.33</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P19" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>11</v>
-      </c>
-      <c r="R19" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>45.67</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>15.17</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>5.33</v>
-      </c>
       <c r="AC19" t="n">
-        <v>17.67</v>
+        <v>17.71</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -8381,70 +8381,70 @@
         <v>2.17</v>
       </c>
       <c r="BG19" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.92</v>
+        <v>11.85</v>
       </c>
       <c r="BI19" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BM19" t="n">
         <v>0.92</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BP19" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.67</v>
+        <v>5.62</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT19" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BU19" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BV19" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW19" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX19" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BY19" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BZ19" t="n">
         <v>2.61</v>
       </c>
-      <c r="BZ19" t="n">
-        <v>2.7</v>
-      </c>
       <c r="CA19" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CC19" t="n">
         <v>3.35</v>
@@ -8453,61 +8453,61 @@
         <v>3.53</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.48</v>
+        <v>3.43</v>
       </c>
       <c r="CH19" t="n">
         <v>1.57</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CK19" t="n">
         <v>1.4</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CX19" t="n">
         <v>1.48</v>
@@ -8522,55 +8522,55 @@
         <v>2.13</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="DH19" t="n">
-        <v>88.58</v>
+        <v>87.84</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="DK19" t="n">
-        <v>4</v>
+        <v>3.69</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
       </c>
       <c r="DM19" t="n">
-        <v>44.66</v>
+        <v>42.31</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.75</v>
+        <v>0.84</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.16</v>
+        <v>11.31</v>
       </c>
       <c r="DQ19" t="n">
-        <v>10.34</v>
+        <v>10.31</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.67</v>
+        <v>9.85</v>
       </c>
       <c r="DS19" t="n">
         <v>0.08</v>
@@ -8582,28 +8582,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.58</v>
+        <v>45.39</v>
       </c>
       <c r="DW19" t="n">
         <v>0.08</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.67</v>
+        <v>12</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.5</v>
+        <v>7.92</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.16</v>
+        <v>4.08</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.34</v>
+        <v>17.38</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -3932,16 +3932,16 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>47.14</v>
+        <v>47</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.14</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.43</v>
+        <v>11.57</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.710000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BC8" t="n">
         <v>2.71</v>
@@ -3950,7 +3950,7 @@
         <v>18.71</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="BF8" t="n">
         <v>1</v>
@@ -4157,16 +4157,16 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.15</v>
+        <v>51.08</v>
       </c>
       <c r="DW8" t="n">
         <v>0.15</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.23</v>
+        <v>12.31</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.460000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ8" t="n">
         <v>3.77</v>
@@ -4175,7 +4175,7 @@
         <v>20.84</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC8" t="n">
         <v>1.23</v>
@@ -4657,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>41.71</v>
+        <v>41.86</v>
       </c>
       <c r="Y10" t="n">
         <v>0.14</v>
@@ -4963,7 +4963,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>41.23</v>
+        <v>41.31</v>
       </c>
       <c r="DW10" t="n">
         <v>0.08</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>0.29</v>
@@ -1469,139 +1469,139 @@
         <v>2.57</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AH2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>97.56999999999999</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>34.29</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BN2" t="n">
         <v>1.5</v>
       </c>
-      <c r="AI2" t="n">
-        <v>99.83</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>32.17</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>42.83</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>17.17</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1.54</v>
-      </c>
       <c r="BO2" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.08</v>
+        <v>4.21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.62</v>
+        <v>4.43</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BV2" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX2" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY2" t="n">
         <v>3.87</v>
@@ -1610,16 +1610,16 @@
         <v>4.32</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="CB2" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="CC2" t="n">
         <v>3.98</v>
       </c>
-      <c r="CC2" t="n">
-        <v>3.91</v>
-      </c>
       <c r="CD2" t="n">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="CE2" t="n">
         <v>1.3</v>
@@ -1637,142 +1637,142 @@
         <v>2.26</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CN2" t="n">
         <v>1.91</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>1.93</v>
       </c>
       <c r="CO2" t="n">
         <v>1.19</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="CR2" t="n">
         <v>1.35</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="DB2" t="n">
         <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DH2" t="n">
-        <v>101.54</v>
+        <v>100.28</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DJ2" t="n">
         <v>2.92</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.16</v>
+        <v>4.28</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DM2" t="n">
-        <v>38.54</v>
+        <v>39.14</v>
       </c>
       <c r="DN2" t="n">
         <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.08</v>
+        <v>12.86</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.46</v>
+        <v>11.64</v>
       </c>
       <c r="DR2" t="n">
-        <v>9.08</v>
+        <v>8.93</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>44.92</v>
+        <v>45.21</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.39</v>
+        <v>12.36</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.23</v>
+        <v>8.43</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.15</v>
+        <v>3.93</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.16</v>
+        <v>18.64</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F3" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="G3" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>120.29</v>
+        <v>120.75</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="K3" t="n">
-        <v>5.71</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>49.29</v>
+        <v>51.25</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="O3" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>9</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>11</v>
+        <v>10.38</v>
       </c>
       <c r="R3" t="n">
-        <v>6.14</v>
+        <v>6.25</v>
       </c>
       <c r="S3" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="T3" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>63</v>
+        <v>62.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.57</v>
+        <v>16.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.86</v>
+        <v>10.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.71</v>
+        <v>5.75</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.71</v>
+        <v>16</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AF3" t="n">
         <v>0.33</v>
@@ -1953,37 +1953,37 @@
         <v>2.83</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.15</v>
+        <v>10.21</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.62</v>
+        <v>4.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.54</v>
+        <v>5.71</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,31 +1992,31 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU3" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV3" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW3" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BX3" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
       <c r="CC3" t="n">
         <v>3.32</v>
@@ -2028,31 +2028,31 @@
         <v>1.26</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CG3" t="n">
         <v>3.56</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CI3" t="n">
         <v>2.33</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CK3" t="n">
         <v>1.5</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CO3" t="n">
         <v>1.16</v>
@@ -2061,121 +2061,121 @@
         <v>1.6</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CR3" t="n">
         <v>1.34</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CT3" t="n">
         <v>3.3</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CX3" t="n">
         <v>1.57</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.36</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="DB3" t="n">
         <v>1.27</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DG3" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="DH3" t="n">
-        <v>110.46</v>
+        <v>111.43</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.84</v>
+        <v>5.07</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="DM3" t="n">
-        <v>46.54</v>
+        <v>47.86</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="DO3" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="DP3" t="n">
-        <v>8.539999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.84</v>
+        <v>11.43</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.38</v>
+        <v>7.36</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>59.69</v>
+        <v>59.78</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.23</v>
+        <v>14.43</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.460000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.77</v>
+        <v>4.86</v>
       </c>
       <c r="EA3" t="n">
-        <v>15.69</v>
+        <v>15.86</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F4" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="G4" t="n">
-        <v>3.14</v>
+        <v>3.38</v>
       </c>
       <c r="H4" t="n">
-        <v>130.29</v>
+        <v>137.88</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="K4" t="n">
-        <v>6.29</v>
+        <v>6.38</v>
       </c>
       <c r="L4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M4" t="n">
-        <v>66.86</v>
+        <v>69</v>
       </c>
       <c r="N4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O4" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>10</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.140000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>5.71</v>
+        <v>5.5</v>
       </c>
       <c r="S4" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="T4" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="U4" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="V4" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>66.43000000000001</v>
+        <v>68.75</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>20.14</v>
+        <v>20.62</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.86</v>
+        <v>12</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.289999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>19.86</v>
+        <v>21</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
         <v>0.17</v>
@@ -2356,34 +2356,34 @@
         <v>3.17</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.85</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.85</v>
+        <v>4.64</v>
       </c>
       <c r="BQ4" t="n">
         <v>5</v>
@@ -2398,28 +2398,28 @@
         <v>100</v>
       </c>
       <c r="BU4" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BV4" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BW4" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX4" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>1.18</v>
       </c>
-      <c r="BZ4" t="n">
-        <v>1.2</v>
-      </c>
       <c r="CA4" t="n">
-        <v>7.32</v>
+        <v>7.59</v>
       </c>
       <c r="CB4" t="n">
-        <v>8.09</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="CC4" t="n">
         <v>1.35</v>
@@ -2434,25 +2434,25 @@
         <v>1.8</v>
       </c>
       <c r="CG4" t="n">
-        <v>4.91</v>
+        <v>4.9</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL4" t="n">
         <v>1.91</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CN4" t="n">
         <v>1.87</v>
@@ -2464,21 +2464,21 @@
         <v>1.29</v>
       </c>
       <c r="CQ4" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="CR4" t="inlineStr"/>
       <c r="CS4" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CX4" t="n">
         <v>1.52</v>
@@ -2487,92 +2487,92 @@
         <v>1.86</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DB4" t="inlineStr"/>
       <c r="DC4" t="n">
         <v>1.36</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="DH4" t="n">
-        <v>130.54</v>
+        <v>134.86</v>
       </c>
       <c r="DI4" t="n">
         <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.69</v>
+        <v>5.79</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM4" t="n">
-        <v>68.16</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.92</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.460000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.38</v>
+        <v>5.29</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>66.23</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>19.15</v>
+        <v>19.5</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.92</v>
+        <v>11.07</v>
       </c>
       <c r="DZ4" t="n">
-        <v>8.23</v>
+        <v>8.43</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.08</v>
+        <v>20.71</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="5">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2675,49 +2675,49 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="AI5" t="n">
-        <v>103.86</v>
+        <v>102.5</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.71</v>
+        <v>3.25</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AN5" t="n">
-        <v>53</v>
+        <v>50.75</v>
       </c>
       <c r="AO5" t="n">
         <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.14</v>
+        <v>11.75</v>
       </c>
       <c r="AR5" t="n">
-        <v>10.86</v>
+        <v>10.88</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.29</v>
+        <v>6.5</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2729,82 +2729,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>51.29</v>
+        <v>50.25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.29</v>
+        <v>10.12</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.57</v>
+        <v>6.38</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.71</v>
+        <v>20.38</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.46</v>
+        <v>10.14</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.92</v>
+        <v>6.64</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU5" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV5" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW5" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX5" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>1.58</v>
@@ -2813,169 +2813,169 @@
         <v>1.59</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.29</v>
+        <v>4.23</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.43</v>
+        <v>4.37</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.65</v>
+        <v>2.59</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.83</v>
+        <v>2.73</v>
       </c>
       <c r="CE5" t="n">
         <v>1.24</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.78</v>
+        <v>3.71</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="CR5" t="n">
         <v>1.34</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="CW5" t="n">
         <v>1.58</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="DB5" t="n">
         <v>1.26</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="DE5" t="n">
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.85</v>
+        <v>3.57</v>
       </c>
       <c r="DH5" t="n">
-        <v>108.92</v>
+        <v>107.78</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.54</v>
+        <v>5.14</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="DM5" t="n">
-        <v>56.38</v>
+        <v>54.86</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.61</v>
+        <v>11.43</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.15</v>
+        <v>10.22</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.85</v>
+        <v>6.93</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>53</v>
+        <v>52.29</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.23</v>
+        <v>12</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.77</v>
+        <v>7.58</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.46</v>
+        <v>4.43</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.07</v>
+        <v>19.5</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="6">
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
@@ -2997,82 +2997,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="G6" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="H6" t="n">
-        <v>88.29000000000001</v>
+        <v>90.38</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="K6" t="n">
-        <v>4.57</v>
+        <v>4.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>37.71</v>
+        <v>41.25</v>
       </c>
       <c r="N6" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O6" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>10.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.859999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="R6" t="n">
-        <v>8.43</v>
+        <v>7.62</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>43.29</v>
+        <v>45.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.43</v>
+        <v>10.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>7</v>
+        <v>7.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>16.14</v>
+        <v>18.38</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3156,70 +3156,70 @@
         <v>1.67</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.46</v>
+        <v>10.36</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.77</v>
+        <v>2.86</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BM6" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.62</v>
+        <v>4.57</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.85</v>
+        <v>5.79</v>
       </c>
       <c r="BR6" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU6" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BV6" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX6" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.63</v>
+        <v>3.42</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.07</v>
+        <v>4.05</v>
       </c>
       <c r="CC6" t="n">
         <v>3.59</v>
@@ -3231,16 +3231,16 @@
         <v>1.25</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="CH6" t="n">
         <v>1.63</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.54</v>
@@ -3249,10 +3249,10 @@
         <v>1.41</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CN6" t="n">
         <v>2.1</v>
@@ -3264,19 +3264,19 @@
         <v>1.6</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CR6" t="n">
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CT6" t="n">
         <v>3.23</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CV6" t="n">
         <v>2.56</v>
@@ -3288,13 +3288,13 @@
         <v>1.52</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.48</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DB6" t="n">
         <v>1.3</v>
@@ -3309,76 +3309,76 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="DH6" t="n">
-        <v>87.69</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.61</v>
+        <v>38.71</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.08</v>
+        <v>10.72</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.39</v>
+        <v>10.22</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.46</v>
+        <v>7.07</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.62</v>
+        <v>46.5</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.85</v>
+        <v>12</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.31</v>
+        <v>7.5</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.54</v>
+        <v>4.5</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.62</v>
+        <v>17.86</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="7">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
@@ -3400,82 +3400,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="H7" t="n">
-        <v>97.83</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="K7" t="n">
-        <v>5.83</v>
+        <v>5.29</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>52</v>
+        <v>51.43</v>
       </c>
       <c r="N7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="O7" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="P7" t="n">
-        <v>9.33</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.67</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>6.67</v>
+        <v>7.14</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="U7" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V7" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>55.33</v>
+        <v>54.71</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.67</v>
+        <v>13.29</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.83</v>
+        <v>8.57</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.83</v>
+        <v>4.71</v>
       </c>
       <c r="AC7" t="n">
-        <v>21.83</v>
+        <v>21.14</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3559,70 +3559,70 @@
         <v>2.14</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.38</v>
+        <v>4.14</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.85</v>
+        <v>7.86</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.38</v>
+        <v>4.14</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="BO7" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.77</v>
+        <v>3.93</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>92.31</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU7" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BV7" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BW7" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BX7" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.37</v>
+        <v>2.26</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.02</v>
+        <v>4.04</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="CC7" t="n">
         <v>2.66</v>
@@ -3634,31 +3634,31 @@
         <v>1.24</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CO7" t="n">
         <v>1.14</v>
@@ -3669,113 +3669,119 @@
       <c r="CQ7" t="n">
         <v>2.32</v>
       </c>
-      <c r="CR7" t="inlineStr"/>
+      <c r="CR7" t="n">
+        <v>1.34</v>
+      </c>
       <c r="CS7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CT7" t="inlineStr"/>
+        <v>2.2</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>3.36</v>
+      </c>
       <c r="CU7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CX7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>2</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DC7" t="n">
         <v>1.57</v>
       </c>
-      <c r="CY7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CZ7" t="n">
+      <c r="DD7" t="n">
         <v>2.38</v>
       </c>
-      <c r="DA7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="DB7" t="inlineStr"/>
-      <c r="DC7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="DD7" t="n">
-        <v>2.32</v>
-      </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="DH7" t="n">
-        <v>102.92</v>
+        <v>103.36</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.08</v>
+        <v>4.86</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="DM7" t="n">
-        <v>50.69</v>
+        <v>50.5</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.07</v>
+        <v>10.36</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.539999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.39</v>
+        <v>7.57</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>55.23</v>
+        <v>54.92</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.93</v>
+        <v>12.79</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.380000000000001</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.54</v>
+        <v>4.5</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.23</v>
+        <v>20.93</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="8">
@@ -3785,94 +3791,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
       </c>
       <c r="E8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="G8" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="H8" t="n">
-        <v>108</v>
+        <v>109.71</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>48.83</v>
+        <v>50.86</v>
       </c>
       <c r="N8" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="O8" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.83</v>
+        <v>13.14</v>
       </c>
       <c r="R8" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T8" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="V8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>55.83</v>
+        <v>56</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.17</v>
+        <v>14.29</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.17</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="AC8" t="n">
-        <v>23.33</v>
+        <v>22.14</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -3956,70 +3962,70 @@
         <v>1</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.31</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.38</v>
+        <v>4.29</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="BR8" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU8" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BV8" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX8" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="CC8" t="n">
         <v>4.25</v>
@@ -4031,19 +4037,19 @@
         <v>1.32</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.32</v>
+        <v>3.28</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK8" t="n">
         <v>1.64</v>
@@ -4052,10 +4058,10 @@
         <v>2.1</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO8" t="n">
         <v>1.23</v>
@@ -4064,16 +4070,16 @@
         <v>1.81</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CU8" t="n">
         <v>1.5</v>
@@ -4082,7 +4088,7 @@
         <v>2.2</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX8" t="n">
         <v>1.7</v>
@@ -4103,82 +4109,82 @@
         <v>1.85</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DH8" t="n">
-        <v>96.69</v>
+        <v>98.34999999999999</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.69</v>
+        <v>4.78</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DM8" t="n">
-        <v>45.77</v>
+        <v>47</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="DO8" t="n">
         <v>2.93</v>
       </c>
       <c r="DP8" t="n">
-        <v>8.84</v>
+        <v>9</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.15</v>
+        <v>12.86</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.08</v>
+        <v>6</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.08</v>
+        <v>51.5</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.31</v>
+        <v>12.93</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.539999999999999</v>
+        <v>9</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.77</v>
+        <v>3.92</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.84</v>
+        <v>20.43</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="9">
@@ -4188,13 +4194,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>0.29</v>
@@ -4281,49 +4287,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AI9" t="n">
-        <v>86</v>
+        <v>83.70999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN9" t="n">
-        <v>32.33</v>
+        <v>30.86</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>12.17</v>
+        <v>12.57</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>7.57</v>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4335,82 +4341,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>48.5</v>
+        <v>47.43</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BA9" t="n">
-        <v>12.17</v>
+        <v>12.43</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.17</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="BD9" t="n">
-        <v>18.17</v>
+        <v>18.14</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.619999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.62</v>
+        <v>2.79</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BO9" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.23</v>
+        <v>4.07</v>
       </c>
       <c r="BR9" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU9" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV9" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>2.69</v>
@@ -4419,46 +4425,46 @@
         <v>2.73</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.92</v>
+        <v>4.86</v>
       </c>
       <c r="CC9" t="n">
-        <v>7.12</v>
+        <v>6.67</v>
       </c>
       <c r="CD9" t="n">
-        <v>7.58</v>
+        <v>7.17</v>
       </c>
       <c r="CE9" t="n">
         <v>1.28</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.6</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CO9" t="n">
         <v>1.16</v>
@@ -4467,13 +4473,13 @@
         <v>1.61</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CT9" t="n">
         <v>3.14</v>
@@ -4482,7 +4488,7 @@
         <v>1.66</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CW9" t="n">
         <v>1.62</v>
@@ -4491,13 +4497,13 @@
         <v>1.51</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.49</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="DB9" t="n">
         <v>1.32</v>
@@ -4506,49 +4512,49 @@
         <v>1.69</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DH9" t="n">
-        <v>86.77</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.77</v>
+        <v>3.71</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DM9" t="n">
-        <v>37.31</v>
+        <v>36.21</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="DP9" t="n">
-        <v>13</v>
+        <v>12.78</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.69</v>
+        <v>12.86</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.380000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4560,28 +4566,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47.46</v>
+        <v>47</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.23</v>
+        <v>13.28</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.539999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.69</v>
+        <v>4.71</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.54</v>
+        <v>18.5</v>
       </c>
       <c r="EB9" t="n">
         <v>1.43</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="10">
@@ -4591,13 +4597,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4684,49 +4690,49 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.67</v>
+        <v>3.71</v>
       </c>
       <c r="AI10" t="n">
-        <v>79</v>
+        <v>84.14</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.5</v>
+        <v>5.43</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AN10" t="n">
-        <v>32.5</v>
+        <v>38.43</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.83</v>
+        <v>11.43</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.83</v>
+        <v>10.14</v>
       </c>
       <c r="AS10" t="n">
-        <v>10.17</v>
+        <v>9.43</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4738,82 +4744,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>40.67</v>
+        <v>44</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.83</v>
+        <v>10.43</v>
       </c>
       <c r="BB10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.83</v>
+        <v>3.43</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.33</v>
+        <v>18.14</v>
       </c>
       <c r="BE10" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.539999999999999</v>
+        <v>9.93</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.23</v>
+        <v>4.14</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.31</v>
+        <v>5.79</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT10" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV10" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX10" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY10" t="n">
         <v>3.46</v>
@@ -4822,73 +4828,73 @@
         <v>3.78</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.18</v>
+        <v>4.13</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.66</v>
+        <v>5.46</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.21</v>
+        <v>5.97</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CK10" t="n">
         <v>1.54</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CN10" t="n">
         <v>1.87</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="CX10" t="n">
         <v>1.6</v>
@@ -4903,55 +4909,55 @@
         <v>1.88</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.62</v>
+        <v>3.14</v>
       </c>
       <c r="DH10" t="n">
-        <v>83.15000000000001</v>
+        <v>85.42</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.84</v>
+        <v>5.28</v>
       </c>
       <c r="DL10" t="n">
         <v>0.85</v>
       </c>
       <c r="DM10" t="n">
-        <v>35.08</v>
+        <v>37.86</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.61</v>
+        <v>10.93</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.54</v>
+        <v>11.14</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.16</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4963,28 +4969,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>41.31</v>
+        <v>42.93</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.77</v>
+        <v>11.43</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.31</v>
+        <v>7.71</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.46</v>
+        <v>3.72</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.61</v>
+        <v>16.64</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="11">
@@ -4994,61 +5000,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="F11" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="H11" t="n">
-        <v>111.17</v>
+        <v>113.43</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="J11" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="K11" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="M11" t="n">
-        <v>53.83</v>
+        <v>53.43</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="P11" t="n">
-        <v>15</v>
+        <v>15.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.67</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>6.17</v>
+        <v>6</v>
       </c>
       <c r="S11" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="T11" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5060,28 +5066,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>54.33</v>
+        <v>55</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.67</v>
+        <v>14</v>
       </c>
       <c r="AA11" t="n">
-        <v>10.17</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.67</v>
+        <v>22.71</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AF11" t="n">
         <v>0.14</v>
@@ -5165,70 +5171,70 @@
         <v>2.14</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>11.15</v>
+        <v>10.79</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="BM11" t="n">
         <v>1</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.69</v>
+        <v>4.64</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.46</v>
+        <v>6.14</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT11" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU11" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BV11" t="n">
-        <v>23.08</v>
+        <v>28.57</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX11" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY11" t="n">
-        <v>3.07</v>
+        <v>2.88</v>
       </c>
       <c r="BZ11" t="n">
-        <v>3.08</v>
+        <v>2.89</v>
       </c>
       <c r="CA11" t="n">
         <v>3.99</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.01</v>
+        <v>4.02</v>
       </c>
       <c r="CC11" t="n">
         <v>3.15</v>
@@ -5243,22 +5249,22 @@
         <v>2.19</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CH11" t="n">
         <v>1.68</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.52</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CM11" t="n">
         <v>2.71</v>
@@ -5279,31 +5285,31 @@
         <v>1.35</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CT11" t="n">
         <v>3.32</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CX11" t="n">
         <v>1.5</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.52</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DB11" t="n">
         <v>1.26</v>
@@ -5315,79 +5321,79 @@
         <v>2.49</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="DH11" t="n">
-        <v>108.15</v>
+        <v>109.5</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.46</v>
+        <v>5.29</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="DM11" t="n">
-        <v>49.61</v>
+        <v>49.72</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.62</v>
+        <v>14.72</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.31</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.08</v>
+        <v>6</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.54</v>
+        <v>53.93</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.54</v>
+        <v>13.28</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.85</v>
+        <v>8.5</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.69</v>
+        <v>4.79</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.08</v>
+        <v>21.64</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="EC11" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="12">
@@ -5397,13 +5403,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0.33</v>
@@ -5487,139 +5493,139 @@
         <v>1.17</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AI12" t="n">
-        <v>91.29000000000001</v>
+        <v>88</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="AM12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>46.12</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BK12" t="n">
         <v>0.43</v>
       </c>
-      <c r="AN12" t="n">
-        <v>40.29</v>
-      </c>
-      <c r="AO12" t="n">
+      <c r="BL12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BM12" t="n">
         <v>0.86</v>
       </c>
-      <c r="AP12" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>11.14</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AU12" t="n">
+      <c r="BN12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BO12" t="n">
         <v>1.14</v>
       </c>
-      <c r="AV12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>47.14</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>11.86</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>19.71</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>1.23</v>
-      </c>
       <c r="BP12" t="n">
-        <v>4.38</v>
+        <v>4.29</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.92</v>
+        <v>5.14</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BV12" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BW12" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX12" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY12" t="n">
         <v>2.31</v>
@@ -5628,28 +5634,28 @@
         <v>2.45</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.76</v>
+        <v>3.81</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.84</v>
+        <v>3.88</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.29</v>
+        <v>4.26</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CI12" t="n">
         <v>2.36</v>
@@ -5664,7 +5670,7 @@
         <v>1.66</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CN12" t="n">
         <v>2.14</v>
@@ -5673,16 +5679,16 @@
         <v>1.17</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CT12" t="n">
         <v>3.22</v>
@@ -5691,10 +5697,10 @@
         <v>1.62</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CX12" t="n">
         <v>1.58</v>
@@ -5712,85 +5718,85 @@
         <v>1.27</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="DH12" t="n">
-        <v>93.62</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.08</v>
+        <v>-0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="DK12" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM12" t="n">
-        <v>40.16</v>
+        <v>39</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DP12" t="n">
-        <v>9.15</v>
+        <v>8.93</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.15</v>
+        <v>10.93</v>
       </c>
       <c r="DR12" t="n">
-        <v>9</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.77</v>
+        <v>47.14</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.08</v>
+        <v>12.5</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.390000000000001</v>
+        <v>7.86</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.69</v>
+        <v>4.64</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.77</v>
+        <v>19.07</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="13">
@@ -5800,13 +5806,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5893,136 +5899,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.67</v>
+        <v>3.14</v>
       </c>
       <c r="AI13" t="n">
-        <v>95.33</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="AL13" t="n">
-        <v>5</v>
+        <v>4.29</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN13" t="n">
-        <v>53.83</v>
+        <v>48.57</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.5</v>
+        <v>11.86</v>
       </c>
       <c r="AR13" t="n">
-        <v>11.33</v>
+        <v>10.71</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.17</v>
+        <v>7.29</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AU13" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>45.67</v>
+        <v>41.29</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.5</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.17</v>
+        <v>6.57</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="BD13" t="n">
-        <v>23.5</v>
+        <v>21.57</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.23</v>
+        <v>9.07</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.69</v>
+        <v>2.79</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.85</v>
+        <v>5.79</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT13" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BU13" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BV13" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX13" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>2.46</v>
@@ -6031,34 +6037,34 @@
         <v>2.55</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.61</v>
+        <v>4.14</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.7</v>
+        <v>4.29</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.32</v>
+        <v>5.7</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.46</v>
+        <v>5.96</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CK13" t="n">
         <v>1.45</v>
@@ -6070,46 +6076,46 @@
         <v>2.55</v>
       </c>
       <c r="CN13" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="CR13" t="n">
         <v>1.34</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="CT13" t="n">
         <v>3.32</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CY13" t="n">
         <v>1.84</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DB13" t="n">
         <v>1.26</v>
@@ -6118,7 +6124,7 @@
         <v>1.69</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
@@ -6127,73 +6133,73 @@
         <v>2.08</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.69</v>
+        <v>3.42</v>
       </c>
       <c r="DH13" t="n">
-        <v>110.23</v>
+        <v>107.15</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.15</v>
+        <v>3.07</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.16</v>
+        <v>4.79</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM13" t="n">
-        <v>56.15</v>
+        <v>53.36</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="DP13" t="n">
-        <v>13</v>
+        <v>12.64</v>
       </c>
       <c r="DQ13" t="n">
-        <v>10.85</v>
+        <v>10.57</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.23</v>
+        <v>7.29</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.62</v>
+        <v>45.29</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.08</v>
+        <v>10.64</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.460000000000001</v>
+        <v>8.07</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="EA13" t="n">
-        <v>23.07</v>
+        <v>22.14</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="14">
@@ -6203,13 +6209,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>6</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0.17</v>
@@ -6293,52 +6299,52 @@
         <v>1.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>4.14</v>
+        <v>3.75</v>
       </c>
       <c r="AI14" t="n">
-        <v>91</v>
+        <v>86.88</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AL14" t="n">
         <v>6</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AN14" t="n">
-        <v>44</v>
+        <v>42.75</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10.14</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.71</v>
+        <v>10.25</v>
       </c>
       <c r="AS14" t="n">
-        <v>10.14</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6350,82 +6356,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>48.43</v>
+        <v>50.25</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>16.57</v>
+        <v>15.62</v>
       </c>
       <c r="BB14" t="n">
-        <v>12.29</v>
+        <v>11.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.29</v>
+        <v>4.12</v>
       </c>
       <c r="BD14" t="n">
-        <v>14.43</v>
+        <v>13.88</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.62</v>
+        <v>10.57</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="BJ14" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.69</v>
+        <v>5.57</v>
       </c>
       <c r="BR14" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS14" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU14" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BV14" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW14" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BX14" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BY14" t="n">
         <v>1.63</v>
@@ -6434,163 +6440,169 @@
         <v>1.73</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.3</v>
+        <v>4.23</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.43</v>
+        <v>4.36</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.84</v>
+        <v>3.6</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.84</v>
+        <v>3.66</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.15</v>
+        <v>4.07</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="CR14" t="inlineStr"/>
+        <v>2.18</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>1.38</v>
+      </c>
       <c r="CS14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="CT14" t="inlineStr"/>
+        <v>2.12</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>3.13</v>
+      </c>
       <c r="CU14" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="CW14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CX14" t="n">
         <v>1.46</v>
       </c>
-      <c r="CX14" t="n">
-        <v>1.44</v>
-      </c>
       <c r="CY14" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="DA14" t="n">
         <v>2.17</v>
       </c>
-      <c r="DB14" t="inlineStr"/>
+      <c r="DB14" t="n">
+        <v>1.32</v>
+      </c>
       <c r="DC14" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="DH14" t="n">
-        <v>94.23</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="DK14" t="n">
-        <v>6.15</v>
+        <v>6.14</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="DM14" t="n">
-        <v>42.77</v>
+        <v>42.14</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="DO14" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.460000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.84</v>
+        <v>10.57</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.539999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.62</v>
+        <v>50.57</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>16.69</v>
+        <v>16.14</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.85</v>
+        <v>5.64</v>
       </c>
       <c r="EA14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="15">
@@ -6600,10 +6612,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -6612,79 +6624,79 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="G15" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="H15" t="n">
-        <v>112</v>
+        <v>109.43</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="K15" t="n">
-        <v>7.67</v>
+        <v>7.14</v>
       </c>
       <c r="L15" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M15" t="n">
-        <v>56.17</v>
+        <v>52.71</v>
       </c>
       <c r="N15" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="P15" t="n">
-        <v>11.17</v>
+        <v>10.43</v>
       </c>
       <c r="Q15" t="n">
-        <v>11</v>
+        <v>11.57</v>
       </c>
       <c r="R15" t="n">
-        <v>6</v>
+        <v>6.29</v>
       </c>
       <c r="S15" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="U15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>53.5</v>
+        <v>51</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.5</v>
+        <v>11.86</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.67</v>
+        <v>7</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.83</v>
+        <v>4.86</v>
       </c>
       <c r="AC15" t="n">
-        <v>23.83</v>
+        <v>22.43</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AE15" t="n">
         <v>2</v>
@@ -6771,70 +6783,70 @@
         <v>1.57</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.23</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP15" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.23</v>
+        <v>5.71</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU15" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV15" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX15" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.86</v>
+        <v>2.72</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.91</v>
+        <v>2.77</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.08</v>
+        <v>4.03</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.13</v>
+        <v>4.09</v>
       </c>
       <c r="CC15" t="n">
         <v>6.72</v>
@@ -6843,61 +6855,61 @@
         <v>6.74</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CR15" t="n">
         <v>1.39</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CX15" t="n">
         <v>1.63</v>
@@ -6912,88 +6924,88 @@
         <v>1.79</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.87</v>
+        <v>2.91</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="DH15" t="n">
-        <v>102.31</v>
+        <v>101.72</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.16</v>
+        <v>5.07</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM15" t="n">
-        <v>48.23</v>
+        <v>47.07</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.92</v>
+        <v>10.57</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10</v>
+        <v>10.36</v>
       </c>
       <c r="DR15" t="n">
-        <v>5.77</v>
+        <v>5.93</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>48.38</v>
+        <v>47.5</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX15" t="n">
-        <v>11.15</v>
+        <v>10.93</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.69</v>
+        <v>7.36</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.84</v>
+        <v>21.28</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="16">
@@ -7003,13 +7015,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7096,136 +7108,136 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BO16" t="n">
         <v>1.43</v>
       </c>
-      <c r="AH16" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>134.71</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>76</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>11.14</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>12.57</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>60.43</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>14.57</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>10.31</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>1.38</v>
-      </c>
       <c r="BP16" t="n">
-        <v>4.54</v>
+        <v>4.14</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.77</v>
+        <v>5.29</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BU16" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BV16" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX16" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY16" t="n">
         <v>2.24</v>
@@ -7234,28 +7246,28 @@
         <v>2.23</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.71</v>
+        <v>2.66</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="CE16" t="n">
         <v>1.25</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CI16" t="n">
         <v>2.46</v>
@@ -7267,13 +7279,13 @@
         <v>1.46</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="CO16" t="n">
         <v>1.14</v>
@@ -7282,7 +7294,7 @@
         <v>1.55</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CR16" t="n">
         <v>1.33</v>
@@ -7294,10 +7306,10 @@
         <v>3.35</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CW16" t="n">
         <v>1.54</v>
@@ -7325,76 +7337,76 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.93</v>
+        <v>2.64</v>
       </c>
       <c r="DH16" t="n">
-        <v>122</v>
+        <v>122.22</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.54</v>
+        <v>5.78</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="DM16" t="n">
-        <v>60.08</v>
+        <v>60.64</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.54</v>
+        <v>10.21</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.23</v>
+        <v>12.14</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.69</v>
+        <v>5.57</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>58</v>
+        <v>58.43</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.31</v>
+        <v>15.93</v>
       </c>
       <c r="DY16" t="n">
-        <v>10.16</v>
+        <v>10.28</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.15</v>
+        <v>5.64</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.08</v>
+        <v>17.93</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="EC16" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="17">
@@ -7404,61 +7416,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F17" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="G17" t="n">
         <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>90.70999999999999</v>
+        <v>86</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.43</v>
+        <v>3.25</v>
       </c>
       <c r="K17" t="n">
-        <v>5.86</v>
+        <v>5.62</v>
       </c>
       <c r="L17" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="M17" t="n">
-        <v>41.29</v>
+        <v>40.12</v>
       </c>
       <c r="N17" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="O17" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>16.29</v>
+        <v>15.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.43</v>
+        <v>11.88</v>
       </c>
       <c r="R17" t="n">
-        <v>6.71</v>
+        <v>6.88</v>
       </c>
       <c r="S17" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T17" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7470,28 +7482,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>34.86</v>
+        <v>35.12</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.43</v>
+        <v>12.38</v>
       </c>
       <c r="AA17" t="n">
-        <v>9</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.14</v>
+        <v>20.12</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AF17" t="n">
         <v>0.17</v>
@@ -7575,70 +7587,70 @@
         <v>1.17</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.31</v>
+        <v>10.29</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="BR17" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU17" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BV17" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW17" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX17" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.22</v>
+        <v>3.18</v>
       </c>
       <c r="BZ17" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="CC17" t="n">
         <v>4.56</v>
@@ -7650,10 +7662,10 @@
         <v>1.33</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CH17" t="n">
         <v>1.5</v>
@@ -7668,7 +7680,7 @@
         <v>1.49</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM17" t="n">
         <v>2.48</v>
@@ -7680,22 +7692,22 @@
         <v>1.24</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="CR17" t="n">
         <v>1.4</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CT17" t="n">
         <v>3.08</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV17" t="n">
         <v>2.11</v>
@@ -7704,67 +7716,67 @@
         <v>1.81</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DB17" t="n">
         <v>1.33</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.98</v>
+        <v>3.03</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="DH17" t="n">
-        <v>90.15000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.46</v>
+        <v>5.35</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="DM17" t="n">
-        <v>40.23</v>
+        <v>39.64</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.54</v>
+        <v>13.07</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.54</v>
+        <v>11.29</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.77</v>
+        <v>7.79</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7776,28 +7788,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>35.93</v>
+        <v>36</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.31</v>
+        <v>12.29</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.77</v>
+        <v>8.57</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.54</v>
+        <v>3.72</v>
       </c>
       <c r="EA17" t="n">
-        <v>19</v>
+        <v>19.57</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="18">
@@ -7807,94 +7819,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
         <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F18" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>107.83</v>
+        <v>104.29</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="K18" t="n">
-        <v>5.17</v>
+        <v>4.57</v>
       </c>
       <c r="L18" t="n">
-        <v>0.83</v>
+        <v>0.57</v>
       </c>
       <c r="M18" t="n">
-        <v>51</v>
+        <v>47.43</v>
       </c>
       <c r="N18" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="O18" t="n">
-        <v>2.67</v>
+        <v>2.14</v>
       </c>
       <c r="P18" t="n">
-        <v>10.33</v>
+        <v>10.43</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.33</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>6.5</v>
+        <v>6.86</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="T18" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="U18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>52.5</v>
+        <v>50.14</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="Z18" t="n">
-        <v>15.33</v>
+        <v>14.43</v>
       </c>
       <c r="AA18" t="n">
-        <v>10.5</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.83</v>
+        <v>4.57</v>
       </c>
       <c r="AC18" t="n">
-        <v>19.5</v>
+        <v>19.43</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AE18" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7978,70 +7990,70 @@
         <v>2.43</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.23</v>
+        <v>3.29</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="BN18" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.77</v>
+        <v>4.36</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.85</v>
+        <v>4.43</v>
       </c>
       <c r="BR18" t="n">
         <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU18" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BV18" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX18" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.5</v>
+        <v>4.43</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.51</v>
+        <v>4.46</v>
       </c>
       <c r="CC18" t="n">
         <v>5.96</v>
@@ -8053,13 +8065,13 @@
         <v>1.26</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CI18" t="n">
         <v>2.41</v>
@@ -8074,7 +8086,7 @@
         <v>1.95</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CN18" t="n">
         <v>1.92</v>
@@ -8086,7 +8098,7 @@
         <v>1.53</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CR18" t="n">
         <v>1.34</v>
@@ -8098,7 +8110,7 @@
         <v>3.32</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CV18" t="n">
         <v>2.64</v>
@@ -8128,79 +8140,79 @@
         <v>2.35</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF18" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="DH18" t="n">
-        <v>94.84</v>
+        <v>94</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.16</v>
+        <v>3.93</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.61</v>
+        <v>40.5</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="DP18" t="n">
-        <v>9.69</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DQ18" t="n">
-        <v>9.69</v>
+        <v>9.43</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.31</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>49.23</v>
+        <v>48.28</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.62</v>
+        <v>12.36</v>
       </c>
       <c r="DY18" t="n">
-        <v>8</v>
+        <v>7.86</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.61</v>
+        <v>4.5</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.31</v>
+        <v>19.28</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="19">
@@ -8210,13 +8222,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
         <v>0.29</v>
@@ -8300,22 +8312,22 @@
         <v>1.86</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AI19" t="n">
-        <v>78.33</v>
+        <v>81</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AL19" t="n">
         <v>3</v>
@@ -8324,115 +8336,115 @@
         <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>34</v>
+        <v>32.86</v>
       </c>
       <c r="AO19" t="n">
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.5</v>
+        <v>10.14</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AS19" t="n">
-        <v>11.17</v>
+        <v>10.57</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>45.5</v>
+        <v>45</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.17</v>
+        <v>10.29</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.17</v>
+        <v>6.86</v>
       </c>
       <c r="BC19" t="n">
-        <v>3</v>
+        <v>3.43</v>
       </c>
       <c r="BD19" t="n">
-        <v>17</v>
+        <v>16.43</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.85</v>
+        <v>11.64</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="BP19" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.62</v>
+        <v>5.57</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU19" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BV19" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX19" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY19" t="n">
         <v>2.55</v>
@@ -8441,61 +8453,61 @@
         <v>2.61</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="CB19" t="n">
         <v>3.77</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="CD19" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="CE19" t="n">
         <v>1.28</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="CH19" t="n">
         <v>1.57</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.55</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CO19" t="n">
         <v>1.18</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CR19" t="n">
         <v>1.35</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CT19" t="n">
         <v>3.26</v>
@@ -8525,85 +8537,85 @@
         <v>1.28</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DH19" t="n">
-        <v>87.84</v>
+        <v>88.5</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
       </c>
       <c r="DM19" t="n">
-        <v>42.31</v>
+        <v>41.14</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.31</v>
+        <v>11.07</v>
       </c>
       <c r="DQ19" t="n">
-        <v>10.31</v>
+        <v>10</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.85</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.39</v>
+        <v>45.14</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX19" t="n">
-        <v>12</v>
+        <v>11.93</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.92</v>
+        <v>7.72</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.08</v>
+        <v>4.22</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.38</v>
+        <v>17.07</v>
       </c>
       <c r="EB19" t="n">
         <v>1.35</v>
       </c>
       <c r="EC19" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -2705,7 +2705,7 @@
         <v>1.12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.75</v>
+        <v>11.88</v>
       </c>
       <c r="AR5" t="n">
         <v>10.88</v>
@@ -2936,7 +2936,7 @@
         <v>1.57</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.43</v>
+        <v>11.5</v>
       </c>
       <c r="DQ5" t="n">
         <v>10.22</v>
@@ -3836,7 +3836,7 @@
         <v>9.289999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.14</v>
+        <v>13.29</v>
       </c>
       <c r="R8" t="n">
         <v>3.43</v>
@@ -4148,7 +4148,7 @@
         <v>9</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.86</v>
+        <v>12.93</v>
       </c>
       <c r="DR8" t="n">
         <v>6</v>
@@ -7162,7 +7162,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>60.88</v>
+        <v>60.62</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>58.43</v>
+        <v>58.28</v>
       </c>
       <c r="DW16" t="n">
         <v>0.07000000000000001</v>
@@ -7885,25 +7885,25 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>50.14</v>
+        <v>50.43</v>
       </c>
       <c r="Y18" t="n">
         <v>0.43</v>
       </c>
       <c r="Z18" t="n">
-        <v>14.43</v>
+        <v>14.71</v>
       </c>
       <c r="AA18" t="n">
-        <v>9.859999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.57</v>
+        <v>4.71</v>
       </c>
       <c r="AC18" t="n">
         <v>19.43</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AE18" t="n">
         <v>2.71</v>
@@ -8191,25 +8191,25 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.28</v>
+        <v>48.43</v>
       </c>
       <c r="DW18" t="n">
         <v>0.22</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.36</v>
+        <v>12.5</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.86</v>
+        <v>7.93</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="EA18" t="n">
         <v>19.28</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="EC18" t="n">
         <v>2.57</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H2" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M2" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P2" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="R2" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="AD2" t="n">
         <v>1.43</v>
       </c>
-      <c r="G2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="H2" t="n">
-        <v>103</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="M2" t="n">
-        <v>44</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="P2" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>10</v>
-      </c>
-      <c r="R2" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>46.71</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12.57</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>20.86</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AE2" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AF2" t="n">
         <v>0.14</v>
@@ -1550,70 +1550,70 @@
         <v>3.14</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.640000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.21</v>
+        <v>4.73</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.43</v>
+        <v>4.47</v>
       </c>
       <c r="BR2" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS2" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT2" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU2" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV2" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX2" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.87</v>
+        <v>3.66</v>
       </c>
       <c r="BZ2" t="n">
-        <v>4.32</v>
+        <v>4.06</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="CC2" t="n">
         <v>3.98</v>
@@ -1622,13 +1622,13 @@
         <v>4.05</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CH2" t="n">
         <v>1.55</v>
@@ -1646,7 +1646,7 @@
         <v>1.93</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CN2" t="n">
         <v>1.91</v>
@@ -1655,7 +1655,7 @@
         <v>1.19</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CQ2" t="n">
         <v>2.7</v>
@@ -1673,19 +1673,19 @@
         <v>1.58</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CW2" t="n">
         <v>1.65</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY2" t="n">
         <v>1.87</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DA2" t="n">
         <v>1.96</v>
@@ -1694,52 +1694,52 @@
         <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF2" t="n">
         <v>1.93</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="DH2" t="n">
-        <v>100.28</v>
+        <v>100.33</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.28</v>
+        <v>4.4</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="DM2" t="n">
-        <v>39.14</v>
+        <v>39.8</v>
       </c>
       <c r="DN2" t="n">
         <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.86</v>
+        <v>12.66</v>
       </c>
       <c r="DQ2" t="n">
-        <v>11.64</v>
+        <v>12.2</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.93</v>
+        <v>8.74</v>
       </c>
       <c r="DS2" t="n">
         <v>0.07000000000000001</v>
@@ -1751,25 +1751,25 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.21</v>
+        <v>45.73</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.36</v>
+        <v>12.47</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.43</v>
+        <v>8.4</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.93</v>
+        <v>4.07</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.64</v>
+        <v>19.27</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="EC2" t="n">
         <v>2.86</v>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>8</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
         <v>0.38</v>
@@ -1872,118 +1872,118 @@
         <v>1.88</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AH3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>96.43000000000001</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AP3" t="n">
         <v>2</v>
       </c>
-      <c r="AI3" t="n">
-        <v>99</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>43.33</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AQ3" t="n">
-        <v>8</v>
+        <v>8.57</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.83</v>
+        <v>12.43</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.83</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AU3" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>55.83</v>
+        <v>55.86</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.83</v>
+        <v>7.71</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.67</v>
+        <v>4.29</v>
       </c>
       <c r="BD3" t="n">
-        <v>15.67</v>
+        <v>15.14</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.71</v>
+        <v>5.73</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,19 +1992,19 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU3" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BV3" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BX3" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY3" t="n">
         <v>1.82</v>
@@ -2013,16 +2013,16 @@
         <v>1.91</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.15</v>
+        <v>4.13</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.32</v>
+        <v>3.27</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.68</v>
+        <v>3.63</v>
       </c>
       <c r="CE3" t="n">
         <v>1.26</v>
@@ -2031,37 +2031,37 @@
         <v>2.29</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="CH3" t="n">
         <v>1.63</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO3" t="n">
         <v>1.16</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CR3" t="n">
         <v>1.34</v>
@@ -2076,106 +2076,106 @@
         <v>1.66</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CX3" t="n">
         <v>1.57</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.36</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DB3" t="n">
         <v>1.27</v>
       </c>
       <c r="DC3" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="DD3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>47.33</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="DQ3" t="n">
+        <v>11.34</v>
+      </c>
+      <c r="DR3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="DS3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>59.53</v>
+      </c>
+      <c r="DW3" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DX3" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="DY3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="DZ3" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="EA3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="EB3" t="n">
         <v>1.62</v>
       </c>
-      <c r="DD3" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="DE3" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="DF3" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="DG3" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="DH3" t="n">
-        <v>111.43</v>
-      </c>
-      <c r="DI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="DK3" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="DL3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="DM3" t="n">
-        <v>47.86</v>
-      </c>
-      <c r="DN3" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="DO3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="DP3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="DQ3" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="DR3" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="DS3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="DT3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="DU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV3" t="n">
-        <v>59.78</v>
-      </c>
-      <c r="DW3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DX3" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="DY3" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="DZ3" t="n">
-        <v>4.86</v>
-      </c>
-      <c r="EA3" t="n">
-        <v>15.86</v>
-      </c>
-      <c r="EB3" t="n">
-        <v>1.6</v>
-      </c>
       <c r="EC3" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="4">
@@ -2582,94 +2582,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="G5" t="n">
-        <v>5.5</v>
+        <v>5.14</v>
       </c>
       <c r="H5" t="n">
-        <v>114.83</v>
+        <v>117.57</v>
       </c>
       <c r="I5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J5" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>7.67</v>
+        <v>7.43</v>
       </c>
       <c r="L5" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="M5" t="n">
-        <v>60.33</v>
+        <v>60.29</v>
       </c>
       <c r="N5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="O5" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="P5" t="n">
-        <v>11</v>
+        <v>11.57</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.33</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>7.5</v>
+        <v>7.14</v>
       </c>
       <c r="S5" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="T5" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>55</v>
+        <v>55.29</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.5</v>
+        <v>13.86</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.17</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.33</v>
+        <v>5.14</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.33</v>
+        <v>17.43</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2753,70 +2753,70 @@
         <v>2.25</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.14</v>
+        <v>10.13</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.64</v>
+        <v>6.53</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT5" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV5" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW5" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY5" t="n">
         <v>1.58</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.23</v>
+        <v>4.26</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="CC5" t="n">
         <v>2.59</v>
@@ -2828,16 +2828,16 @@
         <v>1.24</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CH5" t="n">
         <v>1.64</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.56</v>
@@ -2846,13 +2846,13 @@
         <v>1.47</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CO5" t="n">
         <v>1.14</v>
@@ -2861,37 +2861,37 @@
         <v>1.54</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CR5" t="n">
         <v>1.34</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CT5" t="n">
         <v>3.34</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CX5" t="n">
         <v>1.57</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.39</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DB5" t="n">
         <v>1.26</v>
@@ -2900,19 +2900,19 @@
         <v>1.56</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
       <c r="DH5" t="n">
-        <v>107.78</v>
+        <v>109.53</v>
       </c>
       <c r="DI5" t="n">
         <v>0.07000000000000001</v>
@@ -2921,28 +2921,28 @@
         <v>1.93</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.14</v>
+        <v>5.2</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM5" t="n">
-        <v>54.86</v>
+        <v>55.2</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.5</v>
+        <v>11.74</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.22</v>
+        <v>10.4</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.93</v>
+        <v>6.8</v>
       </c>
       <c r="DS5" t="n">
         <v>0.07000000000000001</v>
@@ -2954,28 +2954,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>52.29</v>
+        <v>52.6</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX5" t="n">
-        <v>12</v>
+        <v>11.87</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.58</v>
+        <v>7.47</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.43</v>
+        <v>4.4</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="EB5" t="n">
         <v>1.47</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="6">
@@ -2985,13 +2985,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3078,136 +3078,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AI6" t="n">
         <v>87</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.33</v>
+        <v>5.14</v>
       </c>
       <c r="AM6" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>12.57</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>0.33</v>
       </c>
-      <c r="AN6" t="n">
-        <v>35.33</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>48.33</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>17.17</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>10.36</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.29</v>
-      </c>
       <c r="BK6" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.57</v>
+        <v>4.6</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.79</v>
+        <v>5.73</v>
       </c>
       <c r="BR6" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS6" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV6" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX6" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY6" t="n">
         <v>3.42</v>
@@ -3216,22 +3216,22 @@
         <v>3.4</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.01</v>
+        <v>4.05</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.59</v>
+        <v>3.85</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.75</v>
+        <v>4.12</v>
       </c>
       <c r="CE6" t="n">
         <v>1.25</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CG6" t="n">
         <v>3.63</v>
@@ -3249,37 +3249,37 @@
         <v>1.41</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CO6" t="n">
         <v>1.15</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CR6" t="n">
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CT6" t="n">
         <v>3.23</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CW6" t="n">
         <v>1.57</v>
@@ -3300,10 +3300,10 @@
         <v>1.3</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
@@ -3312,73 +3312,73 @@
         <v>0.93</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.93000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="DI6" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DK6" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.71</v>
+        <v>38.2</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.72</v>
+        <v>10.87</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.22</v>
+        <v>10.53</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.07</v>
+        <v>7</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.5</v>
+        <v>46.26</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.5</v>
+        <v>7.34</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.5</v>
+        <v>4.27</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.86</v>
+        <v>17.67</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="7">
@@ -3388,13 +3388,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3481,136 +3481,136 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="AI7" t="n">
-        <v>107.29</v>
+        <v>110.38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.14</v>
+        <v>-0.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AN7" t="n">
-        <v>49.57</v>
+        <v>49.25</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.71</v>
+        <v>10.88</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.43</v>
+        <v>9.25</v>
       </c>
       <c r="AS7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH7" t="n">
         <v>8</v>
       </c>
-      <c r="AT7" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>55.14</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>20.71</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>7.86</v>
-      </c>
       <c r="BI7" t="n">
-        <v>4.14</v>
+        <v>4</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK7" t="n">
         <v>1.07</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.29</v>
+        <v>2.13</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BP7" t="n">
         <v>3.93</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU7" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BW7" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BX7" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY7" t="n">
         <v>2.26</v>
@@ -3619,49 +3619,49 @@
         <v>2.64</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.51</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL7" t="n">
         <v>1.88</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP7" t="n">
         <v>1.54</v>
@@ -3670,85 +3670,85 @@
         <v>2.32</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CW7" t="n">
         <v>1.54</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="DA7" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="DH7" t="n">
-        <v>103.36</v>
+        <v>105.27</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.13</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM7" t="n">
-        <v>50.5</v>
+        <v>50.27</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.36</v>
+        <v>10.47</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.57</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.57</v>
+        <v>7.33</v>
       </c>
       <c r="DS7" t="n">
         <v>0.14</v>
@@ -3760,28 +3760,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.92</v>
+        <v>55.26</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.79</v>
+        <v>12.54</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.279999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.93</v>
+        <v>21.13</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="8">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0.29</v>
@@ -3881,139 +3881,139 @@
         <v>1.71</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.29</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.57</v>
+        <v>3.88</v>
       </c>
       <c r="AM8" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AN8" t="n">
-        <v>43.14</v>
+        <v>41.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.710000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.57</v>
+        <v>12.88</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.57</v>
+        <v>7.88</v>
       </c>
       <c r="AT8" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>47</v>
+        <v>46.62</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.57</v>
+        <v>12</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.859999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.71</v>
+        <v>3.38</v>
       </c>
       <c r="BD8" t="n">
-        <v>18.71</v>
+        <v>18.62</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="BF8" t="n">
         <v>1</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.140000000000001</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.29</v>
+        <v>4.2</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.86</v>
+        <v>3.93</v>
       </c>
       <c r="BR8" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS8" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT8" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BV8" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.14</v>
+        <v>13.33</v>
       </c>
       <c r="BX8" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY8" t="n">
         <v>2.29</v>
@@ -4022,16 +4022,16 @@
         <v>2.42</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.25</v>
+        <v>4.03</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.57</v>
+        <v>4.37</v>
       </c>
       <c r="CE8" t="n">
         <v>1.32</v>
@@ -4040,7 +4040,7 @@
         <v>2.61</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CH8" t="n">
         <v>1.5</v>
@@ -4049,22 +4049,22 @@
         <v>2.14</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CK8" t="n">
         <v>1.64</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM8" t="n">
         <v>2.18</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP8" t="n">
         <v>1.81</v>
@@ -4076,7 +4076,7 @@
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CT8" t="n">
         <v>3.18</v>
@@ -4091,100 +4091,100 @@
         <v>1.75</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB8" t="n">
         <v>1.3</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
       <c r="DH8" t="n">
-        <v>98.34999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.78</v>
+        <v>4.87</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DM8" t="n">
-        <v>47</v>
+        <v>45.87</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="DP8" t="n">
-        <v>9</v>
+        <v>8.93</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.93</v>
+        <v>13.07</v>
       </c>
       <c r="DR8" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.5</v>
+        <v>51</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.93</v>
+        <v>13.07</v>
       </c>
       <c r="DY8" t="n">
-        <v>9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.43</v>
+        <v>20.26</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="9">
@@ -4194,61 +4194,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F9" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
-        <v>87.43000000000001</v>
+        <v>86.75</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="J9" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="L9" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="M9" t="n">
-        <v>41.57</v>
+        <v>40.12</v>
       </c>
       <c r="N9" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>12.57</v>
+        <v>12</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.14</v>
+        <v>13</v>
       </c>
       <c r="R9" t="n">
-        <v>8.710000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="T9" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4260,28 +4260,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>46.57</v>
+        <v>45.75</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.14</v>
+        <v>13.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.859999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.29</v>
+        <v>5</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.86</v>
+        <v>18.88</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4365,70 +4365,70 @@
         <v>2.29</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.43</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.07</v>
+        <v>4.2</v>
       </c>
       <c r="BR9" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS9" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT9" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU9" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.86</v>
+        <v>4.76</v>
       </c>
       <c r="CC9" t="n">
         <v>6.67</v>
@@ -4440,121 +4440,121 @@
         <v>1.28</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CI9" t="n">
         <v>2.28</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL9" t="n">
         <v>1.83</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CN9" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CO9" t="n">
         <v>1.16</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CW9" t="n">
         <v>1.62</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="DG9" t="n">
         <v>2</v>
       </c>
       <c r="DH9" t="n">
-        <v>85.56999999999999</v>
+        <v>85.33</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.71</v>
+        <v>3.8</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="DM9" t="n">
-        <v>36.21</v>
+        <v>35.8</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.78</v>
+        <v>12.47</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.86</v>
+        <v>12.8</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.140000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4566,28 +4566,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47</v>
+        <v>46.53</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.28</v>
+        <v>13</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.57</v>
+        <v>8.4</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.71</v>
+        <v>4.6</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.5</v>
+        <v>18.53</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5000,13 +5000,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0.14</v>
@@ -5090,139 +5090,139 @@
         <v>1.71</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="AO11" t="n">
         <v>1</v>
       </c>
-      <c r="AH11" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>105.57</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AP11" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.29</v>
+        <v>14.62</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.859999999999999</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>6</v>
+        <v>6.38</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AU11" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>52.86</v>
+        <v>52.88</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.57</v>
+        <v>11.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.71</v>
+        <v>7.12</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.86</v>
+        <v>4.38</v>
       </c>
       <c r="BD11" t="n">
-        <v>20.57</v>
+        <v>20.75</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.79</v>
+        <v>10.47</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.5</v>
+        <v>3.27</v>
       </c>
       <c r="BJ11" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BM11" t="n">
         <v>0.93</v>
       </c>
-      <c r="BK11" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1</v>
-      </c>
       <c r="BN11" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6.14</v>
+        <v>5.87</v>
       </c>
       <c r="BR11" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS11" t="n">
-        <v>92.86</v>
+        <v>86.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU11" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BV11" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX11" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY11" t="n">
         <v>2.88</v>
@@ -5231,16 +5231,16 @@
         <v>2.89</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="CE11" t="n">
         <v>1.23</v>
@@ -5255,31 +5255,31 @@
         <v>1.68</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CK11" t="n">
         <v>1.4</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CO11" t="n">
         <v>1.14</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
@@ -5294,7 +5294,7 @@
         <v>1.64</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CW11" t="n">
         <v>1.55</v>
@@ -5318,82 +5318,82 @@
         <v>1.61</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="DN11" t="n">
         <v>0.93</v>
       </c>
-      <c r="DG11" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="DH11" t="n">
-        <v>109.5</v>
-      </c>
-      <c r="DI11" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="DJ11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="DK11" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="DL11" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="DM11" t="n">
-        <v>49.72</v>
-      </c>
-      <c r="DN11" t="n">
-        <v>1</v>
-      </c>
       <c r="DO11" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.72</v>
+        <v>14.86</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.359999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="DR11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.93</v>
+        <v>53.87</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.28</v>
+        <v>12.67</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.5</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.79</v>
+        <v>4.53</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.64</v>
+        <v>21.66</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="12">
@@ -5403,61 +5403,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="G12" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="H12" t="n">
-        <v>96.33</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J12" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="K12" t="n">
-        <v>4.33</v>
+        <v>4.14</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>40</v>
+        <v>40.86</v>
       </c>
       <c r="N12" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="O12" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="P12" t="n">
-        <v>8.83</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.17</v>
+        <v>12.14</v>
       </c>
       <c r="R12" t="n">
-        <v>6.83</v>
+        <v>7.29</v>
       </c>
       <c r="S12" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="T12" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5469,28 +5469,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>48.5</v>
+        <v>50.43</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.5</v>
+        <v>14.29</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.17</v>
+        <v>8.57</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.33</v>
+        <v>5.71</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.83</v>
+        <v>19.43</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AF12" t="n">
         <v>0.12</v>
@@ -5574,70 +5574,70 @@
         <v>2.12</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.21</v>
+        <v>3.07</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.43</v>
+        <v>10.33</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.21</v>
+        <v>3.07</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.29</v>
+        <v>4.2</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.14</v>
+        <v>5.2</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BU12" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV12" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW12" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX12" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.81</v>
+        <v>3.77</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.88</v>
+        <v>3.84</v>
       </c>
       <c r="CC12" t="n">
         <v>4.25</v>
@@ -5646,43 +5646,43 @@
         <v>4.26</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.46</v>
+        <v>3.42</v>
       </c>
       <c r="CH12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="CJ12" t="n">
         <v>1.58</v>
-      </c>
-      <c r="CI12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="CJ12" t="n">
-        <v>1.57</v>
       </c>
       <c r="CK12" t="n">
         <v>1.38</v>
       </c>
       <c r="CL12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CP12" t="n">
         <v>1.66</v>
       </c>
-      <c r="CM12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="CP12" t="n">
-        <v>1.64</v>
-      </c>
       <c r="CQ12" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
@@ -5697,10 +5697,10 @@
         <v>1.62</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CX12" t="n">
         <v>1.58</v>
@@ -5715,88 +5715,88 @@
         <v>2.15</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="DH12" t="n">
-        <v>91.56999999999999</v>
+        <v>92.53</v>
       </c>
       <c r="DI12" t="n">
         <v>-0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM12" t="n">
-        <v>39</v>
+        <v>39.47</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="DP12" t="n">
         <v>8.93</v>
       </c>
       <c r="DQ12" t="n">
-        <v>10.93</v>
+        <v>11.4</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.359999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="DS12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="DW12" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="DT12" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV12" t="n">
-        <v>47.14</v>
-      </c>
-      <c r="DW12" t="n">
-        <v>0</v>
-      </c>
       <c r="DX12" t="n">
-        <v>12.5</v>
+        <v>12.54</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.86</v>
+        <v>8.06</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.64</v>
+        <v>4.47</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.07</v>
+        <v>18.93</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="13">
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>7</v>
@@ -5818,82 +5818,82 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="G13" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="H13" t="n">
-        <v>123</v>
+        <v>122.12</v>
       </c>
       <c r="I13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J13" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="K13" t="n">
-        <v>5.29</v>
+        <v>5.75</v>
       </c>
       <c r="L13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M13" t="n">
-        <v>58.14</v>
+        <v>57.25</v>
       </c>
       <c r="N13" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="P13" t="n">
-        <v>13.43</v>
+        <v>12.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.43</v>
+        <v>10.25</v>
       </c>
       <c r="R13" t="n">
-        <v>7.29</v>
+        <v>6.62</v>
       </c>
       <c r="S13" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="T13" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="U13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>49.29</v>
+        <v>49.75</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.43</v>
+        <v>12.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.57</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.71</v>
+        <v>24.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5977,70 +5977,70 @@
         <v>3</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.07</v>
+        <v>9.4</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.21</v>
+        <v>3.67</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.79</v>
+        <v>5.67</v>
       </c>
       <c r="BR13" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS13" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT13" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU13" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BV13" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW13" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.14</v>
+        <v>4.1</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.29</v>
+        <v>4.23</v>
       </c>
       <c r="CC13" t="n">
         <v>5.7</v>
@@ -6049,157 +6049,157 @@
         <v>5.96</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CL13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CY13" t="n">
         <v>1.86</v>
       </c>
-      <c r="CM13" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CO13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="CP13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CQ13" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="CU13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CV13" t="n">
+      <c r="CZ13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>107.73</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="DZ13" t="n">
         <v>2.47</v>
       </c>
-      <c r="CW13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CX13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CY13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CZ13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="DA13" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="DB13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="DC13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="DD13" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="DE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="DG13" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="DH13" t="n">
-        <v>107.15</v>
-      </c>
-      <c r="DI13" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DJ13" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="DK13" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="DL13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DM13" t="n">
-        <v>53.36</v>
-      </c>
-      <c r="DN13" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="DO13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="DP13" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="DQ13" t="n">
-        <v>10.57</v>
-      </c>
-      <c r="DR13" t="n">
-        <v>7.29</v>
-      </c>
-      <c r="DS13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DT13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV13" t="n">
-        <v>45.29</v>
-      </c>
-      <c r="DW13" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="DX13" t="n">
-        <v>10.64</v>
-      </c>
-      <c r="DY13" t="n">
-        <v>8.07</v>
-      </c>
-      <c r="DZ13" t="n">
-        <v>2.58</v>
-      </c>
       <c r="EA13" t="n">
-        <v>22.14</v>
+        <v>23</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="14">
@@ -6209,94 +6209,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F14" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="H14" t="n">
-        <v>98</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="K14" t="n">
-        <v>6.33</v>
+        <v>5.71</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M14" t="n">
-        <v>41.33</v>
+        <v>44</v>
       </c>
       <c r="N14" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O14" t="n">
-        <v>4.33</v>
+        <v>3.86</v>
       </c>
       <c r="P14" t="n">
-        <v>8.67</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>11.14</v>
       </c>
       <c r="R14" t="n">
-        <v>6.67</v>
+        <v>6.14</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="U14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.83</v>
+        <v>17.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.17</v>
+        <v>9.57</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.67</v>
+        <v>7.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>20</v>
+        <v>19.29</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AF14" t="n">
         <v>0.5</v>
@@ -6380,70 +6380,70 @@
         <v>1.75</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.57</v>
+        <v>10.53</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="BJ14" t="n">
         <v>0.93</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BP14" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.57</v>
+        <v>5.6</v>
       </c>
       <c r="BR14" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS14" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT14" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU14" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BV14" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW14" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BX14" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.23</v>
+        <v>4.18</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.36</v>
+        <v>4.33</v>
       </c>
       <c r="CC14" t="n">
         <v>3.6</v>
@@ -6455,16 +6455,16 @@
         <v>1.22</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.07</v>
+        <v>4.05</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.49</v>
@@ -6479,16 +6479,16 @@
         <v>2.75</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CO14" t="n">
         <v>1.12</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
@@ -6503,10 +6503,10 @@
         <v>1.79</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CX14" t="n">
         <v>1.46</v>
@@ -6518,7 +6518,7 @@
         <v>2.63</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DB14" t="n">
         <v>1.32</v>
@@ -6530,46 +6530,46 @@
         <v>2.18</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DF14" t="n">
         <v>0.93</v>
       </c>
       <c r="DG14" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>92.87</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DO14" t="n">
         <v>3</v>
       </c>
-      <c r="DH14" t="n">
-        <v>91.65000000000001</v>
-      </c>
-      <c r="DI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="DK14" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="DL14" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="DM14" t="n">
-        <v>42.14</v>
-      </c>
-      <c r="DN14" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="DO14" t="n">
-        <v>3.14</v>
-      </c>
       <c r="DP14" t="n">
-        <v>9.359999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.57</v>
+        <v>10.67</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.5</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DS14" t="n">
         <v>0.07000000000000001</v>
@@ -6581,28 +6581,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.57</v>
+        <v>50.13</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>16.14</v>
+        <v>16.33</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.64</v>
+        <v>5.73</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="15">
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6702,52 +6702,52 @@
         <v>2</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AI15" t="n">
-        <v>94</v>
+        <v>92.88</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AN15" t="n">
-        <v>41.43</v>
+        <v>39.75</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.86</v>
+        <v>1.38</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.71</v>
+        <v>10.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.140000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.57</v>
+        <v>6</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6759,82 +6759,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>44</v>
+        <v>44.38</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>10</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.71</v>
+        <v>7.25</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="BD15" t="n">
-        <v>20.14</v>
+        <v>21.38</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.640000000000001</v>
+        <v>9.93</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.79</v>
+        <v>2.6</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.71</v>
+        <v>5.6</v>
       </c>
       <c r="BR15" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS15" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT15" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU15" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV15" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX15" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY15" t="n">
         <v>2.72</v>
@@ -6843,31 +6843,31 @@
         <v>2.77</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.09</v>
+        <v>4.04</v>
       </c>
       <c r="CC15" t="n">
-        <v>6.72</v>
+        <v>6.42</v>
       </c>
       <c r="CD15" t="n">
-        <v>6.74</v>
+        <v>6.39</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.12</v>
+        <v>3.09</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.78</v>
@@ -6876,103 +6876,103 @@
         <v>1.61</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CN15" t="n">
         <v>1.77</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY15" t="n">
         <v>2.06</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB15" t="n">
         <v>1.33</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF15" t="n">
         <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="DH15" t="n">
-        <v>101.72</v>
+        <v>100.6</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DK15" t="n">
         <v>5.07</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.14</v>
+        <v>0.4</v>
       </c>
       <c r="DM15" t="n">
-        <v>47.07</v>
+        <v>45.8</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.57</v>
+        <v>10.47</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.36</v>
+        <v>10</v>
       </c>
       <c r="DR15" t="n">
-        <v>5.93</v>
+        <v>6.14</v>
       </c>
       <c r="DS15" t="n">
         <v>0.07000000000000001</v>
@@ -6984,28 +6984,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.5</v>
+        <v>47.47</v>
       </c>
       <c r="DW15" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.93</v>
+        <v>10.54</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.36</v>
+        <v>7.13</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.28</v>
+        <v>21.87</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="16">
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -7027,82 +7027,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="H16" t="n">
-        <v>107.17</v>
+        <v>103.57</v>
       </c>
       <c r="I16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="J16" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="K16" t="n">
-        <v>4.83</v>
+        <v>4.71</v>
       </c>
       <c r="L16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M16" t="n">
-        <v>41.5</v>
+        <v>39.71</v>
       </c>
       <c r="N16" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="O16" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="P16" t="n">
-        <v>9.83</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>11.83</v>
+        <v>12.57</v>
       </c>
       <c r="R16" t="n">
-        <v>5.67</v>
+        <v>5.29</v>
       </c>
       <c r="S16" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="U16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>55.17</v>
+        <v>54</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>16.17</v>
+        <v>15.29</v>
       </c>
       <c r="AA16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.67</v>
+        <v>5.29</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.5</v>
+        <v>19.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7186,70 +7186,70 @@
         <v>1.88</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.36</v>
+        <v>3.13</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.29</v>
+        <v>10</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.36</v>
+        <v>3.13</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.29</v>
+        <v>5.07</v>
       </c>
       <c r="BR16" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS16" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT16" t="n">
-        <v>78.56999999999999</v>
+        <v>73.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV16" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW16" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX16" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="CC16" t="n">
         <v>2.66</v>
@@ -7264,37 +7264,37 @@
         <v>2.2</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="CH16" t="n">
         <v>1.67</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CR16" t="n">
         <v>1.33</v>
@@ -7337,76 +7337,76 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="DH16" t="n">
-        <v>122.22</v>
+        <v>119.53</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.78</v>
+        <v>5.66</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DM16" t="n">
-        <v>60.64</v>
+        <v>58.53</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.14</v>
+        <v>12.47</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.57</v>
+        <v>5.4</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>58.28</v>
+        <v>57.53</v>
       </c>
       <c r="DW16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.93</v>
+        <v>15.54</v>
       </c>
       <c r="DY16" t="n">
-        <v>10.28</v>
+        <v>10.06</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.64</v>
+        <v>5.47</v>
       </c>
       <c r="EA16" t="n">
-        <v>17.93</v>
+        <v>19</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="17">
@@ -7416,13 +7416,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
         <v>0.12</v>
@@ -7506,49 +7506,49 @@
         <v>3</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="AI17" t="n">
-        <v>89.5</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.17</v>
+        <v>1.71</v>
       </c>
       <c r="AL17" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN17" t="n">
-        <v>39</v>
+        <v>40.43</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AQ17" t="n">
-        <v>10.33</v>
+        <v>11.43</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.5</v>
+        <v>10.29</v>
       </c>
       <c r="AS17" t="n">
         <v>9</v>
       </c>
       <c r="AT17" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AU17" t="n">
         <v>1</v>
@@ -7563,82 +7563,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>37.17</v>
+        <v>37.29</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>12.17</v>
+        <v>12</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.5</v>
+        <v>8.43</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="BD17" t="n">
-        <v>18.83</v>
+        <v>19.14</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.17</v>
+        <v>1.71</v>
       </c>
       <c r="BG17" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.29</v>
+        <v>10.2</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL17" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="BP17" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="BQ17" t="n">
         <v>5</v>
       </c>
-      <c r="BQ17" t="n">
-        <v>4.93</v>
-      </c>
       <c r="BR17" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS17" t="n">
-        <v>71.43000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT17" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU17" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV17" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW17" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX17" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY17" t="n">
         <v>3.18</v>
@@ -7647,28 +7647,28 @@
         <v>4</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.56</v>
+        <v>4.32</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.57</v>
+        <v>4.34</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI17" t="n">
         <v>2.06</v>
@@ -7677,25 +7677,25 @@
         <v>1.74</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP17" t="n">
         <v>1.83</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="CR17" t="n">
         <v>1.4</v>
@@ -7731,52 +7731,52 @@
         <v>1.33</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="DH17" t="n">
-        <v>87.5</v>
+        <v>86.27</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.35</v>
+        <v>5.4</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DM17" t="n">
-        <v>39.64</v>
+        <v>40.26</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.57</v>
+        <v>2.47</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.07</v>
+        <v>13.4</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.29</v>
+        <v>11.14</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.79</v>
+        <v>7.87</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7788,28 +7788,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>36</v>
+        <v>36.13</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.29</v>
+        <v>12.2</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.57</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.72</v>
+        <v>3.67</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.57</v>
+        <v>19.66</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
@@ -7819,13 +7819,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>0.14</v>
@@ -7912,136 +7912,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AI18" t="n">
-        <v>83.70999999999999</v>
+        <v>81.88</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.29</v>
+        <v>4.25</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="AN18" t="n">
-        <v>33.57</v>
+        <v>34.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.86</v>
+        <v>1.88</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.140000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AR18" t="n">
         <v>10</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.859999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>46.43</v>
+        <v>46.5</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.29</v>
+        <v>10.12</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.86</v>
+        <v>6.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.43</v>
+        <v>3.88</v>
       </c>
       <c r="BD18" t="n">
-        <v>19.14</v>
+        <v>18.25</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.29</v>
+        <v>3.07</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.640000000000001</v>
+        <v>10.13</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.29</v>
+        <v>3.07</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BN18" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.36</v>
+        <v>4.87</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.43</v>
+        <v>4.47</v>
       </c>
       <c r="BR18" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BS18" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT18" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU18" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BV18" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW18" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX18" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY18" t="n">
         <v>2.48</v>
@@ -8050,31 +8050,31 @@
         <v>2.62</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.43</v>
+        <v>4.37</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.46</v>
+        <v>4.39</v>
       </c>
       <c r="CC18" t="n">
-        <v>5.96</v>
+        <v>5.6</v>
       </c>
       <c r="CD18" t="n">
-        <v>7.16</v>
+        <v>6.68</v>
       </c>
       <c r="CE18" t="n">
         <v>1.26</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.54</v>
@@ -8095,10 +8095,10 @@
         <v>1.14</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="CR18" t="n">
         <v>1.34</v>
@@ -8113,10 +8113,10 @@
         <v>1.72</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CX18" t="n">
         <v>1.54</v>
@@ -8128,91 +8128,91 @@
         <v>2.45</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB18" t="n">
         <v>1.26</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="DE18" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF18" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>92.34</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>40.53</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DO18" t="n">
         <v>2</v>
       </c>
-      <c r="DG18" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="DH18" t="n">
-        <v>94</v>
-      </c>
-      <c r="DI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ18" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="DK18" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="DL18" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="DM18" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="DN18" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="DO18" t="n">
-        <v>1.5</v>
-      </c>
       <c r="DP18" t="n">
-        <v>9.779999999999999</v>
+        <v>10.47</v>
       </c>
       <c r="DQ18" t="n">
-        <v>9.43</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.359999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.43</v>
+        <v>48.33</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.5</v>
+        <v>12.26</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.93</v>
+        <v>8</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.57</v>
+        <v>4.27</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.28</v>
+        <v>18.8</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="19">
@@ -8222,61 +8222,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F19" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="G19" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="H19" t="n">
-        <v>96</v>
+        <v>95.62</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="K19" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>49.43</v>
+        <v>48.25</v>
       </c>
       <c r="N19" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O19" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>10.86</v>
+        <v>10.5</v>
       </c>
       <c r="R19" t="n">
-        <v>8.710000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="T19" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8288,28 +8288,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>45.29</v>
+        <v>46.62</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.57</v>
+        <v>13.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.57</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AB19" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.71</v>
+        <v>18</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
         <v>0.14</v>
@@ -8393,70 +8393,70 @@
         <v>2</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.64</v>
+        <v>11.4</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK19" t="n">
         <v>0.93</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.93</v>
+        <v>4.8</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.57</v>
+        <v>5.53</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT19" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BV19" t="n">
-        <v>14.29</v>
+        <v>20</v>
       </c>
       <c r="BW19" t="n">
-        <v>7.14</v>
+        <v>13.33</v>
       </c>
       <c r="BX19" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BY19" t="n">
         <v>2.55</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="CC19" t="n">
         <v>3.36</v>
@@ -8468,121 +8468,121 @@
         <v>1.28</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.55</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="CR19" t="n">
         <v>1.35</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="DB19" t="n">
         <v>1.28</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="DH19" t="n">
-        <v>88.5</v>
+        <v>88.8</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.64</v>
+        <v>3.53</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
       </c>
       <c r="DM19" t="n">
-        <v>41.14</v>
+        <v>41.07</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.07</v>
+        <v>11.4</v>
       </c>
       <c r="DQ19" t="n">
-        <v>10</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.640000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="DS19" t="n">
         <v>0.07000000000000001</v>
@@ -8594,28 +8594,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.14</v>
+        <v>45.86</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.93</v>
+        <v>12</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.72</v>
+        <v>7.67</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.22</v>
+        <v>4.33</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.07</v>
+        <v>17.27</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>0.25</v>
@@ -2275,118 +2275,118 @@
         <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="AI4" t="n">
-        <v>130.83</v>
+        <v>134.43</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="AK4" t="n">
-        <v>3.17</v>
+        <v>2.71</v>
       </c>
       <c r="AL4" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="AN4" t="n">
-        <v>69.67</v>
+        <v>69.86</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AP4" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>9.57</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>67.14</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BN4" t="n">
         <v>2.33</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>66</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>20.33</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>2.36</v>
       </c>
       <c r="BO4" t="n">
         <v>2.07</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2398,16 +2398,16 @@
         <v>100</v>
       </c>
       <c r="BU4" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BV4" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BW4" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>46.67</v>
       </c>
       <c r="BY4" t="n">
         <v>1.17</v>
@@ -2416,16 +2416,16 @@
         <v>1.18</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.59</v>
+        <v>7.65</v>
       </c>
       <c r="CB4" t="n">
-        <v>8.369999999999999</v>
+        <v>8.41</v>
       </c>
       <c r="CC4" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="CE4" t="n">
         <v>1.15</v>
@@ -2440,28 +2440,28 @@
         <v>1.97</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CK4" t="n">
         <v>1.52</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CQ4" t="n">
         <v>1.8</v>
@@ -2475,16 +2475,16 @@
         <v>2.15</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CX4" t="n">
         <v>1.52</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.48</v>
@@ -2497,82 +2497,82 @@
         <v>1.36</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="DH4" t="n">
-        <v>134.86</v>
+        <v>136.27</v>
       </c>
       <c r="DI4" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.79</v>
+        <v>5.8</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DM4" t="n">
-        <v>69.29000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.710000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.289999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.29</v>
+        <v>5.47</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>67.56999999999999</v>
+        <v>68</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>19.5</v>
+        <v>19.73</v>
       </c>
       <c r="DY4" t="n">
-        <v>11.07</v>
+        <v>11.13</v>
       </c>
       <c r="DZ4" t="n">
-        <v>8.43</v>
+        <v>8.6</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.71</v>
+        <v>20.4</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="5">
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
@@ -4609,50 +4609,50 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="H10" t="n">
-        <v>86.70999999999999</v>
+        <v>82.12</v>
       </c>
       <c r="I10" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="K10" t="n">
-        <v>5.14</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M10" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P10" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="R10" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="T10" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>37.29</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="P10" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="R10" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.14</v>
-      </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
@@ -4663,28 +4663,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>41.86</v>
+        <v>39.88</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.43</v>
+        <v>11.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.43</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>15.14</v>
+        <v>15.62</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4768,70 +4768,70 @@
         <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.93</v>
+        <v>9.67</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.07</v>
+        <v>3.13</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.79</v>
+        <v>5.53</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT10" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX10" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.46</v>
+        <v>4.53</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.78</v>
+        <v>5.21</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.95</v>
+        <v>4.25</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.13</v>
+        <v>4.45</v>
       </c>
       <c r="CC10" t="n">
         <v>5.46</v>
@@ -4840,73 +4840,73 @@
         <v>5.97</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CJ10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>2</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CP10" t="n">
         <v>1.66</v>
       </c>
-      <c r="CK10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>1.69</v>
-      </c>
       <c r="CQ10" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="CR10" t="n">
         <v>1.39</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="CT10" t="n">
         <v>3.06</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DB10" t="n">
         <v>1.33</v>
@@ -4915,49 +4915,49 @@
         <v>1.76</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.14</v>
+        <v>2.93</v>
       </c>
       <c r="DH10" t="n">
-        <v>85.42</v>
+        <v>83.06</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.28</v>
+        <v>4.93</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.86</v>
+        <v>37.4</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.93</v>
+        <v>10.73</v>
       </c>
       <c r="DQ10" t="n">
-        <v>11.14</v>
+        <v>10.8</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.859999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4969,28 +4969,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>42.93</v>
+        <v>41.8</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.43</v>
+        <v>11.13</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.71</v>
+        <v>7.6</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.72</v>
+        <v>3.53</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.64</v>
+        <v>16.8</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="11">
@@ -6088,13 +6088,13 @@
         <v>2.68</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS13" t="n">
         <v>2.47</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CU13" t="n">
         <v>1.62</v>
@@ -6106,22 +6106,22 @@
         <v>1.63</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DD13" t="n">
         <v>2.65</v>
@@ -6852,7 +6852,7 @@
         <v>6.42</v>
       </c>
       <c r="CD15" t="n">
-        <v>6.39</v>
+        <v>6.41</v>
       </c>
       <c r="CE15" t="n">
         <v>1.36</v>
@@ -6897,7 +6897,7 @@
         <v>1.4</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CT15" t="n">
         <v>3.05</v>
@@ -6912,22 +6912,22 @@
         <v>1.81</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY15" t="n">
         <v>2.06</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DD15" t="n">
         <v>2.97</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -1484,7 +1484,7 @@
         <v>0.29</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.14</v>
+        <v>3.29</v>
       </c>
       <c r="AL2" t="n">
         <v>3.14</v>
@@ -1496,7 +1496,7 @@
         <v>34.29</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.71</v>
+        <v>0.86</v>
       </c>
       <c r="AP2" t="n">
         <v>1.57</v>
@@ -1547,7 +1547,7 @@
         <v>1.29</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.14</v>
+        <v>3.29</v>
       </c>
       <c r="BG2" t="n">
         <v>3</v>
@@ -1715,7 +1715,7 @@
         <v>0.27</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="DK2" t="n">
         <v>4.4</v>
@@ -1727,7 +1727,7 @@
         <v>39.8</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="DO2" t="n">
         <v>2.2</v>
@@ -1772,7 +1772,7 @@
         <v>1.36</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="3">
@@ -3803,7 +3803,7 @@
         <v>0.29</v>
       </c>
       <c r="F8" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="G8" t="n">
         <v>2.43</v>
@@ -3815,7 +3815,7 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
@@ -3878,7 +3878,7 @@
         <v>1.64</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AF8" t="n">
         <v>0.12</v>
@@ -4115,7 +4115,7 @@
         <v>0.2</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="DG8" t="n">
         <v>2.07</v>
@@ -4127,7 +4127,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="DK8" t="n">
         <v>4.87</v>
@@ -4184,7 +4184,7 @@
         <v>1.46</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="9">
@@ -6233,7 +6233,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="K14" t="n">
         <v>5.71</v>
@@ -6245,7 +6245,7 @@
         <v>44</v>
       </c>
       <c r="N14" t="n">
-        <v>0.57</v>
+        <v>0.43</v>
       </c>
       <c r="O14" t="n">
         <v>3.86</v>
@@ -6296,7 +6296,7 @@
         <v>1.93</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AF14" t="n">
         <v>0.5</v>
@@ -6545,7 +6545,7 @@
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="DK14" t="n">
         <v>5.86</v>
@@ -6557,7 +6557,7 @@
         <v>43.33</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DO14" t="n">
         <v>3</v>
@@ -6602,7 +6602,7 @@
         <v>1.74</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="15">
@@ -7111,7 +7111,7 @@
         <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.75</v>
+        <v>3.62</v>
       </c>
       <c r="AI16" t="n">
         <v>133.5</v>
@@ -7126,7 +7126,7 @@
         <v>6.5</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="AN16" t="n">
         <v>75</v>
@@ -7135,7 +7135,7 @@
         <v>0.62</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="AQ16" t="n">
         <v>10.5</v>
@@ -7213,10 +7213,10 @@
         <v>1.33</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.13</v>
+        <v>4.4</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.07</v>
+        <v>5.6</v>
       </c>
       <c r="BR16" t="n">
         <v>93.33</v>
@@ -7340,7 +7340,7 @@
         <v>1.33</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="DH16" t="n">
         <v>119.53</v>
@@ -7355,7 +7355,7 @@
         <v>5.66</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.34</v>
+        <v>0.4</v>
       </c>
       <c r="DM16" t="n">
         <v>58.53</v>
@@ -7364,7 +7364,7 @@
         <v>0.66</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="DP16" t="n">
         <v>10.2</v>
@@ -7834,7 +7834,7 @@
         <v>2.43</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="H18" t="n">
         <v>104.29</v>
@@ -7849,7 +7849,7 @@
         <v>4.57</v>
       </c>
       <c r="L18" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="M18" t="n">
         <v>47.43</v>
@@ -7858,7 +7858,7 @@
         <v>0.71</v>
       </c>
       <c r="O18" t="n">
-        <v>2.14</v>
+        <v>2.29</v>
       </c>
       <c r="P18" t="n">
         <v>10.43</v>
@@ -8017,10 +8017,10 @@
         <v>1.13</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.87</v>
+        <v>5.13</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.47</v>
+        <v>5</v>
       </c>
       <c r="BR18" t="n">
         <v>93.33</v>
@@ -8146,7 +8146,7 @@
         <v>2.07</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="DH18" t="n">
         <v>92.34</v>
@@ -8161,7 +8161,7 @@
         <v>4.4</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="DM18" t="n">
         <v>40.53</v>
@@ -8170,7 +8170,7 @@
         <v>0.8</v>
       </c>
       <c r="DO18" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="DP18" t="n">
         <v>10.47</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0.14</v>
@@ -2672,139 +2672,139 @@
         <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AI5" t="n">
-        <v>102.5</v>
+        <v>106.78</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG5" t="n">
         <v>2.75</v>
       </c>
-      <c r="AL5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>50.75</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>50.25</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="BB5" t="n">
+      <c r="BH5" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>6.38</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>20.38</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>6.53</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT5" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BW5" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BX5" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
         <v>1.58</v>
@@ -2813,25 +2813,25 @@
         <v>1.58</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.26</v>
+        <v>4.22</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.73</v>
+        <v>2.66</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CH5" t="n">
         <v>1.64</v>
@@ -2843,16 +2843,16 @@
         <v>1.56</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO5" t="n">
         <v>1.14</v>
@@ -2861,7 +2861,7 @@
         <v>1.54</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CR5" t="n">
         <v>1.34</v>
@@ -2897,85 +2897,85 @@
         <v>1.26</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="DH5" t="n">
-        <v>109.53</v>
+        <v>111.5</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DM5" t="n">
-        <v>55.2</v>
+        <v>54.88</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.74</v>
+        <v>11.37</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.4</v>
+        <v>10.62</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.8</v>
+        <v>6.62</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>52.6</v>
+        <v>53.06</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.87</v>
+        <v>12.13</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.47</v>
+        <v>7.62</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="EA5" t="n">
-        <v>19</v>
+        <v>19.82</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="6">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
@@ -3400,82 +3400,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="G7" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="H7" t="n">
-        <v>99.43000000000001</v>
+        <v>97.62</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="K7" t="n">
-        <v>5.29</v>
+        <v>4.88</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="M7" t="n">
-        <v>51.43</v>
+        <v>48</v>
       </c>
       <c r="N7" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="O7" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.710000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>7.14</v>
+        <v>6.88</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="U7" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="V7" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>54.71</v>
+        <v>52.88</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.29</v>
+        <v>13.12</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.57</v>
+        <v>8.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.71</v>
+        <v>4.88</v>
       </c>
       <c r="AC7" t="n">
-        <v>21.14</v>
+        <v>20.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3559,34 +3559,34 @@
         <v>1.88</v>
       </c>
       <c r="BG7" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="BH7" t="n">
-        <v>8</v>
+        <v>7.94</v>
       </c>
       <c r="BI7" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
       <c r="BQ7" t="n">
         <v>4</v>
@@ -3595,34 +3595,34 @@
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BV7" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BX7" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.26</v>
+        <v>2.39</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="CA7" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="CC7" t="n">
         <v>2.63</v>
@@ -3634,40 +3634,40 @@
         <v>1.25</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO7" t="n">
         <v>1.15</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CR7" t="n">
         <v>1.35</v>
@@ -3682,10 +3682,10 @@
         <v>1.71</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CX7" t="n">
         <v>1.63</v>
@@ -3703,85 +3703,85 @@
         <v>1.27</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="DH7" t="n">
-        <v>105.27</v>
+        <v>104</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.87</v>
+        <v>4.69</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM7" t="n">
-        <v>50.27</v>
+        <v>48.62</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.47</v>
+        <v>10.69</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.460000000000001</v>
+        <v>9.18</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.33</v>
+        <v>7.19</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>55.26</v>
+        <v>54.32</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.54</v>
+        <v>12.5</v>
       </c>
       <c r="DY7" t="n">
-        <v>8.130000000000001</v>
+        <v>8</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.13</v>
+        <v>20.94</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="8">
@@ -3791,94 +3791,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="G8" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="H8" t="n">
-        <v>109.71</v>
+        <v>109.75</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="L8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>50.86</v>
+        <v>49.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="O8" t="n">
-        <v>3.57</v>
+        <v>3.12</v>
       </c>
       <c r="P8" t="n">
-        <v>9.289999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.29</v>
+        <v>12.88</v>
       </c>
       <c r="R8" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="S8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="V8" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.29</v>
+        <v>15</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.140000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.14</v>
+        <v>5.38</v>
       </c>
       <c r="AC8" t="n">
-        <v>22.14</v>
+        <v>21.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
         <v>0.12</v>
@@ -3962,70 +3962,70 @@
         <v>1</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.130000000000001</v>
+        <v>7.81</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.93</v>
+        <v>3.81</v>
       </c>
       <c r="BR8" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS8" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BU8" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BV8" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW8" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC8" t="n">
         <v>4.03</v>
@@ -4034,31 +4034,31 @@
         <v>4.37</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CN8" t="n">
         <v>1.74</v>
@@ -4067,22 +4067,22 @@
         <v>1.24</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CT8" t="n">
         <v>3.18</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV8" t="n">
         <v>2.2</v>
@@ -4091,7 +4091,7 @@
         <v>1.75</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY8" t="n">
         <v>2.13</v>
@@ -4109,82 +4109,82 @@
         <v>1.86</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="DH8" t="n">
-        <v>97.06</v>
+        <v>97.88</v>
       </c>
       <c r="DI8" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.87</v>
+        <v>4.56</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM8" t="n">
-        <v>45.87</v>
+        <v>45.5</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="DP8" t="n">
-        <v>8.93</v>
+        <v>9.18</v>
       </c>
       <c r="DQ8" t="n">
-        <v>13.07</v>
+        <v>12.88</v>
       </c>
       <c r="DR8" t="n">
-        <v>5.8</v>
+        <v>5.82</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51</v>
+        <v>51.56</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.07</v>
+        <v>13.5</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.859999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.2</v>
+        <v>4.38</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.26</v>
+        <v>19.94</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -4194,13 +4194,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>0.25</v>
@@ -4287,49 +4287,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>83.70999999999999</v>
+        <v>81.62</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN9" t="n">
-        <v>30.86</v>
+        <v>30.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>12.75</v>
       </c>
       <c r="AR9" t="n">
-        <v>12.57</v>
+        <v>12.62</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.57</v>
+        <v>8.25</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4341,82 +4341,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>47.43</v>
+        <v>46.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>12.43</v>
+        <v>12.12</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.289999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.14</v>
+        <v>4.25</v>
       </c>
       <c r="BD9" t="n">
-        <v>18.14</v>
+        <v>17.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.529999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.27</v>
+        <v>4.06</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.2</v>
+        <v>4.06</v>
       </c>
       <c r="BR9" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS9" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT9" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV9" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY9" t="n">
         <v>2.68</v>
@@ -4425,136 +4425,136 @@
         <v>2.71</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.76</v>
+        <v>4.69</v>
       </c>
       <c r="CC9" t="n">
-        <v>6.67</v>
+        <v>6.46</v>
       </c>
       <c r="CD9" t="n">
-        <v>7.17</v>
+        <v>6.87</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="CH9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CP9" t="n">
         <v>1.63</v>
       </c>
-      <c r="CI9" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CO9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="CP9" t="n">
-        <v>1.6</v>
-      </c>
       <c r="CQ9" t="n">
-        <v>2.48</v>
+        <v>2.53</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CT9" t="n">
         <v>3.18</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="DB9" t="n">
         <v>1.3</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="DG9" t="n">
         <v>2</v>
       </c>
       <c r="DH9" t="n">
-        <v>85.33</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.8</v>
+        <v>35.31</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.47</v>
+        <v>12.38</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.8</v>
+        <v>12.81</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.27</v>
+        <v>8.57</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4566,28 +4566,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.53</v>
+        <v>46.12</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DX9" t="n">
-        <v>13</v>
+        <v>12.81</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.4</v>
+        <v>8.19</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.53</v>
+        <v>18.19</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="EC9" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="10">
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
@@ -4609,49 +4609,49 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="H10" t="n">
-        <v>82.12</v>
+        <v>86.11</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="L10" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="M10" t="n">
-        <v>36.5</v>
+        <v>36.56</v>
       </c>
       <c r="N10" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="O10" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="P10" t="n">
-        <v>10.12</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.38</v>
+        <v>10.89</v>
       </c>
       <c r="R10" t="n">
-        <v>8.380000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4663,28 +4663,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>39.88</v>
+        <v>41.56</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z10" t="n">
-        <v>11.75</v>
+        <v>12</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.119999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="AC10" t="n">
-        <v>15.62</v>
+        <v>16.89</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4768,70 +4768,70 @@
         <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.67</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.13</v>
+        <v>3.19</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM10" t="n">
         <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.13</v>
+        <v>4.19</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.53</v>
+        <v>5.44</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT10" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BU10" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY10" t="n">
-        <v>4.53</v>
+        <v>4.32</v>
       </c>
       <c r="BZ10" t="n">
-        <v>5.21</v>
+        <v>4.95</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.25</v>
+        <v>4.21</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.45</v>
+        <v>4.39</v>
       </c>
       <c r="CC10" t="n">
         <v>5.46</v>
@@ -4843,19 +4843,19 @@
         <v>1.28</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CK10" t="n">
         <v>1.53</v>
@@ -4864,49 +4864,49 @@
         <v>2</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO10" t="n">
         <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY10" t="n">
         <v>1.93</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DB10" t="n">
         <v>1.33</v>
@@ -4915,7 +4915,7 @@
         <v>1.76</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
@@ -4924,40 +4924,40 @@
         <v>1</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="DH10" t="n">
-        <v>83.06</v>
+        <v>85.25</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.93</v>
+        <v>4.94</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.4</v>
+        <v>37.38</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO10" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.73</v>
+        <v>10.63</v>
       </c>
       <c r="DQ10" t="n">
-        <v>10.8</v>
+        <v>10.56</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.869999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4969,28 +4969,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>41.8</v>
+        <v>42.63</v>
       </c>
       <c r="DW10" t="n">
         <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.13</v>
+        <v>11.31</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.6</v>
+        <v>7.62</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.53</v>
+        <v>3.69</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.8</v>
+        <v>17.44</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="11">
@@ -5403,13 +5403,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>0.29</v>
@@ -5493,139 +5493,139 @@
         <v>1.29</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AI12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>38.25</v>
+        <v>38.56</v>
       </c>
       <c r="AO12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>11.44</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BM12" t="n">
         <v>0.88</v>
       </c>
-      <c r="AP12" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>46.12</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0.87</v>
-      </c>
       <c r="BN12" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BV12" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW12" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX12" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BY12" t="n">
         <v>2.32</v>
@@ -5634,28 +5634,28 @@
         <v>2.47</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.25</v>
+        <v>4.04</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.26</v>
+        <v>4.07</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CI12" t="n">
         <v>2.34</v>
@@ -5664,106 +5664,106 @@
         <v>1.58</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CO12" t="n">
         <v>1.18</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="DB12" t="n">
         <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DH12" t="n">
-        <v>92.53</v>
+        <v>92.81</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM12" t="n">
-        <v>39.47</v>
+        <v>39.57</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.93</v>
+        <v>8.82</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.4</v>
+        <v>11.25</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.4</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DS12" t="n">
         <v>0.06</v>
@@ -5775,28 +5775,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>48.13</v>
+        <v>47.94</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.54</v>
+        <v>13.06</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.06</v>
+        <v>8.31</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.47</v>
+        <v>4.75</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.93</v>
+        <v>18.94</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="13">
@@ -5806,13 +5806,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5899,136 +5899,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AI13" t="n">
-        <v>91.29000000000001</v>
+        <v>94</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.43</v>
+        <v>3</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.29</v>
+        <v>3.88</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>48.57</v>
+        <v>45.75</v>
       </c>
       <c r="AO13" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP13" t="n">
         <v>1</v>
       </c>
-      <c r="AP13" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AQ13" t="n">
-        <v>11.86</v>
+        <v>11.38</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.71</v>
+        <v>10.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.29</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>41.29</v>
+        <v>41.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.859999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.57</v>
+        <v>6.12</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.29</v>
+        <v>2.75</v>
       </c>
       <c r="BD13" t="n">
-        <v>21.57</v>
+        <v>22</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BF13" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.67</v>
+        <v>5.44</v>
       </c>
       <c r="BR13" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS13" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT13" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU13" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BV13" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX13" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
         <v>2.38</v>
@@ -6037,91 +6037,91 @@
         <v>2.49</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.1</v>
+        <v>4.03</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.23</v>
+        <v>4.17</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.96</v>
+        <v>5.71</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CK13" t="n">
         <v>1.46</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="DA13" t="n">
         <v>1.97</v>
       </c>
-      <c r="CO13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CP13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CQ13" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="CU13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CV13" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="CW13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CX13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CY13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CZ13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="DA13" t="n">
-        <v>1.99</v>
-      </c>
       <c r="DB13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="DD13" t="n">
         <v>2.65</v>
@@ -6130,76 +6130,76 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.47</v>
+        <v>3.32</v>
       </c>
       <c r="DH13" t="n">
-        <v>107.73</v>
+        <v>108.06</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.07</v>
+        <v>4.81</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM13" t="n">
-        <v>53.2</v>
+        <v>51.5</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.14</v>
+        <v>11.88</v>
       </c>
       <c r="DQ13" t="n">
-        <v>10.46</v>
+        <v>10.38</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.93</v>
+        <v>7.31</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>45.8</v>
+        <v>45.62</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.8</v>
+        <v>10.69</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.34</v>
+        <v>8</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.47</v>
+        <v>2.68</v>
       </c>
       <c r="EA13" t="n">
-        <v>23</v>
+        <v>23.12</v>
       </c>
       <c r="EB13" t="n">
         <v>1.25</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="14">
@@ -7416,94 +7416,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F17" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="H17" t="n">
-        <v>86</v>
+        <v>91.44</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="K17" t="n">
-        <v>5.62</v>
+        <v>5.22</v>
       </c>
       <c r="L17" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>40.12</v>
+        <v>40.67</v>
       </c>
       <c r="N17" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="P17" t="n">
-        <v>15.12</v>
+        <v>14.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.88</v>
+        <v>11.44</v>
       </c>
       <c r="R17" t="n">
-        <v>6.88</v>
+        <v>6.56</v>
       </c>
       <c r="S17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>37.56</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.38</v>
       </c>
-      <c r="T17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>35.12</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>20.12</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AE17" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AF17" t="n">
         <v>0.14</v>
@@ -7587,70 +7587,70 @@
         <v>1.71</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.2</v>
+        <v>9.75</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.87</v>
+        <v>4.62</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5</v>
+        <v>4.81</v>
       </c>
       <c r="BR17" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS17" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT17" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BV17" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW17" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX17" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="BZ17" t="n">
-        <v>4</v>
+        <v>3.79</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="CC17" t="n">
         <v>4.32</v>
@@ -7659,22 +7659,22 @@
         <v>4.34</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CK17" t="n">
         <v>1.48</v>
@@ -7683,100 +7683,100 @@
         <v>1.88</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.99</v>
+        <v>3.06</v>
       </c>
       <c r="CR17" t="n">
         <v>1.4</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="DD17" t="n">
         <v>3.05</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="DH17" t="n">
-        <v>86.27</v>
+        <v>89.31</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.4</v>
+        <v>5.18</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM17" t="n">
-        <v>40.26</v>
+        <v>40.56</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.47</v>
+        <v>2.37</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.4</v>
+        <v>13.12</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.14</v>
+        <v>10.94</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.87</v>
+        <v>7.63</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7788,28 +7788,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>36.13</v>
+        <v>37.44</v>
       </c>
       <c r="DW17" t="n">
         <v>0.06</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.2</v>
+        <v>12.44</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.529999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.66</v>
+        <v>19.87</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="18">

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0.25</v>
@@ -1469,139 +1469,139 @@
         <v>2.62</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>97.56999999999999</v>
+        <v>101.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK2" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>34.29</v>
+        <v>36.12</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.71</v>
+        <v>13.12</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.29</v>
+        <v>13.62</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.289999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>43.71</v>
+        <v>44.25</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.14</v>
+        <v>12.75</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.289999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="BD2" t="n">
-        <v>16.43</v>
+        <v>16.75</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="BK2" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.73</v>
+        <v>4.62</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.47</v>
+        <v>4.25</v>
       </c>
       <c r="BR2" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS2" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT2" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BV2" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX2" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
         <v>3.66</v>
@@ -1610,31 +1610,31 @@
         <v>4.06</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.98</v>
+        <v>3.93</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.05</v>
+        <v>4.06</v>
       </c>
       <c r="CE2" t="n">
         <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.62</v>
@@ -1649,130 +1649,130 @@
         <v>2.46</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CO2" t="n">
         <v>1.19</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="CR2" t="n">
         <v>1.35</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CU2" t="n">
         <v>1.58</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CW2" t="n">
         <v>1.65</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CY2" t="n">
         <v>1.87</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB2" t="n">
         <v>1.28</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="DH2" t="n">
-        <v>100.33</v>
+        <v>102.12</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>39.8</v>
+        <v>40.37</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.66</v>
+        <v>12.43</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.2</v>
+        <v>12.43</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.74</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.73</v>
+        <v>45.88</v>
       </c>
       <c r="DW2" t="n">
         <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.47</v>
+        <v>12.75</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.4</v>
+        <v>8.81</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.07</v>
+        <v>3.94</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.27</v>
+        <v>19.25</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F3" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="H3" t="n">
-        <v>120.75</v>
+        <v>118.67</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="L3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M3" t="n">
-        <v>51.25</v>
+        <v>50.78</v>
       </c>
       <c r="N3" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="P3" t="n">
-        <v>8.880000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.38</v>
+        <v>10.33</v>
       </c>
       <c r="R3" t="n">
-        <v>6.25</v>
+        <v>6.11</v>
       </c>
       <c r="S3" t="n">
-        <v>0.75</v>
+        <v>1.11</v>
       </c>
       <c r="T3" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="U3" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="V3" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>62.75</v>
+        <v>62.11</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.62</v>
+        <v>16.56</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.88</v>
+        <v>11</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.75</v>
+        <v>5.56</v>
       </c>
       <c r="AC3" t="n">
-        <v>16</v>
+        <v>17.11</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AF3" t="n">
         <v>0.29</v>
@@ -1953,37 +1953,37 @@
         <v>2.71</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.53</v>
+        <v>3.62</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.2</v>
+        <v>10.06</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.53</v>
+        <v>3.62</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.87</v>
+        <v>1.06</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.47</v>
+        <v>4.38</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.73</v>
+        <v>5.69</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -1992,31 +1992,31 @@
         <v>100</v>
       </c>
       <c r="BT3" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BU3" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BW3" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BX3" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.13</v>
+        <v>4.11</v>
       </c>
       <c r="CC3" t="n">
         <v>3.27</v>
@@ -2028,16 +2028,16 @@
         <v>1.26</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.57</v>
+        <v>3.59</v>
       </c>
       <c r="CH3" t="n">
         <v>1.63</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.57</v>
@@ -2049,31 +2049,31 @@
         <v>1.85</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO3" t="n">
         <v>1.16</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CR3" t="n">
         <v>1.34</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CT3" t="n">
         <v>3.3</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CV3" t="n">
         <v>2.52</v>
@@ -2082,16 +2082,16 @@
         <v>1.59</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB3" t="n">
         <v>1.27</v>
@@ -2103,79 +2103,79 @@
         <v>2.49</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.27</v>
+        <v>3.19</v>
       </c>
       <c r="DH3" t="n">
-        <v>109.4</v>
+        <v>108.94</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DM3" t="n">
-        <v>47.33</v>
+        <v>47.32</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="DO3" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DP3" t="n">
-        <v>8.74</v>
+        <v>9</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.34</v>
+        <v>11.25</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.6</v>
+        <v>7.44</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>59.53</v>
+        <v>59.38</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.46</v>
+        <v>14.56</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.4</v>
+        <v>9.56</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="EA3" t="n">
-        <v>15.6</v>
+        <v>16.25</v>
       </c>
       <c r="EB3" t="n">
         <v>1.62</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="F4" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="G4" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="H4" t="n">
-        <v>137.88</v>
+        <v>136</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="K4" t="n">
-        <v>6.38</v>
+        <v>6.33</v>
       </c>
       <c r="L4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M4" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="P4" t="n">
-        <v>9.619999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.880000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="R4" t="n">
-        <v>5.5</v>
+        <v>5.56</v>
       </c>
       <c r="S4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="T4" t="n">
-        <v>3.88</v>
+        <v>4.33</v>
       </c>
       <c r="U4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>68.75</v>
+        <v>68.67</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>20.62</v>
+        <v>20.11</v>
       </c>
       <c r="AA4" t="n">
-        <v>12</v>
+        <v>11.33</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.619999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>21</v>
+        <v>20.89</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AF4" t="n">
         <v>0.14</v>
@@ -2356,37 +2356,37 @@
         <v>2.71</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.4</v>
+        <v>4.69</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.4</v>
+        <v>9.31</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.4</v>
+        <v>4.69</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.33</v>
+        <v>2.56</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.6</v>
+        <v>4.44</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.8</v>
+        <v>4.88</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2398,28 +2398,28 @@
         <v>100</v>
       </c>
       <c r="BU4" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BV4" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BW4" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BX4" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BZ4" t="n">
         <v>1.18</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.65</v>
+        <v>7.7</v>
       </c>
       <c r="CB4" t="n">
-        <v>8.41</v>
+        <v>8.57</v>
       </c>
       <c r="CC4" t="n">
         <v>1.31</v>
@@ -2431,31 +2431,31 @@
         <v>1.15</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CG4" t="n">
-        <v>4.9</v>
+        <v>4.93</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CK4" t="n">
         <v>1.52</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="CO4" t="n">
         <v>1.05</v>
@@ -2464,18 +2464,18 @@
         <v>1.28</v>
       </c>
       <c r="CQ4" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CR4" t="inlineStr"/>
       <c r="CS4" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CW4" t="n">
         <v>1.76</v>
@@ -2484,13 +2484,13 @@
         <v>1.52</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.48</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="DB4" t="inlineStr"/>
       <c r="DC4" t="n">
@@ -2500,52 +2500,52 @@
         <v>1.76</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="DG4" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="DH4" t="n">
-        <v>136.27</v>
+        <v>135.31</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.8</v>
+        <v>5.81</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DM4" t="n">
-        <v>69.40000000000001</v>
+        <v>68.81</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.73</v>
+        <v>0.68</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.470000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.47</v>
+        <v>5.5</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2557,22 +2557,22 @@
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>19.73</v>
+        <v>19.5</v>
       </c>
       <c r="DY4" t="n">
-        <v>11.13</v>
+        <v>10.81</v>
       </c>
       <c r="DZ4" t="n">
-        <v>8.6</v>
+        <v>8.69</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.4</v>
+        <v>20.37</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="5">
@@ -2985,94 +2985,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F6" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="H6" t="n">
-        <v>90.38</v>
+        <v>90.44</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="K6" t="n">
-        <v>4.75</v>
+        <v>4.44</v>
       </c>
       <c r="L6" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="M6" t="n">
-        <v>41.25</v>
+        <v>39.56</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O6" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="P6" t="n">
-        <v>10.38</v>
+        <v>11</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.75</v>
+        <v>8.67</v>
       </c>
       <c r="R6" t="n">
-        <v>7.62</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="T6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>45.89</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>17.78</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>45.12</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>18.38</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.12</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3156,70 +3156,70 @@
         <v>1.57</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.33</v>
+        <v>9.94</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.73</v>
+        <v>5.44</v>
       </c>
       <c r="BR6" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BT6" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU6" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BV6" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX6" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.42</v>
+        <v>3.26</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="CC6" t="n">
         <v>3.85</v>
@@ -3228,157 +3228,157 @@
         <v>4.12</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CK6" t="n">
         <v>1.41</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CO6" t="n">
         <v>1.15</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="CR6" t="n">
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.48</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="DE6" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.8</v>
+        <v>88.94</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.93</v>
+        <v>4.75</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.2</v>
+        <v>37.44</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.87</v>
+        <v>11.19</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.53</v>
+        <v>10.38</v>
       </c>
       <c r="DR6" t="n">
-        <v>7</v>
+        <v>7.31</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.26</v>
+        <v>46.62</v>
       </c>
       <c r="DW6" t="n">
         <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.6</v>
+        <v>11.63</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.34</v>
+        <v>7.19</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.27</v>
+        <v>4.44</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.67</v>
+        <v>17.38</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="7">
@@ -4663,7 +4663,7 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>41.56</v>
+        <v>41.67</v>
       </c>
       <c r="Y10" t="n">
         <v>0.11</v>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>42.63</v>
+        <v>42.69</v>
       </c>
       <c r="DW10" t="n">
         <v>0.06</v>
@@ -5550,7 +5550,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>46</v>
+        <v>45.89</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -5775,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.94</v>
+        <v>47.88</v>
       </c>
       <c r="DW12" t="n">
         <v>0.06</v>
@@ -7015,13 +7015,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7105,139 +7105,139 @@
         <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="AI16" t="n">
-        <v>133.5</v>
+        <v>131</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>71.67</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>15.11</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="BE16" t="n">
         <v>1.88</v>
       </c>
-      <c r="AL16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN16" t="n">
+      <c r="BF16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="BT16" t="n">
         <v>75</v>
       </c>
-      <c r="AO16" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>60.62</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>15.75</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>18.25</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>10</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>93.33</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>80</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>73.33</v>
-      </c>
       <c r="BU16" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BV16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX16" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY16" t="n">
         <v>2.19</v>
@@ -7246,16 +7246,16 @@
         <v>2.19</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="CE16" t="n">
         <v>1.25</v>
@@ -7264,28 +7264,28 @@
         <v>2.2</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="CH16" t="n">
         <v>1.67</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.52</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CL16" t="n">
         <v>1.82</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CO16" t="n">
         <v>1.13</v>
@@ -7300,7 +7300,7 @@
         <v>1.33</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CT16" t="n">
         <v>3.35</v>
@@ -7318,92 +7318,92 @@
         <v>1.54</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.43</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DB16" t="inlineStr"/>
       <c r="DC16" t="n">
         <v>1.58</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DE16" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="DG16" t="n">
         <v>3</v>
       </c>
       <c r="DH16" t="n">
-        <v>119.53</v>
+        <v>119</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.66</v>
+        <v>5.5</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DM16" t="n">
-        <v>58.53</v>
+        <v>57.69</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.2</v>
+        <v>10.25</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.47</v>
+        <v>12.44</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.4</v>
+        <v>5.44</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>57.53</v>
+        <v>56.63</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.54</v>
+        <v>15.19</v>
       </c>
       <c r="DY16" t="n">
-        <v>10.06</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.47</v>
+        <v>5.57</v>
       </c>
       <c r="EA16" t="n">
         <v>19</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="EC16" t="n">
         <v>1.94</v>
@@ -7488,10 +7488,10 @@
         <v>0.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.78</v>
+        <v>12.89</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.890000000000001</v>
+        <v>9</v>
       </c>
       <c r="AB17" t="n">
         <v>3.89</v>
@@ -7794,10 +7794,10 @@
         <v>0.06</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.44</v>
+        <v>12.5</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.69</v>
+        <v>8.75</v>
       </c>
       <c r="DZ17" t="n">
         <v>3.75</v>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
         <v>0.25</v>
@@ -8312,139 +8312,139 @@
         <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG19" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AI19" t="n">
-        <v>81</v>
+        <v>78.75</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AL19" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AM19" t="n">
         <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>32.86</v>
+        <v>32</v>
       </c>
       <c r="AO19" t="n">
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.14</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.140000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AS19" t="n">
-        <v>10.57</v>
+        <v>10.38</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.29</v>
+        <v>2.12</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>45</v>
+        <v>43.38</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.29</v>
+        <v>10</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.86</v>
+        <v>6.62</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="BD19" t="n">
-        <v>16.43</v>
+        <v>15.88</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BF19" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.4</v>
+        <v>11.19</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.8</v>
+        <v>1.12</v>
       </c>
       <c r="BM19" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.8</v>
+        <v>4.62</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.53</v>
+        <v>5.56</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT19" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BU19" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BV19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BW19" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BX19" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BY19" t="n">
         <v>2.55</v>
@@ -8453,85 +8453,85 @@
         <v>2.59</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.66</v>
+        <v>3.96</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.75</v>
+        <v>4.21</v>
       </c>
       <c r="CC19" t="n">
-        <v>3.36</v>
+        <v>4.81</v>
       </c>
       <c r="CD19" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="CG19" t="n">
         <v>3.55</v>
       </c>
-      <c r="CE19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CF19" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="CG19" t="n">
-        <v>3.43</v>
-      </c>
       <c r="CH19" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CK19" t="n">
         <v>1.42</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="CR19" t="n">
         <v>1.35</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="CT19" t="n">
         <v>3.24</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX19" t="n">
         <v>1.5</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.5</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DB19" t="n">
         <v>1.28</v>
@@ -8543,79 +8543,79 @@
         <v>2.69</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DH19" t="n">
-        <v>88.8</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.53</v>
+        <v>3.44</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
       </c>
       <c r="DM19" t="n">
-        <v>41.07</v>
+        <v>40.12</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.4</v>
+        <v>11.06</v>
       </c>
       <c r="DQ19" t="n">
-        <v>9.869999999999999</v>
+        <v>9.69</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.4</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.86</v>
+        <v>45</v>
       </c>
       <c r="DW19" t="n">
         <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>12</v>
+        <v>11.75</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.67</v>
+        <v>7.5</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.27</v>
+        <v>16.94</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0.33</v>
@@ -2275,115 +2275,115 @@
         <v>1.56</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>134.43</v>
+        <v>133.25</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.14</v>
+        <v>-0.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.14</v>
+        <v>5.25</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN4" t="n">
-        <v>69.86</v>
+        <v>69</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.289999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>9.57</v>
+        <v>8.75</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.43</v>
+        <v>5.25</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>67.14</v>
+        <v>67.75</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>18.71</v>
+        <v>18.75</v>
       </c>
       <c r="BB4" t="n">
-        <v>10.14</v>
+        <v>10.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>8.57</v>
+        <v>8.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.71</v>
+        <v>19.88</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.69</v>
+        <v>4.65</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.31</v>
+        <v>9.35</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.69</v>
+        <v>4.65</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BK4" t="n">
         <v>0.88</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BO4" t="n">
         <v>2.12</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.44</v>
+        <v>4.47</v>
       </c>
       <c r="BQ4" t="n">
         <v>4.88</v>
@@ -2398,16 +2398,16 @@
         <v>100</v>
       </c>
       <c r="BU4" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BV4" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BW4" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY4" t="n">
         <v>1.16</v>
@@ -2416,16 +2416,16 @@
         <v>1.18</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.7</v>
+        <v>7.66</v>
       </c>
       <c r="CB4" t="n">
-        <v>8.57</v>
+        <v>8.5</v>
       </c>
       <c r="CC4" t="n">
         <v>1.31</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="CE4" t="n">
         <v>1.15</v>
@@ -2434,19 +2434,19 @@
         <v>1.79</v>
       </c>
       <c r="CG4" t="n">
-        <v>4.93</v>
+        <v>4.92</v>
       </c>
       <c r="CH4" t="n">
         <v>1.98</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL4" t="n">
         <v>1.88</v>
@@ -2484,10 +2484,10 @@
         <v>1.52</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DA4" t="n">
         <v>1.99</v>
@@ -2500,79 +2500,79 @@
         <v>1.76</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="DH4" t="n">
-        <v>135.31</v>
+        <v>134.71</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.81</v>
+        <v>5.82</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM4" t="n">
-        <v>68.81</v>
+        <v>68.47</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.31</v>
+        <v>9</v>
       </c>
       <c r="DQ4" t="n">
-        <v>9</v>
+        <v>8.65</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.5</v>
+        <v>5.41</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>68</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>19.5</v>
+        <v>19.47</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.81</v>
+        <v>10.82</v>
       </c>
       <c r="DZ4" t="n">
-        <v>8.69</v>
+        <v>8.65</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.37</v>
+        <v>20.41</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="5">
@@ -2582,94 +2582,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F5" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="G5" t="n">
-        <v>5.14</v>
+        <v>4.75</v>
       </c>
       <c r="H5" t="n">
-        <v>117.57</v>
+        <v>117.75</v>
       </c>
       <c r="I5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="K5" t="n">
-        <v>7.43</v>
+        <v>6.88</v>
       </c>
       <c r="L5" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M5" t="n">
-        <v>60.29</v>
+        <v>57.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="O5" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="P5" t="n">
-        <v>11.57</v>
+        <v>11.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.859999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>7.14</v>
+        <v>6.88</v>
       </c>
       <c r="S5" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>55.29</v>
+        <v>54.12</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.86</v>
+        <v>14.38</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.710000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.14</v>
+        <v>5.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>17.43</v>
+        <v>17.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AF5" t="n">
         <v>0.11</v>
@@ -2753,70 +2753,70 @@
         <v>2.33</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.94</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.56</v>
+        <v>3.47</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.38</v>
+        <v>6.24</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU5" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV5" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW5" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.22</v>
+        <v>4.28</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="CC5" t="n">
         <v>2.52</v>
@@ -2837,37 +2837,37 @@
         <v>1.64</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO5" t="n">
         <v>1.14</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CR5" t="n">
         <v>1.34</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CT5" t="n">
         <v>3.34</v>
@@ -2876,10 +2876,10 @@
         <v>1.69</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CX5" t="n">
         <v>1.57</v>
@@ -2897,22 +2897,22 @@
         <v>1.26</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF5" t="n">
         <v>1.12</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="DH5" t="n">
-        <v>111.5</v>
+        <v>111.94</v>
       </c>
       <c r="DI5" t="n">
         <v>0.06</v>
@@ -2921,28 +2921,28 @@
         <v>2</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.19</v>
+        <v>5.06</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM5" t="n">
-        <v>54.88</v>
+        <v>53.88</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.37</v>
+        <v>11.53</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.62</v>
+        <v>10.47</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.62</v>
+        <v>6.53</v>
       </c>
       <c r="DS5" t="n">
         <v>0.06</v>
@@ -2954,28 +2954,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>53.06</v>
+        <v>52.64</v>
       </c>
       <c r="DW5" t="n">
         <v>0.12</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.13</v>
+        <v>12.47</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.62</v>
+        <v>7.77</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.82</v>
+        <v>19.71</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="6">
@@ -2985,13 +2985,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0.11</v>
@@ -3078,136 +3078,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AI6" t="n">
-        <v>87</v>
+        <v>83.38</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.14</v>
+        <v>4.75</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>34.71</v>
+        <v>34.38</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.43</v>
+        <v>11.25</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.57</v>
+        <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.29</v>
+        <v>6.62</v>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>47.57</v>
+        <v>45.88</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.43</v>
+        <v>11.75</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.29</v>
+        <v>6.62</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.14</v>
+        <v>5.12</v>
       </c>
       <c r="BD6" t="n">
-        <v>16.86</v>
+        <v>18</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.94</v>
+        <v>9.82</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.44</v>
+        <v>5.18</v>
       </c>
       <c r="BR6" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT6" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU6" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BV6" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BW6" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BX6" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BY6" t="n">
         <v>3.26</v>
@@ -3216,25 +3216,25 @@
         <v>3.24</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.12</v>
+        <v>4.09</v>
       </c>
       <c r="CE6" t="n">
         <v>1.26</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CH6" t="n">
         <v>1.62</v>
@@ -3252,10 +3252,10 @@
         <v>1.79</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CO6" t="n">
         <v>1.15</v>
@@ -3270,7 +3270,7 @@
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CT6" t="n">
         <v>3.25</v>
@@ -3279,7 +3279,7 @@
         <v>1.66</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CW6" t="n">
         <v>1.58</v>
@@ -3288,97 +3288,97 @@
         <v>1.51</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DB6" t="n">
         <v>1.29</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="DE6" t="n">
         <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="DH6" t="n">
-        <v>88.94</v>
+        <v>87.12</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.75</v>
+        <v>4.59</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DM6" t="n">
-        <v>37.44</v>
+        <v>37.12</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.19</v>
+        <v>11.12</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.38</v>
+        <v>10.71</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.31</v>
+        <v>7.41</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.62</v>
+        <v>45.89</v>
       </c>
       <c r="DW6" t="n">
         <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.63</v>
+        <v>11.35</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.19</v>
+        <v>6.88</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.44</v>
+        <v>4.47</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.38</v>
+        <v>17.88</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="7">
@@ -3388,13 +3388,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3478,52 +3478,52 @@
         <v>1.38</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AI7" t="n">
-        <v>110.38</v>
+        <v>107.33</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.25</v>
+        <v>-0.11</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.5</v>
+        <v>4.22</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AN7" t="n">
-        <v>49.25</v>
+        <v>45.89</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.88</v>
+        <v>11.33</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.25</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.5</v>
+        <v>7.44</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3535,58 +3535,58 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>55.75</v>
+        <v>54.22</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.88</v>
+        <v>11.89</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.75</v>
+        <v>7.67</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.12</v>
+        <v>4.22</v>
       </c>
       <c r="BD7" t="n">
-        <v>21.12</v>
+        <v>20.67</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.12</v>
+        <v>4.18</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.94</v>
+        <v>8.18</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.12</v>
+        <v>4.18</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="BK7" t="n">
         <v>1.06</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.88</v>
+        <v>4.12</v>
       </c>
       <c r="BQ7" t="n">
         <v>4</v>
@@ -3595,22 +3595,22 @@
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU7" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BV7" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BW7" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BX7" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BY7" t="n">
         <v>2.39</v>
@@ -3619,22 +3619,22 @@
         <v>2.75</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.84</v>
+        <v>3.06</v>
       </c>
       <c r="CE7" t="n">
         <v>1.25</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CG7" t="n">
         <v>3.71</v>
@@ -3643,31 +3643,31 @@
         <v>1.65</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CR7" t="n">
         <v>1.35</v>
@@ -3691,97 +3691,97 @@
         <v>1.63</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.27</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="DB7" t="n">
         <v>1.27</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DE7" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="DH7" t="n">
-        <v>104</v>
+        <v>102.76</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.69</v>
+        <v>4.53</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM7" t="n">
-        <v>48.62</v>
+        <v>46.88</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.69</v>
+        <v>10.94</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.18</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.19</v>
+        <v>7.18</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.32</v>
+        <v>53.59</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.5</v>
+        <v>12.47</v>
       </c>
       <c r="DY7" t="n">
-        <v>8</v>
+        <v>7.94</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.94</v>
+        <v>20.71</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="8">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0.25</v>
@@ -3881,139 +3881,139 @@
         <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.62</v>
+        <v>0.89</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AI8" t="n">
-        <v>86</v>
+        <v>85.78</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AN8" t="n">
-        <v>41.5</v>
+        <v>40.44</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.619999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.88</v>
+        <v>12.78</v>
       </c>
       <c r="AS8" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>45.44</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BH8" t="n">
         <v>7.88</v>
       </c>
-      <c r="AT8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>46.62</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>8.619999999999999</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>18.62</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>7.81</v>
-      </c>
       <c r="BI8" t="n">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN8" t="n">
         <v>1.94</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="BP8" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="BR8" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU8" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV8" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW8" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX8" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY8" t="n">
         <v>2.2</v>
@@ -4028,16 +4028,16 @@
         <v>3.8</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.03</v>
+        <v>4.07</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="CE8" t="n">
         <v>1.33</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CG8" t="n">
         <v>3.25</v>
@@ -4052,10 +4052,10 @@
         <v>1.69</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CM8" t="n">
         <v>2.19</v>
@@ -4067,22 +4067,22 @@
         <v>1.24</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CT8" t="n">
         <v>3.18</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CV8" t="n">
         <v>2.2</v>
@@ -4094,10 +4094,10 @@
         <v>1.68</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DA8" t="n">
         <v>1.73</v>
@@ -4106,85 +4106,85 @@
         <v>1.3</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="DE8" t="n">
         <v>0.18</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="DH8" t="n">
-        <v>97.88</v>
+        <v>97.06</v>
       </c>
       <c r="DI8" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.56</v>
+        <v>4.41</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DM8" t="n">
-        <v>45.5</v>
+        <v>44.7</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.18</v>
+        <v>9.59</v>
       </c>
       <c r="DQ8" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>50.64</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DX8" t="n">
         <v>12.88</v>
       </c>
-      <c r="DR8" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="DS8" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="DT8" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="DU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV8" t="n">
-        <v>51.56</v>
-      </c>
-      <c r="DW8" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DX8" t="n">
-        <v>13.5</v>
-      </c>
       <c r="DY8" t="n">
-        <v>9.119999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.38</v>
+        <v>4.18</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.94</v>
+        <v>20.06</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="9">
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4690,13 +4690,13 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="AI10" t="n">
-        <v>84.14</v>
+        <v>87.12</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -4705,34 +4705,34 @@
         <v>2</v>
       </c>
       <c r="AL10" t="n">
-        <v>5.43</v>
+        <v>4.88</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AN10" t="n">
-        <v>38.43</v>
+        <v>38.88</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.43</v>
+        <v>11.25</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.14</v>
+        <v>10.25</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.43</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4744,82 +4744,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>44</v>
+        <v>45.75</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.43</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.14</v>
+        <v>20.75</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="BF10" t="n">
         <v>2</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.619999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="BJ10" t="n">
         <v>0.88</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM10" t="n">
         <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.19</v>
+        <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.44</v>
+        <v>5.35</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT10" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BU10" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV10" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW10" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX10" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY10" t="n">
         <v>4.32</v>
@@ -4828,31 +4828,31 @@
         <v>4.95</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.21</v>
+        <v>4.17</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.39</v>
+        <v>4.36</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.46</v>
+        <v>5.4</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.97</v>
+        <v>5.83</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="CH10" t="n">
         <v>1.58</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.67</v>
@@ -4861,40 +4861,40 @@
         <v>1.53</v>
       </c>
       <c r="CL10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CM10" t="n">
         <v>2.41</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP10" t="n">
         <v>1.67</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CR10" t="n">
         <v>1.38</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CX10" t="n">
         <v>1.58</v>
@@ -4909,55 +4909,55 @@
         <v>1.9</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="DH10" t="n">
-        <v>85.25</v>
+        <v>86.59</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.94</v>
+        <v>4.71</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.38</v>
+        <v>37.65</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.63</v>
+        <v>10.59</v>
       </c>
       <c r="DQ10" t="n">
-        <v>10.56</v>
+        <v>10.59</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.06</v>
+        <v>8.83</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4969,28 +4969,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>42.69</v>
+        <v>43.59</v>
       </c>
       <c r="DW10" t="n">
         <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.31</v>
+        <v>11.53</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.62</v>
+        <v>7.82</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.44</v>
+        <v>18.71</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="11">
@@ -5000,94 +5000,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F11" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="G11" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="H11" t="n">
-        <v>113.43</v>
+        <v>117.25</v>
       </c>
       <c r="I11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="J11" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="K11" t="n">
         <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="M11" t="n">
-        <v>53.43</v>
+        <v>55</v>
       </c>
       <c r="N11" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="O11" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="P11" t="n">
-        <v>15.14</v>
+        <v>15.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.859999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="S11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>55</v>
+        <v>56.38</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.289999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.71</v>
+        <v>5.38</v>
       </c>
       <c r="AC11" t="n">
-        <v>22.71</v>
+        <v>22.38</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
         <v>0.12</v>
@@ -5171,67 +5171,67 @@
         <v>2.12</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.27</v>
+        <v>3.44</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.47</v>
+        <v>10.31</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.27</v>
+        <v>3.44</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.87</v>
+        <v>1.06</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.87</v>
+        <v>5.56</v>
       </c>
       <c r="BR11" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS11" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BU11" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BV11" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>66.67</v>
+        <v>68.75</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.89</v>
+        <v>2.77</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="CB11" t="n">
         <v>4.01</v>
@@ -5243,43 +5243,43 @@
         <v>3.34</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CH11" t="n">
         <v>1.68</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CK11" t="n">
         <v>1.4</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CO11" t="n">
         <v>1.14</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
@@ -5297,19 +5297,19 @@
         <v>2.61</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CX11" t="n">
         <v>1.5</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.52</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="DB11" t="n">
         <v>1.26</v>
@@ -5318,82 +5318,82 @@
         <v>1.61</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="DH11" t="n">
-        <v>109.2</v>
+        <v>111.38</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.07</v>
+        <v>5.12</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM11" t="n">
-        <v>48.53</v>
+        <v>49.62</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.86</v>
+        <v>14.93</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.4</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.2</v>
+        <v>5.94</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.87</v>
+        <v>54.63</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.67</v>
+        <v>13</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.130000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.53</v>
+        <v>4.88</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.66</v>
+        <v>21.56</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="12">
@@ -5403,61 +5403,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F12" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="H12" t="n">
-        <v>97.70999999999999</v>
+        <v>96.12</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.14</v>
+        <v>-0.25</v>
       </c>
       <c r="J12" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="K12" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>40.86</v>
+        <v>40.88</v>
       </c>
       <c r="N12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="O12" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="P12" t="n">
-        <v>8.859999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.14</v>
+        <v>11.12</v>
       </c>
       <c r="R12" t="n">
-        <v>7.29</v>
+        <v>7.88</v>
       </c>
       <c r="S12" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="T12" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5469,28 +5469,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>50.43</v>
+        <v>47.62</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.29</v>
+        <v>13.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.57</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.71</v>
+        <v>5.38</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.43</v>
+        <v>18.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AF12" t="n">
         <v>0.11</v>
@@ -5574,34 +5574,34 @@
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN12" t="n">
         <v>1.94</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="BQ12" t="n">
         <v>5.12</v>
@@ -5610,34 +5610,34 @@
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU12" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BV12" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW12" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX12" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.32</v>
+        <v>3.13</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.47</v>
+        <v>3.64</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.76</v>
+        <v>3.95</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.82</v>
+        <v>4.02</v>
       </c>
       <c r="CC12" t="n">
         <v>4.04</v>
@@ -5646,46 +5646,46 @@
         <v>4.07</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.58</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL12" t="n">
         <v>1.69</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS12" t="n">
         <v>2.4</v>
@@ -5697,7 +5697,7 @@
         <v>1.61</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CW12" t="n">
         <v>1.59</v>
@@ -5706,13 +5706,13 @@
         <v>1.55</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="DB12" t="n">
         <v>1.29</v>
@@ -5721,49 +5721,49 @@
         <v>1.68</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="DH12" t="n">
-        <v>92.81</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="DI12" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="DK12" t="n">
         <v>3.88</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DM12" t="n">
-        <v>39.57</v>
+        <v>39.65</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.82</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DQ12" t="n">
-        <v>11.25</v>
+        <v>10.82</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.619999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="DS12" t="n">
         <v>0.06</v>
@@ -5775,28 +5775,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.88</v>
+        <v>46.7</v>
       </c>
       <c r="DW12" t="n">
         <v>0.06</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.06</v>
+        <v>12.76</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.31</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.94</v>
+        <v>18.71</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="13">
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
@@ -5818,82 +5818,82 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="G13" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="H13" t="n">
-        <v>122.12</v>
+        <v>122.33</v>
       </c>
       <c r="I13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="K13" t="n">
-        <v>5.75</v>
+        <v>5.56</v>
       </c>
       <c r="L13" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="M13" t="n">
-        <v>57.25</v>
+        <v>55.89</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="P13" t="n">
-        <v>12.38</v>
+        <v>12.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.25</v>
+        <v>10.22</v>
       </c>
       <c r="R13" t="n">
-        <v>6.62</v>
+        <v>6.78</v>
       </c>
       <c r="S13" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T13" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="U13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>49.75</v>
+        <v>48.89</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.5</v>
+        <v>12.56</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.880000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AC13" t="n">
-        <v>24.25</v>
+        <v>24.56</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5977,70 +5977,70 @@
         <v>2.62</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="BH13" t="n">
-        <v>9</v>
+        <v>8.76</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.44</v>
+        <v>5.35</v>
       </c>
       <c r="BR13" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS13" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT13" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU13" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV13" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="CC13" t="n">
         <v>5.4</v>
@@ -6055,28 +6055,28 @@
         <v>2.51</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CH13" t="n">
         <v>1.56</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL13" t="n">
         <v>1.88</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO13" t="n">
         <v>1.22</v>
@@ -6094,13 +6094,13 @@
         <v>2.54</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CW13" t="n">
         <v>1.65</v>
@@ -6118,55 +6118,55 @@
         <v>1.97</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC13" t="n">
         <v>1.77</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="DH13" t="n">
-        <v>108.06</v>
+        <v>109</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.81</v>
+        <v>4.77</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DM13" t="n">
-        <v>51.5</v>
+        <v>51.12</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.88</v>
+        <v>11.82</v>
       </c>
       <c r="DQ13" t="n">
-        <v>10.38</v>
+        <v>10.35</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.31</v>
+        <v>7.35</v>
       </c>
       <c r="DS13" t="n">
         <v>0.18</v>
@@ -6178,25 +6178,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>45.62</v>
+        <v>45.41</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.69</v>
+        <v>10.83</v>
       </c>
       <c r="DY13" t="n">
-        <v>8</v>
+        <v>7.94</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="EA13" t="n">
-        <v>23.12</v>
+        <v>23.36</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="EC13" t="n">
         <v>2.18</v>
@@ -6209,94 +6209,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F14" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="G14" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="H14" t="n">
-        <v>99.70999999999999</v>
+        <v>101.25</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="K14" t="n">
-        <v>5.71</v>
+        <v>5.88</v>
       </c>
       <c r="L14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M14" t="n">
-        <v>44</v>
+        <v>45.12</v>
       </c>
       <c r="N14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="O14" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="P14" t="n">
-        <v>8.859999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>11.14</v>
+        <v>11.75</v>
       </c>
       <c r="R14" t="n">
-        <v>6.14</v>
+        <v>5.5</v>
       </c>
       <c r="S14" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="T14" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="U14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>50</v>
+        <v>51.75</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>17.14</v>
+        <v>17.62</v>
       </c>
       <c r="AA14" t="n">
-        <v>9.57</v>
+        <v>10.12</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.57</v>
+        <v>7.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>19.29</v>
+        <v>19.62</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AF14" t="n">
         <v>0.5</v>
@@ -6380,70 +6380,70 @@
         <v>1.75</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.27</v>
+        <v>3.19</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.53</v>
+        <v>10.44</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.27</v>
+        <v>3.19</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.93</v>
+        <v>4.94</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BR14" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS14" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT14" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU14" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BV14" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW14" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BX14" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="BZ14" t="n">
         <v>1.79</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.18</v>
+        <v>4.16</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="CC14" t="n">
         <v>3.6</v>
@@ -6452,157 +6452,157 @@
         <v>3.66</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.05</v>
+        <v>4.01</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="CT14" t="n">
         <v>3.13</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="DB14" t="n">
         <v>1.32</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="DH14" t="n">
-        <v>92.87</v>
+        <v>94.06</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.86</v>
+        <v>5.94</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM14" t="n">
-        <v>43.33</v>
+        <v>43.94</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO14" t="n">
         <v>3</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.4</v>
+        <v>9.57</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.67</v>
+        <v>11</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.130000000000001</v>
+        <v>7.69</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.13</v>
+        <v>51</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>16.33</v>
+        <v>16.62</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.6</v>
+        <v>10.81</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.73</v>
+        <v>5.81</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.4</v>
+        <v>16.75</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="15">
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6702,52 +6702,52 @@
         <v>2</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AI15" t="n">
-        <v>92.88</v>
+        <v>91</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN15" t="n">
-        <v>39.75</v>
+        <v>38.67</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.5</v>
+        <v>10.33</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.619999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AS15" t="n">
-        <v>6</v>
+        <v>6.11</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6759,82 +6759,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>44.38</v>
+        <v>43.78</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.380000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="BD15" t="n">
-        <v>21.38</v>
+        <v>20.78</v>
       </c>
       <c r="BE15" t="n">
         <v>1.04</v>
       </c>
       <c r="BF15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BN15" t="n">
         <v>1.5</v>
       </c>
-      <c r="BG15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BO15" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.33</v>
+        <v>4.38</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.6</v>
+        <v>5.62</v>
       </c>
       <c r="BR15" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS15" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT15" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU15" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX15" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
         <v>2.72</v>
@@ -6843,40 +6843,40 @@
         <v>2.77</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.04</v>
+        <v>4.01</v>
       </c>
       <c r="CC15" t="n">
-        <v>6.42</v>
+        <v>6.15</v>
       </c>
       <c r="CD15" t="n">
-        <v>6.41</v>
+        <v>6.2</v>
       </c>
       <c r="CE15" t="n">
         <v>1.36</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CH15" t="n">
         <v>1.46</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.78</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CM15" t="n">
         <v>2.24</v>
@@ -6888,124 +6888,124 @@
         <v>1.26</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CR15" t="n">
         <v>1.4</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB15" t="n">
         <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="DE15" t="n">
         <v>0.06</v>
       </c>
       <c r="DF15" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="DH15" t="n">
-        <v>100.6</v>
+        <v>99.06</v>
       </c>
       <c r="DI15" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.07</v>
+        <v>5</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DM15" t="n">
-        <v>45.8</v>
+        <v>44.81</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.47</v>
+        <v>10.37</v>
       </c>
       <c r="DQ15" t="n">
         <v>10</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.14</v>
+        <v>6.19</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.47</v>
+        <v>46.94</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.54</v>
+        <v>10.44</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.13</v>
+        <v>7</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.87</v>
+        <v>21.5</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="16">
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -7027,79 +7027,79 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="G16" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="H16" t="n">
-        <v>103.57</v>
+        <v>103.12</v>
       </c>
       <c r="I16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J16" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="K16" t="n">
-        <v>4.71</v>
+        <v>5.38</v>
       </c>
       <c r="L16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M16" t="n">
-        <v>39.71</v>
+        <v>41.38</v>
       </c>
       <c r="N16" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O16" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="P16" t="n">
-        <v>9.859999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.57</v>
+        <v>12.88</v>
       </c>
       <c r="R16" t="n">
-        <v>5.29</v>
+        <v>5.25</v>
       </c>
       <c r="S16" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="T16" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="U16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>54</v>
+        <v>54.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.29</v>
+        <v>15.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>10</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.29</v>
+        <v>6</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.86</v>
+        <v>20.12</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AE16" t="n">
         <v>2</v>
@@ -7186,70 +7186,70 @@
         <v>1.89</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.880000000000001</v>
+        <v>10</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BM16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.31</v>
+        <v>4.53</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.56</v>
+        <v>5.47</v>
       </c>
       <c r="BR16" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS16" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BU16" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BV16" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BW16" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX16" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="CA16" t="n">
         <v>4.06</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="CC16" t="n">
         <v>2.72</v>
@@ -7261,7 +7261,7 @@
         <v>1.25</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CG16" t="n">
         <v>3.7</v>
@@ -7276,16 +7276,16 @@
         <v>1.52</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CO16" t="n">
         <v>1.13</v>
@@ -7294,7 +7294,7 @@
         <v>1.54</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CR16" t="n">
         <v>1.33</v>
@@ -7315,95 +7315,95 @@
         <v>1.54</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="DB16" t="inlineStr"/>
       <c r="DC16" t="n">
         <v>1.58</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DE16" t="n">
         <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="DG16" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="DH16" t="n">
-        <v>119</v>
+        <v>117.88</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ16" t="n">
         <v>2.06</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.5</v>
+        <v>5.77</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM16" t="n">
-        <v>57.69</v>
+        <v>57.42</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.25</v>
+        <v>10.12</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.44</v>
+        <v>12.59</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.44</v>
+        <v>5.41</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>56.63</v>
+        <v>56.71</v>
       </c>
       <c r="DW16" t="n">
         <v>0.06</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.19</v>
+        <v>15.47</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.619999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.57</v>
+        <v>5.88</v>
       </c>
       <c r="EA16" t="n">
-        <v>19</v>
+        <v>19.17</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="EC16" t="n">
         <v>1.94</v>
@@ -7819,13 +7819,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>0.14</v>
@@ -7912,136 +7912,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AI18" t="n">
-        <v>81.88</v>
+        <v>82.33</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN18" t="n">
-        <v>34.5</v>
+        <v>33.22</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.5</v>
+        <v>10.22</v>
       </c>
       <c r="AR18" t="n">
-        <v>10</v>
+        <v>10.44</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.380000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT18" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>46.5</v>
+        <v>47.33</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>10.12</v>
+        <v>9.67</v>
       </c>
       <c r="BB18" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BW18" t="n">
         <v>6.25</v>
       </c>
-      <c r="BC18" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>18.25</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BP18" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="BQ18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BR18" t="n">
-        <v>93.33</v>
-      </c>
-      <c r="BS18" t="n">
-        <v>80</v>
-      </c>
-      <c r="BT18" t="n">
-        <v>60</v>
-      </c>
-      <c r="BU18" t="n">
-        <v>46.67</v>
-      </c>
-      <c r="BV18" t="n">
-        <v>20</v>
-      </c>
-      <c r="BW18" t="n">
-        <v>6.67</v>
-      </c>
       <c r="BX18" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BY18" t="n">
         <v>2.48</v>
@@ -8050,16 +8050,16 @@
         <v>2.62</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.37</v>
+        <v>4.42</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.39</v>
+        <v>4.44</v>
       </c>
       <c r="CC18" t="n">
-        <v>5.6</v>
+        <v>5.87</v>
       </c>
       <c r="CD18" t="n">
-        <v>6.68</v>
+        <v>6.8</v>
       </c>
       <c r="CE18" t="n">
         <v>1.26</v>
@@ -8074,22 +8074,22 @@
         <v>1.64</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CK18" t="n">
         <v>1.48</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CO18" t="n">
         <v>1.14</v>
@@ -8098,13 +8098,13 @@
         <v>1.55</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CR18" t="n">
         <v>1.34</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CT18" t="n">
         <v>3.32</v>
@@ -8113,10 +8113,10 @@
         <v>1.72</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CX18" t="n">
         <v>1.54</v>
@@ -8140,79 +8140,79 @@
         <v>2.4</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF18" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="DH18" t="n">
-        <v>92.34</v>
+        <v>91.94</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.86</v>
+        <v>2.68</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM18" t="n">
-        <v>40.53</v>
+        <v>39.44</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.47</v>
+        <v>10.31</v>
       </c>
       <c r="DQ18" t="n">
-        <v>9.470000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.33</v>
+        <v>48.69</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.26</v>
+        <v>11.88</v>
       </c>
       <c r="DY18" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.27</v>
+        <v>4.19</v>
       </c>
       <c r="EA18" t="n">
-        <v>18.8</v>
+        <v>18.75</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="19">
@@ -8222,94 +8222,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="G19" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="H19" t="n">
-        <v>95.62</v>
+        <v>103.33</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="M19" t="n">
-        <v>48.25</v>
+        <v>48.78</v>
       </c>
       <c r="N19" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="P19" t="n">
-        <v>12.5</v>
+        <v>12.22</v>
       </c>
       <c r="Q19" t="n">
-        <v>10.5</v>
+        <v>10.22</v>
       </c>
       <c r="R19" t="n">
-        <v>8.380000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="T19" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>46.62</v>
+        <v>48.22</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.5</v>
+        <v>13.44</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.380000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="AC19" t="n">
-        <v>18</v>
+        <v>17.78</v>
       </c>
       <c r="AD19" t="n">
         <v>1.56</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AF19" t="n">
         <v>0.12</v>
@@ -8393,16 +8393,16 @@
         <v>1.88</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.19</v>
+        <v>11.18</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK19" t="n">
         <v>0.9399999999999999</v>
@@ -8411,52 +8411,52 @@
         <v>1.12</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BN19" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.56</v>
+        <v>5.59</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BU19" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BV19" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW19" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BX19" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.21</v>
+        <v>4.17</v>
       </c>
       <c r="CC19" t="n">
         <v>4.81</v>
@@ -8465,157 +8465,157 @@
         <v>5.54</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.55</v>
+        <v>3.52</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CT19" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="CU19" t="n">
         <v>1.62</v>
       </c>
-      <c r="CQ19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CS19" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="CT19" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="CU19" t="n">
-        <v>1.64</v>
-      </c>
       <c r="CV19" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF19" t="n">
         <v>1.06</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.56</v>
+        <v>1.76</v>
       </c>
       <c r="DH19" t="n">
-        <v>87.18000000000001</v>
+        <v>91.76000000000001</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.44</v>
+        <v>3.65</v>
       </c>
       <c r="DL19" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DM19" t="n">
-        <v>40.12</v>
+        <v>40.88</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.06</v>
+        <v>11</v>
       </c>
       <c r="DQ19" t="n">
-        <v>9.69</v>
+        <v>9.59</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.380000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45</v>
+        <v>45.94</v>
       </c>
       <c r="DW19" t="n">
         <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.75</v>
+        <v>11.82</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.5</v>
+        <v>7.53</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.94</v>
+        <v>16.89</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="G2" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="H2" t="n">
-        <v>102.75</v>
+        <v>103.22</v>
       </c>
       <c r="I2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J2" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>5.22</v>
       </c>
       <c r="L2" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="M2" t="n">
-        <v>44.62</v>
+        <v>43.22</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="O2" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="P2" t="n">
-        <v>11.75</v>
+        <v>11.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.25</v>
+        <v>12</v>
       </c>
       <c r="R2" t="n">
-        <v>8.25</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="T2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>47.5</v>
+        <v>47.56</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.75</v>
+        <v>12.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>21.75</v>
+        <v>21</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AF2" t="n">
         <v>0.12</v>
@@ -1550,70 +1550,70 @@
         <v>3</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.880000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.62</v>
+        <v>4.41</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="BR2" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS2" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT2" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BU2" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV2" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.66</v>
+        <v>3.55</v>
       </c>
       <c r="BZ2" t="n">
-        <v>4.06</v>
+        <v>3.91</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
       <c r="CC2" t="n">
         <v>3.93</v>
@@ -1622,124 +1622,124 @@
         <v>4.06</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.34</v>
+        <v>3.29</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DA2" t="n">
         <v>1.93</v>
       </c>
-      <c r="CM2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>1.95</v>
-      </c>
       <c r="DB2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="DD2" t="n">
         <v>2.76</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="DG2" t="n">
         <v>2.12</v>
       </c>
       <c r="DH2" t="n">
-        <v>102.12</v>
+        <v>102.41</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.25</v>
+        <v>4.18</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM2" t="n">
-        <v>40.37</v>
+        <v>39.88</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.43</v>
+        <v>12.23</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.43</v>
+        <v>12.76</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.380000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="DS2" t="n">
         <v>0.06</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.88</v>
+        <v>46</v>
       </c>
       <c r="DW2" t="n">
         <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.75</v>
+        <v>12.53</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.81</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.25</v>
+        <v>19</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="3">
@@ -2419,13 +2419,13 @@
         <v>7.66</v>
       </c>
       <c r="CB4" t="n">
-        <v>8.5</v>
+        <v>8.48</v>
       </c>
       <c r="CC4" t="n">
         <v>1.31</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CE4" t="n">
         <v>1.15</v>
@@ -2475,10 +2475,10 @@
         <v>2.16</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CX4" t="n">
         <v>1.52</v>
@@ -2490,14 +2490,14 @@
         <v>2.47</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB4" t="inlineStr"/>
       <c r="DC4" t="n">
         <v>1.36</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DE4" t="n">
         <v>0.23</v>
@@ -3219,13 +3219,13 @@
         <v>4.02</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="CC6" t="n">
         <v>3.78</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="CE6" t="n">
         <v>1.26</v>
@@ -3270,7 +3270,7 @@
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CT6" t="n">
         <v>3.25</v>
@@ -3279,7 +3279,7 @@
         <v>1.66</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CW6" t="n">
         <v>1.58</v>
@@ -3300,10 +3300,10 @@
         <v>1.29</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="DE6" t="n">
         <v>0.06</v>
@@ -3388,13 +3388,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3478,52 +3478,52 @@
         <v>1.38</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>107.33</v>
+        <v>105.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>4.22</v>
+        <v>3.9</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN7" t="n">
-        <v>45.89</v>
+        <v>45.4</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11.33</v>
+        <v>11.7</v>
       </c>
       <c r="AR7" t="n">
-        <v>9.109999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.44</v>
+        <v>7.9</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3535,82 +3535,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>54.22</v>
+        <v>52.8</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.89</v>
+        <v>11.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.67</v>
+        <v>7.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>20.67</v>
+        <v>21.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.18</v>
+        <v>4.28</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.18</v>
+        <v>8</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.18</v>
+        <v>4.28</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BK7" t="n">
         <v>1.06</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
       <c r="BO7" t="n">
         <v>1.94</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.12</v>
+        <v>4.17</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT7" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BV7" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BW7" t="n">
-        <v>29.41</v>
+        <v>33.33</v>
       </c>
       <c r="BX7" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BY7" t="n">
         <v>2.39</v>
@@ -3619,25 +3619,25 @@
         <v>2.75</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="CE7" t="n">
         <v>1.25</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CH7" t="n">
         <v>1.65</v>
@@ -3655,31 +3655,31 @@
         <v>1.92</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CR7" t="n">
         <v>1.35</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CT7" t="n">
         <v>3.34</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CV7" t="n">
         <v>2.61</v>
@@ -3688,100 +3688,100 @@
         <v>1.55</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="DB7" t="n">
         <v>1.27</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>102.76</v>
+        <v>101.89</v>
       </c>
       <c r="DI7" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.53</v>
+        <v>4.34</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM7" t="n">
-        <v>46.88</v>
+        <v>46.56</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.94</v>
+        <v>11.17</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.109999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.18</v>
+        <v>7.45</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.59</v>
+        <v>52.84</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.47</v>
+        <v>12.22</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.94</v>
+        <v>7.72</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.71</v>
+        <v>21.06</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="8">
@@ -4025,13 +4025,13 @@
         <v>3.76</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="CC8" t="n">
         <v>4.07</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="CE8" t="n">
         <v>1.33</v>
@@ -4100,7 +4100,7 @@
         <v>2.2</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB8" t="n">
         <v>1.3</v>
@@ -4109,7 +4109,7 @@
         <v>1.85</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="DE8" t="n">
         <v>0.18</v>
@@ -5234,7 +5234,7 @@
         <v>3.97</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="CC11" t="n">
         <v>3.19</v>
@@ -5297,7 +5297,7 @@
         <v>2.61</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CX11" t="n">
         <v>1.5</v>
@@ -5318,7 +5318,7 @@
         <v>1.61</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="DE11" t="n">
         <v>0.12</v>
@@ -5631,13 +5631,13 @@
         <v>3.13</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.64</v>
+        <v>3.45</v>
       </c>
       <c r="CA12" t="n">
         <v>3.95</v>
       </c>
       <c r="CB12" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="CC12" t="n">
         <v>4.04</v>
@@ -5697,13 +5697,13 @@
         <v>1.61</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY12" t="n">
         <v>1.74</v>
@@ -6437,13 +6437,13 @@
         <v>1.7</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CA14" t="n">
         <v>4.16</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.3</v>
+        <v>4.31</v>
       </c>
       <c r="CC14" t="n">
         <v>3.6</v>
@@ -6500,10 +6500,10 @@
         <v>3.13</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CW14" t="n">
         <v>1.49</v>
@@ -6527,7 +6527,7 @@
         <v>1.51</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DE14" t="n">
         <v>0.31</v>
@@ -7416,13 +7416,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>0.11</v>
@@ -7506,49 +7506,49 @@
         <v>2.89</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AI17" t="n">
-        <v>86.56999999999999</v>
+        <v>88</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.14</v>
+        <v>4.88</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN17" t="n">
-        <v>40.43</v>
+        <v>40.38</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.43</v>
+        <v>12.25</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.29</v>
+        <v>10.12</v>
       </c>
       <c r="AS17" t="n">
-        <v>9</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AU17" t="n">
         <v>1</v>
@@ -7563,82 +7563,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>37.29</v>
+        <v>39.12</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BA17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.43</v>
+        <v>9</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>19.14</v>
+        <v>20.25</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BF17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BN17" t="n">
         <v>1.71</v>
       </c>
-      <c r="BG17" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BO17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.62</v>
+        <v>4.41</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="BR17" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT17" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BU17" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV17" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW17" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX17" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY17" t="n">
         <v>3.05</v>
@@ -7647,136 +7647,136 @@
         <v>3.79</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.32</v>
+        <v>4.13</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.34</v>
+        <v>4.16</v>
       </c>
       <c r="CE17" t="n">
         <v>1.35</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="CH17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="CU17" t="n">
         <v>1.48</v>
       </c>
-      <c r="CI17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="CJ17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CK17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CL17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CM17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="CN17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="CO17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CP17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CQ17" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CS17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="CT17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="CU17" t="n">
-        <v>1.49</v>
-      </c>
       <c r="CV17" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CW17" t="n">
         <v>1.82</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="DB17" t="n">
         <v>1.34</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="DD17" t="n">
         <v>3.05</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="DH17" t="n">
-        <v>89.31</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.18</v>
+        <v>5.06</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DM17" t="n">
-        <v>40.56</v>
+        <v>40.53</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.12</v>
+        <v>13.41</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.94</v>
+        <v>10.82</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.63</v>
+        <v>7.53</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7788,28 +7788,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>37.44</v>
+        <v>38.29</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.5</v>
+        <v>12.71</v>
       </c>
       <c r="DY17" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="EA17" t="n">
-        <v>19.87</v>
+        <v>20.35</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.37</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="18">
@@ -7819,94 +7819,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F18" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="G18" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>104.29</v>
+        <v>106.88</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="K18" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M18" t="n">
-        <v>47.43</v>
+        <v>49.12</v>
       </c>
       <c r="N18" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O18" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>10.43</v>
+        <v>10.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>8.859999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>6.86</v>
+        <v>6.62</v>
       </c>
       <c r="S18" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="T18" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="U18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>50.43</v>
+        <v>51.62</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="Z18" t="n">
-        <v>14.71</v>
+        <v>14.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>10</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="AC18" t="n">
-        <v>19.43</v>
+        <v>20.62</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7990,70 +7990,70 @@
         <v>2.33</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.06</v>
+        <v>3.24</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.880000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.06</v>
+        <v>3.24</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BP18" t="n">
         <v>4.94</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.94</v>
+        <v>4.65</v>
       </c>
       <c r="BR18" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS18" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU18" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BV18" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BW18" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BX18" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="BZ18" t="n">
         <v>2.62</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.42</v>
+        <v>4.37</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.44</v>
+        <v>4.38</v>
       </c>
       <c r="CC18" t="n">
         <v>5.87</v>
@@ -8065,31 +8065,31 @@
         <v>1.26</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CH18" t="n">
         <v>1.64</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.55</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO18" t="n">
         <v>1.14</v>
@@ -8098,121 +8098,121 @@
         <v>1.55</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CR18" t="n">
         <v>1.34</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CT18" t="n">
         <v>3.32</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CV18" t="n">
         <v>2.59</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="DB18" t="n">
         <v>1.26</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="DE18" t="n">
         <v>0.06</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="DH18" t="n">
-        <v>91.94</v>
+        <v>93.88</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM18" t="n">
-        <v>39.44</v>
+        <v>40.7</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="DO18" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.31</v>
+        <v>10.17</v>
       </c>
       <c r="DQ18" t="n">
-        <v>9.75</v>
+        <v>10.05</v>
       </c>
       <c r="DR18" t="n">
-        <v>8.06</v>
+        <v>7.88</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>48.69</v>
+        <v>49.35</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.88</v>
+        <v>11.94</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.69</v>
+        <v>7.77</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="EA18" t="n">
-        <v>18.75</v>
+        <v>19.35</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F2" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="G2" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="H2" t="n">
-        <v>103.22</v>
+        <v>100.8</v>
       </c>
       <c r="I2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J2" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="K2" t="n">
-        <v>5.22</v>
+        <v>5.6</v>
       </c>
       <c r="L2" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="M2" t="n">
-        <v>43.22</v>
+        <v>42.2</v>
       </c>
       <c r="N2" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>11.44</v>
+        <v>11.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="R2" t="n">
-        <v>8.220000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="S2" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>47.56</v>
+        <v>47.3</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.33</v>
+        <v>12.4</v>
       </c>
       <c r="AA2" t="n">
         <v>8</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AD2" t="n">
         <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AF2" t="n">
         <v>0.12</v>
@@ -1550,70 +1550,70 @@
         <v>3</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.710000000000001</v>
+        <v>9.06</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.41</v>
+        <v>4.72</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.29</v>
+        <v>4.33</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS2" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT2" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU2" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BV2" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX2" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.91</v>
+        <v>3.79</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="CC2" t="n">
         <v>3.93</v>
@@ -1622,43 +1622,43 @@
         <v>4.06</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
@@ -1673,106 +1673,106 @@
         <v>1.56</v>
       </c>
       <c r="CV2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CZ2" t="n">
         <v>2.34</v>
       </c>
-      <c r="CW2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>2.37</v>
-      </c>
       <c r="DA2" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="DB2" t="n">
         <v>1.29</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.76</v>
+        <v>2.81</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DH2" t="n">
-        <v>102.41</v>
+        <v>101.11</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.18</v>
+        <v>4.44</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM2" t="n">
-        <v>39.88</v>
+        <v>39.5</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.06</v>
+        <v>2.33</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.23</v>
+        <v>12.16</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.76</v>
+        <v>12.83</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.35</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>46</v>
+        <v>45.94</v>
       </c>
       <c r="DW2" t="n">
         <v>0.06</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.53</v>
+        <v>12.56</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.529999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="EA2" t="n">
-        <v>19</v>
+        <v>19.06</v>
       </c>
       <c r="EB2" t="n">
         <v>1.37</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0.33</v>
@@ -1872,139 +1872,139 @@
         <v>2.11</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AI3" t="n">
-        <v>96.43000000000001</v>
+        <v>98.88</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN3" t="n">
-        <v>42.86</v>
+        <v>44.25</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AP3" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.57</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.43</v>
+        <v>13</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.140000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>55.86</v>
+        <v>56.62</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.71</v>
+        <v>7.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="BD3" t="n">
-        <v>15.14</v>
+        <v>16</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.62</v>
+        <v>3.47</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.06</v>
+        <v>9.94</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.62</v>
+        <v>3.47</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.69</v>
+        <v>5.53</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>100</v>
+        <v>94.12</v>
       </c>
       <c r="BT3" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU3" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV3" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW3" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BX3" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY3" t="n">
         <v>1.85</v>
@@ -2013,19 +2013,19 @@
         <v>1.94</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.11</v>
+        <v>4.09</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.27</v>
+        <v>3.18</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.63</v>
+        <v>3.54</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CF3" t="n">
         <v>2.28</v>
@@ -2037,22 +2037,22 @@
         <v>1.63</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CK3" t="n">
         <v>1.49</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM3" t="n">
         <v>2.49</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO3" t="n">
         <v>1.16</v>
@@ -2061,25 +2061,25 @@
         <v>1.58</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CR3" t="n">
         <v>1.34</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CT3" t="n">
         <v>3.3</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CX3" t="n">
         <v>1.56</v>
@@ -2088,7 +2088,7 @@
         <v>1.86</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA3" t="n">
         <v>1.97</v>
@@ -2103,79 +2103,79 @@
         <v>2.49</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.19</v>
+        <v>3.06</v>
       </c>
       <c r="DH3" t="n">
-        <v>108.94</v>
+        <v>109.36</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM3" t="n">
-        <v>47.32</v>
+        <v>47.71</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="DP3" t="n">
-        <v>9</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.25</v>
+        <v>11.59</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.44</v>
+        <v>7.41</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>59.38</v>
+        <v>59.53</v>
       </c>
       <c r="DW3" t="n">
         <v>0.12</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.56</v>
+        <v>14.18</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.56</v>
+        <v>9.35</v>
       </c>
       <c r="DZ3" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.25</v>
+        <v>16.59</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0.33</v>
@@ -2275,118 +2275,118 @@
         <v>1.56</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="n">
-        <v>133.25</v>
+        <v>130.11</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.25</v>
+        <v>5.67</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="AN4" t="n">
-        <v>69</v>
+        <v>66.22</v>
       </c>
       <c r="AO4" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.619999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.75</v>
+        <v>8.56</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.25</v>
+        <v>5.33</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.38</v>
+        <v>3.56</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>67.75</v>
+        <v>66.67</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>18.75</v>
+        <v>18.78</v>
       </c>
       <c r="BB4" t="n">
-        <v>10.25</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BC4" t="n">
-        <v>8.5</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.88</v>
+        <v>19.44</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.65</v>
+        <v>4.72</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.35</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.65</v>
+        <v>4.72</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.47</v>
+        <v>4.33</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.88</v>
+        <v>5.28</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2398,16 +2398,16 @@
         <v>100</v>
       </c>
       <c r="BU4" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BV4" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BW4" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BX4" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY4" t="n">
         <v>1.16</v>
@@ -2416,16 +2416,16 @@
         <v>1.18</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.66</v>
+        <v>7.52</v>
       </c>
       <c r="CB4" t="n">
-        <v>8.48</v>
+        <v>8.26</v>
       </c>
       <c r="CC4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="CE4" t="n">
         <v>1.15</v>
@@ -2434,16 +2434,16 @@
         <v>1.79</v>
       </c>
       <c r="CG4" t="n">
-        <v>4.92</v>
+        <v>4.91</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="CK4" t="n">
         <v>1.51</v>
@@ -2475,19 +2475,19 @@
         <v>2.16</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CX4" t="n">
         <v>1.52</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="DA4" t="n">
         <v>1.98</v>
@@ -2497,82 +2497,82 @@
         <v>1.36</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="DG4" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="DH4" t="n">
-        <v>134.71</v>
+        <v>133.06</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.82</v>
+        <v>6</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DM4" t="n">
-        <v>68.47</v>
+        <v>67.11</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="DP4" t="n">
-        <v>9</v>
+        <v>8.83</v>
       </c>
       <c r="DQ4" t="n">
-        <v>8.65</v>
+        <v>8.56</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.41</v>
+        <v>5.44</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>68.23999999999999</v>
+        <v>67.67</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>19.47</v>
+        <v>19.44</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.82</v>
+        <v>10.61</v>
       </c>
       <c r="DZ4" t="n">
-        <v>8.65</v>
+        <v>8.84</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.41</v>
+        <v>20.17</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="5">
@@ -2582,94 +2582,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F5" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="G5" t="n">
-        <v>4.75</v>
+        <v>4.11</v>
       </c>
       <c r="H5" t="n">
-        <v>117.75</v>
+        <v>122.22</v>
       </c>
       <c r="I5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J5" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="K5" t="n">
-        <v>6.88</v>
+        <v>6.67</v>
       </c>
       <c r="L5" t="n">
-        <v>0.62</v>
+        <v>0.44</v>
       </c>
       <c r="M5" t="n">
-        <v>57.5</v>
+        <v>57.22</v>
       </c>
       <c r="N5" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="P5" t="n">
-        <v>11.88</v>
+        <v>11.56</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.619999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="R5" t="n">
-        <v>6.88</v>
+        <v>6.67</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="U5" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="V5" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>54.12</v>
+        <v>55.11</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.38</v>
+        <v>13.89</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.880000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.5</v>
+        <v>5.56</v>
       </c>
       <c r="AC5" t="n">
-        <v>17.5</v>
+        <v>17.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AF5" t="n">
         <v>0.11</v>
@@ -2753,70 +2753,70 @@
         <v>2.33</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.710000000000001</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.47</v>
+        <v>3.22</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.24</v>
+        <v>5.83</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT5" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU5" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BV5" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BW5" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BX5" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.28</v>
+        <v>4.3</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="CC5" t="n">
         <v>2.52</v>
@@ -2828,154 +2828,154 @@
         <v>1.25</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.68</v>
+        <v>3.64</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="CR5" t="n">
         <v>1.34</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="DE5" t="n">
         <v>0.11</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.41</v>
+        <v>3.16</v>
       </c>
       <c r="DH5" t="n">
-        <v>111.94</v>
+        <v>114.5</v>
       </c>
       <c r="DI5" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DK5" t="n">
         <v>5.06</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="DM5" t="n">
-        <v>53.88</v>
+        <v>53.94</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.77</v>
+        <v>0.84</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.53</v>
+        <v>11.39</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.47</v>
+        <v>10.44</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.53</v>
+        <v>6.44</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>52.64</v>
+        <v>53.22</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.47</v>
+        <v>12.34</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.77</v>
+        <v>7.56</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.71</v>
+        <v>4.78</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.71</v>
+        <v>19.73</v>
       </c>
       <c r="EB5" t="n">
         <v>1.52</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="6">
@@ -2985,13 +2985,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0.11</v>
@@ -3081,133 +3081,133 @@
         <v>1</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AI6" t="n">
-        <v>83.38</v>
+        <v>83.33</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.75</v>
+        <v>4.78</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>34.38</v>
+        <v>34</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.25</v>
+        <v>12</v>
       </c>
       <c r="AR6" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.62</v>
+        <v>7.22</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>45.88</v>
+        <v>45.56</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.75</v>
+        <v>11.11</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.62</v>
+        <v>6.56</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.12</v>
+        <v>4.56</v>
       </c>
       <c r="BD6" t="n">
-        <v>18</v>
+        <v>17.56</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.82</v>
+        <v>9.67</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="BR6" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BS6" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU6" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BV6" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW6" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX6" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BY6" t="n">
         <v>3.26</v>
@@ -3216,67 +3216,67 @@
         <v>3.24</v>
       </c>
       <c r="CA6" t="n">
-        <v>4.02</v>
+        <v>3.98</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.06</v>
+        <v>4.03</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.78</v>
+        <v>3.69</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.08</v>
+        <v>3.95</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="CH6" t="n">
         <v>1.62</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.55</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL6" t="n">
         <v>1.79</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CR6" t="n">
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CT6" t="n">
         <v>3.25</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CV6" t="n">
         <v>2.52</v>
@@ -3285,100 +3285,100 @@
         <v>1.58</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC6" t="n">
         <v>1.67</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="DE6" t="n">
         <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="DH6" t="n">
-        <v>87.12</v>
+        <v>86.88</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.59</v>
+        <v>4.61</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM6" t="n">
-        <v>37.12</v>
+        <v>36.78</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.12</v>
+        <v>11.5</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.71</v>
+        <v>11</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.41</v>
+        <v>7.66</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.89</v>
+        <v>45.72</v>
       </c>
       <c r="DW6" t="n">
         <v>0.06</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.35</v>
+        <v>11.06</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.88</v>
+        <v>6.84</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.47</v>
+        <v>4.22</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.88</v>
+        <v>17.67</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="7">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0.25</v>
@@ -3881,139 +3881,139 @@
         <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AI8" t="n">
-        <v>85.78</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AN8" t="n">
-        <v>40.44</v>
+        <v>40</v>
       </c>
       <c r="AO8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BJ8" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="AP8" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>12.78</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>45.44</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>7.89</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.59</v>
-      </c>
       <c r="BK8" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.06</v>
+        <v>4.39</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.82</v>
+        <v>3.89</v>
       </c>
       <c r="BR8" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS8" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT8" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU8" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BV8" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX8" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY8" t="n">
         <v>2.2</v>
@@ -4022,25 +4022,25 @@
         <v>2.35</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.07</v>
+        <v>3.93</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.45</v>
+        <v>4.29</v>
       </c>
       <c r="CE8" t="n">
         <v>1.33</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CH8" t="n">
         <v>1.49</v>
@@ -4052,25 +4052,25 @@
         <v>1.69</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CO8" t="n">
         <v>1.24</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
@@ -4091,100 +4091,100 @@
         <v>1.75</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB8" t="n">
         <v>1.3</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD8" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="DH8" t="n">
-        <v>97.06</v>
+        <v>96.89</v>
       </c>
       <c r="DI8" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.41</v>
+        <v>4.5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM8" t="n">
-        <v>44.7</v>
+        <v>44.22</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.59</v>
+        <v>9.83</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.83</v>
+        <v>12.72</v>
       </c>
       <c r="DR8" t="n">
-        <v>5.88</v>
+        <v>5.89</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.64</v>
+        <v>50.89</v>
       </c>
       <c r="DW8" t="n">
         <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.88</v>
+        <v>12.83</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.06</v>
+        <v>19.61</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="9">
@@ -4194,61 +4194,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="H9" t="n">
-        <v>86.75</v>
+        <v>89.78</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="K9" t="n">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M9" t="n">
-        <v>40.12</v>
+        <v>41</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>12</v>
+        <v>12.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>13.56</v>
       </c>
       <c r="R9" t="n">
-        <v>8.880000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4260,28 +4260,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.75</v>
+        <v>47</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.5</v>
+        <v>14.78</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AB9" t="n">
-        <v>5</v>
+        <v>5.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.88</v>
+        <v>18.11</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4365,70 +4365,70 @@
         <v>2.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.19</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.06</v>
+        <v>4.12</v>
       </c>
       <c r="BR9" t="n">
-        <v>87.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BT9" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU9" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV9" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY9" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BZ9" t="n">
         <v>2.68</v>
       </c>
-      <c r="BZ9" t="n">
-        <v>2.71</v>
-      </c>
       <c r="CA9" t="n">
-        <v>4.16</v>
+        <v>4.12</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.69</v>
+        <v>4.63</v>
       </c>
       <c r="CC9" t="n">
         <v>6.46</v>
@@ -4440,13 +4440,13 @@
         <v>1.29</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.48</v>
+        <v>3.45</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CI9" t="n">
         <v>2.26</v>
@@ -4467,43 +4467,43 @@
         <v>1.97</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP9" t="n">
         <v>1.63</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CV9" t="n">
         <v>2.42</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DA9" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="DB9" t="n">
         <v>1.3</v>
@@ -4512,49 +4512,49 @@
         <v>1.72</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="DE9" t="n">
         <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="DG9" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DH9" t="n">
-        <v>84.18000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.31</v>
+        <v>36.06</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.38</v>
+        <v>12.59</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.81</v>
+        <v>13.12</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.57</v>
+        <v>8.59</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4566,28 +4566,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.12</v>
+        <v>46.76</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.81</v>
+        <v>13.53</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.19</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.62</v>
+        <v>5.06</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.19</v>
+        <v>17.82</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="10">
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4690,49 +4690,49 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.38</v>
+        <v>3.56</v>
       </c>
       <c r="AI10" t="n">
-        <v>87.12</v>
+        <v>85.56</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN10" t="n">
-        <v>38.88</v>
+        <v>38.44</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.25</v>
+        <v>11.33</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.25</v>
+        <v>10.22</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.880000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4744,82 +4744,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>45.75</v>
+        <v>44</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>11</v>
+        <v>11.22</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.5</v>
+        <v>7.78</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="BD10" t="n">
-        <v>20.75</v>
+        <v>20.44</v>
       </c>
       <c r="BE10" t="n">
         <v>1.23</v>
       </c>
       <c r="BF10" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.35</v>
+        <v>9.67</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.18</v>
+        <v>3.11</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM10" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP10" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.35</v>
+        <v>5.78</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT10" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BU10" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX10" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY10" t="n">
         <v>4.32</v>
@@ -4831,28 +4831,28 @@
         <v>4.17</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.4</v>
+        <v>5.31</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.83</v>
+        <v>5.74</v>
       </c>
       <c r="CE10" t="n">
         <v>1.29</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CH10" t="n">
         <v>1.58</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.67</v>
@@ -4861,7 +4861,7 @@
         <v>1.53</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CM10" t="n">
         <v>2.41</v>
@@ -4870,13 +4870,13 @@
         <v>1.88</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP10" t="n">
         <v>1.67</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CR10" t="n">
         <v>1.38</v>
@@ -4894,7 +4894,7 @@
         <v>2.26</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX10" t="n">
         <v>1.58</v>
@@ -4912,10 +4912,10 @@
         <v>1.32</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
@@ -4924,40 +4924,40 @@
         <v>1.06</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="DH10" t="n">
-        <v>86.59</v>
+        <v>85.84</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.71</v>
+        <v>4.78</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.65</v>
+        <v>37.5</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.59</v>
+        <v>10.66</v>
       </c>
       <c r="DQ10" t="n">
-        <v>10.59</v>
+        <v>10.56</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.83</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4969,28 +4969,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>43.59</v>
+        <v>42.84</v>
       </c>
       <c r="DW10" t="n">
         <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.53</v>
+        <v>11.61</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.82</v>
+        <v>7.94</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.71</v>
+        <v>18.67</v>
       </c>
       <c r="EB10" t="n">
         <v>1.27</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="11">
@@ -5000,94 +5000,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
       </c>
       <c r="E11" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="F11" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="H11" t="n">
-        <v>117.25</v>
+        <v>116.44</v>
       </c>
       <c r="I11" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="J11" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>5.67</v>
       </c>
       <c r="L11" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="M11" t="n">
-        <v>55</v>
+        <v>53.22</v>
       </c>
       <c r="N11" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="O11" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="P11" t="n">
-        <v>15.25</v>
+        <v>15.44</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.880000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="R11" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="U11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>56.38</v>
+        <v>54.33</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.119999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.38</v>
+        <v>5.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>22.38</v>
+        <v>21.22</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AF11" t="n">
         <v>0.12</v>
@@ -5171,70 +5171,70 @@
         <v>2.12</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.44</v>
+        <v>3.29</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.31</v>
+        <v>10.18</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.44</v>
+        <v>3.29</v>
       </c>
       <c r="BJ11" t="n">
         <v>1.06</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
       <c r="BR11" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS11" t="n">
-        <v>87.5</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU11" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BV11" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BW11" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX11" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="CB11" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="CC11" t="n">
         <v>3.19</v>
@@ -5246,31 +5246,31 @@
         <v>1.24</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CH11" t="n">
         <v>1.68</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CO11" t="n">
         <v>1.14</v>
@@ -5279,7 +5279,7 @@
         <v>1.54</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
@@ -5294,22 +5294,22 @@
         <v>1.64</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CX11" t="n">
         <v>1.5</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.52</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DB11" t="n">
         <v>1.26</v>
@@ -5318,49 +5318,49 @@
         <v>1.61</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="DH11" t="n">
-        <v>111.38</v>
+        <v>111.29</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="DM11" t="n">
-        <v>49.62</v>
+        <v>49</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.93</v>
+        <v>15.05</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.380000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.94</v>
+        <v>6</v>
       </c>
       <c r="DS11" t="n">
         <v>0.18</v>
@@ -5372,28 +5372,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>54.63</v>
+        <v>53.65</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>13</v>
+        <v>13.35</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.119999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.88</v>
+        <v>5.06</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.56</v>
+        <v>21</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="12">
@@ -5403,61 +5403,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="G12" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="H12" t="n">
-        <v>96.12</v>
+        <v>98.78</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="J12" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="K12" t="n">
-        <v>4.12</v>
+        <v>4.67</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>40.88</v>
+        <v>45.22</v>
       </c>
       <c r="N12" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="O12" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>8.119999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.12</v>
+        <v>11</v>
       </c>
       <c r="R12" t="n">
-        <v>7.88</v>
+        <v>7.56</v>
       </c>
       <c r="S12" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="T12" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5469,28 +5469,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>47.62</v>
+        <v>49.22</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.5</v>
+        <v>14.22</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.119999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.38</v>
+        <v>5.44</v>
       </c>
       <c r="AC12" t="n">
-        <v>18.88</v>
+        <v>20.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AF12" t="n">
         <v>0.11</v>
@@ -5574,70 +5574,70 @@
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.24</v>
+        <v>10.44</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL12" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BN12" t="n">
         <v>1.94</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.12</v>
+        <v>5.17</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT12" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU12" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BV12" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW12" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX12" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="CB12" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="CC12" t="n">
         <v>4.04</v>
@@ -5649,16 +5649,16 @@
         <v>1.29</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.58</v>
@@ -5667,52 +5667,52 @@
         <v>1.4</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP12" t="n">
         <v>1.65</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.4</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DB12" t="n">
         <v>1.29</v>
@@ -5724,46 +5724,46 @@
         <v>2.58</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="DH12" t="n">
-        <v>92.34999999999999</v>
+        <v>93.89</v>
       </c>
       <c r="DI12" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.71</v>
+        <v>1.84</v>
       </c>
       <c r="DK12" t="n">
-        <v>3.88</v>
+        <v>4.17</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM12" t="n">
-        <v>39.65</v>
+        <v>41.89</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.470000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="DQ12" t="n">
-        <v>10.82</v>
+        <v>10.78</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.76</v>
+        <v>9.5</v>
       </c>
       <c r="DS12" t="n">
         <v>0.06</v>
@@ -5775,28 +5775,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.7</v>
+        <v>47.56</v>
       </c>
       <c r="DW12" t="n">
         <v>0.06</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.76</v>
+        <v>13.16</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.109999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.65</v>
+        <v>4.72</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.71</v>
+        <v>19.44</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="13">
@@ -5806,13 +5806,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5899,136 +5899,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AI13" t="n">
-        <v>94</v>
+        <v>94.33</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN13" t="n">
-        <v>45.75</v>
+        <v>44.89</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AP13" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.38</v>
+        <v>11.22</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>8.67</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>41.5</v>
+        <v>41.11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.880000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.12</v>
+        <v>5.78</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.75</v>
+        <v>3.22</v>
       </c>
       <c r="BD13" t="n">
-        <v>22</v>
+        <v>21.22</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.76</v>
+        <v>9.06</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.35</v>
+        <v>3.61</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.35</v>
+        <v>5.39</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS13" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT13" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX13" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY13" t="n">
         <v>2.3</v>
@@ -6037,28 +6037,28 @@
         <v>2.41</v>
       </c>
       <c r="CA13" t="n">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.4</v>
+        <v>5.18</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.71</v>
+        <v>5.47</v>
       </c>
       <c r="CE13" t="n">
         <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CI13" t="n">
         <v>2.23</v>
@@ -6073,43 +6073,43 @@
         <v>1.88</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO13" t="n">
         <v>1.22</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CR13" t="n">
         <v>1.38</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CT13" t="n">
         <v>3.17</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX13" t="n">
         <v>1.53</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.46</v>
@@ -6130,76 +6130,76 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="DH13" t="n">
-        <v>109</v>
+        <v>108.33</v>
       </c>
       <c r="DI13" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM13" t="n">
-        <v>51.12</v>
+        <v>50.39</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.82</v>
+        <v>11.72</v>
       </c>
       <c r="DQ13" t="n">
-        <v>10.35</v>
+        <v>10.11</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.35</v>
+        <v>7.72</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>45.41</v>
+        <v>45</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.83</v>
+        <v>10.78</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.94</v>
+        <v>7.67</v>
       </c>
       <c r="DZ13" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="EA13" t="n">
-        <v>23.36</v>
+        <v>22.89</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="14">
@@ -6209,94 +6209,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F14" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="G14" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="H14" t="n">
-        <v>101.25</v>
+        <v>100.56</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="K14" t="n">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="L14" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M14" t="n">
-        <v>45.12</v>
+        <v>44.22</v>
       </c>
       <c r="N14" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="O14" t="n">
-        <v>3.75</v>
+        <v>3.33</v>
       </c>
       <c r="P14" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="Q14" t="n">
-        <v>11.75</v>
+        <v>11.11</v>
       </c>
       <c r="R14" t="n">
-        <v>5.5</v>
+        <v>5.22</v>
       </c>
       <c r="S14" t="n">
-        <v>0.75</v>
+        <v>1.22</v>
       </c>
       <c r="T14" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="U14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>51.75</v>
+        <v>50.67</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>17.62</v>
+        <v>17.56</v>
       </c>
       <c r="AA14" t="n">
-        <v>10.12</v>
+        <v>10.44</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.5</v>
+        <v>7.11</v>
       </c>
       <c r="AC14" t="n">
-        <v>19.62</v>
+        <v>19.67</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF14" t="n">
         <v>0.5</v>
@@ -6380,70 +6380,70 @@
         <v>1.75</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.19</v>
+        <v>3.35</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.44</v>
+        <v>10.65</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.19</v>
+        <v>3.35</v>
       </c>
       <c r="BJ14" t="n">
         <v>0.88</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.38</v>
+        <v>0.65</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.94</v>
+        <v>4.76</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.5</v>
+        <v>5.88</v>
       </c>
       <c r="BR14" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS14" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU14" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BV14" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BW14" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BX14" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BY14" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="BZ14" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.16</v>
+        <v>4.21</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.31</v>
+        <v>4.32</v>
       </c>
       <c r="CC14" t="n">
         <v>3.6</v>
@@ -6455,40 +6455,40 @@
         <v>1.23</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.01</v>
+        <v>4.06</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CK14" t="n">
         <v>1.41</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
@@ -6503,73 +6503,73 @@
         <v>1.78</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CW14" t="n">
         <v>1.49</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DB14" t="n">
         <v>1.32</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.94</v>
+        <v>3.06</v>
       </c>
       <c r="DH14" t="n">
-        <v>94.06</v>
+        <v>94.12</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.94</v>
+        <v>5.88</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM14" t="n">
-        <v>43.94</v>
+        <v>43.53</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="DO14" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.57</v>
+        <v>9.41</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11</v>
+        <v>10.71</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.69</v>
+        <v>7.41</v>
       </c>
       <c r="DS14" t="n">
         <v>0.06</v>
@@ -6581,28 +6581,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51</v>
+        <v>50.47</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>16.62</v>
+        <v>16.65</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.81</v>
+        <v>10.94</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.81</v>
+        <v>5.7</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.75</v>
+        <v>16.95</v>
       </c>
       <c r="EB14" t="n">
         <v>1.77</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="15">
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6702,52 +6702,52 @@
         <v>2</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>91</v>
+        <v>90.3</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.67</v>
+        <v>38.6</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.33</v>
+        <v>10.4</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.779999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.11</v>
+        <v>6.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6759,82 +6759,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>43.78</v>
+        <v>43.1</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.33</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BB15" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>20.78</v>
+        <v>20.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="BH15" t="n">
         <v>10</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="BO15" t="n">
         <v>1.12</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.38</v>
+        <v>4.06</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.62</v>
+        <v>5.24</v>
       </c>
       <c r="BR15" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS15" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU15" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX15" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY15" t="n">
         <v>2.72</v>
@@ -6843,22 +6843,22 @@
         <v>2.77</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.97</v>
+        <v>4.02</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.01</v>
+        <v>4.09</v>
       </c>
       <c r="CC15" t="n">
-        <v>6.15</v>
+        <v>6.49</v>
       </c>
       <c r="CD15" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="CE15" t="n">
         <v>1.36</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CG15" t="n">
         <v>3.08</v>
@@ -6867,19 +6867,19 @@
         <v>1.46</v>
       </c>
       <c r="CI15" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL15" t="n">
         <v>2.11</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CN15" t="n">
         <v>1.77</v>
@@ -6891,88 +6891,88 @@
         <v>1.87</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CR15" t="n">
         <v>1.4</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CU15" t="n">
         <v>1.49</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DB15" t="n">
         <v>1.34</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="DD15" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="DE15" t="n">
         <v>0.06</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="DH15" t="n">
-        <v>99.06</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="DI15" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="DK15" t="n">
         <v>5</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.44</v>
+        <v>0.35</v>
       </c>
       <c r="DM15" t="n">
-        <v>44.81</v>
+        <v>44.41</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.37</v>
+        <v>10.41</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10</v>
+        <v>9.94</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.19</v>
+        <v>6.47</v>
       </c>
       <c r="DS15" t="n">
         <v>0.06</v>
@@ -6984,28 +6984,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46.94</v>
+        <v>46.35</v>
       </c>
       <c r="DW15" t="n">
         <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.44</v>
+        <v>10.35</v>
       </c>
       <c r="DY15" t="n">
-        <v>7</v>
+        <v>6.82</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.44</v>
+        <v>3.53</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.5</v>
+        <v>21.29</v>
       </c>
       <c r="EB15" t="n">
         <v>1.23</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="16">
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -7027,82 +7027,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="H16" t="n">
-        <v>103.12</v>
+        <v>102.67</v>
       </c>
       <c r="I16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J16" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="K16" t="n">
-        <v>5.38</v>
+        <v>5.11</v>
       </c>
       <c r="L16" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="M16" t="n">
-        <v>41.38</v>
+        <v>41.11</v>
       </c>
       <c r="N16" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O16" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="P16" t="n">
-        <v>9.619999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.88</v>
+        <v>12.67</v>
       </c>
       <c r="R16" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="S16" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>54.5</v>
+        <v>54.78</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.88</v>
+        <v>15.44</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.880000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="AB16" t="n">
-        <v>6</v>
+        <v>5.78</v>
       </c>
       <c r="AC16" t="n">
-        <v>20.12</v>
+        <v>19.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AF16" t="n">
         <v>0.11</v>
@@ -7186,70 +7186,70 @@
         <v>1.89</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="BH16" t="n">
-        <v>10</v>
+        <v>10.06</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.53</v>
+        <v>4.67</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.47</v>
+        <v>5.39</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS16" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT16" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BU16" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BV16" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX16" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="CA16" t="n">
         <v>4.06</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.05</v>
+        <v>4.06</v>
       </c>
       <c r="CC16" t="n">
         <v>2.72</v>
@@ -7261,152 +7261,154 @@
         <v>1.25</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CK16" t="n">
         <v>1.47</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CN16" t="n">
         <v>1.96</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="CR16" t="n">
         <v>1.33</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CX16" t="n">
         <v>1.55</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DA16" t="n">
-        <v>2</v>
-      </c>
-      <c r="DB16" t="inlineStr"/>
+        <v>1.99</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>1.26</v>
+      </c>
       <c r="DC16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="DE16" t="n">
         <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="DH16" t="n">
-        <v>117.88</v>
+        <v>116.83</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.77</v>
+        <v>5.61</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
       <c r="DM16" t="n">
-        <v>57.42</v>
+        <v>56.39</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.12</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.59</v>
+        <v>12.5</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.41</v>
+        <v>5.78</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>56.71</v>
+        <v>56.72</v>
       </c>
       <c r="DW16" t="n">
         <v>0.06</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.47</v>
+        <v>15.28</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.59</v>
+        <v>9.5</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.88</v>
+        <v>5.78</v>
       </c>
       <c r="EA16" t="n">
-        <v>19.17</v>
+        <v>18.83</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="17">
@@ -7416,13 +7418,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>0.11</v>
@@ -7506,49 +7508,49 @@
         <v>2.89</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="AI17" t="n">
-        <v>88</v>
+        <v>90.67</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.88</v>
+        <v>5.22</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AN17" t="n">
-        <v>40.38</v>
+        <v>42.11</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.25</v>
+        <v>12.11</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.12</v>
+        <v>9.67</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.619999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AU17" t="n">
         <v>1</v>
@@ -7563,82 +7565,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>39.12</v>
+        <v>39.56</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA17" t="n">
-        <v>12.5</v>
+        <v>13.33</v>
       </c>
       <c r="BB17" t="n">
-        <v>9</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.25</v>
+        <v>20.44</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.529999999999999</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL17" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.41</v>
+        <v>4.56</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="BR17" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS17" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT17" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU17" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV17" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW17" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX17" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY17" t="n">
         <v>3.05</v>
@@ -7647,31 +7649,31 @@
         <v>3.79</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.13</v>
+        <v>4.29</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.16</v>
+        <v>4.33</v>
       </c>
       <c r="CE17" t="n">
         <v>1.35</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CH17" t="n">
         <v>1.47</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.76</v>
@@ -7680,34 +7682,34 @@
         <v>1.49</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CN17" t="n">
         <v>1.93</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CV17" t="n">
         <v>2.09</v>
@@ -7722,7 +7724,7 @@
         <v>1.92</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DA17" t="n">
         <v>1.92</v>
@@ -7731,52 +7733,52 @@
         <v>1.34</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="DE17" t="n">
         <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DH17" t="n">
-        <v>89.81999999999999</v>
+        <v>91.06</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.06</v>
+        <v>5.22</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="DM17" t="n">
-        <v>40.53</v>
+        <v>41.39</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.41</v>
+        <v>13.27</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.82</v>
+        <v>10.56</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.53</v>
+        <v>7.61</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7788,28 +7790,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>38.29</v>
+        <v>38.56</v>
       </c>
       <c r="DW17" t="n">
         <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.71</v>
+        <v>13.11</v>
       </c>
       <c r="DY17" t="n">
-        <v>9</v>
+        <v>9.44</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.71</v>
+        <v>3.66</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.35</v>
+        <v>20.44</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="18">
@@ -8222,94 +8224,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F19" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="G19" t="n">
-        <v>1.89</v>
+        <v>2.5</v>
       </c>
       <c r="H19" t="n">
-        <v>103.33</v>
+        <v>107.3</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="L19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M19" t="n">
-        <v>48.78</v>
+        <v>50</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="O19" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="P19" t="n">
-        <v>12.22</v>
+        <v>12</v>
       </c>
       <c r="Q19" t="n">
-        <v>10.22</v>
+        <v>10.4</v>
       </c>
       <c r="R19" t="n">
-        <v>8.220000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="S19" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="U19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>48.22</v>
+        <v>50.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.44</v>
+        <v>13.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.33</v>
+        <v>8.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="AC19" t="n">
-        <v>17.78</v>
+        <v>18.4</v>
       </c>
       <c r="AD19" t="n">
         <v>1.56</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AF19" t="n">
         <v>0.12</v>
@@ -8393,70 +8395,70 @@
         <v>1.88</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.18</v>
+        <v>11.39</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BK19" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BL19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BN19" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.65</v>
+        <v>4.5</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.59</v>
+        <v>6</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT19" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BV19" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW19" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BX19" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.51</v>
+        <v>2.43</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.94</v>
+        <v>3.95</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="CC19" t="n">
         <v>4.81</v>
@@ -8471,7 +8473,7 @@
         <v>2.38</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CH19" t="n">
         <v>1.59</v>
@@ -8483,25 +8485,25 @@
         <v>1.59</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP19" t="n">
         <v>1.64</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
@@ -8516,73 +8518,73 @@
         <v>1.62</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CW19" t="n">
         <v>1.61</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DB19" t="n">
         <v>1.3</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.06</v>
+        <v>1.17</v>
       </c>
       <c r="DG19" t="n">
-        <v>1.76</v>
+        <v>2.11</v>
       </c>
       <c r="DH19" t="n">
-        <v>91.76000000000001</v>
+        <v>94.61</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM19" t="n">
-        <v>40.88</v>
+        <v>42</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="DP19" t="n">
-        <v>11</v>
+        <v>10.94</v>
       </c>
       <c r="DQ19" t="n">
-        <v>9.59</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.24</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DS19" t="n">
         <v>0.11</v>
@@ -8594,28 +8596,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>45.94</v>
+        <v>47.28</v>
       </c>
       <c r="DW19" t="n">
         <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.82</v>
+        <v>11.89</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.53</v>
+        <v>7.61</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="EA19" t="n">
-        <v>16.89</v>
+        <v>17.28</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -3944,10 +3944,10 @@
         <v>0.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="BC8" t="n">
         <v>3.3</v>
@@ -4169,10 +4169,10 @@
         <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.83</v>
+        <v>12.89</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.609999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="DZ8" t="n">
         <v>4.22</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -4194,13 +4194,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0.22</v>
@@ -4287,136 +4287,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="AH9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>83.67</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>31.67</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>17.22</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN9" t="n">
         <v>1.5</v>
       </c>
-      <c r="AI9" t="n">
-        <v>81.62</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>12.62</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>12.12</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1.59</v>
-      </c>
       <c r="BO9" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.94</v>
+        <v>3.83</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.12</v>
+        <v>4.28</v>
       </c>
       <c r="BR9" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BS9" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV9" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>2.65</v>
@@ -4425,55 +4425,55 @@
         <v>2.68</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.12</v>
+        <v>4.05</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.63</v>
+        <v>4.54</v>
       </c>
       <c r="CC9" t="n">
-        <v>6.46</v>
+        <v>6.02</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.87</v>
+        <v>6.41</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.45</v>
+        <v>3.39</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="CR9" t="n">
         <v>1.36</v>
@@ -4488,73 +4488,73 @@
         <v>1.62</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DH9" t="n">
-        <v>85.94</v>
+        <v>86.72</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="DM9" t="n">
-        <v>36.06</v>
+        <v>36.34</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.59</v>
+        <v>12.61</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.12</v>
+        <v>13.23</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.59</v>
+        <v>8.44</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -4566,28 +4566,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.76</v>
+        <v>47.34</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.53</v>
+        <v>13.06</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.470000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.06</v>
+        <v>4.89</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.82</v>
+        <v>17.67</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -6612,10 +6612,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
@@ -6624,82 +6624,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="H15" t="n">
-        <v>109.43</v>
+        <v>109.88</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="J15" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="K15" t="n">
-        <v>7.14</v>
+        <v>6.88</v>
       </c>
       <c r="L15" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="M15" t="n">
-        <v>52.71</v>
+        <v>49.88</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
       <c r="P15" t="n">
-        <v>10.43</v>
+        <v>11</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.57</v>
+        <v>11.75</v>
       </c>
       <c r="R15" t="n">
-        <v>6.29</v>
+        <v>6.12</v>
       </c>
       <c r="S15" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="T15" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.86</v>
+        <v>11.38</v>
       </c>
       <c r="AA15" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.86</v>
+        <v>4.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>22.43</v>
+        <v>22.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AE15" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AF15" t="n">
         <v>0.1</v>
@@ -6783,70 +6783,70 @@
         <v>1.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="BH15" t="n">
-        <v>10</v>
+        <v>9.94</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.76</v>
+        <v>2.61</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.24</v>
+        <v>5.33</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.12</v>
+        <v>88.89</v>
       </c>
       <c r="BS15" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BT15" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU15" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV15" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX15" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="CA15" t="n">
-        <v>4.02</v>
+        <v>3.95</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.09</v>
+        <v>4.03</v>
       </c>
       <c r="CC15" t="n">
         <v>6.49</v>
@@ -6855,43 +6855,43 @@
         <v>6.6</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.08</v>
+        <v>3.03</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="CR15" t="n">
         <v>1.4</v>
@@ -6906,106 +6906,106 @@
         <v>1.49</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="DE15" t="n">
         <v>0.06</v>
       </c>
       <c r="DF15" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="DH15" t="n">
-        <v>98.18000000000001</v>
+        <v>99</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="DK15" t="n">
         <v>5</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="DM15" t="n">
-        <v>44.41</v>
+        <v>43.61</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.41</v>
+        <v>10.67</v>
       </c>
       <c r="DQ15" t="n">
-        <v>9.94</v>
+        <v>10.11</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.47</v>
+        <v>6.39</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46.35</v>
+        <v>46.17</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.35</v>
+        <v>10.22</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.82</v>
+        <v>6.72</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.29</v>
+        <v>21.39</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="16">

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0.2</v>
@@ -1469,139 +1469,139 @@
         <v>2.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AI2" t="n">
-        <v>101.5</v>
+        <v>98</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK2" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AL2" t="n">
         <v>3</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>36.12</v>
+        <v>35.56</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.12</v>
+        <v>12.22</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.62</v>
+        <v>13.22</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.5</v>
+        <v>8.44</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AU2" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>44.25</v>
+        <v>42.67</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.75</v>
+        <v>13.11</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.119999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="BD2" t="n">
-        <v>16.75</v>
+        <v>16</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BF2" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.06</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.72</v>
+        <v>4.74</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.33</v>
+        <v>4.47</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT2" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU2" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV2" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX2" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY2" t="n">
         <v>3.45</v>
@@ -1610,85 +1610,85 @@
         <v>3.79</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.76</v>
+        <v>4.14</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.85</v>
+        <v>4.23</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.93</v>
+        <v>5.38</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.06</v>
+        <v>5.72</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.27</v>
+        <v>3.42</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="CT2" t="n">
         <v>3.21</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY2" t="n">
         <v>1.92</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB2" t="n">
         <v>1.29</v>
@@ -1703,43 +1703,43 @@
         <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="DG2" t="n">
         <v>2.11</v>
       </c>
       <c r="DH2" t="n">
-        <v>101.11</v>
+        <v>99.47</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM2" t="n">
-        <v>39.5</v>
+        <v>39.05</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.16</v>
+        <v>11.79</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.83</v>
+        <v>12.68</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.109999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="DS2" t="n">
         <v>0.05</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.94</v>
+        <v>45.11</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.56</v>
+        <v>12.74</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.5</v>
+        <v>8.58</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.05</v>
+        <v>4.16</v>
       </c>
       <c r="EA2" t="n">
-        <v>19.06</v>
+        <v>18.58</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="H3" t="n">
-        <v>118.67</v>
+        <v>116.1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="K3" t="n">
-        <v>5.89</v>
+        <v>5.8</v>
       </c>
       <c r="L3" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="M3" t="n">
-        <v>50.78</v>
+        <v>49.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O3" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="P3" t="n">
-        <v>9.33</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.33</v>
+        <v>10.2</v>
       </c>
       <c r="R3" t="n">
-        <v>6.11</v>
+        <v>6.2</v>
       </c>
       <c r="S3" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>62.11</v>
+        <v>60.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.56</v>
+        <v>16.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>11</v>
+        <v>10.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.56</v>
+        <v>5.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.11</v>
+        <v>16.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AF3" t="n">
         <v>0.25</v>
@@ -1953,70 +1953,70 @@
         <v>2.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.47</v>
+        <v>3.33</v>
       </c>
       <c r="BH3" t="n">
         <v>9.94</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.47</v>
+        <v>3.33</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BK3" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.53</v>
+        <v>5.5</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>94.12</v>
+        <v>88.89</v>
       </c>
       <c r="BT3" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU3" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV3" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW3" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BX3" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.05</v>
+        <v>4.08</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.09</v>
+        <v>4.11</v>
       </c>
       <c r="CC3" t="n">
         <v>3.18</v>
@@ -2031,10 +2031,10 @@
         <v>2.28</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.59</v>
+        <v>3.61</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CI3" t="n">
         <v>2.38</v>
@@ -2049,7 +2049,7 @@
         <v>1.86</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CN3" t="n">
         <v>1.95</v>
@@ -2058,16 +2058,16 @@
         <v>1.16</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CR3" t="n">
         <v>1.34</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CT3" t="n">
         <v>3.3</v>
@@ -2085,97 +2085,97 @@
         <v>1.56</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.39</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DB3" t="n">
         <v>1.27</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="DH3" t="n">
-        <v>109.36</v>
+        <v>108.45</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="DM3" t="n">
-        <v>47.71</v>
+        <v>46.94</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="DP3" t="n">
-        <v>8.880000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.59</v>
+        <v>11.44</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.41</v>
+        <v>7.39</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>59.53</v>
+        <v>59</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.18</v>
+        <v>14.11</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.35</v>
+        <v>9.33</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.83</v>
+        <v>4.78</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.59</v>
+        <v>16.17</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="H4" t="n">
-        <v>136</v>
+        <v>137.9</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="K4" t="n">
-        <v>6.33</v>
+        <v>6.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>68</v>
+        <v>67.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O4" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>9.33</v>
+        <v>9.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.56</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>5.56</v>
+        <v>6.1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="T4" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>68.67</v>
+        <v>68.8</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>20.11</v>
+        <v>19.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.33</v>
+        <v>11.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.779999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>20.89</v>
+        <v>20.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AF4" t="n">
         <v>0.11</v>
@@ -2356,37 +2356,37 @@
         <v>2.11</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.72</v>
+        <v>4.63</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.609999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.72</v>
+        <v>4.63</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.33</v>
+        <v>4.37</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.28</v>
+        <v>5.37</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2398,28 +2398,28 @@
         <v>100</v>
       </c>
       <c r="BU4" t="n">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BV4" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BW4" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BX4" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY4" t="n">
         <v>1.16</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.52</v>
+        <v>7.7</v>
       </c>
       <c r="CB4" t="n">
-        <v>8.26</v>
+        <v>8.4</v>
       </c>
       <c r="CC4" t="n">
         <v>1.32</v>
@@ -2434,34 +2434,34 @@
         <v>1.79</v>
       </c>
       <c r="CG4" t="n">
-        <v>4.91</v>
+        <v>4.97</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CK4" t="n">
         <v>1.51</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CO4" t="n">
         <v>1.05</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CQ4" t="n">
         <v>1.78</v>
@@ -2475,10 +2475,10 @@
         <v>2.16</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CX4" t="n">
         <v>1.52</v>
@@ -2487,7 +2487,7 @@
         <v>1.85</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="DA4" t="n">
         <v>1.98</v>
@@ -2500,79 +2500,79 @@
         <v>1.76</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="DH4" t="n">
-        <v>133.06</v>
+        <v>134.21</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="DK4" t="n">
-        <v>6</v>
+        <v>6.16</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DM4" t="n">
-        <v>67.11</v>
+        <v>67</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="DP4" t="n">
-        <v>8.83</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DQ4" t="n">
-        <v>8.56</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.44</v>
+        <v>5.74</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>67.67</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>19.44</v>
+        <v>19.21</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.61</v>
+        <v>10.53</v>
       </c>
       <c r="DZ4" t="n">
-        <v>8.84</v>
+        <v>8.68</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.17</v>
+        <v>20.05</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="5">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0.11</v>
@@ -2672,139 +2672,139 @@
         <v>1.33</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AI5" t="n">
-        <v>106.78</v>
+        <v>104.6</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN5" t="n">
-        <v>50.67</v>
+        <v>50.3</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.22</v>
+        <v>11.7</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.22</v>
+        <v>11</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.22</v>
+        <v>6.3</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>51.33</v>
+        <v>50.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.78</v>
+        <v>11.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.78</v>
+        <v>7.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.67</v>
+        <v>21.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="BG5" t="n">
         <v>2.89</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.720000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="BI5" t="n">
         <v>2.89</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.83</v>
+        <v>5.74</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BU5" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV5" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW5" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BY5" t="n">
         <v>1.53</v>
@@ -2813,34 +2813,34 @@
         <v>1.53</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.3</v>
+        <v>4.26</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.45</v>
+        <v>4.39</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.64</v>
+        <v>3.59</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CK5" t="n">
         <v>1.48</v>
@@ -2849,19 +2849,19 @@
         <v>1.89</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="CR5" t="n">
         <v>1.34</v>
@@ -2876,10 +2876,10 @@
         <v>1.68</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CX5" t="n">
         <v>1.59</v>
@@ -2894,88 +2894,88 @@
         <v>1.96</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DF5" t="n">
         <v>1.11</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="DH5" t="n">
-        <v>114.5</v>
+        <v>112.95</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.06</v>
+        <v>4.9</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM5" t="n">
-        <v>53.94</v>
+        <v>53.58</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.39</v>
+        <v>11.63</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.44</v>
+        <v>10.37</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.44</v>
+        <v>6.48</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>53.22</v>
+        <v>52.74</v>
       </c>
       <c r="DW5" t="n">
         <v>0.11</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.34</v>
+        <v>12.47</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.56</v>
+        <v>7.68</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.73</v>
+        <v>19.69</v>
       </c>
       <c r="EB5" t="n">
         <v>1.52</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="6">
@@ -2985,91 +2985,91 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="G6" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="n">
-        <v>90.44</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="K6" t="n">
-        <v>4.44</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>39.56</v>
+        <v>38.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O6" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
         <v>11</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.67</v>
+        <v>8.4</v>
       </c>
       <c r="R6" t="n">
-        <v>8.109999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="U6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>45.89</v>
+        <v>45.7</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z6" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.11</v>
+        <v>7.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.78</v>
+        <v>17.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -3159,67 +3159,67 @@
         <v>2.89</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.67</v>
+        <v>9.42</v>
       </c>
       <c r="BI6" t="n">
         <v>2.89</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.5</v>
+        <v>4.32</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.17</v>
+        <v>5.11</v>
       </c>
       <c r="BR6" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT6" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU6" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV6" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW6" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX6" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="CC6" t="n">
         <v>3.69</v>
@@ -3234,13 +3234,13 @@
         <v>2.32</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CH6" t="n">
         <v>1.62</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.55</v>
@@ -3249,13 +3249,13 @@
         <v>1.42</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO6" t="n">
         <v>1.16</v>
@@ -3279,22 +3279,22 @@
         <v>1.65</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CW6" t="n">
         <v>1.58</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DB6" t="n">
         <v>1.28</v>
@@ -3303,49 +3303,49 @@
         <v>1.67</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF6" t="n">
         <v>0.84</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="DH6" t="n">
-        <v>86.88</v>
+        <v>85.84</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.61</v>
+        <v>4.42</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.78</v>
+        <v>36.26</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.39</v>
+        <v>2.27</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.5</v>
+        <v>11.47</v>
       </c>
       <c r="DQ6" t="n">
-        <v>11</v>
+        <v>10.74</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.66</v>
+        <v>7.79</v>
       </c>
       <c r="DS6" t="n">
         <v>0.16</v>
@@ -3357,28 +3357,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.72</v>
+        <v>45.63</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.06</v>
+        <v>11.1</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.84</v>
+        <v>6.95</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.22</v>
+        <v>4.16</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.67</v>
+        <v>17.74</v>
       </c>
       <c r="EB6" t="n">
         <v>1.26</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="7">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
@@ -3400,82 +3400,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="H7" t="n">
-        <v>97.62</v>
+        <v>95.22</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="K7" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="M7" t="n">
-        <v>48</v>
+        <v>45.89</v>
       </c>
       <c r="N7" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="O7" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>10.5</v>
+        <v>10.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.119999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>6.88</v>
+        <v>7.11</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="T7" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>52.88</v>
+        <v>52.22</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>13.12</v>
+        <v>12.67</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.88</v>
+        <v>4.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.75</v>
+        <v>21.11</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AF7" t="n">
         <v>0.2</v>
@@ -3559,70 +3559,70 @@
         <v>2.1</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
       <c r="BH7" t="n">
-        <v>8</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.28</v>
+        <v>4.26</v>
       </c>
       <c r="BJ7" t="n">
         <v>0.89</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.78</v>
+        <v>3.95</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT7" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BU7" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BV7" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BW7" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BX7" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="CC7" t="n">
         <v>2.8</v>
@@ -3637,7 +3637,7 @@
         <v>2.24</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CH7" t="n">
         <v>1.65</v>
@@ -3652,7 +3652,7 @@
         <v>1.5</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CM7" t="n">
         <v>2.44</v>
@@ -3661,19 +3661,19 @@
         <v>1.92</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="CP7" t="n">
         <v>1.55</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CR7" t="n">
         <v>1.35</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CT7" t="n">
         <v>3.34</v>
@@ -3682,19 +3682,19 @@
         <v>1.7</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CW7" t="n">
         <v>1.55</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CY7" t="n">
         <v>1.92</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="DA7" t="n">
         <v>1.91</v>
@@ -3712,76 +3712,76 @@
         <v>0.11</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="DG7" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DH7" t="n">
-        <v>101.89</v>
+        <v>100.53</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.34</v>
+        <v>4.42</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM7" t="n">
-        <v>46.56</v>
+        <v>45.63</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.17</v>
+        <v>11</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.050000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.45</v>
+        <v>7.53</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>52.84</v>
+        <v>52.53</v>
       </c>
       <c r="DW7" t="n">
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.22</v>
+        <v>12.05</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.72</v>
+        <v>7.63</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.5</v>
+        <v>4.42</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.06</v>
+        <v>21.21</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="8">
@@ -3791,94 +3791,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="G8" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="H8" t="n">
-        <v>109.75</v>
+        <v>107.67</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="K8" t="n">
-        <v>5.25</v>
+        <v>5.22</v>
       </c>
       <c r="L8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M8" t="n">
-        <v>49.5</v>
+        <v>49.22</v>
       </c>
       <c r="N8" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="O8" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>9.75</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.88</v>
+        <v>12.33</v>
       </c>
       <c r="R8" t="n">
-        <v>3.75</v>
+        <v>4.56</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T8" t="n">
         <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>56.5</v>
+        <v>55.56</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>14.78</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.619999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.38</v>
+        <v>5.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.25</v>
+        <v>20.78</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AF8" t="n">
         <v>0.1</v>
@@ -3962,70 +3962,70 @@
         <v>1.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.279999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN8" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="BR8" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS8" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT8" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BU8" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV8" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX8" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="CC8" t="n">
         <v>3.93</v>
@@ -4037,10 +4037,10 @@
         <v>1.33</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CH8" t="n">
         <v>1.49</v>
@@ -4052,16 +4052,16 @@
         <v>1.69</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CO8" t="n">
         <v>1.24</v>
@@ -4070,121 +4070,121 @@
         <v>1.83</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CU8" t="n">
         <v>1.5</v>
       </c>
       <c r="CV8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CZ8" t="n">
         <v>2.2</v>
       </c>
-      <c r="CW8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CX8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CY8" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="CZ8" t="n">
-        <v>2.19</v>
-      </c>
       <c r="DA8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB8" t="n">
         <v>1.3</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="DH8" t="n">
-        <v>96.89</v>
+        <v>96.58</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM8" t="n">
-        <v>44.22</v>
+        <v>44.37</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.83</v>
+        <v>9.58</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.72</v>
+        <v>12.47</v>
       </c>
       <c r="DR8" t="n">
-        <v>5.89</v>
+        <v>6.16</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.89</v>
+        <v>50.74</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.89</v>
+        <v>12.9</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.66</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.22</v>
+        <v>4.26</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.61</v>
+        <v>19.47</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="9">
@@ -4428,13 +4428,13 @@
         <v>4.05</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="CC9" t="n">
         <v>6.02</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.41</v>
+        <v>6.43</v>
       </c>
       <c r="CE9" t="n">
         <v>1.31</v>
@@ -4488,16 +4488,16 @@
         <v>1.62</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CW9" t="n">
         <v>1.66</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.33</v>
@@ -4506,7 +4506,7 @@
         <v>1.95</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DC9" t="n">
         <v>1.77</v>
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>9</v>
@@ -4609,49 +4609,49 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="G10" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H10" t="n">
-        <v>86.11</v>
+        <v>83.3</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="M10" t="n">
-        <v>36.56</v>
+        <v>38.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O10" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="P10" t="n">
         <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.89</v>
+        <v>10.7</v>
       </c>
       <c r="R10" t="n">
-        <v>8.779999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="S10" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4663,28 +4663,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>41.67</v>
+        <v>40.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.109999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>16.89</v>
+        <v>17.2</v>
       </c>
       <c r="AD10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.33</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4771,64 +4771,64 @@
         <v>3.11</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.67</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="BI10" t="n">
         <v>3.11</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.89</v>
+        <v>3.79</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.78</v>
+        <v>5.58</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BV10" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX10" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY10" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="BZ10" t="n">
-        <v>4.95</v>
+        <v>4.93</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.17</v>
+        <v>4.16</v>
       </c>
       <c r="CB10" t="n">
         <v>4.34</v>
@@ -4843,40 +4843,40 @@
         <v>1.29</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.45</v>
+        <v>3.47</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CL10" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CO10" t="n">
         <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="CR10" t="n">
         <v>1.38</v>
@@ -4891,73 +4891,73 @@
         <v>1.61</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CX10" t="n">
         <v>1.58</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.37</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DB10" t="n">
         <v>1.32</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="DH10" t="n">
-        <v>85.84</v>
+        <v>84.37</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.5</v>
+        <v>38.58</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.66</v>
+        <v>10.63</v>
       </c>
       <c r="DQ10" t="n">
-        <v>10.56</v>
+        <v>10.47</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.890000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4969,28 +4969,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>42.84</v>
+        <v>41.95</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.61</v>
+        <v>11.37</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.94</v>
+        <v>7.79</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.66</v>
+        <v>3.58</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.67</v>
+        <v>18.73</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="11">
@@ -5000,13 +5000,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0.22</v>
@@ -5090,139 +5090,139 @@
         <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>105.5</v>
+        <v>107.67</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.25</v>
+        <v>4.44</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN11" t="n">
-        <v>44.25</v>
+        <v>44.67</v>
       </c>
       <c r="AO11" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AP11" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.62</v>
+        <v>14.78</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.880000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.38</v>
+        <v>6.33</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>52.88</v>
+        <v>52.89</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>11.5</v>
+        <v>11.33</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.12</v>
+        <v>6.89</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="BD11" t="n">
-        <v>20.75</v>
+        <v>21.33</v>
       </c>
       <c r="BE11" t="n">
         <v>1.36</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.18</v>
+        <v>10.28</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="BJ11" t="n">
         <v>1.06</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.76</v>
+        <v>4.78</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.41</v>
+        <v>5.5</v>
       </c>
       <c r="BR11" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS11" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU11" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BV11" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW11" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX11" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY11" t="n">
         <v>2.69</v>
@@ -5231,16 +5231,16 @@
         <v>2.73</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.98</v>
+        <v>3.97</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.34</v>
+        <v>3.23</v>
       </c>
       <c r="CE11" t="n">
         <v>1.24</v>
@@ -5249,7 +5249,7 @@
         <v>2.21</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CH11" t="n">
         <v>1.68</v>
@@ -5264,19 +5264,19 @@
         <v>1.41</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO11" t="n">
         <v>1.14</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CQ11" t="n">
         <v>2.3</v>
@@ -5294,22 +5294,22 @@
         <v>1.64</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CW11" t="n">
         <v>1.54</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DB11" t="n">
         <v>1.26</v>
@@ -5321,79 +5321,79 @@
         <v>2.47</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF11" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DH11" t="n">
-        <v>111.29</v>
+        <v>112.06</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="DK11" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM11" t="n">
-        <v>49</v>
+        <v>48.94</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="DP11" t="n">
-        <v>15.05</v>
+        <v>15.11</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.24</v>
+        <v>9.17</v>
       </c>
       <c r="DR11" t="n">
         <v>6</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.65</v>
+        <v>53.61</v>
       </c>
       <c r="DW11" t="n">
         <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.35</v>
+        <v>13.16</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.289999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DZ11" t="n">
         <v>5.06</v>
       </c>
       <c r="EA11" t="n">
-        <v>21</v>
+        <v>21.27</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5403,13 +5403,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0.22</v>
@@ -5493,139 +5493,139 @@
         <v>1.44</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>89</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK12" t="n">
         <v>2</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>38.56</v>
+        <v>39.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.779999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR12" t="n">
-        <v>10.56</v>
+        <v>10</v>
       </c>
       <c r="AS12" t="n">
-        <v>11.44</v>
+        <v>10.9</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>45.89</v>
+        <v>46.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.11</v>
+        <v>12.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.109999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC12" t="n">
         <v>4</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.56</v>
+        <v>18.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BF12" t="n">
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.44</v>
+        <v>10.42</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.17</v>
+        <v>5.21</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT12" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU12" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV12" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW12" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX12" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BY12" t="n">
         <v>3.01</v>
@@ -5634,70 +5634,70 @@
         <v>3.3</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="CC12" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="CD12" t="n">
         <v>4.04</v>
       </c>
-      <c r="CD12" t="n">
-        <v>4.07</v>
-      </c>
       <c r="CE12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="CH12" t="n">
         <v>1.58</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CO12" t="n">
         <v>1.18</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CU12" t="n">
         <v>1.6</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CW12" t="n">
         <v>1.59</v>
@@ -5706,97 +5706,97 @@
         <v>1.55</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DB12" t="n">
         <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DH12" t="n">
-        <v>93.89</v>
+        <v>93.69</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ12" t="n">
         <v>1.84</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
       <c r="DL12" t="n">
         <v>0.16</v>
       </c>
       <c r="DM12" t="n">
-        <v>41.89</v>
+        <v>42.21</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.33</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DQ12" t="n">
-        <v>10.78</v>
+        <v>10.47</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.5</v>
+        <v>9.32</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.56</v>
+        <v>47.79</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.16</v>
+        <v>13.47</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.44</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.72</v>
+        <v>4.68</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.44</v>
+        <v>19.21</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="13">
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
@@ -5818,82 +5818,82 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G13" t="n">
-        <v>3.67</v>
+        <v>4.1</v>
       </c>
       <c r="H13" t="n">
-        <v>122.33</v>
+        <v>124</v>
       </c>
       <c r="I13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="K13" t="n">
-        <v>5.56</v>
+        <v>6.5</v>
       </c>
       <c r="L13" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="M13" t="n">
-        <v>55.89</v>
+        <v>58</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="P13" t="n">
-        <v>12.22</v>
+        <v>11.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.22</v>
+        <v>10.1</v>
       </c>
       <c r="R13" t="n">
-        <v>6.78</v>
+        <v>6.7</v>
       </c>
       <c r="S13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>0.78</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="V13" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>48.89</v>
+        <v>49.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.56</v>
+        <v>13.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.56</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>24.56</v>
+        <v>24.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5977,70 +5977,70 @@
         <v>2.78</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.06</v>
+        <v>9.42</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.72</v>
+        <v>2.79</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.61</v>
+        <v>3.79</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.39</v>
+        <v>5.58</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU13" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BV13" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW13" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX13" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY13" t="n">
         <v>2.3</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.11</v>
+        <v>4.08</v>
       </c>
       <c r="CC13" t="n">
         <v>5.18</v>
@@ -6049,10 +6049,10 @@
         <v>5.47</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CG13" t="n">
         <v>3.28</v>
@@ -6061,7 +6061,7 @@
         <v>1.55</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.65</v>
@@ -6070,13 +6070,13 @@
         <v>1.47</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO13" t="n">
         <v>1.22</v>
@@ -6085,22 +6085,22 @@
         <v>1.72</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CR13" t="n">
         <v>1.38</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CW13" t="n">
         <v>1.66</v>
@@ -6109,7 +6109,7 @@
         <v>1.53</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.46</v>
@@ -6121,10 +6121,10 @@
         <v>1.31</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
@@ -6133,73 +6133,73 @@
         <v>1.84</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.22</v>
+        <v>3.47</v>
       </c>
       <c r="DH13" t="n">
-        <v>108.33</v>
+        <v>109.95</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.78</v>
+        <v>5.32</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="DM13" t="n">
-        <v>50.39</v>
+        <v>51.79</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.72</v>
+        <v>11.53</v>
       </c>
       <c r="DQ13" t="n">
-        <v>10.11</v>
+        <v>10.05</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.72</v>
+        <v>7.63</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>45</v>
+        <v>45.74</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DX13" t="n">
-        <v>10.78</v>
+        <v>11.26</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.67</v>
+        <v>7.84</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.11</v>
+        <v>3.42</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.89</v>
+        <v>23.16</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="14">
@@ -6209,13 +6209,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>0.11</v>
@@ -6299,52 +6299,52 @@
         <v>1.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.75</v>
+        <v>3.33</v>
       </c>
       <c r="AI14" t="n">
-        <v>86.88</v>
+        <v>93.11</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AL14" t="n">
-        <v>6</v>
+        <v>5.33</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN14" t="n">
-        <v>42.75</v>
+        <v>44.89</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.880000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.25</v>
+        <v>10.22</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.880000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6356,82 +6356,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>50.25</v>
+        <v>52.89</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>15.62</v>
+        <v>15.11</v>
       </c>
       <c r="BB14" t="n">
-        <v>11.5</v>
+        <v>10.56</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.12</v>
+        <v>4.56</v>
       </c>
       <c r="BD14" t="n">
-        <v>13.88</v>
+        <v>14.22</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.65</v>
+        <v>10.28</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.65</v>
+        <v>0.78</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.76</v>
+        <v>4.61</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.88</v>
+        <v>5.67</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS14" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU14" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BV14" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW14" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BX14" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY14" t="n">
         <v>2.12</v>
@@ -6443,13 +6443,13 @@
         <v>4.21</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.6</v>
+        <v>3.39</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.66</v>
+        <v>3.44</v>
       </c>
       <c r="CE14" t="n">
         <v>1.23</v>
@@ -6458,13 +6458,13 @@
         <v>2.12</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="CH14" t="n">
         <v>1.71</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.49</v>
@@ -6476,16 +6476,16 @@
         <v>1.78</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO14" t="n">
         <v>1.12</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CQ14" t="n">
         <v>2.2</v>
@@ -6503,7 +6503,7 @@
         <v>1.78</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CW14" t="n">
         <v>1.49</v>
@@ -6518,7 +6518,7 @@
         <v>2.48</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DB14" t="n">
         <v>1.32</v>
@@ -6530,46 +6530,46 @@
         <v>2.19</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="DG14" t="n">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="DH14" t="n">
-        <v>94.12</v>
+        <v>96.84</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM14" t="n">
-        <v>43.53</v>
+        <v>44.56</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.82</v>
+        <v>2.66</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.41</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.71</v>
+        <v>10.66</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.41</v>
+        <v>7.39</v>
       </c>
       <c r="DS14" t="n">
         <v>0.06</v>
@@ -6581,28 +6581,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>50.47</v>
+        <v>51.78</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>16.65</v>
+        <v>16.33</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.94</v>
+        <v>10.5</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.7</v>
+        <v>5.84</v>
       </c>
       <c r="EA14" t="n">
         <v>16.95</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="15">
@@ -6840,7 +6840,7 @@
         <v>2.74</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CA15" t="n">
         <v>3.95</v>
@@ -6906,28 +6906,28 @@
         <v>1.49</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.24</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB15" t="n">
         <v>1.35</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DD15" t="n">
         <v>3.05</v>
@@ -7015,13 +7015,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
         <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7105,139 +7105,139 @@
         <v>1.89</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AL16" t="n">
-        <v>6.11</v>
+        <v>5.9</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN16" t="n">
-        <v>71.67</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.56</v>
+        <v>10.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>12.33</v>
+        <v>12.2</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.56</v>
+        <v>5.6</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>58.67</v>
+        <v>58.4</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>15.11</v>
+        <v>15.3</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.33</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.78</v>
+        <v>6</v>
       </c>
       <c r="BD16" t="n">
-        <v>18.33</v>
+        <v>18.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.06</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.67</v>
+        <v>4.47</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.39</v>
+        <v>5.32</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BU16" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV16" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX16" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY16" t="n">
         <v>2.08</v>
@@ -7246,16 +7246,16 @@
         <v>2.07</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.84</v>
+        <v>2.79</v>
       </c>
       <c r="CE16" t="n">
         <v>1.25</v>
@@ -7264,31 +7264,31 @@
         <v>2.21</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CH16" t="n">
         <v>1.66</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM16" t="n">
         <v>2.52</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="CP16" t="n">
         <v>1.55</v>
@@ -7309,7 +7309,7 @@
         <v>1.68</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CW16" t="n">
         <v>1.55</v>
@@ -7318,13 +7318,13 @@
         <v>1.55</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB16" t="n">
         <v>1.26</v>
@@ -7336,46 +7336,46 @@
         <v>2.43</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="DH16" t="n">
-        <v>116.83</v>
+        <v>118.11</v>
       </c>
       <c r="DI16" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.61</v>
+        <v>5.53</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM16" t="n">
-        <v>56.39</v>
+        <v>56.53</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.67</v>
+        <v>2.58</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.890000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.5</v>
+        <v>12.42</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.78</v>
+        <v>5.79</v>
       </c>
       <c r="DS16" t="n">
         <v>0.16</v>
@@ -7387,28 +7387,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>56.72</v>
+        <v>56.69</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.28</v>
+        <v>15.37</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.5</v>
+        <v>9.48</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.78</v>
+        <v>5.9</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.83</v>
+        <v>18.68</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="17">
@@ -7418,61 +7418,61 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
       </c>
       <c r="E17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F17" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="G17" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H17" t="n">
-        <v>91.44</v>
+        <v>93.5</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="K17" t="n">
-        <v>5.22</v>
+        <v>5.4</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M17" t="n">
-        <v>40.67</v>
+        <v>42.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O17" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>14.44</v>
+        <v>14</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.44</v>
+        <v>11.9</v>
       </c>
       <c r="R17" t="n">
-        <v>6.56</v>
+        <v>6.6</v>
       </c>
       <c r="S17" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="T17" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7484,28 +7484,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>37.56</v>
+        <v>39.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.89</v>
+        <v>12.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.44</v>
+        <v>20.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="AF17" t="n">
         <v>0.11</v>
@@ -7589,70 +7589,70 @@
         <v>1.44</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.609999999999999</v>
+        <v>9.58</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="BO17" t="n">
         <v>1.11</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.56</v>
+        <v>4.58</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="BR17" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS17" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU17" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV17" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW17" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX17" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.79</v>
+        <v>3.74</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="CC17" t="n">
         <v>4.29</v>
@@ -7661,43 +7661,43 @@
         <v>4.33</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="CH17" t="n">
         <v>1.47</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.76</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL17" t="n">
         <v>1.92</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP17" t="n">
         <v>1.88</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="CR17" t="n">
         <v>1.4</v>
@@ -7733,52 +7733,52 @@
         <v>1.34</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="DH17" t="n">
-        <v>91.06</v>
+        <v>92.16</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.39</v>
+        <v>2.26</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.22</v>
+        <v>5.31</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="DM17" t="n">
-        <v>41.39</v>
+        <v>42.26</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.27</v>
+        <v>13.1</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.56</v>
+        <v>10.84</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.61</v>
+        <v>7.58</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7790,28 +7790,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>38.56</v>
+        <v>39.48</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.11</v>
+        <v>12.95</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.44</v>
+        <v>9.32</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.44</v>
+        <v>20.42</v>
       </c>
       <c r="EB17" t="n">
         <v>1.38</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="18">
@@ -7821,13 +7821,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
         <v>0.12</v>
@@ -7914,136 +7914,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>82.33</v>
+        <v>84.5</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN18" t="n">
-        <v>33.22</v>
+        <v>35.4</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.22</v>
+        <v>10.1</v>
       </c>
       <c r="AR18" t="n">
-        <v>10.44</v>
+        <v>10</v>
       </c>
       <c r="AS18" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BL18" t="n">
         <v>1.11</v>
       </c>
-      <c r="AV18" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>47.33</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>18.22</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BM18" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BN18" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP18" t="n">
         <v>4.94</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS18" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BT18" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU18" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BV18" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BW18" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX18" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY18" t="n">
         <v>2.51</v>
@@ -8052,16 +8052,16 @@
         <v>2.62</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.37</v>
+        <v>4.38</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.38</v>
+        <v>4.39</v>
       </c>
       <c r="CC18" t="n">
-        <v>5.87</v>
+        <v>5.78</v>
       </c>
       <c r="CD18" t="n">
-        <v>6.8</v>
+        <v>6.67</v>
       </c>
       <c r="CE18" t="n">
         <v>1.26</v>
@@ -8070,7 +8070,7 @@
         <v>2.25</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="CH18" t="n">
         <v>1.64</v>
@@ -8082,13 +8082,13 @@
         <v>1.55</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL18" t="n">
         <v>1.95</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CN18" t="n">
         <v>1.93</v>
@@ -8100,7 +8100,7 @@
         <v>1.55</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CR18" t="n">
         <v>1.34</v>
@@ -8115,7 +8115,7 @@
         <v>1.71</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CW18" t="n">
         <v>1.56</v>
@@ -8124,7 +8124,7 @@
         <v>1.56</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.41</v>
@@ -8136,52 +8136,52 @@
         <v>1.26</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DD18" t="n">
         <v>2.42</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="DH18" t="n">
-        <v>93.88</v>
+        <v>94.45</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.29</v>
+        <v>4.33</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM18" t="n">
-        <v>40.7</v>
+        <v>41.5</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.17</v>
+        <v>10.11</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.05</v>
+        <v>9.83</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.88</v>
+        <v>7.78</v>
       </c>
       <c r="DS18" t="n">
         <v>0.11</v>
@@ -8193,28 +8193,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>49.35</v>
+        <v>49.39</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.94</v>
+        <v>12.22</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.77</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.35</v>
+        <v>19.5</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="19">
@@ -8224,13 +8224,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>0.2</v>
@@ -8314,139 +8314,139 @@
         <v>1.9</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AI19" t="n">
-        <v>78.75</v>
+        <v>79.89</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="AM19" t="n">
         <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>32</v>
+        <v>31.67</v>
       </c>
       <c r="AO19" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.619999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.880000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AS19" t="n">
-        <v>10.38</v>
+        <v>10.44</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>43.38</v>
+        <v>43.11</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.62</v>
+        <v>6.44</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="BD19" t="n">
-        <v>15.88</v>
+        <v>16.33</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.39</v>
+        <v>11.63</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BL19" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.5</v>
+        <v>4.63</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6</v>
+        <v>6.16</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BU19" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BV19" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW19" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BX19" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BY19" t="n">
         <v>2.39</v>
@@ -8455,34 +8455,34 @@
         <v>2.43</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.16</v>
+        <v>4.13</v>
       </c>
       <c r="CC19" t="n">
-        <v>4.81</v>
+        <v>4.6</v>
       </c>
       <c r="CD19" t="n">
-        <v>5.54</v>
+        <v>5.28</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CK19" t="n">
         <v>1.44</v>
@@ -8497,31 +8497,31 @@
         <v>2.01</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CU19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CW19" t="n">
         <v>1.62</v>
-      </c>
-      <c r="CV19" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="CW19" t="n">
-        <v>1.61</v>
       </c>
       <c r="CX19" t="n">
         <v>1.54</v>
@@ -8539,22 +8539,22 @@
         <v>1.3</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="DH19" t="n">
-        <v>94.61</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
@@ -8563,61 +8563,61 @@
         <v>1.95</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.95</v>
+        <v>3.79</v>
       </c>
       <c r="DL19" t="n">
         <v>0.11</v>
       </c>
       <c r="DM19" t="n">
-        <v>42</v>
+        <v>41.32</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DO19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DP19" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="DQ19" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="DR19" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="DS19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DT19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV19" t="n">
+        <v>46.95</v>
+      </c>
+      <c r="DW19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DX19" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="DY19" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="DZ19" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="EA19" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="EB19" t="n">
         <v>1.33</v>
       </c>
-      <c r="DP19" t="n">
-        <v>10.94</v>
-      </c>
-      <c r="DQ19" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="DR19" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="DS19" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DT19" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV19" t="n">
-        <v>47.28</v>
-      </c>
-      <c r="DW19" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DX19" t="n">
-        <v>11.89</v>
-      </c>
-      <c r="DY19" t="n">
-        <v>7.61</v>
-      </c>
-      <c r="DZ19" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="EA19" t="n">
-        <v>17.28</v>
-      </c>
-      <c r="EB19" t="n">
-        <v>1.36</v>
-      </c>
       <c r="EC19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -3857,7 +3857,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>55.56</v>
+        <v>55.44</v>
       </c>
       <c r="Y8" t="n">
         <v>0.11</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.74</v>
+        <v>50.68</v>
       </c>
       <c r="DW8" t="n">
         <v>0.1</v>
@@ -5000,13 +5000,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0.22</v>
@@ -5090,139 +5090,139 @@
         <v>1.67</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AI11" t="n">
-        <v>107.67</v>
+        <v>106.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.44</v>
+        <v>4.7</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.33</v>
+        <v>0.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>44.67</v>
+        <v>44.7</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.78</v>
+        <v>14.3</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.67</v>
+        <v>9.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.33</v>
+        <v>6.7</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>52.89</v>
+        <v>51.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>11.33</v>
+        <v>11.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.89</v>
+        <v>7.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="BD11" t="n">
-        <v>21.33</v>
+        <v>21.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.28</v>
+        <v>10.42</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BM11" t="n">
         <v>1</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.78</v>
+        <v>4.89</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="BR11" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BU11" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BV11" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW11" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX11" t="n">
-        <v>66.67</v>
+        <v>63.16</v>
       </c>
       <c r="BY11" t="n">
         <v>2.69</v>
@@ -5231,31 +5231,31 @@
         <v>2.73</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="CE11" t="n">
         <v>1.24</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.51</v>
@@ -5276,10 +5276,10 @@
         <v>1.14</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
@@ -5294,10 +5294,10 @@
         <v>1.64</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CX11" t="n">
         <v>1.51</v>
@@ -5324,43 +5324,43 @@
         <v>0.16</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="DH11" t="n">
-        <v>112.06</v>
+        <v>111.21</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.06</v>
+        <v>5.16</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM11" t="n">
-        <v>48.94</v>
+        <v>48.74</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.66</v>
+        <v>2.89</v>
       </c>
       <c r="DP11" t="n">
-        <v>15.11</v>
+        <v>14.84</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.17</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DR11" t="n">
-        <v>6</v>
+        <v>6.21</v>
       </c>
       <c r="DS11" t="n">
         <v>0.16</v>
@@ -5372,25 +5372,25 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.61</v>
+        <v>53</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.16</v>
+        <v>13.11</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.109999999999999</v>
+        <v>8.16</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5.06</v>
+        <v>4.95</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.27</v>
+        <v>21.21</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="EC11" t="n">
         <v>2</v>
@@ -5550,7 +5550,7 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -5565,7 +5565,7 @@
         <v>4</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="BE12" t="n">
         <v>1.38</v>
@@ -5775,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.79</v>
+        <v>47.84</v>
       </c>
       <c r="DW12" t="n">
         <v>0.05</v>
@@ -5790,7 +5790,7 @@
         <v>4.68</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.21</v>
+        <v>19.26</v>
       </c>
       <c r="EB12" t="n">
         <v>1.49</v>
@@ -6209,13 +6209,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>0.11</v>
@@ -6299,52 +6299,52 @@
         <v>1.11</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.33</v>
+        <v>3.2</v>
       </c>
       <c r="AI14" t="n">
-        <v>93.11</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.33</v>
+        <v>5.1</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN14" t="n">
-        <v>44.89</v>
+        <v>46</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP14" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.779999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.56</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6356,82 +6356,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>52.89</v>
+        <v>53</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>15.11</v>
+        <v>14.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>10.56</v>
+        <v>10.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.56</v>
+        <v>4.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>14.22</v>
+        <v>15</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.28</v>
+        <v>10.11</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL14" t="n">
         <v>1.11</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN14" t="n">
         <v>1.89</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.61</v>
+        <v>4.47</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.67</v>
+        <v>5.63</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BU14" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BV14" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW14" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BX14" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY14" t="n">
         <v>2.12</v>
@@ -6440,55 +6440,55 @@
         <v>2.05</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.21</v>
+        <v>4.17</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.39</v>
+        <v>3.21</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.44</v>
+        <v>3.27</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="CG14" t="n">
-        <v>4.04</v>
+        <v>3.98</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL14" t="n">
         <v>1.78</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
@@ -6503,22 +6503,22 @@
         <v>1.78</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="CX14" t="n">
         <v>1.52</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DB14" t="n">
         <v>1.32</v>
@@ -6530,79 +6530,79 @@
         <v>2.19</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="DH14" t="n">
-        <v>96.84</v>
+        <v>99</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.56</v>
+        <v>5.42</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM14" t="n">
-        <v>44.56</v>
+        <v>45.16</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.390000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.66</v>
+        <v>10.42</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.39</v>
+        <v>7.31</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.78</v>
+        <v>51.9</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>16.33</v>
+        <v>16.11</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.5</v>
+        <v>10.31</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.84</v>
+        <v>5.79</v>
       </c>
       <c r="EA14" t="n">
-        <v>16.95</v>
+        <v>17.21</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="15">
@@ -6612,10 +6612,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
@@ -6624,82 +6624,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="H15" t="n">
-        <v>109.88</v>
+        <v>110.22</v>
       </c>
       <c r="I15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J15" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="K15" t="n">
-        <v>6.88</v>
+        <v>6.56</v>
       </c>
       <c r="L15" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M15" t="n">
-        <v>49.88</v>
+        <v>48.44</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="O15" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="P15" t="n">
-        <v>11</v>
+        <v>10.44</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.75</v>
+        <v>11.22</v>
       </c>
       <c r="R15" t="n">
-        <v>6.12</v>
+        <v>6.44</v>
       </c>
       <c r="S15" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="V15" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>50</v>
+        <v>49.56</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.38</v>
+        <v>10.89</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.75</v>
+        <v>6.56</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.62</v>
+        <v>4.33</v>
       </c>
       <c r="AC15" t="n">
-        <v>22.5</v>
+        <v>22.22</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AF15" t="n">
         <v>0.1</v>
@@ -6783,70 +6783,70 @@
         <v>1.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.94</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.94</v>
+        <v>3.84</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.33</v>
+        <v>5.32</v>
       </c>
       <c r="BR15" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS15" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT15" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU15" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV15" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX15" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.74</v>
+        <v>2.94</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.79</v>
+        <v>3.03</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.95</v>
+        <v>3.93</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="CC15" t="n">
         <v>6.49</v>
@@ -6855,10 +6855,10 @@
         <v>6.6</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CG15" t="n">
         <v>3.03</v>
@@ -6873,25 +6873,25 @@
         <v>1.83</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.26</v>
+        <v>3.29</v>
       </c>
       <c r="CR15" t="n">
         <v>1.4</v>
@@ -6906,22 +6906,22 @@
         <v>1.49</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.24</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DB15" t="n">
         <v>1.35</v>
@@ -6933,79 +6933,79 @@
         <v>3.05</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DH15" t="n">
-        <v>99</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="DK15" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM15" t="n">
-        <v>43.61</v>
+        <v>43.26</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.67</v>
+        <v>10.42</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.11</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.39</v>
+        <v>6.52</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46.17</v>
+        <v>46.16</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.22</v>
+        <v>10.05</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.72</v>
+        <v>6.63</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.39</v>
+        <v>21.31</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="16">
@@ -7821,94 +7821,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F18" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="H18" t="n">
-        <v>106.88</v>
+        <v>106</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="L18" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>49.12</v>
+        <v>50.67</v>
       </c>
       <c r="N18" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="P18" t="n">
-        <v>10.12</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.619999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="R18" t="n">
-        <v>6.62</v>
+        <v>6.67</v>
       </c>
       <c r="S18" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="T18" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="U18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>51.62</v>
+        <v>52.33</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>14.5</v>
+        <v>15.78</v>
       </c>
       <c r="AA18" t="n">
-        <v>9.880000000000001</v>
+        <v>11.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.62</v>
+        <v>4.44</v>
       </c>
       <c r="AC18" t="n">
-        <v>20.62</v>
+        <v>21.67</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7992,70 +7992,70 @@
         <v>2.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.609999999999999</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.94</v>
+        <v>5.05</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.67</v>
+        <v>4.74</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT18" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BU18" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV18" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW18" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX18" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.51</v>
+        <v>2.62</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.38</v>
+        <v>4.34</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.39</v>
+        <v>4.36</v>
       </c>
       <c r="CC18" t="n">
         <v>5.78</v>
@@ -8067,10 +8067,10 @@
         <v>1.26</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CH18" t="n">
         <v>1.64</v>
@@ -8085,22 +8085,22 @@
         <v>1.48</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CM18" t="n">
         <v>2.49</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP18" t="n">
         <v>1.55</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CR18" t="n">
         <v>1.34</v>
@@ -8115,13 +8115,13 @@
         <v>1.71</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CW18" t="n">
         <v>1.56</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CY18" t="n">
         <v>1.87</v>
@@ -8145,76 +8145,76 @@
         <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="DH18" t="n">
-        <v>94.45</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.33</v>
+        <v>4.42</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM18" t="n">
-        <v>41.5</v>
+        <v>42.63</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.66</v>
+        <v>0.63</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.11</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DQ18" t="n">
-        <v>9.83</v>
+        <v>9.84</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.78</v>
+        <v>7.74</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>49.39</v>
+        <v>49.84</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.22</v>
+        <v>12.95</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.109999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.11</v>
+        <v>4.05</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.5</v>
+        <v>20.05</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -5147,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.1</v>
@@ -5372,7 +5372,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53</v>
+        <v>52.95</v>
       </c>
       <c r="DW11" t="n">
         <v>0.05</v>
@@ -5403,61 +5403,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="H12" t="n">
-        <v>98.78</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="J12" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="K12" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>45.22</v>
+        <v>45.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="P12" t="n">
-        <v>7.89</v>
+        <v>7.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="R12" t="n">
-        <v>7.56</v>
+        <v>8</v>
       </c>
       <c r="S12" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5469,28 +5469,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>49.22</v>
+        <v>48.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.22</v>
+        <v>14.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.779999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.44</v>
+        <v>5.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.33</v>
+        <v>20.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF12" t="n">
         <v>0.2</v>
@@ -5574,64 +5574,64 @@
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.42</v>
+        <v>10.25</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL12" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.47</v>
+        <v>4.4</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.21</v>
+        <v>5.15</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU12" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV12" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW12" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX12" t="n">
-        <v>73.68000000000001</v>
+        <v>70</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.01</v>
+        <v>2.91</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="CA12" t="n">
         <v>3.9</v>
@@ -5646,7 +5646,7 @@
         <v>4.04</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CF12" t="n">
         <v>2.38</v>
@@ -5658,16 +5658,16 @@
         <v>1.58</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CK12" t="n">
         <v>1.41</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CM12" t="n">
         <v>2.72</v>
@@ -5682,7 +5682,7 @@
         <v>1.66</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
@@ -5697,7 +5697,7 @@
         <v>1.6</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CW12" t="n">
         <v>1.59</v>
@@ -5706,64 +5706,64 @@
         <v>1.55</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.39</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DB12" t="n">
         <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="DH12" t="n">
-        <v>93.69</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.21</v>
+        <v>4.15</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DM12" t="n">
-        <v>42.21</v>
+        <v>42.65</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.369999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="DQ12" t="n">
-        <v>10.47</v>
+        <v>10.75</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.32</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="DS12" t="n">
         <v>0.05</v>
@@ -5775,28 +5775,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.84</v>
+        <v>47.55</v>
       </c>
       <c r="DW12" t="n">
         <v>0.05</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.47</v>
+        <v>13.55</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.789999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.68</v>
+        <v>4.6</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.26</v>
+        <v>19.45</v>
       </c>
       <c r="EB12" t="n">
         <v>1.49</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="13">
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>52.33</v>
+        <v>52.44</v>
       </c>
       <c r="Y18" t="n">
         <v>0.33</v>
@@ -8193,7 +8193,7 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>49.84</v>
+        <v>49.89</v>
       </c>
       <c r="DW18" t="n">
         <v>0.16</v>
@@ -8224,13 +8224,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
         <v>0.2</v>
@@ -8314,139 +8314,139 @@
         <v>1.9</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP19" t="n">
         <v>1</v>
       </c>
-      <c r="AH19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>79.89</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>31.67</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AP19" t="n">
+      <c r="AQ19" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE19" t="n">
         <v>1.11</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>10.44</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>43.11</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>16.33</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.07</v>
-      </c>
       <c r="BF19" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.63</v>
+        <v>11.4</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BL19" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BN19" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.63</v>
+        <v>4.55</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.16</v>
+        <v>6.05</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>84.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT19" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BU19" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BV19" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW19" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BX19" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BY19" t="n">
         <v>2.39</v>
@@ -8458,19 +8458,19 @@
         <v>3.92</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.13</v>
+        <v>4.11</v>
       </c>
       <c r="CC19" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="CD19" t="n">
-        <v>5.28</v>
+        <v>5.12</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CG19" t="n">
         <v>3.48</v>
@@ -8479,31 +8479,31 @@
         <v>1.58</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CO19" t="n">
         <v>1.19</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
@@ -8518,7 +8518,7 @@
         <v>1.61</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CW19" t="n">
         <v>1.62</v>
@@ -8527,64 +8527,64 @@
         <v>1.54</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.43</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DB19" t="n">
         <v>1.3</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="DG19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="DH19" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="DI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ19" t="n">
         <v>2.05</v>
       </c>
-      <c r="DH19" t="n">
-        <v>94.31999999999999</v>
-      </c>
-      <c r="DI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ19" t="n">
-        <v>1.95</v>
-      </c>
       <c r="DK19" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM19" t="n">
-        <v>41.32</v>
+        <v>41.6</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="DP19" t="n">
-        <v>10.95</v>
+        <v>11.2</v>
       </c>
       <c r="DQ19" t="n">
-        <v>9.630000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.210000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="DS19" t="n">
         <v>0.1</v>
@@ -8596,28 +8596,28 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>46.95</v>
+        <v>47.5</v>
       </c>
       <c r="DW19" t="n">
         <v>0.05</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.63</v>
+        <v>11.75</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.47</v>
+        <v>7.65</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.16</v>
+        <v>4.1</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.42</v>
+        <v>17.7</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="H2" t="n">
-        <v>100.8</v>
+        <v>100.18</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="K2" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="M2" t="n">
-        <v>42.2</v>
+        <v>41.45</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>11.4</v>
+        <v>11.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.2</v>
+        <v>12.27</v>
       </c>
       <c r="R2" t="n">
-        <v>7.8</v>
+        <v>8.09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>47.3</v>
+        <v>47</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.4</v>
+        <v>12.36</v>
       </c>
       <c r="AA2" t="n">
-        <v>8</v>
+        <v>7.82</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.9</v>
+        <v>20.91</v>
       </c>
       <c r="AD2" t="n">
         <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AF2" t="n">
         <v>0.11</v>
@@ -1553,67 +1553,67 @@
         <v>3.05</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.210000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="BI2" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.74</v>
+        <v>4.85</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.47</v>
+        <v>4.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS2" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT2" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU2" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV2" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX2" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.79</v>
+        <v>3.64</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.23</v>
+        <v>4.17</v>
       </c>
       <c r="CC2" t="n">
         <v>5.38</v>
@@ -1622,43 +1622,43 @@
         <v>5.72</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.42</v>
+        <v>3.37</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
@@ -1673,73 +1673,73 @@
         <v>1.6</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="DD2" t="n">
         <v>2.81</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DH2" t="n">
-        <v>99.47</v>
+        <v>99.2</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM2" t="n">
-        <v>39.05</v>
+        <v>38.8</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.84</v>
+        <v>0.9</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.79</v>
+        <v>11.95</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.68</v>
+        <v>12.7</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.1</v>
+        <v>8.25</v>
       </c>
       <c r="DS2" t="n">
         <v>0.05</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.11</v>
+        <v>45.05</v>
       </c>
       <c r="DW2" t="n">
         <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.74</v>
+        <v>12.7</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.58</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.16</v>
+        <v>4.25</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.58</v>
+        <v>18.7</v>
       </c>
       <c r="EB2" t="n">
         <v>1.38</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0.3</v>
@@ -1872,139 +1872,139 @@
         <v>2.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AI3" t="n">
-        <v>98.88</v>
+        <v>100.78</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN3" t="n">
-        <v>44.25</v>
+        <v>42.78</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.380000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="AR3" t="n">
-        <v>13</v>
+        <v>12.78</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.880000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>56.62</v>
+        <v>56.78</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.5</v>
+        <v>11.44</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.5</v>
+        <v>7.44</v>
       </c>
       <c r="BC3" t="n">
         <v>4</v>
       </c>
       <c r="BD3" t="n">
-        <v>16</v>
+        <v>16.11</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.33</v>
+        <v>3.37</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.94</v>
+        <v>10</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.33</v>
+        <v>3.37</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BO3" t="n">
         <v>2.11</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.44</v>
+        <v>4.53</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.5</v>
+        <v>5.47</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT3" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU3" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BV3" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW3" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BX3" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY3" t="n">
         <v>1.82</v>
@@ -2013,43 +2013,43 @@
         <v>1.91</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.08</v>
+        <v>4.06</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.11</v>
+        <v>4.09</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.18</v>
+        <v>3.07</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="CE3" t="n">
         <v>1.25</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CK3" t="n">
         <v>1.49</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CN3" t="n">
         <v>1.95</v>
@@ -2067,115 +2067,115 @@
         <v>1.34</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CT3" t="n">
         <v>3.3</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CW3" t="n">
         <v>1.58</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="DB3" t="n">
         <v>1.27</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="DG3" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="DH3" t="n">
-        <v>108.45</v>
+        <v>108.84</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.22</v>
+        <v>5.1</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM3" t="n">
-        <v>46.94</v>
+        <v>46.11</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DP3" t="n">
-        <v>8.720000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.44</v>
+        <v>11.42</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.39</v>
+        <v>7.47</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>59</v>
+        <v>58.95</v>
       </c>
       <c r="DW3" t="n">
         <v>0.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.11</v>
+        <v>13.95</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.33</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.17</v>
+        <v>16.21</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0.3</v>
@@ -2275,118 +2275,118 @@
         <v>1.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AI4" t="n">
-        <v>130.11</v>
+        <v>131.8</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.67</v>
+        <v>6</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.44</v>
+        <v>0.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>66.22</v>
+        <v>68</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.33</v>
+        <v>9.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.56</v>
+        <v>8.9</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.33</v>
+        <v>5.3</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>66.67</v>
+        <v>67.2</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>18.78</v>
+        <v>18.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.890000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>8.890000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.44</v>
+        <v>19.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.74</v>
+        <v>9.85</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BO4" t="n">
         <v>2</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.37</v>
+        <v>4.1</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.37</v>
+        <v>5.05</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2398,16 +2398,16 @@
         <v>100</v>
       </c>
       <c r="BU4" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BV4" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BW4" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BX4" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY4" t="n">
         <v>1.16</v>
@@ -2416,10 +2416,10 @@
         <v>1.17</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.7</v>
+        <v>7.63</v>
       </c>
       <c r="CB4" t="n">
-        <v>8.4</v>
+        <v>8.31</v>
       </c>
       <c r="CC4" t="n">
         <v>1.32</v>
@@ -2434,13 +2434,13 @@
         <v>1.79</v>
       </c>
       <c r="CG4" t="n">
-        <v>4.97</v>
+        <v>4.94</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.72</v>
@@ -2449,30 +2449,30 @@
         <v>1.51</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CO4" t="n">
         <v>1.05</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CQ4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CR4" t="inlineStr"/>
       <c r="CS4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CV4" t="n">
         <v>2.28</v>
@@ -2481,98 +2481,98 @@
         <v>1.74</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB4" t="inlineStr"/>
       <c r="DC4" t="n">
         <v>1.36</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="DH4" t="n">
-        <v>134.21</v>
+        <v>134.85</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.1</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.16</v>
+        <v>6.3</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.37</v>
+        <v>0.3</v>
       </c>
       <c r="DM4" t="n">
-        <v>67</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="DP4" t="n">
-        <v>8.890000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="DQ4" t="n">
-        <v>8.369999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.74</v>
+        <v>5.7</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>67.79000000000001</v>
+        <v>68</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>19.21</v>
+        <v>18.9</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.53</v>
+        <v>10.3</v>
       </c>
       <c r="DZ4" t="n">
-        <v>8.68</v>
+        <v>8.6</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.05</v>
+        <v>20.15</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="5">
@@ -2582,94 +2582,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="G5" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="H5" t="n">
-        <v>122.22</v>
+        <v>115</v>
       </c>
       <c r="I5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="K5" t="n">
-        <v>6.67</v>
+        <v>7.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>57.22</v>
+        <v>56.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="P5" t="n">
-        <v>11.56</v>
+        <v>11.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.67</v>
+        <v>9.6</v>
       </c>
       <c r="R5" t="n">
-        <v>6.67</v>
+        <v>6.9</v>
       </c>
       <c r="S5" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="V5" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>55.11</v>
+        <v>56.1</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.89</v>
+        <v>14.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.33</v>
+        <v>8.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.56</v>
+        <v>5.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>17.78</v>
+        <v>18</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AF5" t="n">
         <v>0.2</v>
@@ -2753,70 +2753,70 @@
         <v>2.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.68</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.74</v>
+        <v>5.75</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT5" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BU5" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BV5" t="n">
-        <v>21.05</v>
+        <v>25</v>
       </c>
       <c r="BW5" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BX5" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.26</v>
+        <v>4.34</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.39</v>
+        <v>4.5</v>
       </c>
       <c r="CC5" t="n">
         <v>2.47</v>
@@ -2828,28 +2828,28 @@
         <v>1.26</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="CH5" t="n">
         <v>1.62</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK5" t="n">
         <v>1.48</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN5" t="n">
         <v>1.93</v>
@@ -2858,10 +2858,10 @@
         <v>1.16</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CR5" t="n">
         <v>1.34</v>
@@ -2876,19 +2876,19 @@
         <v>1.68</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="DA5" t="n">
         <v>1.96</v>
@@ -2897,22 +2897,22 @@
         <v>1.29</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="DH5" t="n">
-        <v>112.95</v>
+        <v>109.8</v>
       </c>
       <c r="DI5" t="n">
         <v>0.05</v>
@@ -2921,61 +2921,61 @@
         <v>2</v>
       </c>
       <c r="DK5" t="n">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM5" t="n">
-        <v>53.58</v>
+        <v>53.55</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.63</v>
+        <v>11.6</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.37</v>
+        <v>10.3</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.48</v>
+        <v>6.6</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>52.74</v>
+        <v>53.35</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.47</v>
+        <v>12.8</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.68</v>
+        <v>8</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.69</v>
+        <v>19.7</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="6">
@@ -2985,13 +2985,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0.1</v>
@@ -3078,136 +3078,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AI6" t="n">
-        <v>83.33</v>
+        <v>81.7</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.78</v>
+        <v>4.6</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>34</v>
+        <v>32.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.33</v>
+        <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.22</v>
+        <v>7.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AU6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BE6" t="n">
         <v>1.22</v>
       </c>
-      <c r="AV6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>45.56</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>17.56</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.27</v>
-      </c>
       <c r="BF6" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.42</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="BR6" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BS6" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU6" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV6" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW6" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX6" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BY6" t="n">
         <v>3.22</v>
@@ -3216,31 +3216,31 @@
         <v>3.21</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.97</v>
+        <v>3.94</v>
       </c>
       <c r="CB6" t="n">
-        <v>4.02</v>
+        <v>4</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.69</v>
+        <v>3.63</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.95</v>
+        <v>3.89</v>
       </c>
       <c r="CE6" t="n">
         <v>1.27</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.55</v>
@@ -3249,13 +3249,13 @@
         <v>1.42</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM6" t="n">
         <v>2.67</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO6" t="n">
         <v>1.16</v>
@@ -3264,22 +3264,22 @@
         <v>1.61</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CR6" t="n">
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CT6" t="n">
         <v>3.25</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CW6" t="n">
         <v>1.58</v>
@@ -3291,10 +3291,10 @@
         <v>1.79</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DB6" t="n">
         <v>1.28</v>
@@ -3303,82 +3303,82 @@
         <v>1.67</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="DE6" t="n">
         <v>0.05</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="DH6" t="n">
-        <v>85.84</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.42</v>
+        <v>4.35</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.26</v>
+        <v>35.4</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.47</v>
+        <v>11.6</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.74</v>
+        <v>10.7</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.79</v>
+        <v>7.8</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.63</v>
+        <v>44.95</v>
       </c>
       <c r="DW6" t="n">
         <v>0.05</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.1</v>
+        <v>10.9</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.95</v>
+        <v>6.85</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.16</v>
+        <v>4.05</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.74</v>
+        <v>17.45</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="7">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
@@ -3400,82 +3400,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="H7" t="n">
-        <v>95.22</v>
+        <v>97.5</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L7" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="M7" t="n">
-        <v>45.89</v>
+        <v>46.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>10.22</v>
+        <v>10.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.890000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="R7" t="n">
-        <v>7.11</v>
+        <v>6.9</v>
       </c>
       <c r="S7" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>52.22</v>
+        <v>51.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.67</v>
+        <v>12.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.67</v>
+        <v>4.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>21.11</v>
+        <v>20.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AF7" t="n">
         <v>0.2</v>
@@ -3559,70 +3559,70 @@
         <v>2.1</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.210000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BK7" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BM7" t="n">
         <v>1</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.21</v>
+        <v>4.3</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT7" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BU7" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BV7" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BW7" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BX7" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.94</v>
+        <v>3.93</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="CC7" t="n">
         <v>2.8</v>
@@ -3631,157 +3631,157 @@
         <v>3.03</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.51</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL7" t="n">
         <v>1.93</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP7" t="n">
         <v>1.55</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CR7" t="n">
         <v>1.35</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CT7" t="n">
         <v>3.34</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CW7" t="n">
         <v>1.55</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DB7" t="n">
         <v>1.27</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DH7" t="n">
-        <v>100.53</v>
+        <v>101.4</v>
       </c>
       <c r="DI7" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.42</v>
+        <v>4.6</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM7" t="n">
-        <v>45.63</v>
+        <v>46.15</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="DP7" t="n">
         <v>11</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.42</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.53</v>
+        <v>7.4</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>52.53</v>
+        <v>52</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DX7" t="n">
-        <v>12.05</v>
+        <v>12</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.63</v>
+        <v>7.6</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="EA7" t="n">
-        <v>21.21</v>
+        <v>20.85</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="8">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
         <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0.22</v>
@@ -3881,139 +3881,139 @@
         <v>1.89</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG8" t="n">
         <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AI8" t="n">
-        <v>86.59999999999999</v>
+        <v>82.64</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="AM8" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>40.45</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>44.91</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BK8" t="n">
         <v>0.7</v>
       </c>
-      <c r="AN8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO8" t="n">
+      <c r="BL8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BM8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU8" t="n">
+      <c r="BN8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BO8" t="n">
         <v>1.3</v>
       </c>
-      <c r="AV8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>8.369999999999999</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.37</v>
-      </c>
       <c r="BP8" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="BQ8" t="n">
         <v>4</v>
       </c>
       <c r="BR8" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS8" t="n">
-        <v>89.47</v>
+        <v>85</v>
       </c>
       <c r="BT8" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BU8" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV8" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW8" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX8" t="n">
-        <v>68.42</v>
+        <v>65</v>
       </c>
       <c r="BY8" t="n">
         <v>2.18</v>
@@ -4022,40 +4022,40 @@
         <v>2.31</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.78</v>
+        <v>3.81</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.93</v>
+        <v>4.02</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.29</v>
+        <v>4.37</v>
       </c>
       <c r="CE8" t="n">
         <v>1.33</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CH8" t="n">
         <v>1.49</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.69</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CM8" t="n">
         <v>2.2</v>
@@ -4067,10 +4067,10 @@
         <v>1.24</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
@@ -4106,85 +4106,85 @@
         <v>1.3</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF8" t="n">
         <v>1.1</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="DH8" t="n">
-        <v>96.58</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.53</v>
+        <v>4.4</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM8" t="n">
-        <v>44.37</v>
+        <v>44.4</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.58</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.47</v>
+        <v>12.55</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.16</v>
+        <v>6.3</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.68</v>
+        <v>49.65</v>
       </c>
       <c r="DW8" t="n">
         <v>0.1</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.630000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.26</v>
+        <v>4.15</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.47</v>
+        <v>19</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="9">
@@ -4194,94 +4194,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F9" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="G9" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>89.78</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J9" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>0.44</v>
+        <v>0.3</v>
       </c>
       <c r="M9" t="n">
-        <v>41</v>
+        <v>39.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>12.44</v>
+        <v>12.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.56</v>
+        <v>13.7</v>
       </c>
       <c r="R9" t="n">
-        <v>8.890000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>47</v>
+        <v>45.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.78</v>
+        <v>14.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.78</v>
+        <v>5.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.11</v>
+        <v>16.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4365,70 +4365,70 @@
         <v>2.33</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.17</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="BL9" t="n">
         <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.83</v>
+        <v>3.58</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="BR9" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BS9" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU9" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BV9" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.65</v>
+        <v>3.32</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.68</v>
+        <v>3.38</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.05</v>
+        <v>4.17</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.53</v>
+        <v>4.64</v>
       </c>
       <c r="CC9" t="n">
         <v>6.02</v>
@@ -4437,157 +4437,157 @@
         <v>6.43</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.39</v>
+        <v>3.43</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO9" t="n">
         <v>1.19</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="CR9" t="n">
         <v>1.36</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="CT9" t="n">
         <v>3.2</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CW9" t="n">
         <v>1.66</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="DB9" t="n">
         <v>1.32</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="DE9" t="n">
         <v>0.11</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="DG9" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="DH9" t="n">
-        <v>86.72</v>
+        <v>84.42</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.39</v>
+        <v>2.58</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="DM9" t="n">
-        <v>36.34</v>
+        <v>35.74</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.61</v>
+        <v>12.58</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.23</v>
+        <v>13.32</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.44</v>
+        <v>8.32</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47.34</v>
+        <v>46.32</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.06</v>
+        <v>13.1</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.16</v>
+        <v>8.26</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.89</v>
+        <v>4.84</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.67</v>
+        <v>17.05</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="EC9" t="n">
-        <v>2</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="10">
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4690,49 +4690,49 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="AI10" t="n">
-        <v>85.56</v>
+        <v>80.2</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AL10" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>38.44</v>
+        <v>38.6</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.33</v>
+        <v>11.3</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.22</v>
+        <v>10.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4744,82 +4744,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>44</v>
+        <v>43.1</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.22</v>
+        <v>11.3</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.78</v>
+        <v>7.9</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>20.44</v>
+        <v>19.9</v>
       </c>
       <c r="BE10" t="n">
         <v>1.23</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.369999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BM10" t="n">
         <v>1.05</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.79</v>
+        <v>4.05</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.58</v>
+        <v>5.6</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BT10" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BU10" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BV10" t="n">
-        <v>5.26</v>
+        <v>10</v>
       </c>
       <c r="BW10" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX10" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY10" t="n">
         <v>4.35</v>
@@ -4828,43 +4828,43 @@
         <v>4.93</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.16</v>
+        <v>4.26</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.34</v>
+        <v>4.46</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.31</v>
+        <v>5.9</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.74</v>
+        <v>6.26</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CH10" t="n">
         <v>1.59</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CK10" t="n">
         <v>1.52</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CN10" t="n">
         <v>1.89</v>
@@ -4873,10 +4873,10 @@
         <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CR10" t="n">
         <v>1.38</v>
@@ -4891,31 +4891,31 @@
         <v>1.61</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY10" t="n">
         <v>1.91</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB10" t="n">
         <v>1.32</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
@@ -4924,40 +4924,40 @@
         <v>1.05</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="DH10" t="n">
-        <v>84.37</v>
+        <v>81.75</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.74</v>
+        <v>4.65</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DM10" t="n">
-        <v>38.58</v>
+        <v>38.65</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.63</v>
+        <v>10.65</v>
       </c>
       <c r="DQ10" t="n">
-        <v>10.47</v>
+        <v>10.5</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.789999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4969,28 +4969,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>41.95</v>
+        <v>41.6</v>
       </c>
       <c r="DW10" t="n">
         <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.37</v>
+        <v>11.4</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.79</v>
+        <v>7.85</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.73</v>
+        <v>18.55</v>
       </c>
       <c r="EB10" t="n">
         <v>1.25</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11">
@@ -5000,94 +5000,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F11" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="H11" t="n">
-        <v>116.44</v>
+        <v>114.6</v>
       </c>
       <c r="I11" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="J11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M11" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.67</v>
       </c>
-      <c r="K11" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="M11" t="n">
-        <v>53.22</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="P11" t="n">
-        <v>15.44</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="R11" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>54.33</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>21.22</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AF11" t="n">
         <v>0.1</v>
@@ -5171,70 +5171,70 @@
         <v>2.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.42</v>
+        <v>10.55</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BM11" t="n">
         <v>1</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.89</v>
+        <v>5.05</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.53</v>
+        <v>5.5</v>
       </c>
       <c r="BR11" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS11" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT11" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BU11" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BV11" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW11" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX11" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="CC11" t="n">
         <v>3</v>
@@ -5243,154 +5243,154 @@
         <v>3.1</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.72</v>
+        <v>3.68</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CW11" t="n">
         <v>1.55</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DB11" t="n">
         <v>1.26</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="DH11" t="n">
-        <v>111.21</v>
+        <v>110.55</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.16</v>
+        <v>5.05</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="DM11" t="n">
-        <v>48.74</v>
+        <v>47.5</v>
       </c>
       <c r="DN11" t="n">
         <v>0.9</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.84</v>
+        <v>14.65</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.050000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.21</v>
+        <v>6.45</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>52.95</v>
+        <v>53.25</v>
       </c>
       <c r="DW11" t="n">
         <v>0.05</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.11</v>
+        <v>12.9</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.16</v>
+        <v>8</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.21</v>
+        <v>21.5</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="EC11" t="n">
         <v>2</v>
@@ -5637,7 +5637,7 @@
         <v>3.9</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="CC12" t="n">
         <v>4.01</v>
@@ -5697,7 +5697,7 @@
         <v>1.6</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CW12" t="n">
         <v>1.59</v>
@@ -5721,7 +5721,7 @@
         <v>1.68</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="DE12" t="n">
         <v>0.2</v>
@@ -5806,13 +5806,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -5899,136 +5899,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AI13" t="n">
-        <v>94.33</v>
+        <v>95.2</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="AL13" t="n">
         <v>4</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN13" t="n">
-        <v>44.89</v>
+        <v>43.9</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.22</v>
+        <v>11.4</v>
       </c>
       <c r="AR13" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>95</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>75</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>55</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>35</v>
+      </c>
+      <c r="BV13" t="n">
         <v>10</v>
       </c>
-      <c r="AS13" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>41.11</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>21.22</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>9.42</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>94.73999999999999</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>73.68000000000001</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>52.63</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>36.84</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>10.53</v>
-      </c>
       <c r="BW13" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX13" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY13" t="n">
         <v>2.3</v>
@@ -6037,25 +6037,25 @@
         <v>2.4</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.08</v>
+        <v>4.11</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.18</v>
+        <v>5.22</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.47</v>
+        <v>5.49</v>
       </c>
       <c r="CE13" t="n">
         <v>1.32</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CH13" t="n">
         <v>1.55</v>
@@ -6067,13 +6067,13 @@
         <v>1.65</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CL13" t="n">
         <v>1.87</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CN13" t="n">
         <v>1.95</v>
@@ -6085,22 +6085,22 @@
         <v>1.72</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CR13" t="n">
         <v>1.38</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CT13" t="n">
         <v>3.16</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CW13" t="n">
         <v>1.66</v>
@@ -6115,91 +6115,91 @@
         <v>2.46</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DB13" t="n">
         <v>1.31</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="DH13" t="n">
-        <v>109.95</v>
+        <v>109.6</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.32</v>
+        <v>5.25</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM13" t="n">
-        <v>51.79</v>
+        <v>50.95</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.53</v>
+        <v>11.6</v>
       </c>
       <c r="DQ13" t="n">
-        <v>10.05</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.63</v>
+        <v>7.65</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>45.74</v>
+        <v>44.95</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.26</v>
+        <v>11.25</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.84</v>
+        <v>7.8</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="EA13" t="n">
-        <v>23.16</v>
+        <v>22.9</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14">
@@ -6209,94 +6209,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="G14" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="H14" t="n">
-        <v>100.56</v>
+        <v>106.1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="L14" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M14" t="n">
-        <v>44.22</v>
+        <v>47.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.33</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>11.11</v>
+        <v>11.3</v>
       </c>
       <c r="R14" t="n">
-        <v>5.22</v>
+        <v>5.6</v>
       </c>
       <c r="S14" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="U14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>50.67</v>
+        <v>52.6</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>17.56</v>
+        <v>17.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>10.44</v>
+        <v>10.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.11</v>
+        <v>6.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>19.67</v>
+        <v>20</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
         <v>0.4</v>
@@ -6380,70 +6380,70 @@
         <v>1.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.11</v>
+        <v>10.05</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.47</v>
+        <v>4.35</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.63</v>
+        <v>5.7</v>
       </c>
       <c r="BR14" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS14" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT14" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU14" t="n">
-        <v>47.37</v>
+        <v>45</v>
       </c>
       <c r="BV14" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW14" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BX14" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.3</v>
+        <v>4.31</v>
       </c>
       <c r="CC14" t="n">
         <v>3.21</v>
@@ -6458,22 +6458,22 @@
         <v>2.17</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="CH14" t="n">
         <v>1.69</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CK14" t="n">
         <v>1.42</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM14" t="n">
         <v>2.69</v>
@@ -6485,25 +6485,25 @@
         <v>1.13</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CT14" t="n">
         <v>3.13</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CW14" t="n">
         <v>1.52</v>
@@ -6524,52 +6524,52 @@
         <v>1.32</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="DD14" t="n">
         <v>2.19</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="DH14" t="n">
-        <v>99</v>
+        <v>101.85</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.42</v>
+        <v>5.4</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM14" t="n">
-        <v>45.16</v>
+        <v>46.6</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.32</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.42</v>
+        <v>10.55</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.31</v>
+        <v>7.4</v>
       </c>
       <c r="DS14" t="n">
         <v>0.05</v>
@@ -6581,28 +6581,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>51.9</v>
+        <v>52.8</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>16.11</v>
+        <v>16.05</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.31</v>
+        <v>10.35</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.79</v>
+        <v>5.7</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.21</v>
+        <v>17.5</v>
       </c>
       <c r="EB14" t="n">
         <v>1.75</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="15">
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6702,139 +6702,139 @@
         <v>1.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AI15" t="n">
-        <v>90.3</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.6</v>
+        <v>39.18</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.4</v>
+        <v>10.64</v>
       </c>
       <c r="AR15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.6</v>
+        <v>6.45</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AU15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>44.27</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL15" t="n">
         <v>0.8</v>
       </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>9.789999999999999</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>0.79</v>
-      </c>
       <c r="BM15" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="BO15" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BP15" t="n">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.32</v>
+        <v>5.2</v>
       </c>
       <c r="BR15" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS15" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT15" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU15" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV15" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX15" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY15" t="n">
         <v>2.94</v>
@@ -6843,55 +6843,55 @@
         <v>3.03</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.93</v>
+        <v>3.89</v>
       </c>
       <c r="CB15" t="n">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="CC15" t="n">
-        <v>6.49</v>
+        <v>6.26</v>
       </c>
       <c r="CD15" t="n">
-        <v>6.6</v>
+        <v>6.37</v>
       </c>
       <c r="CE15" t="n">
         <v>1.38</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CK15" t="n">
         <v>1.61</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CN15" t="n">
         <v>1.77</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.29</v>
+        <v>3.36</v>
       </c>
       <c r="CR15" t="n">
         <v>1.4</v>
@@ -6906,10 +6906,10 @@
         <v>1.49</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX15" t="n">
         <v>1.66</v>
@@ -6921,13 +6921,13 @@
         <v>2.24</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB15" t="n">
         <v>1.35</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="DD15" t="n">
         <v>3.05</v>
@@ -6939,73 +6939,73 @@
         <v>0.9</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.42</v>
+        <v>2.35</v>
       </c>
       <c r="DH15" t="n">
-        <v>99.73999999999999</v>
+        <v>100.65</v>
       </c>
       <c r="DI15" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DK15" t="n">
         <v>4.95</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="DM15" t="n">
-        <v>43.26</v>
+        <v>43.35</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.42</v>
+        <v>10.55</v>
       </c>
       <c r="DQ15" t="n">
-        <v>9.949999999999999</v>
+        <v>10.15</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.52</v>
+        <v>6.45</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46.16</v>
+        <v>46.65</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.05</v>
+        <v>10.4</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.63</v>
+        <v>6.9</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.31</v>
+        <v>21.35</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="16">
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
@@ -7027,82 +7027,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="G16" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="H16" t="n">
-        <v>102.67</v>
+        <v>97.8</v>
       </c>
       <c r="I16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J16" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="K16" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="L16" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M16" t="n">
-        <v>41.11</v>
+        <v>42.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="P16" t="n">
-        <v>9.220000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.67</v>
+        <v>12.8</v>
       </c>
       <c r="R16" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="S16" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="U16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>54.78</v>
+        <v>56.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.44</v>
+        <v>15.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.67</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.78</v>
+        <v>5.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.33</v>
+        <v>18.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
         <v>0.1</v>
@@ -7186,70 +7186,70 @@
         <v>1.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.789999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BM16" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.32</v>
+        <v>5.25</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS16" t="n">
-        <v>84.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT16" t="n">
-        <v>73.68000000000001</v>
+        <v>70</v>
       </c>
       <c r="BU16" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV16" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW16" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX16" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="CA16" t="n">
         <v>4.05</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="CC16" t="n">
         <v>2.65</v>
@@ -7261,34 +7261,34 @@
         <v>1.25</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="CP16" t="n">
         <v>1.55</v>
@@ -7309,22 +7309,22 @@
         <v>1.68</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="DB16" t="n">
         <v>1.26</v>
@@ -7333,82 +7333,82 @@
         <v>1.59</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="DE16" t="n">
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="DG16" t="n">
         <v>2.95</v>
       </c>
       <c r="DH16" t="n">
-        <v>118.11</v>
+        <v>114.9</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ16" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.53</v>
+        <v>5.55</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM16" t="n">
-        <v>56.53</v>
+        <v>56.25</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.74</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.42</v>
+        <v>12.5</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.79</v>
+        <v>5.85</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>56.69</v>
+        <v>57.35</v>
       </c>
       <c r="DW16" t="n">
         <v>0.05</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.37</v>
+        <v>15.5</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.48</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.9</v>
+        <v>5.95</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.68</v>
+        <v>18.3</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="17">
@@ -7418,13 +7418,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>0.1</v>
@@ -7508,49 +7508,49 @@
         <v>2.6</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="AI17" t="n">
-        <v>90.67</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.22</v>
+        <v>5.7</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.33</v>
+        <v>0.7</v>
       </c>
       <c r="AN17" t="n">
-        <v>42.11</v>
+        <v>44.1</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.11</v>
+        <v>12.7</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.67</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.67</v>
+        <v>8.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AU17" t="n">
         <v>1</v>
@@ -7565,82 +7565,82 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>39.56</v>
+        <v>39.7</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA17" t="n">
-        <v>13.33</v>
+        <v>13.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.890000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.44</v>
+        <v>20.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.58</v>
+        <v>9.75</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.58</v>
+        <v>4.75</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="BR17" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS17" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT17" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU17" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BV17" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW17" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX17" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY17" t="n">
         <v>3.12</v>
@@ -7649,25 +7649,25 @@
         <v>3.74</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.29</v>
+        <v>4.26</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="CE17" t="n">
         <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CH17" t="n">
         <v>1.47</v>
@@ -7688,7 +7688,7 @@
         <v>2.44</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CO17" t="n">
         <v>1.27</v>
@@ -7697,16 +7697,16 @@
         <v>1.88</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CR17" t="n">
         <v>1.4</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="CU17" t="n">
         <v>1.49</v>
@@ -7721,64 +7721,64 @@
         <v>1.58</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.38</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DC17" t="n">
         <v>1.96</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="DE17" t="n">
         <v>0.1</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.16</v>
+        <v>92.05</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.31</v>
+        <v>5.55</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.63</v>
+        <v>0.8</v>
       </c>
       <c r="DM17" t="n">
-        <v>42.26</v>
+        <v>43.25</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.1</v>
+        <v>13.35</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.84</v>
+        <v>10.85</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.58</v>
+        <v>7.55</v>
       </c>
       <c r="DS17" t="n">
         <v>0</v>
@@ -7790,25 +7790,25 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>39.48</v>
+        <v>39.55</v>
       </c>
       <c r="DW17" t="n">
         <v>0.1</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.95</v>
+        <v>13.1</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.32</v>
+        <v>9.5</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.42</v>
+        <v>20.45</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="EC17" t="n">
         <v>2.05</v>
@@ -7821,94 +7821,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F18" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="H18" t="n">
-        <v>106</v>
+        <v>111.4</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="K18" t="n">
-        <v>4.67</v>
+        <v>4.9</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M18" t="n">
-        <v>50.67</v>
+        <v>52.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="P18" t="n">
-        <v>9.779999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.67</v>
+        <v>10.1</v>
       </c>
       <c r="R18" t="n">
-        <v>6.67</v>
+        <v>6.5</v>
       </c>
       <c r="S18" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="T18" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>52.44</v>
+        <v>54</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>15.78</v>
+        <v>16</v>
       </c>
       <c r="AA18" t="n">
-        <v>11.33</v>
+        <v>11.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.44</v>
+        <v>4.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>21.67</v>
+        <v>21.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7992,70 +7992,70 @@
         <v>2.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.789999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL18" t="n">
         <v>1.05</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BP18" t="n">
         <v>5.05</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.74</v>
+        <v>4.75</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS18" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT18" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU18" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV18" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW18" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX18" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.76</v>
+        <v>2.71</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.34</v>
+        <v>4.3</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.36</v>
+        <v>4.32</v>
       </c>
       <c r="CC18" t="n">
         <v>5.78</v>
@@ -8064,19 +8064,19 @@
         <v>6.67</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.55</v>
@@ -8097,25 +8097,25 @@
         <v>1.15</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CR18" t="n">
         <v>1.34</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CT18" t="n">
         <v>3.32</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CW18" t="n">
         <v>1.56</v>
@@ -8127,49 +8127,49 @@
         <v>1.87</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DB18" t="n">
         <v>1.26</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="DE18" t="n">
         <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="DH18" t="n">
-        <v>94.68000000000001</v>
+        <v>97.95</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.42</v>
+        <v>4.55</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM18" t="n">
-        <v>42.63</v>
+        <v>44.05</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="DO18" t="n">
         <v>2</v>
@@ -8178,10 +8178,10 @@
         <v>9.949999999999999</v>
       </c>
       <c r="DQ18" t="n">
-        <v>9.84</v>
+        <v>10.05</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.74</v>
+        <v>7.6</v>
       </c>
       <c r="DS18" t="n">
         <v>0.1</v>
@@ -8193,28 +8193,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>49.89</v>
+        <v>50.8</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.95</v>
+        <v>13.2</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.890000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.05</v>
+        <v>20.15</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19">
@@ -8464,7 +8464,7 @@
         <v>4.5</v>
       </c>
       <c r="CD19" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="CE19" t="n">
         <v>1.28</v>
@@ -8542,7 +8542,7 @@
         <v>1.74</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="DE19" t="n">
         <v>0.2</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -3938,7 +3938,7 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>44.91</v>
+        <v>45</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.09</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.65</v>
+        <v>49.7</v>
       </c>
       <c r="DW8" t="n">
         <v>0.1</v>
@@ -7081,7 +7081,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>56.3</v>
+        <v>56.2</v>
       </c>
       <c r="Y16" t="n">
         <v>0.1</v>
@@ -7387,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>57.35</v>
+        <v>57.3</v>
       </c>
       <c r="DW16" t="n">
         <v>0.05</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0.18</v>
@@ -1469,139 +1469,139 @@
         <v>2.55</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>98</v>
+        <v>95.3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN2" t="n">
-        <v>35.56</v>
+        <v>35.3</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.22</v>
+        <v>12</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.22</v>
+        <v>13.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.44</v>
+        <v>8.4</v>
       </c>
       <c r="AT2" t="n">
         <v>2</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>42.67</v>
+        <v>44.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.11</v>
+        <v>13.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.220000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.25</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.85</v>
+        <v>4.86</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="BR2" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT2" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BU2" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV2" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW2" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX2" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY2" t="n">
         <v>3.31</v>
@@ -1610,25 +1610,25 @@
         <v>3.64</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.09</v>
+        <v>4.06</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="CC2" t="n">
-        <v>5.38</v>
+        <v>5.18</v>
       </c>
       <c r="CD2" t="n">
-        <v>5.72</v>
+        <v>5.54</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CH2" t="n">
         <v>1.54</v>
@@ -1658,7 +1658,7 @@
         <v>1.77</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
@@ -1685,61 +1685,61 @@
         <v>1.93</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DA2" t="n">
         <v>1.9</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC2" t="n">
         <v>1.81</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="DH2" t="n">
-        <v>99.2</v>
+        <v>97.86</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="DM2" t="n">
-        <v>38.8</v>
+        <v>38.52</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.95</v>
+        <v>11.86</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.7</v>
+        <v>12.67</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.25</v>
+        <v>8.24</v>
       </c>
       <c r="DS2" t="n">
         <v>0.05</v>
@@ -1751,28 +1751,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.05</v>
+        <v>45.81</v>
       </c>
       <c r="DW2" t="n">
         <v>0.05</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.7</v>
+        <v>12.76</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.449999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.25</v>
+        <v>4.34</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.7</v>
+        <v>18.81</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0.3</v>
@@ -1872,139 +1872,139 @@
         <v>2.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AI3" t="n">
-        <v>100.78</v>
+        <v>104.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN3" t="n">
-        <v>42.78</v>
+        <v>43.3</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.56</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.78</v>
+        <v>12.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AU3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>56.78</v>
+        <v>57.2</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.44</v>
+        <v>11.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.44</v>
+        <v>7.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>16.11</v>
+        <v>15.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="BH3" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.37</v>
+        <v>3.3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BK3" t="n">
         <v>1</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.53</v>
+        <v>4.35</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.47</v>
+        <v>5.35</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT3" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU3" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV3" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BX3" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY3" t="n">
         <v>1.82</v>
@@ -2013,55 +2013,55 @@
         <v>1.91</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.07</v>
+        <v>2.97</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="CE3" t="n">
         <v>1.25</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.62</v>
+        <v>3.59</v>
       </c>
       <c r="CH3" t="n">
         <v>1.63</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK3" t="n">
         <v>1.49</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM3" t="n">
         <v>2.49</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CO3" t="n">
         <v>1.16</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CR3" t="n">
         <v>1.34</v>
@@ -2076,7 +2076,7 @@
         <v>1.65</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CW3" t="n">
         <v>1.58</v>
@@ -2085,13 +2085,13 @@
         <v>1.57</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB3" t="n">
         <v>1.27</v>
@@ -2100,82 +2100,82 @@
         <v>1.61</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="DH3" t="n">
-        <v>108.84</v>
+        <v>110.2</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.1</v>
+        <v>4.95</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM3" t="n">
-        <v>46.11</v>
+        <v>46.2</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="DP3" t="n">
-        <v>8.789999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.42</v>
+        <v>11.2</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.47</v>
+        <v>7.15</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>58.95</v>
+        <v>59.05</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.95</v>
+        <v>13.75</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.210000000000001</v>
+        <v>9.15</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.74</v>
+        <v>4.6</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.21</v>
+        <v>16.05</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="4">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0.1</v>
@@ -2672,139 +2672,139 @@
         <v>1.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AI5" t="n">
-        <v>104.6</v>
+        <v>101.55</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.3</v>
+        <v>3.73</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AN5" t="n">
-        <v>50.3</v>
+        <v>63</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.7</v>
+        <v>11.55</v>
       </c>
       <c r="AR5" t="n">
-        <v>11</v>
+        <v>11.18</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.3</v>
+        <v>6.45</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>50.6</v>
+        <v>51.91</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.2</v>
+        <v>12.09</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.4</v>
+        <v>21.64</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="BG5" t="n">
         <v>3</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.949999999999999</v>
+        <v>10.05</v>
       </c>
       <c r="BI5" t="n">
         <v>3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL5" t="n">
         <v>1.05</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.6</v>
+        <v>3.81</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU5" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV5" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW5" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY5" t="n">
         <v>1.5</v>
@@ -2813,16 +2813,16 @@
         <v>1.51</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="CE5" t="n">
         <v>1.26</v>
@@ -2831,7 +2831,7 @@
         <v>2.26</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CH5" t="n">
         <v>1.62</v>
@@ -2840,19 +2840,19 @@
         <v>2.27</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CK5" t="n">
         <v>1.48</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO5" t="n">
         <v>1.16</v>
@@ -2861,7 +2861,7 @@
         <v>1.56</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CR5" t="n">
         <v>1.34</v>
@@ -2885,13 +2885,13 @@
         <v>1.58</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.38</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DB5" t="n">
         <v>1.29</v>
@@ -2903,79 +2903,79 @@
         <v>2.47</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="DH5" t="n">
-        <v>109.8</v>
+        <v>107.95</v>
       </c>
       <c r="DI5" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>60.05</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DO5" t="n">
         <v>2</v>
       </c>
-      <c r="DK5" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>53.55</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>1.8</v>
-      </c>
       <c r="DP5" t="n">
-        <v>11.6</v>
+        <v>11.53</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.3</v>
+        <v>10.43</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.6</v>
+        <v>6.66</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>53.35</v>
+        <v>53.91</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.8</v>
+        <v>13.19</v>
       </c>
       <c r="DY5" t="n">
-        <v>8</v>
+        <v>8.43</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.8</v>
+        <v>4.76</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.7</v>
+        <v>19.91</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="6">
@@ -2985,94 +2985,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="H6" t="n">
-        <v>88.09999999999999</v>
+        <v>87.27</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M6" t="n">
-        <v>38.3</v>
+        <v>37.45</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>10.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.4</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>8.300000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>45.7</v>
+        <v>45.09</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.1</v>
+        <v>10.91</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.3</v>
+        <v>6.91</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.9</v>
+        <v>17.64</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3156,70 +3156,70 @@
         <v>1.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.449999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.35</v>
+        <v>4.19</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BR6" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BS6" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT6" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU6" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV6" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW6" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX6" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="CB6" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="CC6" t="n">
         <v>3.63</v>
@@ -3231,40 +3231,40 @@
         <v>1.27</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
       <c r="CH6" t="n">
         <v>1.61</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.55</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO6" t="n">
         <v>1.16</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CR6" t="n">
         <v>1.36</v>
@@ -3279,7 +3279,7 @@
         <v>1.64</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CW6" t="n">
         <v>1.58</v>
@@ -3288,97 +3288,97 @@
         <v>1.54</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DB6" t="n">
         <v>1.28</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DG6" t="n">
         <v>2.05</v>
       </c>
       <c r="DH6" t="n">
-        <v>84.90000000000001</v>
+        <v>84.62</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.35</v>
+        <v>4.24</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM6" t="n">
-        <v>35.4</v>
+        <v>35.09</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.6</v>
+        <v>11.38</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.7</v>
+        <v>10.72</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.95</v>
+        <v>44.67</v>
       </c>
       <c r="DW6" t="n">
         <v>0.05</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.9</v>
+        <v>10.81</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.85</v>
+        <v>6.67</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.05</v>
+        <v>4.14</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.45</v>
+        <v>17.34</v>
       </c>
       <c r="EB6" t="n">
         <v>1.23</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="7">
@@ -3388,13 +3388,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3478,52 +3478,52 @@
         <v>1.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AI7" t="n">
-        <v>105.3</v>
+        <v>107.27</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="AN7" t="n">
-        <v>45.4</v>
+        <v>44.82</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11.7</v>
+        <v>11.64</v>
       </c>
       <c r="AR7" t="n">
         <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.9</v>
+        <v>8.18</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3535,82 +3535,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>52.8</v>
+        <v>54.64</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.5</v>
+        <v>10.73</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.3</v>
+        <v>6.82</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.2</v>
+        <v>3.91</v>
       </c>
       <c r="BD7" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.25</v>
+        <v>4.14</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.35</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.25</v>
+        <v>4.14</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BM7" t="n">
         <v>1</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT7" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BV7" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BW7" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BX7" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BY7" t="n">
         <v>2.48</v>
@@ -3619,40 +3619,40 @@
         <v>2.87</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CK7" t="n">
         <v>1.51</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM7" t="n">
         <v>2.43</v>
@@ -3664,124 +3664,124 @@
         <v>1.15</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.34</v>
+        <v>3.23</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CX7" t="n">
         <v>1.63</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.26</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="DH7" t="n">
-        <v>101.4</v>
+        <v>102.62</v>
       </c>
       <c r="DI7" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.6</v>
+        <v>4.48</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DM7" t="n">
-        <v>46.15</v>
+        <v>45.81</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DP7" t="n">
         <v>11</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.449999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.4</v>
+        <v>7.57</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>12</v>
+        <v>11.57</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.6</v>
+        <v>7.33</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.4</v>
+        <v>4.24</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.85</v>
+        <v>20.71</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="8">
@@ -3791,94 +3791,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="H8" t="n">
-        <v>107.67</v>
+        <v>99.7</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="K8" t="n">
-        <v>5.22</v>
+        <v>5.1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>49.22</v>
+        <v>48.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>9.220000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.33</v>
+        <v>12.3</v>
       </c>
       <c r="R8" t="n">
-        <v>4.56</v>
+        <v>5.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="U8" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V8" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>55.44</v>
+        <v>53.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.78</v>
+        <v>14</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.44</v>
+        <v>9</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.78</v>
+        <v>20.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AF8" t="n">
         <v>0.09</v>
@@ -3962,70 +3962,70 @@
         <v>1.36</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.35</v>
+        <v>8.52</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4</v>
+        <v>4.24</v>
       </c>
       <c r="BR8" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS8" t="n">
-        <v>85</v>
+        <v>80.95</v>
       </c>
       <c r="BT8" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BU8" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV8" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW8" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX8" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CC8" t="n">
         <v>4.02</v>
@@ -4052,25 +4052,25 @@
         <v>1.69</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CM8" t="n">
         <v>2.2</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
@@ -4091,13 +4091,13 @@
         <v>1.74</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA8" t="n">
         <v>1.74</v>
@@ -4106,85 +4106,85 @@
         <v>1.3</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF8" t="n">
         <v>1.1</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.90000000000001</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="DM8" t="n">
-        <v>44.4</v>
+        <v>44.19</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.76</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.55</v>
+        <v>12.53</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.3</v>
+        <v>6.48</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>49.7</v>
+        <v>48.9</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.8</v>
+        <v>12.52</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.65</v>
+        <v>8.48</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="EA8" t="n">
         <v>19</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="9">
@@ -4194,13 +4194,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0.2</v>
@@ -4287,49 +4287,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>83.67</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AL9" t="n">
-        <v>3.67</v>
+        <v>4.1</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>31.67</v>
+        <v>32</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AP9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.78</v>
+        <v>12.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>12.89</v>
+        <v>12.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4341,82 +4341,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>47.67</v>
+        <v>48.1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.33</v>
+        <v>11.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>17.22</v>
+        <v>17.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.369999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="BL9" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BO9" t="n">
         <v>1</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BR9" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BS9" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT9" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>31.58</v>
+        <v>30</v>
       </c>
       <c r="BV9" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>3.32</v>
@@ -4425,28 +4425,28 @@
         <v>3.38</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
       <c r="CC9" t="n">
-        <v>6.02</v>
+        <v>5.66</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.43</v>
+        <v>6.04</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF9" t="n">
         <v>2.42</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI9" t="n">
         <v>2.22</v>
@@ -4455,106 +4455,106 @@
         <v>1.64</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL9" t="n">
         <v>1.9</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO9" t="n">
         <v>1.19</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="CR9" t="n">
         <v>1.36</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CV9" t="n">
         <v>2.37</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX9" t="n">
         <v>1.62</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="DB9" t="n">
         <v>1.32</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="DH9" t="n">
-        <v>84.42</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.63</v>
+        <v>3.85</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.74</v>
+        <v>35.7</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.58</v>
+        <v>12.5</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.32</v>
+        <v>12.95</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DS9" t="n">
         <v>0.05</v>
@@ -4566,28 +4566,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.32</v>
+        <v>46.6</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.1</v>
+        <v>13.15</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.26</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.05</v>
+        <v>17.4</v>
       </c>
       <c r="EB9" t="n">
         <v>1.42</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10">
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
@@ -4609,49 +4609,49 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2</v>
+        <v>2.82</v>
       </c>
       <c r="H10" t="n">
-        <v>83.3</v>
+        <v>80.73</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="M10" t="n">
-        <v>38.7</v>
+        <v>37.45</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O10" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.7</v>
+        <v>10.73</v>
       </c>
       <c r="R10" t="n">
-        <v>8.6</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4663,28 +4663,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>40.1</v>
+        <v>40.82</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>11.5</v>
+        <v>12.27</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.8</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.2</v>
+        <v>17.36</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4768,70 +4768,70 @@
         <v>2.1</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.65</v>
+        <v>10.05</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM10" t="n">
         <v>1.05</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP10" t="n">
         <v>4.05</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>75</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW10" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX10" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY10" t="n">
-        <v>4.35</v>
+        <v>4.22</v>
       </c>
       <c r="BZ10" t="n">
-        <v>4.93</v>
+        <v>4.75</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.26</v>
+        <v>4.22</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.46</v>
+        <v>4.41</v>
       </c>
       <c r="CC10" t="n">
         <v>5.9</v>
@@ -4840,13 +4840,13 @@
         <v>6.26</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF10" t="n">
         <v>2.4</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="CH10" t="n">
         <v>1.59</v>
@@ -4855,7 +4855,7 @@
         <v>2.18</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CK10" t="n">
         <v>1.52</v>
@@ -4864,7 +4864,7 @@
         <v>1.97</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CN10" t="n">
         <v>1.89</v>
@@ -4873,22 +4873,22 @@
         <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CR10" t="n">
         <v>1.38</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="CT10" t="n">
         <v>3.14</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CV10" t="n">
         <v>2.27</v>
@@ -4900,64 +4900,64 @@
         <v>1.57</v>
       </c>
       <c r="CY10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DA10" t="n">
         <v>1.91</v>
-      </c>
-      <c r="CZ10" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="DA10" t="n">
-        <v>1.92</v>
       </c>
       <c r="DB10" t="n">
         <v>1.32</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="DH10" t="n">
-        <v>81.75</v>
+        <v>80.48</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.65</v>
+        <v>4.9</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="DM10" t="n">
-        <v>38.65</v>
+        <v>38</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.65</v>
+        <v>10.43</v>
       </c>
       <c r="DQ10" t="n">
-        <v>10.5</v>
+        <v>10.53</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4969,28 +4969,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>41.6</v>
+        <v>41.91</v>
       </c>
       <c r="DW10" t="n">
         <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.4</v>
+        <v>11.81</v>
       </c>
       <c r="DY10" t="n">
-        <v>7.85</v>
+        <v>8.24</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.55</v>
+        <v>18.57</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="11">
@@ -5806,94 +5806,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="G13" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="H13" t="n">
-        <v>124</v>
+        <v>117.36</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="K13" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M13" t="n">
-        <v>58</v>
+        <v>56.36</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="P13" t="n">
-        <v>11.8</v>
+        <v>11.82</v>
       </c>
       <c r="Q13" t="n">
-        <v>10.1</v>
+        <v>9.91</v>
       </c>
       <c r="R13" t="n">
-        <v>6.7</v>
+        <v>6.82</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>49.9</v>
+        <v>48.91</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.699999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="AC13" t="n">
-        <v>24.9</v>
+        <v>24.82</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5977,70 +5977,70 @@
         <v>2.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.4</v>
+        <v>9.43</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL13" t="n">
         <v>0.95</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.65</v>
+        <v>5.62</v>
       </c>
       <c r="BR13" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT13" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU13" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BV13" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW13" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX13" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.11</v>
+        <v>4.09</v>
       </c>
       <c r="CC13" t="n">
         <v>5.22</v>
@@ -6055,22 +6055,22 @@
         <v>2.52</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CH13" t="n">
         <v>1.55</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.65</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM13" t="n">
         <v>2.51</v>
@@ -6085,7 +6085,7 @@
         <v>1.72</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CR13" t="n">
         <v>1.38</v>
@@ -6100,7 +6100,7 @@
         <v>1.58</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CW13" t="n">
         <v>1.66</v>
@@ -6115,91 +6115,91 @@
         <v>2.46</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="DE13" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.45</v>
+        <v>3.48</v>
       </c>
       <c r="DH13" t="n">
-        <v>109.6</v>
+        <v>106.81</v>
       </c>
       <c r="DI13" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.25</v>
+        <v>5.28</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM13" t="n">
-        <v>50.95</v>
+        <v>50.43</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.6</v>
+        <v>11.62</v>
       </c>
       <c r="DQ13" t="n">
-        <v>9.699999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.65</v>
+        <v>7.67</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.95</v>
+        <v>44.67</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.25</v>
+        <v>11.19</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.8</v>
+        <v>7.62</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.45</v>
+        <v>3.57</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.9</v>
+        <v>22.95</v>
       </c>
       <c r="EB13" t="n">
         <v>1.33</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="14">
@@ -6612,10 +6612,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
@@ -6624,82 +6624,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="G15" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="H15" t="n">
-        <v>110.22</v>
+        <v>102.8</v>
       </c>
       <c r="I15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J15" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="K15" t="n">
-        <v>6.56</v>
+        <v>6.4</v>
       </c>
       <c r="L15" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M15" t="n">
-        <v>48.44</v>
+        <v>49.2</v>
       </c>
       <c r="N15" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O15" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>10.44</v>
+        <v>10.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.22</v>
+        <v>11</v>
       </c>
       <c r="R15" t="n">
-        <v>6.44</v>
+        <v>6.2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="U15" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="V15" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>49.56</v>
+        <v>47.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>10.89</v>
+        <v>11.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.56</v>
+        <v>6.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>22.22</v>
+        <v>21.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF15" t="n">
         <v>0.09</v>
@@ -6783,67 +6783,67 @@
         <v>1.45</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="BO15" t="n">
         <v>1.05</v>
       </c>
       <c r="BP15" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="BR15" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS15" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT15" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU15" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV15" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW15" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX15" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.03</v>
+        <v>3.24</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="CB15" t="n">
         <v>3.97</v>
@@ -6858,7 +6858,7 @@
         <v>1.38</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CG15" t="n">
         <v>3</v>
@@ -6867,7 +6867,7 @@
         <v>1.44</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.84</v>
@@ -6876,7 +6876,7 @@
         <v>1.61</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CM15" t="n">
         <v>2.23</v>
@@ -6888,10 +6888,10 @@
         <v>1.29</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CR15" t="n">
         <v>1.4</v>
@@ -6906,7 +6906,7 @@
         <v>1.49</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CW15" t="n">
         <v>1.89</v>
@@ -6927,7 +6927,7 @@
         <v>1.35</v>
       </c>
       <c r="DC15" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DD15" t="n">
         <v>3.05</v>
@@ -6936,76 +6936,76 @@
         <v>0.05</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DH15" t="n">
-        <v>100.65</v>
+        <v>97.56999999999999</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="DK15" t="n">
         <v>4.95</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM15" t="n">
-        <v>43.35</v>
+        <v>43.95</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.55</v>
+        <v>10.48</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.15</v>
+        <v>10.09</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.45</v>
+        <v>6.33</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46.65</v>
+        <v>45.95</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.4</v>
+        <v>10.62</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.9</v>
+        <v>6.95</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.35</v>
+        <v>21.14</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="16">
@@ -7015,13 +7015,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7105,139 +7105,139 @@
         <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="AI16" t="n">
-        <v>132</v>
+        <v>127.09</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.9</v>
+        <v>5.82</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN16" t="n">
-        <v>70.40000000000001</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.2</v>
+        <v>10.18</v>
       </c>
       <c r="AR16" t="n">
-        <v>12.2</v>
+        <v>11.91</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>58.4</v>
+        <v>59.27</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>15.3</v>
+        <v>14.55</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.300000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="BC16" t="n">
-        <v>6</v>
+        <v>5.73</v>
       </c>
       <c r="BD16" t="n">
-        <v>18.1</v>
+        <v>18.64</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.699999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM16" t="n">
         <v>0.95</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="BR16" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT16" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU16" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV16" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW16" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX16" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY16" t="n">
         <v>2.04</v>
@@ -7246,55 +7246,55 @@
         <v>2.03</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="CB16" t="n">
         <v>4.05</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.79</v>
+        <v>2.69</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="CH16" t="n">
         <v>1.65</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CK16" t="n">
         <v>1.49</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO16" t="n">
         <v>1.14</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="CR16" t="n">
         <v>1.33</v>
@@ -7309,106 +7309,106 @@
         <v>1.68</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="DE16" t="n">
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="DH16" t="n">
-        <v>114.9</v>
+        <v>113.14</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ16" t="n">
         <v>2</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.55</v>
+        <v>5.52</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM16" t="n">
-        <v>56.25</v>
+        <v>56.81</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DP16" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.5</v>
+        <v>12.33</v>
       </c>
       <c r="DR16" t="n">
-        <v>5.85</v>
+        <v>5.81</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>57.3</v>
+        <v>57.81</v>
       </c>
       <c r="DW16" t="n">
         <v>0.05</v>
       </c>
       <c r="DX16" t="n">
-        <v>15.5</v>
+        <v>15.1</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.550000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.95</v>
+        <v>5.81</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.3</v>
+        <v>18.57</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="17">
@@ -7418,94 +7418,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="G17" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="H17" t="n">
-        <v>93.5</v>
+        <v>90.73</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="K17" t="n">
-        <v>5.4</v>
+        <v>5.36</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="M17" t="n">
-        <v>42.4</v>
+        <v>41.91</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="P17" t="n">
-        <v>14</v>
+        <v>13.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.9</v>
+        <v>11.73</v>
       </c>
       <c r="R17" t="n">
-        <v>6.6</v>
+        <v>6.36</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>39.4</v>
+        <v>38.27</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.6</v>
+        <v>12.45</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.4</v>
+        <v>20.36</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AF17" t="n">
         <v>0.1</v>
@@ -7589,70 +7589,70 @@
         <v>1.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.75</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL17" t="n">
         <v>0.9</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="BR17" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS17" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT17" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU17" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV17" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW17" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX17" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.12</v>
+        <v>3.03</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CC17" t="n">
         <v>4.26</v>
@@ -7670,7 +7670,7 @@
         <v>3.11</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CI17" t="n">
         <v>2.03</v>
@@ -7682,13 +7682,13 @@
         <v>1.5</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CO17" t="n">
         <v>1.27</v>
@@ -7703,13 +7703,13 @@
         <v>1.4</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV17" t="n">
         <v>2.09</v>
@@ -7721,13 +7721,13 @@
         <v>1.58</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="DB17" t="n">
         <v>1.33</v>
@@ -7736,82 +7736,82 @@
         <v>1.96</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="DH17" t="n">
-        <v>92.05</v>
+        <v>90.67</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.55</v>
+        <v>5.52</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DM17" t="n">
-        <v>43.25</v>
+        <v>42.95</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.35</v>
+        <v>13.15</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.85</v>
+        <v>10.81</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.55</v>
+        <v>7.38</v>
       </c>
       <c r="DS17" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DT17" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>39.55</v>
+        <v>38.95</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX17" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.5</v>
+        <v>9.43</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.45</v>
+        <v>20.43</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="18">
@@ -7821,13 +7821,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
         <v>0.1</v>
@@ -7914,136 +7914,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="AI18" t="n">
-        <v>84.5</v>
+        <v>84.55</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN18" t="n">
-        <v>35.4</v>
+        <v>37.27</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.1</v>
+        <v>10.27</v>
       </c>
       <c r="AR18" t="n">
-        <v>10</v>
+        <v>9.91</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.699999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="AT18" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AU18" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BL18" t="n">
         <v>1</v>
       </c>
-      <c r="AV18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>1.05</v>
-      </c>
       <c r="BM18" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="BO18" t="n">
         <v>1.1</v>
       </c>
       <c r="BP18" t="n">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.75</v>
+        <v>4.95</v>
       </c>
       <c r="BR18" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>80</v>
+        <v>76.19</v>
       </c>
       <c r="BT18" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU18" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV18" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW18" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX18" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BY18" t="n">
         <v>2.58</v>
@@ -8052,31 +8052,31 @@
         <v>2.71</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.3</v>
+        <v>4.26</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.32</v>
+        <v>4.28</v>
       </c>
       <c r="CC18" t="n">
-        <v>5.78</v>
+        <v>5.58</v>
       </c>
       <c r="CD18" t="n">
-        <v>6.67</v>
+        <v>6.41</v>
       </c>
       <c r="CE18" t="n">
         <v>1.27</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.55</v>
@@ -8085,22 +8085,22 @@
         <v>1.48</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CO18" t="n">
         <v>1.15</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CR18" t="n">
         <v>1.34</v>
@@ -8115,106 +8115,106 @@
         <v>1.7</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CX18" t="n">
         <v>1.55</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="DE18" t="n">
         <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="DH18" t="n">
-        <v>97.95</v>
+        <v>97.34</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.55</v>
+        <v>4.72</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM18" t="n">
-        <v>44.05</v>
+        <v>44.62</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="DO18" t="n">
         <v>2</v>
       </c>
       <c r="DP18" t="n">
-        <v>9.949999999999999</v>
+        <v>10.05</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10.05</v>
+        <v>10</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.6</v>
+        <v>7.67</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>50.8</v>
+        <v>51.57</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.2</v>
+        <v>13.38</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.050000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.15</v>
+        <v>4.19</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.15</v>
+        <v>20.57</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="19">
@@ -8224,94 +8224,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="H19" t="n">
-        <v>107.3</v>
+        <v>101.36</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="K19" t="n">
-        <v>4.8</v>
+        <v>4.73</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M19" t="n">
-        <v>50</v>
+        <v>56.18</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="P19" t="n">
-        <v>12</v>
+        <v>12.09</v>
       </c>
       <c r="Q19" t="n">
-        <v>10.4</v>
+        <v>10.36</v>
       </c>
       <c r="R19" t="n">
-        <v>8.1</v>
+        <v>8.09</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>50.4</v>
+        <v>49</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.4</v>
+        <v>13.27</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.4</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AB19" t="n">
-        <v>5</v>
+        <v>4.73</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.4</v>
+        <v>18.73</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AF19" t="n">
         <v>0.2</v>
@@ -8395,64 +8395,64 @@
         <v>2.1</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.4</v>
+        <v>11.43</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK19" t="n">
         <v>0.9</v>
       </c>
       <c r="BL19" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN19" t="n">
         <v>1.9</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.55</v>
+        <v>4.71</v>
       </c>
       <c r="BQ19" t="n">
-        <v>6.05</v>
+        <v>5.95</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT19" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU19" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BV19" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW19" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX19" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.39</v>
+        <v>2.56</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.43</v>
+        <v>2.64</v>
       </c>
       <c r="CA19" t="n">
         <v>3.92</v>
@@ -8488,7 +8488,7 @@
         <v>1.43</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM19" t="n">
         <v>2.66</v>
@@ -8503,7 +8503,7 @@
         <v>1.64</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
@@ -8539,85 +8539,85 @@
         <v>1.3</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DH19" t="n">
-        <v>95.90000000000001</v>
+        <v>93.33</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DM19" t="n">
-        <v>41.6</v>
+        <v>45.24</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.2</v>
+        <v>11.29</v>
       </c>
       <c r="DQ19" t="n">
-        <v>9.550000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.25</v>
+        <v>9.19</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>47.5</v>
+        <v>46.9</v>
       </c>
       <c r="DW19" t="n">
         <v>0.05</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.75</v>
+        <v>11.76</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.65</v>
+        <v>7.76</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.7</v>
+        <v>17.91</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="EC19" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="H4" t="n">
-        <v>137.9</v>
+        <v>136.18</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="K4" t="n">
-        <v>6.6</v>
+        <v>6.73</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="M4" t="n">
-        <v>67.7</v>
+        <v>68.91</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="P4" t="n">
-        <v>9.4</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="R4" t="n">
-        <v>6.1</v>
+        <v>6.09</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>68.8</v>
+        <v>67.55</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.6</v>
+        <v>20.27</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.1</v>
+        <v>11.27</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AC4" t="n">
-        <v>20.6</v>
+        <v>19.73</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF4" t="n">
         <v>0.1</v>
@@ -2356,37 +2356,37 @@
         <v>2.3</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.85</v>
+        <v>9.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="BO4" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.05</v>
+        <v>5.24</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2398,28 +2398,28 @@
         <v>100</v>
       </c>
       <c r="BU4" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BV4" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BW4" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BX4" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.63</v>
+        <v>7.58</v>
       </c>
       <c r="CB4" t="n">
-        <v>8.31</v>
+        <v>8.24</v>
       </c>
       <c r="CC4" t="n">
         <v>1.32</v>
@@ -2440,22 +2440,22 @@
         <v>1.98</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CK4" t="n">
         <v>1.51</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CO4" t="n">
         <v>1.05</v>
@@ -2475,22 +2475,22 @@
         <v>2.15</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CX4" t="n">
         <v>1.53</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.46</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DB4" t="inlineStr"/>
       <c r="DC4" t="n">
@@ -2500,79 +2500,79 @@
         <v>1.78</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="DH4" t="n">
-        <v>134.85</v>
+        <v>134.09</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.1</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.3</v>
+        <v>6.38</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DM4" t="n">
-        <v>67.84999999999999</v>
+        <v>68.48</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.25</v>
+        <v>9.34</v>
       </c>
       <c r="DQ4" t="n">
-        <v>8.550000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.7</v>
+        <v>5.71</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>68</v>
+        <v>67.38</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>18.9</v>
+        <v>19.28</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.3</v>
+        <v>10.43</v>
       </c>
       <c r="DZ4" t="n">
-        <v>8.6</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="EA4" t="n">
-        <v>20.15</v>
+        <v>19.72</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="5">
@@ -5000,13 +5000,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>0.2</v>
@@ -5090,139 +5090,139 @@
         <v>1.7</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AI11" t="n">
-        <v>106.5</v>
+        <v>103</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN11" t="n">
-        <v>44.7</v>
+        <v>43.73</v>
       </c>
       <c r="AO11" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.3</v>
+        <v>13.82</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.4</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.7</v>
+        <v>7.36</v>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>51.7</v>
+        <v>51.09</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="BA11" t="n">
-        <v>11.4</v>
+        <v>11.18</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.1</v>
+        <v>6.91</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="BD11" t="n">
-        <v>21.2</v>
+        <v>20.27</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.55</v>
+        <v>10.57</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.3</v>
+        <v>3.43</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BM11" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="BP11" t="n">
-        <v>5.05</v>
+        <v>4.9</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="BR11" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BU11" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BV11" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BW11" t="n">
-        <v>10</v>
+        <v>14.29</v>
       </c>
       <c r="BX11" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BY11" t="n">
         <v>2.6</v>
@@ -5231,28 +5231,28 @@
         <v>2.65</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.89</v>
+        <v>4.02</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.95</v>
+        <v>4.09</v>
       </c>
       <c r="CC11" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.1</v>
+        <v>3.64</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CI11" t="n">
         <v>2.48</v>
@@ -5264,7 +5264,7 @@
         <v>1.42</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CM11" t="n">
         <v>2.67</v>
@@ -5276,10 +5276,10 @@
         <v>1.15</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CR11" t="n">
         <v>1.34</v>
@@ -5303,7 +5303,7 @@
         <v>1.52</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.47</v>
@@ -5321,76 +5321,76 @@
         <v>2.5</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="DH11" t="n">
-        <v>110.55</v>
+        <v>108.52</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="DM11" t="n">
-        <v>47.5</v>
+        <v>46.86</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.65</v>
+        <v>14.38</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.449999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.45</v>
+        <v>6.81</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.25</v>
+        <v>52.86</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.9</v>
+        <v>12.71</v>
       </c>
       <c r="DY11" t="n">
-        <v>8</v>
+        <v>7.86</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.9</v>
+        <v>4.86</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.5</v>
+        <v>21</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="EC11" t="n">
         <v>2</v>
@@ -5403,61 +5403,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="G12" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H12" t="n">
-        <v>97.09999999999999</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>45.8</v>
+        <v>46.09</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="O12" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="P12" t="n">
-        <v>7.9</v>
+        <v>7.82</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.5</v>
+        <v>11.64</v>
       </c>
       <c r="R12" t="n">
-        <v>8</v>
+        <v>7.73</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5469,28 +5469,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>48.5</v>
+        <v>48.27</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.3</v>
+        <v>13.91</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.1</v>
+        <v>8.91</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.6</v>
+        <v>20.73</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF12" t="n">
         <v>0.2</v>
@@ -5577,67 +5577,67 @@
         <v>3.05</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.25</v>
+        <v>10.1</v>
       </c>
       <c r="BI12" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL12" t="n">
         <v>0.95</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.15</v>
+        <v>5.05</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT12" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU12" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV12" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW12" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX12" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="CA12" t="n">
         <v>3.9</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="CC12" t="n">
         <v>4.01</v>
@@ -5649,28 +5649,28 @@
         <v>1.29</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.44</v>
+        <v>3.46</v>
       </c>
       <c r="CH12" t="n">
         <v>1.58</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CK12" t="n">
         <v>1.41</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CN12" t="n">
         <v>2.09</v>
@@ -5679,28 +5679,28 @@
         <v>1.18</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CT12" t="n">
         <v>3.24</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CX12" t="n">
         <v>1.55</v>
@@ -5718,52 +5718,52 @@
         <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DH12" t="n">
-        <v>93.09999999999999</v>
+        <v>93.67</v>
       </c>
       <c r="DI12" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM12" t="n">
-        <v>42.65</v>
+        <v>42.95</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.35</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DQ12" t="n">
-        <v>10.75</v>
+        <v>10.86</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.449999999999999</v>
+        <v>9.24</v>
       </c>
       <c r="DS12" t="n">
         <v>0.05</v>
@@ -5775,28 +5775,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.55</v>
+        <v>47.47</v>
       </c>
       <c r="DW12" t="n">
         <v>0.05</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.55</v>
+        <v>13.38</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.949999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.6</v>
+        <v>4.52</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.45</v>
+        <v>19.57</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="13">
@@ -6209,13 +6209,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
         <v>0.1</v>
@@ -6299,52 +6299,52 @@
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.9</v>
+        <v>1.18</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AI14" t="n">
-        <v>97.59999999999999</v>
+        <v>97.91</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.1</v>
+        <v>4.91</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN14" t="n">
-        <v>46</v>
+        <v>45.55</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.6</v>
+        <v>9.91</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6356,82 +6356,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>53</v>
+        <v>53.09</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>14.8</v>
+        <v>15.18</v>
       </c>
       <c r="BB14" t="n">
-        <v>10.2</v>
+        <v>10.64</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="BD14" t="n">
-        <v>15</v>
+        <v>15.18</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.05</v>
+        <v>9.9</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BL14" t="n">
         <v>1.05</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.7</v>
+        <v>5.57</v>
       </c>
       <c r="BR14" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU14" t="n">
-        <v>45</v>
+        <v>42.86</v>
       </c>
       <c r="BV14" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW14" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY14" t="n">
         <v>2.06</v>
@@ -6440,16 +6440,16 @@
         <v>2</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.31</v>
+        <v>4.3</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.27</v>
+        <v>3.15</v>
       </c>
       <c r="CE14" t="n">
         <v>1.24</v>
@@ -6458,7 +6458,7 @@
         <v>2.17</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.96</v>
+        <v>3.95</v>
       </c>
       <c r="CH14" t="n">
         <v>1.69</v>
@@ -6467,16 +6467,16 @@
         <v>2.5</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CK14" t="n">
         <v>1.42</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CN14" t="n">
         <v>2.05</v>
@@ -6485,10 +6485,10 @@
         <v>1.13</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
@@ -6503,7 +6503,7 @@
         <v>1.77</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="CW14" t="n">
         <v>1.52</v>
@@ -6530,46 +6530,46 @@
         <v>2.19</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="DH14" t="n">
-        <v>101.85</v>
+        <v>101.81</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.4</v>
+        <v>5.29</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.6</v>
+        <v>46.34</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.050000000000001</v>
+        <v>9.24</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.55</v>
+        <v>10.38</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.4</v>
+        <v>7.62</v>
       </c>
       <c r="DS14" t="n">
         <v>0.05</v>
@@ -6581,28 +6581,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>52.8</v>
+        <v>52.86</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>16.05</v>
+        <v>16.19</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.35</v>
+        <v>10.57</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.7</v>
+        <v>5.62</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.5</v>
+        <v>17.48</v>
       </c>
       <c r="EB14" t="n">
         <v>1.75</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="15">

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="H3" t="n">
-        <v>116.1</v>
+        <v>118.36</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="K3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M3" t="n">
-        <v>49.1</v>
+        <v>49.82</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O3" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="P3" t="n">
-        <v>9</v>
+        <v>8.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.2</v>
+        <v>10.27</v>
       </c>
       <c r="R3" t="n">
-        <v>6.2</v>
+        <v>6.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>60.9</v>
+        <v>61.55</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.2</v>
+        <v>15.82</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.8</v>
+        <v>10.27</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.4</v>
+        <v>5.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.3</v>
+        <v>16.27</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AF3" t="n">
         <v>0.2</v>
@@ -1953,70 +1953,70 @@
         <v>2.1</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.76</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BK3" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BO3" t="n">
         <v>2.1</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.35</v>
+        <v>4.38</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.35</v>
+        <v>5.38</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT3" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU3" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW3" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BX3" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.04</v>
+        <v>4.05</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
       <c r="CC3" t="n">
         <v>2.97</v>
@@ -2025,157 +2025,157 @@
         <v>3.25</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL3" t="n">
         <v>1.88</v>
       </c>
       <c r="CM3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CV3" t="n">
         <v>2.49</v>
       </c>
-      <c r="CN3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="CO3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="CP3" t="n">
+      <c r="CW3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CX3" t="n">
         <v>1.58</v>
       </c>
-      <c r="CQ3" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="CT3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="CW3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CX3" t="n">
-        <v>1.57</v>
-      </c>
       <c r="CY3" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="DB3" t="n">
         <v>1.27</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="DH3" t="n">
-        <v>110.2</v>
+        <v>111.66</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="DK3" t="n">
-        <v>4.95</v>
+        <v>5.1</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM3" t="n">
-        <v>46.2</v>
+        <v>46.72</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DP3" t="n">
-        <v>8.9</v>
+        <v>8.81</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.2</v>
+        <v>11.19</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.15</v>
+        <v>7.09</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>59.05</v>
+        <v>59.48</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.75</v>
+        <v>13.67</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.15</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.6</v>
+        <v>4.72</v>
       </c>
       <c r="EA3" t="n">
         <v>16.05</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>0.27</v>
@@ -2275,118 +2275,118 @@
         <v>1.55</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AI4" t="n">
-        <v>131.8</v>
+        <v>132.64</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AL4" t="n">
-        <v>6</v>
+        <v>5.82</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>68</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.1</v>
+        <v>8.82</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.3</v>
+        <v>5.82</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>67.2</v>
+        <v>67</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>18.2</v>
+        <v>17.55</v>
       </c>
       <c r="BB4" t="n">
-        <v>9.5</v>
+        <v>8.91</v>
       </c>
       <c r="BC4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.7</v>
+        <v>19.45</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.67</v>
+        <v>4.59</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.9</v>
+        <v>9.73</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.67</v>
+        <v>4.59</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BP4" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.24</v>
+        <v>5.18</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2398,16 +2398,16 @@
         <v>100</v>
       </c>
       <c r="BU4" t="n">
-        <v>76.19</v>
+        <v>72.73</v>
       </c>
       <c r="BV4" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BW4" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BX4" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY4" t="n">
         <v>1.17</v>
@@ -2416,34 +2416,34 @@
         <v>1.18</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.58</v>
+        <v>7.51</v>
       </c>
       <c r="CB4" t="n">
-        <v>8.24</v>
+        <v>8.15</v>
       </c>
       <c r="CC4" t="n">
         <v>1.32</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CE4" t="n">
         <v>1.15</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CG4" t="n">
-        <v>4.94</v>
+        <v>4.92</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CI4" t="n">
         <v>2.17</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CK4" t="n">
         <v>1.51</v>
@@ -2458,27 +2458,27 @@
         <v>1.91</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="CP4" t="n">
         <v>1.28</v>
       </c>
       <c r="CQ4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CR4" t="inlineStr"/>
       <c r="CS4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CX4" t="n">
         <v>1.53</v>
@@ -2490,7 +2490,7 @@
         <v>2.46</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="DB4" t="inlineStr"/>
       <c r="DC4" t="n">
@@ -2500,79 +2500,79 @@
         <v>1.78</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="DH4" t="n">
-        <v>134.09</v>
+        <v>134.41</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.38</v>
+        <v>6.28</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="DM4" t="n">
-        <v>68.48</v>
+        <v>68.36</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.34</v>
+        <v>9.18</v>
       </c>
       <c r="DQ4" t="n">
-        <v>8.48</v>
+        <v>8.5</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.71</v>
+        <v>5.95</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>67.38</v>
+        <v>67.27</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>19.28</v>
+        <v>18.91</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.43</v>
+        <v>10.09</v>
       </c>
       <c r="DZ4" t="n">
-        <v>8.859999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.72</v>
+        <v>19.59</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="5">
@@ -2582,94 +2582,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="H5" t="n">
-        <v>115</v>
+        <v>114.09</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="K5" t="n">
-        <v>7.2</v>
+        <v>7.18</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M5" t="n">
-        <v>56.8</v>
+        <v>57.09</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="O5" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="P5" t="n">
-        <v>11.5</v>
+        <v>11.36</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.6</v>
+        <v>9.18</v>
       </c>
       <c r="R5" t="n">
-        <v>6.9</v>
+        <v>6.82</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>56.1</v>
+        <v>56</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.4</v>
+        <v>14.36</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.9</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.5</v>
+        <v>5.73</v>
       </c>
       <c r="AC5" t="n">
         <v>18</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AF5" t="n">
         <v>0.18</v>
@@ -2753,70 +2753,70 @@
         <v>2.09</v>
       </c>
       <c r="BG5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.05</v>
+        <v>10</v>
       </c>
       <c r="BI5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL5" t="n">
         <v>1.05</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.81</v>
+        <v>3.77</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.67</v>
+        <v>5.68</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT5" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU5" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BV5" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW5" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX5" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CA5" t="n">
         <v>4.33</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
       <c r="CC5" t="n">
         <v>2.38</v>
@@ -2831,7 +2831,7 @@
         <v>2.26</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CH5" t="n">
         <v>1.62</v>
@@ -2858,10 +2858,10 @@
         <v>1.16</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CR5" t="n">
         <v>1.34</v>
@@ -2882,13 +2882,13 @@
         <v>1.66</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY5" t="n">
         <v>1.87</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="DA5" t="n">
         <v>1.97</v>
@@ -2903,79 +2903,79 @@
         <v>2.47</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="DH5" t="n">
-        <v>107.95</v>
+        <v>107.82</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ5" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.38</v>
+        <v>5.45</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM5" t="n">
-        <v>60.05</v>
+        <v>60.04</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="DO5" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.53</v>
+        <v>11.46</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.43</v>
+        <v>10.18</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.66</v>
+        <v>6.64</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>53.91</v>
+        <v>53.96</v>
       </c>
       <c r="DW5" t="n">
         <v>0.09</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.19</v>
+        <v>13.22</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.43</v>
+        <v>8.32</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.76</v>
+        <v>4.91</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.91</v>
+        <v>19.82</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="6">
@@ -2985,13 +2985,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0.18</v>
@@ -3078,136 +3078,136 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AH6" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AI6" t="n">
-        <v>81.7</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.6</v>
+        <v>4.91</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN6" t="n">
-        <v>32.5</v>
+        <v>35</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.2</v>
+        <v>12.09</v>
       </c>
       <c r="AR6" t="n">
-        <v>13</v>
+        <v>12.82</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.3</v>
+        <v>6.73</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>44.2</v>
+        <v>45.27</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.7</v>
+        <v>11.55</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.4</v>
+        <v>7.36</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.3</v>
+        <v>4.18</v>
       </c>
       <c r="BD6" t="n">
-        <v>17</v>
+        <v>17.27</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.19</v>
+        <v>9.23</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="BR6" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT6" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU6" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX6" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BY6" t="n">
         <v>3.2</v>
@@ -3216,85 +3216,85 @@
         <v>3.24</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="CC6" t="n">
         <v>3.63</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.89</v>
+        <v>3.85</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CY6" t="n">
         <v>1.82</v>
       </c>
-      <c r="CM6" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>1.81</v>
-      </c>
       <c r="CZ6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="DB6" t="n">
         <v>1.28</v>
@@ -3303,82 +3303,82 @@
         <v>1.68</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="DE6" t="n">
         <v>0.09</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="DH6" t="n">
-        <v>84.62</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.24</v>
+        <v>4.41</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM6" t="n">
-        <v>35.09</v>
+        <v>36.22</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.38</v>
+        <v>11.37</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.72</v>
+        <v>10.73</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.9</v>
+        <v>7.59</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.67</v>
+        <v>45.18</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.81</v>
+        <v>11.23</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.67</v>
+        <v>7.14</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.34</v>
+        <v>17.45</v>
       </c>
       <c r="EB6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="EC6" t="n">
         <v>1.23</v>
-      </c>
-      <c r="EC6" t="n">
-        <v>1.19</v>
       </c>
     </row>
     <row r="7">
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
@@ -3400,82 +3400,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="H7" t="n">
-        <v>97.5</v>
+        <v>93.27</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="K7" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="M7" t="n">
-        <v>46.9</v>
+        <v>44.09</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="P7" t="n">
-        <v>10.3</v>
+        <v>10.36</v>
       </c>
       <c r="Q7" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="R7" t="n">
-        <v>6.9</v>
+        <v>7.45</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>51.2</v>
+        <v>50.55</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.5</v>
+        <v>12.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.9</v>
+        <v>7.45</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.4</v>
+        <v>20.09</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.45</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.3</v>
       </c>
       <c r="AF7" t="n">
         <v>0.18</v>
@@ -3559,70 +3559,70 @@
         <v>2.09</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.289999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="BK7" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BM7" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT7" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU7" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BV7" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BW7" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BX7" t="n">
-        <v>76.19</v>
+        <v>72.73</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="CC7" t="n">
         <v>2.86</v>
@@ -3631,19 +3631,19 @@
         <v>3.07</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CH7" t="n">
         <v>1.63</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.52</v>
@@ -3652,34 +3652,34 @@
         <v>1.51</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CV7" t="n">
         <v>2.56</v>
@@ -3691,64 +3691,64 @@
         <v>1.63</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="DE7" t="n">
         <v>0.09</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="DG7" t="n">
         <v>2.09</v>
       </c>
       <c r="DH7" t="n">
-        <v>102.62</v>
+        <v>100.27</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.48</v>
+        <v>4.36</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM7" t="n">
-        <v>45.81</v>
+        <v>44.46</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="DP7" t="n">
         <v>11</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.43</v>
+        <v>9.5</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.57</v>
+        <v>7.82</v>
       </c>
       <c r="DS7" t="n">
         <v>0.14</v>
@@ -3760,28 +3760,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53</v>
+        <v>52.6</v>
       </c>
       <c r="DW7" t="n">
         <v>0.09</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.57</v>
+        <v>11.59</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.33</v>
+        <v>7.14</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.24</v>
+        <v>4.46</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.71</v>
+        <v>20.54</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="8">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>0.2</v>
@@ -3881,139 +3881,139 @@
         <v>1.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG8" t="n">
         <v>1</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AI8" t="n">
-        <v>82.64</v>
+        <v>81.25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.73</v>
+        <v>3.92</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AN8" t="n">
-        <v>40.45</v>
+        <v>38.83</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10.27</v>
+        <v>9.92</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.73</v>
+        <v>12.33</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.73</v>
+        <v>8</v>
       </c>
       <c r="AT8" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>45</v>
+        <v>44.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.18</v>
+        <v>11.33</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>8.17</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.55</v>
+        <v>17.25</v>
       </c>
       <c r="BE8" t="n">
         <v>1.22</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.52</v>
+        <v>8.68</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.29</v>
+        <v>4.36</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.24</v>
+        <v>4.32</v>
       </c>
       <c r="BR8" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS8" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BU8" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV8" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX8" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY8" t="n">
         <v>2.16</v>
@@ -4025,13 +4025,13 @@
         <v>3.73</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="CE8" t="n">
         <v>1.33</v>
@@ -4043,7 +4043,7 @@
         <v>3.24</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CI8" t="n">
         <v>2.14</v>
@@ -4058,7 +4058,7 @@
         <v>2.13</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN8" t="n">
         <v>1.75</v>
@@ -4070,7 +4070,7 @@
         <v>1.81</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
@@ -4091,100 +4091,100 @@
         <v>1.74</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB8" t="n">
         <v>1.3</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DD8" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="DH8" t="n">
-        <v>90.76000000000001</v>
+        <v>89.64</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.38</v>
+        <v>4.46</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM8" t="n">
-        <v>44.19</v>
+        <v>43.13</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.76</v>
+        <v>9.59</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.53</v>
+        <v>12.32</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.48</v>
+        <v>6.68</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.9</v>
+        <v>48.45</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.52</v>
+        <v>12.54</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.48</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="EA8" t="n">
-        <v>19</v>
+        <v>18.77</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -4194,94 +4194,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>85.09999999999999</v>
+        <v>86.18000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="M9" t="n">
-        <v>39.4</v>
+        <v>39.82</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="P9" t="n">
-        <v>12.4</v>
+        <v>12.36</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.7</v>
+        <v>13.09</v>
       </c>
       <c r="R9" t="n">
-        <v>8.6</v>
+        <v>8.27</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.1</v>
+        <v>46.18</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.7</v>
+        <v>14.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.6</v>
+        <v>5.45</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.9</v>
+        <v>17.73</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4365,70 +4365,70 @@
         <v>2.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.85</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="BL9" t="n">
         <v>0.95</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="BO9" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="BR9" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BS9" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU9" t="n">
-        <v>30</v>
+        <v>33.33</v>
       </c>
       <c r="BV9" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.32</v>
+        <v>3.23</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.38</v>
+        <v>3.29</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.58</v>
+        <v>4.51</v>
       </c>
       <c r="CC9" t="n">
         <v>5.66</v>
@@ -4440,25 +4440,25 @@
         <v>1.31</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK9" t="n">
         <v>1.49</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CM9" t="n">
         <v>2.47</v>
@@ -4467,31 +4467,31 @@
         <v>1.93</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="CW9" t="n">
         <v>1.68</v>
-      </c>
-      <c r="CQ9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CS9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="CT9" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="CU9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CV9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="CW9" t="n">
-        <v>1.67</v>
       </c>
       <c r="CX9" t="n">
         <v>1.62</v>
@@ -4515,46 +4515,46 @@
         <v>2.68</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="DG9" t="n">
         <v>2</v>
       </c>
       <c r="DH9" t="n">
-        <v>82.34999999999999</v>
+        <v>83.05</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.7</v>
+        <v>36.1</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.7</v>
+        <v>0.66</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.5</v>
+        <v>12.47</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.95</v>
+        <v>12.67</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0.05</v>
@@ -4566,28 +4566,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.6</v>
+        <v>47.09</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DX9" t="n">
         <v>13.15</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.4</v>
+        <v>17.81</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="10">
@@ -5000,94 +5000,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="G11" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="H11" t="n">
-        <v>114.6</v>
+        <v>112.82</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="K11" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="L11" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="M11" t="n">
-        <v>50.3</v>
+        <v>52</v>
       </c>
       <c r="N11" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="P11" t="n">
-        <v>15</v>
+        <v>14.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.5</v>
+        <v>9.18</v>
       </c>
       <c r="R11" t="n">
-        <v>6.2</v>
+        <v>6.09</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>54.8</v>
+        <v>55.36</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.4</v>
+        <v>15.36</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.9</v>
+        <v>9.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.5</v>
+        <v>5.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.8</v>
+        <v>21.64</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AF11" t="n">
         <v>0.09</v>
@@ -5171,70 +5171,70 @@
         <v>2.27</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.57</v>
+        <v>10.64</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.71</v>
+        <v>0.82</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.67</v>
+        <v>5.68</v>
       </c>
       <c r="BR11" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS11" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT11" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU11" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BV11" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BW11" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX11" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="CC11" t="n">
         <v>3.5</v>
@@ -5243,34 +5243,34 @@
         <v>3.64</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.75</v>
+        <v>3.73</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CK11" t="n">
         <v>1.42</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO11" t="n">
         <v>1.15</v>
@@ -5279,13 +5279,13 @@
         <v>1.55</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CR11" t="n">
         <v>1.34</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CT11" t="n">
         <v>3.33</v>
@@ -5294,22 +5294,22 @@
         <v>1.63</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CX11" t="n">
         <v>1.52</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.47</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB11" t="n">
         <v>1.26</v>
@@ -5318,82 +5318,82 @@
         <v>1.62</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF11" t="n">
         <v>1.09</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DH11" t="n">
-        <v>108.52</v>
+        <v>107.91</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="DM11" t="n">
-        <v>46.86</v>
+        <v>47.86</v>
       </c>
       <c r="DN11" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.38</v>
+        <v>14.09</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.529999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.81</v>
+        <v>6.72</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>52.86</v>
+        <v>53.22</v>
       </c>
       <c r="DW11" t="n">
         <v>0.09</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.71</v>
+        <v>13.27</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.86</v>
+        <v>8.32</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.86</v>
+        <v>4.95</v>
       </c>
       <c r="EA11" t="n">
-        <v>21</v>
+        <v>20.96</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="EC11" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="12">
@@ -5403,13 +5403,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0.18</v>
@@ -5493,139 +5493,139 @@
         <v>1.36</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AI12" t="n">
-        <v>89.09999999999999</v>
+        <v>88.73</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AN12" t="n">
-        <v>39.5</v>
+        <v>40.36</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP12" t="n">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="AR12" t="n">
         <v>10</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.9</v>
+        <v>10.36</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>46.6</v>
+        <v>46.27</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.8</v>
+        <v>12.55</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="BC12" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.3</v>
+        <v>18.82</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BF12" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.1</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.05</v>
+        <v>4.91</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT12" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU12" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BV12" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX12" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BY12" t="n">
         <v>2.95</v>
@@ -5634,28 +5634,28 @@
         <v>3.22</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.01</v>
+        <v>4.14</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.04</v>
+        <v>4.22</v>
       </c>
       <c r="CE12" t="n">
         <v>1.29</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CI12" t="n">
         <v>2.34</v>
@@ -5664,7 +5664,7 @@
         <v>1.57</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL12" t="n">
         <v>1.72</v>
@@ -5679,16 +5679,16 @@
         <v>1.18</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CT12" t="n">
         <v>3.24</v>
@@ -5697,7 +5697,7 @@
         <v>1.61</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CW12" t="n">
         <v>1.58</v>
@@ -5706,97 +5706,97 @@
         <v>1.55</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.39</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DB12" t="n">
         <v>1.29</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="DH12" t="n">
-        <v>93.67</v>
+        <v>93.28</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.14</v>
+        <v>4.18</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DM12" t="n">
-        <v>42.95</v>
+        <v>43.22</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.289999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DQ12" t="n">
-        <v>10.86</v>
+        <v>10.82</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.24</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.47</v>
+        <v>47.27</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.38</v>
+        <v>13.23</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.859999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.52</v>
+        <v>4.46</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.57</v>
+        <v>19.78</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="13">
@@ -5806,13 +5806,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0.09</v>
@@ -5899,136 +5899,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AI13" t="n">
-        <v>95.2</v>
+        <v>93.55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="AL13" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN13" t="n">
-        <v>43.9</v>
+        <v>42.64</v>
       </c>
       <c r="AO13" t="n">
         <v>1</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11.4</v>
+        <v>10.82</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.300000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.6</v>
+        <v>8.27</v>
       </c>
       <c r="AT13" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>40</v>
+        <v>40.45</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.9</v>
+        <v>5.82</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="BD13" t="n">
-        <v>20.9</v>
+        <v>21.09</v>
       </c>
       <c r="BE13" t="n">
         <v>1.14</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.43</v>
+        <v>9.41</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.57</v>
+        <v>0.68</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BL13" t="n">
         <v>0.95</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.62</v>
+        <v>5.64</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS13" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT13" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU13" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BV13" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX13" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY13" t="n">
         <v>2.27</v>
@@ -6037,22 +6037,22 @@
         <v>2.37</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="CB13" t="n">
         <v>4.09</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.22</v>
+        <v>5.18</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.49</v>
+        <v>5.48</v>
       </c>
       <c r="CE13" t="n">
         <v>1.32</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CG13" t="n">
         <v>3.28</v>
@@ -6076,7 +6076,7 @@
         <v>2.51</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CO13" t="n">
         <v>1.22</v>
@@ -6085,7 +6085,7 @@
         <v>1.72</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="CR13" t="n">
         <v>1.38</v>
@@ -6112,7 +6112,7 @@
         <v>1.85</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DA13" t="n">
         <v>1.97</v>
@@ -6121,85 +6121,85 @@
         <v>1.3</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.48</v>
+        <v>3.41</v>
       </c>
       <c r="DH13" t="n">
-        <v>106.81</v>
+        <v>105.46</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.28</v>
+        <v>5.14</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DM13" t="n">
-        <v>50.43</v>
+        <v>49.5</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.62</v>
+        <v>11.32</v>
       </c>
       <c r="DQ13" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.67</v>
+        <v>7.55</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.67</v>
+        <v>44.68</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.19</v>
+        <v>11.14</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.62</v>
+        <v>7.5</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.57</v>
+        <v>3.64</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.95</v>
+        <v>22.96</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="14">
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6702,139 +6702,139 @@
         <v>1.5</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>92.81999999999999</v>
+        <v>90.83</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="AM15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>38.58</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>43.25</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>10.08</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>7.42</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>20.58</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BK15" t="n">
         <v>0.45</v>
       </c>
-      <c r="AN15" t="n">
-        <v>39.18</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>10.64</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>9.27</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>44.27</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>20.64</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>0.48</v>
-      </c>
       <c r="BL15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.19</v>
+        <v>5.23</v>
       </c>
       <c r="BR15" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS15" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU15" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX15" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY15" t="n">
         <v>3.1</v>
@@ -6843,16 +6843,16 @@
         <v>3.24</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.97</v>
+        <v>3.99</v>
       </c>
       <c r="CC15" t="n">
         <v>6.26</v>
       </c>
       <c r="CD15" t="n">
-        <v>6.37</v>
+        <v>6.38</v>
       </c>
       <c r="CE15" t="n">
         <v>1.38</v>
@@ -6861,13 +6861,13 @@
         <v>2.82</v>
       </c>
       <c r="CG15" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CH15" t="n">
         <v>1.44</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.84</v>
@@ -6876,10 +6876,10 @@
         <v>1.61</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CN15" t="n">
         <v>1.77</v>
@@ -6891,7 +6891,7 @@
         <v>1.94</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CR15" t="n">
         <v>1.4</v>
@@ -6900,7 +6900,7 @@
         <v>2.78</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CU15" t="n">
         <v>1.49</v>
@@ -6912,100 +6912,100 @@
         <v>1.89</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DA15" t="n">
         <v>1.75</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC15" t="n">
         <v>1.99</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="DH15" t="n">
-        <v>97.56999999999999</v>
+        <v>96.27</v>
       </c>
       <c r="DI15" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.95</v>
+        <v>4.86</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DM15" t="n">
-        <v>43.95</v>
+        <v>43.41</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.48</v>
+        <v>10.5</v>
       </c>
       <c r="DQ15" t="n">
-        <v>10.09</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.33</v>
+        <v>6.23</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.95</v>
+        <v>45.32</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.62</v>
+        <v>10.63</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.95</v>
+        <v>7.09</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.67</v>
+        <v>3.55</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.14</v>
+        <v>21.09</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="16">
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>11</v>
@@ -7027,82 +7027,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="H16" t="n">
-        <v>97.8</v>
+        <v>97.09</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="K16" t="n">
-        <v>5.2</v>
+        <v>4.91</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M16" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O16" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="P16" t="n">
-        <v>9.699999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.8</v>
+        <v>12.55</v>
       </c>
       <c r="R16" t="n">
-        <v>6.1</v>
+        <v>6.45</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>56.2</v>
+        <v>56.27</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.7</v>
+        <v>15.45</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.9</v>
+        <v>5.73</v>
       </c>
       <c r="AC16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AF16" t="n">
         <v>0.09</v>
@@ -7186,70 +7186,70 @@
         <v>1.82</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.710000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="BM16" t="n">
         <v>0.95</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.24</v>
+        <v>5.09</v>
       </c>
       <c r="BR16" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS16" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BU16" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BV16" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX16" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.04</v>
+        <v>4.08</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.05</v>
+        <v>4.08</v>
       </c>
       <c r="CC16" t="n">
         <v>2.57</v>
@@ -7261,10 +7261,10 @@
         <v>1.26</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="CH16" t="n">
         <v>1.65</v>
@@ -7276,31 +7276,31 @@
         <v>1.54</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CO16" t="n">
         <v>1.14</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CR16" t="n">
         <v>1.33</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CT16" t="n">
         <v>3.36</v>
@@ -7318,97 +7318,97 @@
         <v>1.57</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.36</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="DB16" t="n">
         <v>1.27</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="DH16" t="n">
-        <v>113.14</v>
+        <v>112.09</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ16" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>56.09</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>6</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>57.77</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>15</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="EC16" t="n">
         <v>2</v>
-      </c>
-      <c r="DK16" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="DL16" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="DM16" t="n">
-        <v>56.81</v>
-      </c>
-      <c r="DN16" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="DO16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="DP16" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="DQ16" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="DR16" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="DS16" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DT16" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV16" t="n">
-        <v>57.81</v>
-      </c>
-      <c r="DW16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="DX16" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="DY16" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="DZ16" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="EA16" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="EB16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="EC16" t="n">
-        <v>1.91</v>
       </c>
     </row>
     <row r="17">
@@ -7418,13 +7418,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>0.09</v>
@@ -7508,139 +7508,139 @@
         <v>2.73</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AI17" t="n">
-        <v>90.59999999999999</v>
+        <v>90.27</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.7</v>
+        <v>5.45</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AN17" t="n">
-        <v>44.1</v>
+        <v>43.55</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.7</v>
+        <v>12.18</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.91</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.5</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AU17" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>39.7</v>
+        <v>40</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA17" t="n">
-        <v>13.6</v>
+        <v>13.45</v>
       </c>
       <c r="BB17" t="n">
-        <v>10.2</v>
+        <v>9.91</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.5</v>
+        <v>20.55</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.619999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.67</v>
+        <v>0.73</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BM17" t="n">
         <v>0.86</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.62</v>
+        <v>4.59</v>
       </c>
       <c r="BR17" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS17" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT17" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU17" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BV17" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BW17" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX17" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY17" t="n">
         <v>3.03</v>
@@ -7649,25 +7649,25 @@
         <v>3.6</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.79</v>
+        <v>3.76</v>
       </c>
       <c r="CC17" t="n">
-        <v>4.26</v>
+        <v>4.16</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.35</v>
+        <v>4.25</v>
       </c>
       <c r="CE17" t="n">
         <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.71</v>
+        <v>2.74</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="CH17" t="n">
         <v>1.46</v>
@@ -7682,7 +7682,7 @@
         <v>1.5</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CM17" t="n">
         <v>2.43</v>
@@ -7694,19 +7694,19 @@
         <v>1.27</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="CR17" t="n">
         <v>1.4</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CU17" t="n">
         <v>1.48</v>
@@ -7724,7 +7724,7 @@
         <v>1.94</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DA17" t="n">
         <v>1.9</v>
@@ -7742,76 +7742,76 @@
         <v>0.09</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="DH17" t="n">
-        <v>90.67</v>
+        <v>90.5</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.52</v>
+        <v>5.4</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="DM17" t="n">
-        <v>42.95</v>
+        <v>42.73</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.15</v>
+        <v>12.86</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.81</v>
+        <v>10.82</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.38</v>
+        <v>7.46</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>38.95</v>
+        <v>39.14</v>
       </c>
       <c r="DW17" t="n">
         <v>0.09</v>
       </c>
       <c r="DX17" t="n">
-        <v>13</v>
+        <v>12.95</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.43</v>
+        <v>9.32</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.57</v>
+        <v>3.64</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.43</v>
+        <v>20.45</v>
       </c>
       <c r="EB17" t="n">
         <v>1.38</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="18">
@@ -7821,94 +7821,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
         <v>11</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="H18" t="n">
-        <v>111.4</v>
+        <v>107.18</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="K18" t="n">
-        <v>4.9</v>
+        <v>4.64</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M18" t="n">
-        <v>52.7</v>
+        <v>51.36</v>
       </c>
       <c r="N18" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="O18" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="P18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.82</v>
       </c>
       <c r="Q18" t="n">
-        <v>10.1</v>
+        <v>9.73</v>
       </c>
       <c r="R18" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="T18" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>54</v>
+        <v>52.27</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>16</v>
+        <v>15.82</v>
       </c>
       <c r="AA18" t="n">
-        <v>11.4</v>
+        <v>11.36</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="AC18" t="n">
-        <v>21.7</v>
+        <v>20.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7992,70 +7992,70 @@
         <v>2.27</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.9</v>
+        <v>9.73</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="BL18" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.95</v>
+        <v>4.82</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.95</v>
+        <v>4.91</v>
       </c>
       <c r="BR18" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS18" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT18" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU18" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV18" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW18" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX18" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.58</v>
+        <v>3.14</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.71</v>
+        <v>3.26</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.26</v>
+        <v>4.35</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.28</v>
+        <v>4.37</v>
       </c>
       <c r="CC18" t="n">
         <v>5.58</v>
@@ -8067,13 +8067,13 @@
         <v>1.27</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CI18" t="n">
         <v>2.37</v>
@@ -8085,7 +8085,7 @@
         <v>1.48</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM18" t="n">
         <v>2.48</v>
@@ -8097,22 +8097,22 @@
         <v>1.15</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="CR18" t="n">
         <v>1.34</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CT18" t="n">
         <v>3.32</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CV18" t="n">
         <v>2.54</v>
@@ -8124,10 +8124,10 @@
         <v>1.55</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DA18" t="n">
         <v>1.96</v>
@@ -8136,52 +8136,52 @@
         <v>1.28</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="DH18" t="n">
-        <v>97.34</v>
+        <v>95.86</v>
       </c>
       <c r="DI18" t="n">
         <v>0</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.72</v>
+        <v>4.6</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM18" t="n">
-        <v>44.62</v>
+        <v>44.32</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="DO18" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.05</v>
+        <v>10.04</v>
       </c>
       <c r="DQ18" t="n">
-        <v>10</v>
+        <v>9.82</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.67</v>
+        <v>7.59</v>
       </c>
       <c r="DS18" t="n">
         <v>0.09</v>
@@ -8193,28 +8193,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.57</v>
+        <v>50.82</v>
       </c>
       <c r="DW18" t="n">
         <v>0.14</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.38</v>
+        <v>13.41</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.19</v>
+        <v>9.27</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.19</v>
+        <v>4.14</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.57</v>
+        <v>20.23</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F2" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="H2" t="n">
-        <v>100.18</v>
+        <v>99.42</v>
       </c>
       <c r="I2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J2" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.55</v>
+        <v>5.42</v>
       </c>
       <c r="L2" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="M2" t="n">
-        <v>41.45</v>
+        <v>42.08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="P2" t="n">
-        <v>11.73</v>
+        <v>11.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.27</v>
+        <v>11.92</v>
       </c>
       <c r="R2" t="n">
-        <v>8.09</v>
+        <v>8.33</v>
       </c>
       <c r="S2" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="T2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>47</v>
+        <v>47.17</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.36</v>
+        <v>12.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.82</v>
+        <v>7.83</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.91</v>
+        <v>20.67</v>
       </c>
       <c r="AD2" t="n">
         <v>1.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AF2" t="n">
         <v>0.1</v>
@@ -1550,70 +1550,70 @@
         <v>2.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.289999999999999</v>
+        <v>9.27</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BL2" t="n">
         <v>0.86</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.86</v>
+        <v>4.82</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.43</v>
+        <v>4.45</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS2" t="n">
-        <v>80.95</v>
+        <v>77.27</v>
       </c>
       <c r="BT2" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU2" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV2" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX2" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.31</v>
+        <v>3.18</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.06</v>
+        <v>4.03</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.15</v>
+        <v>4.13</v>
       </c>
       <c r="CC2" t="n">
         <v>5.18</v>
@@ -1628,7 +1628,7 @@
         <v>2.51</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CH2" t="n">
         <v>1.54</v>
@@ -1640,13 +1640,13 @@
         <v>1.68</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL2" t="n">
         <v>2</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CN2" t="n">
         <v>1.89</v>
@@ -1658,7 +1658,7 @@
         <v>1.77</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
@@ -1667,7 +1667,7 @@
         <v>2.48</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CU2" t="n">
         <v>1.6</v>
@@ -1676,25 +1676,25 @@
         <v>2.29</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DB2" t="n">
         <v>1.3</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="DD2" t="n">
         <v>2.82</v>
@@ -1703,76 +1703,76 @@
         <v>0.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="DH2" t="n">
-        <v>97.86</v>
+        <v>97.55</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.38</v>
+        <v>4.37</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM2" t="n">
-        <v>38.52</v>
+        <v>39</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.86</v>
+        <v>11.73</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.67</v>
+        <v>12.46</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.24</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.81</v>
+        <v>45.96</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.76</v>
+        <v>12.73</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.43</v>
+        <v>8.41</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.34</v>
+        <v>4.32</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.81</v>
+        <v>18.77</v>
       </c>
       <c r="EB2" t="n">
         <v>1.39</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="3">
@@ -4260,7 +4260,7 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>46.18</v>
+        <v>46.09</v>
       </c>
       <c r="Y9" t="n">
         <v>0.18</v>
@@ -4566,7 +4566,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47.09</v>
+        <v>47.05</v>
       </c>
       <c r="DW9" t="n">
         <v>0.28</v>
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4690,136 +4690,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.4</v>
+        <v>3.27</v>
       </c>
       <c r="AI10" t="n">
-        <v>80.2</v>
+        <v>83</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="AM10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>39.18</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>43.82</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>20.09</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BK10" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN10" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="BE10" t="n">
+      <c r="BL10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BO10" t="n">
         <v>1.23</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1.29</v>
       </c>
       <c r="BP10" t="n">
         <v>4.05</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="BT10" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU10" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BV10" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX10" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY10" t="n">
         <v>4.22</v>
@@ -4828,28 +4828,28 @@
         <v>4.75</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.22</v>
+        <v>4.18</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.41</v>
+        <v>4.38</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.9</v>
+        <v>5.72</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.26</v>
+        <v>6.05</v>
       </c>
       <c r="CE10" t="n">
         <v>1.29</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI10" t="n">
         <v>2.18</v>
@@ -4864,7 +4864,7 @@
         <v>1.97</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CN10" t="n">
         <v>1.89</v>
@@ -4873,46 +4873,46 @@
         <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CQ10" t="n">
         <v>2.58</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS10" t="n">
         <v>2.52</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CX10" t="n">
         <v>1.57</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DA10" t="n">
         <v>1.91</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DD10" t="n">
         <v>2.68</v>
@@ -4921,43 +4921,43 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="DH10" t="n">
-        <v>80.48</v>
+        <v>81.87</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.9</v>
+        <v>4.91</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="DM10" t="n">
-        <v>38</v>
+        <v>38.32</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.43</v>
+        <v>10.36</v>
       </c>
       <c r="DQ10" t="n">
-        <v>10.53</v>
+        <v>10.46</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.859999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4969,28 +4969,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>41.91</v>
+        <v>42.32</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.81</v>
+        <v>12</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.24</v>
+        <v>8.5</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.57</v>
+        <v>18.72</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="11">
@@ -6209,25 +6209,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="H14" t="n">
-        <v>106.1</v>
+        <v>112.18</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -6236,64 +6236,64 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>5.7</v>
+        <v>5.73</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="M14" t="n">
-        <v>47.2</v>
+        <v>53.18</v>
       </c>
       <c r="N14" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="P14" t="n">
-        <v>8.5</v>
+        <v>8.27</v>
       </c>
       <c r="Q14" t="n">
-        <v>11.3</v>
+        <v>11.18</v>
       </c>
       <c r="R14" t="n">
-        <v>5.6</v>
+        <v>5.64</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T14" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>52.6</v>
+        <v>54</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>17.3</v>
+        <v>17.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>10.5</v>
+        <v>10.45</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.8</v>
+        <v>7.09</v>
       </c>
       <c r="AC14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -6380,70 +6380,70 @@
         <v>1.73</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.9</v>
+        <v>9.82</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="BP14" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>95.45</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>86.36</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>63.64</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>45.45</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>2</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="CB14" t="n">
         <v>4.33</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>95.23999999999999</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>19.05</v>
-      </c>
-      <c r="BX14" t="n">
-        <v>52.38</v>
-      </c>
-      <c r="BY14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BZ14" t="n">
-        <v>2</v>
-      </c>
-      <c r="CA14" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="CB14" t="n">
-        <v>4.3</v>
       </c>
       <c r="CC14" t="n">
         <v>3.1</v>
@@ -6458,10 +6458,10 @@
         <v>2.17</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.95</v>
+        <v>3.97</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CI14" t="n">
         <v>2.5</v>
@@ -6470,16 +6470,16 @@
         <v>1.51</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CO14" t="n">
         <v>1.13</v>
@@ -6488,19 +6488,19 @@
         <v>1.51</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CT14" t="n">
         <v>3.13</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CV14" t="n">
         <v>2.75</v>
@@ -6512,13 +6512,13 @@
         <v>1.52</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.46</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DB14" t="n">
         <v>1.32</v>
@@ -6527,82 +6527,82 @@
         <v>1.49</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.81</v>
+        <v>2.72</v>
       </c>
       <c r="DH14" t="n">
-        <v>101.81</v>
+        <v>105.04</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.29</v>
+        <v>5.32</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="DM14" t="n">
-        <v>46.34</v>
+        <v>49.36</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.24</v>
+        <v>9.09</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.38</v>
+        <v>10.36</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.62</v>
+        <v>7.54</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>52.86</v>
+        <v>53.54</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>16.19</v>
+        <v>16.36</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.57</v>
+        <v>10.54</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.62</v>
+        <v>5.82</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.48</v>
+        <v>18.09</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="15">
@@ -7565,7 +7565,7 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>40</v>
+        <v>40.09</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.09</v>
@@ -7790,7 +7790,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>39.14</v>
+        <v>39.18</v>
       </c>
       <c r="DW17" t="n">
         <v>0.09</v>
@@ -8224,13 +8224,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>0.18</v>
@@ -8314,139 +8314,139 @@
         <v>1.82</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AI19" t="n">
-        <v>84.5</v>
+        <v>82.36</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AM19" t="n">
         <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>33.2</v>
+        <v>32.27</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP19" t="n">
         <v>1</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.4</v>
+        <v>10.36</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.699999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AS19" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>44.6</v>
+        <v>43.45</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.9</v>
+        <v>6.91</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="BD19" t="n">
-        <v>17</v>
+        <v>16.64</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.43</v>
+        <v>11.27</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BL19" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.76</v>
+        <v>0.82</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.71</v>
+        <v>4.77</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.95</v>
+        <v>5.77</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT19" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU19" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BV19" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW19" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX19" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BY19" t="n">
         <v>2.56</v>
@@ -8455,31 +8455,31 @@
         <v>2.64</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.11</v>
+        <v>4.15</v>
       </c>
       <c r="CC19" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="CD19" t="n">
-        <v>5.11</v>
+        <v>5.17</v>
       </c>
       <c r="CE19" t="n">
         <v>1.28</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.59</v>
@@ -8488,73 +8488,73 @@
         <v>1.43</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="CT19" t="n">
         <v>3.16</v>
       </c>
       <c r="CU19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="CW19" t="n">
         <v>1.61</v>
-      </c>
-      <c r="CV19" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="CW19" t="n">
-        <v>1.62</v>
       </c>
       <c r="CX19" t="n">
         <v>1.54</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.43</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DB19" t="n">
         <v>1.3</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="DH19" t="n">
-        <v>93.33</v>
+        <v>91.86</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
@@ -8563,28 +8563,28 @@
         <v>2</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="DL19" t="n">
         <v>0.09</v>
       </c>
       <c r="DM19" t="n">
-        <v>45.24</v>
+        <v>44.22</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="DO19" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.29</v>
+        <v>11.22</v>
       </c>
       <c r="DQ19" t="n">
-        <v>9.57</v>
+        <v>9.4</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.19</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DS19" t="n">
         <v>0.09</v>
@@ -8596,25 +8596,25 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>46.9</v>
+        <v>46.22</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.76</v>
+        <v>11.68</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.76</v>
+        <v>7.73</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4</v>
+        <v>3.96</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.91</v>
+        <v>17.69</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="EC19" t="n">
         <v>1.95</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0.17</v>
@@ -1469,139 +1469,139 @@
         <v>2.42</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.1</v>
+        <v>2.27</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AI2" t="n">
-        <v>95.3</v>
+        <v>96.45</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.1</v>
+        <v>3.73</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN2" t="n">
-        <v>35.3</v>
+        <v>38.55</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12</v>
+        <v>12.36</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.1</v>
+        <v>12.73</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.4</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AT2" t="n">
         <v>2</v>
       </c>
       <c r="AU2" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>44.5</v>
+        <v>45</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.2</v>
+        <v>13.36</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="BD2" t="n">
-        <v>16.5</v>
+        <v>17.18</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.27</v>
+        <v>9.48</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.82</v>
+        <v>4.91</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.45</v>
+        <v>4.57</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS2" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT2" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU2" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BV2" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX2" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY2" t="n">
         <v>3.18</v>
@@ -1610,16 +1610,16 @@
         <v>3.5</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="CC2" t="n">
-        <v>5.18</v>
+        <v>5.01</v>
       </c>
       <c r="CD2" t="n">
-        <v>5.54</v>
+        <v>5.35</v>
       </c>
       <c r="CE2" t="n">
         <v>1.33</v>
@@ -1628,7 +1628,7 @@
         <v>2.51</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="CH2" t="n">
         <v>1.54</v>
@@ -1637,19 +1637,19 @@
         <v>2.16</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CK2" t="n">
         <v>1.51</v>
       </c>
       <c r="CL2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CO2" t="n">
         <v>1.22</v>
@@ -1658,7 +1658,7 @@
         <v>1.77</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
@@ -1673,7 +1673,7 @@
         <v>1.6</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CW2" t="n">
         <v>1.69</v>
@@ -1682,13 +1682,13 @@
         <v>1.57</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.37</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DB2" t="n">
         <v>1.3</v>
@@ -1700,79 +1700,79 @@
         <v>2.82</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="DH2" t="n">
-        <v>97.55</v>
+        <v>98</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.37</v>
+        <v>4.61</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM2" t="n">
-        <v>39</v>
+        <v>40.39</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.73</v>
+        <v>11.91</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.46</v>
+        <v>12.31</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.359999999999999</v>
+        <v>8.34</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>45.96</v>
+        <v>46.13</v>
       </c>
       <c r="DW2" t="n">
         <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.73</v>
+        <v>12.82</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.41</v>
+        <v>8.43</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.32</v>
+        <v>4.39</v>
       </c>
       <c r="EA2" t="n">
-        <v>18.77</v>
+        <v>19</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
         <v>11</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>0.27</v>
@@ -1872,139 +1872,139 @@
         <v>1.91</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AI3" t="n">
-        <v>104.3</v>
+        <v>106</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AN3" t="n">
-        <v>43.3</v>
+        <v>46.55</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>12.2</v>
+        <v>12.45</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.1</v>
+        <v>7.45</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>57.2</v>
+        <v>57.91</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.3</v>
+        <v>11.73</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.5</v>
+        <v>8.18</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BD3" t="n">
-        <v>15.8</v>
+        <v>16.45</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.76</v>
+        <v>9.73</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="BJ3" t="n">
         <v>1.14</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.38</v>
+        <v>5.32</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>90.48</v>
+        <v>86.36</v>
       </c>
       <c r="BT3" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU3" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BV3" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW3" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX3" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY3" t="n">
         <v>1.79</v>
@@ -2013,31 +2013,31 @@
         <v>1.87</v>
       </c>
       <c r="CA3" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="CB3" t="n">
         <v>4.05</v>
       </c>
-      <c r="CB3" t="n">
-        <v>4.09</v>
-      </c>
       <c r="CC3" t="n">
-        <v>2.97</v>
+        <v>2.91</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="CE3" t="n">
         <v>1.26</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.58</v>
@@ -2046,7 +2046,7 @@
         <v>1.5</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CM3" t="n">
         <v>2.48</v>
@@ -2058,10 +2058,10 @@
         <v>1.17</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="CR3" t="n">
         <v>1.35</v>
@@ -2076,100 +2076,100 @@
         <v>1.64</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DG3" t="n">
         <v>2.95</v>
       </c>
       <c r="DH3" t="n">
-        <v>111.66</v>
+        <v>112.18</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ3" t="n">
         <v>2.09</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM3" t="n">
-        <v>46.72</v>
+        <v>48.18</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DP3" t="n">
-        <v>8.81</v>
+        <v>8.73</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.19</v>
+        <v>11.36</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.09</v>
+        <v>6.82</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>59.48</v>
+        <v>59.73</v>
       </c>
       <c r="DW3" t="n">
         <v>0.09</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.67</v>
+        <v>13.78</v>
       </c>
       <c r="DY3" t="n">
-        <v>8.949999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.72</v>
+        <v>4.55</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.05</v>
+        <v>16.36</v>
       </c>
       <c r="EB3" t="n">
         <v>1.54</v>
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F4" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="H4" t="n">
-        <v>136.18</v>
+        <v>135.08</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="K4" t="n">
-        <v>6.73</v>
+        <v>6.83</v>
       </c>
       <c r="L4" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="M4" t="n">
-        <v>68.91</v>
+        <v>68.58</v>
       </c>
       <c r="N4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="O4" t="n">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>9.550000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.09</v>
+        <v>8.25</v>
       </c>
       <c r="R4" t="n">
-        <v>6.09</v>
+        <v>6</v>
       </c>
       <c r="S4" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="V4" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>67.55</v>
+        <v>66.17</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>20.27</v>
+        <v>20.58</v>
       </c>
       <c r="AA4" t="n">
-        <v>11.27</v>
+        <v>11.42</v>
       </c>
       <c r="AB4" t="n">
-        <v>9</v>
+        <v>9.17</v>
       </c>
       <c r="AC4" t="n">
-        <v>19.73</v>
+        <v>19</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AF4" t="n">
         <v>0.09</v>
@@ -2356,37 +2356,37 @@
         <v>2.18</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.59</v>
+        <v>4.61</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.73</v>
+        <v>9.74</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.59</v>
+        <v>4.61</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BO4" t="n">
         <v>2.09</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.91</v>
+        <v>4.09</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.18</v>
+        <v>5.04</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2398,28 +2398,28 @@
         <v>100</v>
       </c>
       <c r="BU4" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BV4" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BW4" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BX4" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>1.17</v>
       </c>
-      <c r="BZ4" t="n">
-        <v>1.18</v>
-      </c>
       <c r="CA4" t="n">
-        <v>7.51</v>
+        <v>7.62</v>
       </c>
       <c r="CB4" t="n">
-        <v>8.15</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="CC4" t="n">
         <v>1.32</v>
@@ -2431,13 +2431,13 @@
         <v>1.15</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CG4" t="n">
-        <v>4.92</v>
+        <v>4.97</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="CI4" t="n">
         <v>2.17</v>
@@ -2446,10 +2446,10 @@
         <v>1.7</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CM4" t="n">
         <v>2.46</v>
@@ -2458,13 +2458,13 @@
         <v>1.91</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CQ4" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="CR4" t="inlineStr"/>
       <c r="CS4" t="n">
@@ -2481,16 +2481,16 @@
         <v>1.72</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.46</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="DB4" t="inlineStr"/>
       <c r="DC4" t="n">
@@ -2500,79 +2500,79 @@
         <v>1.78</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
       <c r="DH4" t="n">
-        <v>134.41</v>
+        <v>133.91</v>
       </c>
       <c r="DI4" t="n">
         <v>-0.09</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.28</v>
+        <v>6.35</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DM4" t="n">
-        <v>68.36</v>
+        <v>68.22</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.55</v>
+        <v>2.74</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.18</v>
+        <v>9.17</v>
       </c>
       <c r="DQ4" t="n">
-        <v>8.5</v>
+        <v>8.57</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.95</v>
+        <v>5.91</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>67.27</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>18.91</v>
+        <v>19.13</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.09</v>
+        <v>10.22</v>
       </c>
       <c r="DZ4" t="n">
-        <v>8.82</v>
+        <v>8.92</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.59</v>
+        <v>19.22</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="5">
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>0.18</v>
@@ -2672,139 +2672,139 @@
         <v>1.55</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
-        <v>101.55</v>
+        <v>100.75</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.73</v>
+        <v>3.58</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.55</v>
+        <v>11.67</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.18</v>
+        <v>11.17</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>51.91</v>
+        <v>51.33</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.09</v>
+        <v>12</v>
       </c>
       <c r="BB5" t="n">
-        <v>8</v>
+        <v>7.83</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.64</v>
+        <v>21.83</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="BH5" t="n">
-        <v>10</v>
+        <v>9.91</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL5" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.68</v>
+        <v>5.65</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU5" t="n">
-        <v>27.27</v>
+        <v>30.43</v>
       </c>
       <c r="BV5" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW5" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY5" t="n">
         <v>1.51</v>
@@ -2813,34 +2813,34 @@
         <v>1.52</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.48</v>
+        <v>4.46</v>
       </c>
       <c r="CC5" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="CD5" t="n">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="CE5" t="n">
         <v>1.26</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="CH5" t="n">
         <v>1.62</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CK5" t="n">
         <v>1.48</v>
@@ -2858,10 +2858,10 @@
         <v>1.16</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CR5" t="n">
         <v>1.34</v>
@@ -2876,10 +2876,10 @@
         <v>1.68</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX5" t="n">
         <v>1.57</v>
@@ -2903,79 +2903,79 @@
         <v>2.47</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="DH5" t="n">
-        <v>107.82</v>
+        <v>107.13</v>
       </c>
       <c r="DI5" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ5" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>59.65</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="DO5" t="n">
         <v>2</v>
       </c>
-      <c r="DK5" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="DL5" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="DM5" t="n">
-        <v>60.04</v>
-      </c>
-      <c r="DN5" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="DO5" t="n">
-        <v>2.04</v>
-      </c>
       <c r="DP5" t="n">
-        <v>11.46</v>
+        <v>11.52</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.18</v>
+        <v>10.22</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.64</v>
+        <v>6.65</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>53.96</v>
+        <v>53.56</v>
       </c>
       <c r="DW5" t="n">
         <v>0.09</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.22</v>
+        <v>13.13</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.32</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.82</v>
+        <v>20</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="6">
@@ -2985,13 +2985,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0.18</v>
@@ -3081,133 +3081,133 @@
         <v>1</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AI6" t="n">
-        <v>83.81999999999999</v>
+        <v>84.08</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.91</v>
+        <v>4.75</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN6" t="n">
-        <v>35</v>
+        <v>34.33</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.09</v>
+        <v>11.75</v>
       </c>
       <c r="AR6" t="n">
-        <v>12.82</v>
+        <v>12.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.73</v>
+        <v>6.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>45.27</v>
+        <v>46.75</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.55</v>
+        <v>11.58</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.36</v>
+        <v>7.58</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>17.27</v>
+        <v>17.25</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.23</v>
+        <v>9.09</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.18</v>
+        <v>4.13</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.05</v>
+        <v>4.96</v>
       </c>
       <c r="BR6" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS6" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT6" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU6" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV6" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW6" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX6" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BY6" t="n">
         <v>3.2</v>
@@ -3216,31 +3216,31 @@
         <v>3.24</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.63</v>
+        <v>3.67</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.56</v>
@@ -3249,37 +3249,37 @@
         <v>1.44</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CO6" t="n">
         <v>1.17</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CR6" t="n">
         <v>1.35</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CT6" t="n">
         <v>3.26</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CW6" t="n">
         <v>1.59</v>
@@ -3288,64 +3288,64 @@
         <v>1.56</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB6" t="n">
         <v>1.28</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="DE6" t="n">
         <v>0.09</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="DH6" t="n">
-        <v>85.54000000000001</v>
+        <v>85.61</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.22</v>
+        <v>35.82</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.37</v>
+        <v>11.22</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.73</v>
+        <v>10.65</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.59</v>
+        <v>7.43</v>
       </c>
       <c r="DS6" t="n">
         <v>0.13</v>
@@ -3357,28 +3357,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.18</v>
+        <v>45.96</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.23</v>
+        <v>11.26</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.14</v>
+        <v>7.26</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.45</v>
+        <v>17.44</v>
       </c>
       <c r="EB6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="EC6" t="n">
         <v>1.26</v>
-      </c>
-      <c r="EC6" t="n">
-        <v>1.23</v>
       </c>
     </row>
     <row r="7">
@@ -3388,13 +3388,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3478,139 +3478,139 @@
         <v>1.45</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="n">
-        <v>107.27</v>
+        <v>102.25</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.73</v>
+        <v>3.58</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN7" t="n">
-        <v>44.82</v>
+        <v>43.33</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11.64</v>
+        <v>11.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>9</v>
+        <v>8.92</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.18</v>
+        <v>8.17</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>54.64</v>
+        <v>54.17</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.73</v>
+        <v>10.58</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.82</v>
+        <v>6.75</v>
       </c>
       <c r="BC7" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>20.42</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="BQ7" t="n">
         <v>3.91</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>4</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BT7" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BU7" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BV7" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BW7" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BX7" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BY7" t="n">
         <v>2.43</v>
@@ -3619,40 +3619,40 @@
         <v>2.81</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.89</v>
+        <v>4.16</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.97</v>
+        <v>4.38</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.86</v>
+        <v>4.04</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.07</v>
+        <v>4.73</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CK7" t="n">
         <v>1.51</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CM7" t="n">
         <v>2.42</v>
@@ -3661,13 +3661,13 @@
         <v>1.9</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
@@ -3682,22 +3682,22 @@
         <v>1.66</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="DB7" t="n">
         <v>1.28</v>
@@ -3712,76 +3712,76 @@
         <v>0.09</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DH7" t="n">
-        <v>100.27</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="DI7" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.36</v>
+        <v>4.26</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM7" t="n">
-        <v>44.46</v>
+        <v>43.69</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="DP7" t="n">
-        <v>11</v>
+        <v>10.95</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.5</v>
+        <v>9.44</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.82</v>
+        <v>7.83</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>52.6</v>
+        <v>52.44</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.59</v>
+        <v>11.47</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.14</v>
+        <v>7.08</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.46</v>
+        <v>4.39</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.54</v>
+        <v>20.26</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="8">
@@ -3791,94 +3791,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="H8" t="n">
-        <v>99.7</v>
+        <v>98.36</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>5.1</v>
+        <v>4.91</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M8" t="n">
-        <v>48.3</v>
+        <v>46.09</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="P8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.3</v>
+        <v>11.91</v>
       </c>
       <c r="R8" t="n">
-        <v>5.1</v>
+        <v>5.73</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="T8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>53.2</v>
+        <v>51.73</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z8" t="n">
-        <v>14</v>
+        <v>13.64</v>
       </c>
       <c r="AA8" t="n">
-        <v>9</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>5</v>
+        <v>5.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.6</v>
+        <v>20.64</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AF8" t="n">
         <v>0.08</v>
@@ -3965,67 +3965,67 @@
         <v>3.09</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.68</v>
+        <v>8.57</v>
       </c>
       <c r="BI8" t="n">
         <v>3.09</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.36</v>
+        <v>4.3</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.32</v>
+        <v>4.26</v>
       </c>
       <c r="BR8" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS8" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT8" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU8" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV8" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW8" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX8" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="CC8" t="n">
         <v>4.05</v>
@@ -4034,7 +4034,7 @@
         <v>4.4</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF8" t="n">
         <v>2.62</v>
@@ -4043,13 +4043,13 @@
         <v>3.24</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI8" t="n">
         <v>2.14</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CK8" t="n">
         <v>1.62</v>
@@ -4061,7 +4061,7 @@
         <v>2.21</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CO8" t="n">
         <v>1.23</v>
@@ -4070,7 +4070,7 @@
         <v>1.81</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
@@ -4079,16 +4079,16 @@
         <v>2.68</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CU8" t="n">
         <v>1.5</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CX8" t="n">
         <v>1.66</v>
@@ -4103,7 +4103,7 @@
         <v>1.75</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="DC8" t="n">
         <v>1.84</v>
@@ -4121,70 +4121,70 @@
         <v>2.04</v>
       </c>
       <c r="DH8" t="n">
-        <v>89.64</v>
+        <v>89.43000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.46</v>
+        <v>4.39</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM8" t="n">
-        <v>43.13</v>
+        <v>42.3</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.59</v>
+        <v>9.57</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.32</v>
+        <v>12.13</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.68</v>
+        <v>6.91</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.45</v>
+        <v>47.96</v>
       </c>
       <c r="DW8" t="n">
         <v>0.13</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.54</v>
+        <v>12.43</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.550000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.77</v>
+        <v>18.87</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="9">
@@ -4194,13 +4194,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
         <v>11</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0.18</v>
@@ -4287,49 +4287,49 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AI9" t="n">
-        <v>79.59999999999999</v>
+        <v>81.36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AN9" t="n">
         <v>32</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.6</v>
+        <v>12.64</v>
       </c>
       <c r="AR9" t="n">
-        <v>12.2</v>
+        <v>12.55</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>8.91</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4341,82 +4341,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>48.1</v>
+        <v>48.73</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.6</v>
+        <v>11.82</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.5</v>
+        <v>7.64</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.1</v>
+        <v>4.18</v>
       </c>
       <c r="BD9" t="n">
-        <v>17.9</v>
+        <v>17.55</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="BH9" t="n">
         <v>8.859999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.48</v>
+        <v>4.55</v>
       </c>
       <c r="BR9" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT9" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>31.82</v>
       </c>
       <c r="BV9" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY9" t="n">
         <v>3.23</v>
@@ -4425,16 +4425,16 @@
         <v>3.29</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.51</v>
+        <v>4.47</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.66</v>
+        <v>5.44</v>
       </c>
       <c r="CD9" t="n">
-        <v>6.04</v>
+        <v>5.83</v>
       </c>
       <c r="CE9" t="n">
         <v>1.31</v>
@@ -4443,13 +4443,13 @@
         <v>2.46</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.65</v>
@@ -4458,13 +4458,13 @@
         <v>1.49</v>
       </c>
       <c r="CL9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CN9" t="n">
         <v>1.92</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>1.93</v>
       </c>
       <c r="CO9" t="n">
         <v>1.2</v>
@@ -4479,10 +4479,10 @@
         <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CU9" t="n">
         <v>1.61</v>
@@ -4497,97 +4497,97 @@
         <v>1.62</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.3</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="DC9" t="n">
         <v>1.76</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="DE9" t="n">
         <v>0.09</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="DG9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DH9" t="n">
-        <v>83.05</v>
+        <v>83.77</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.95</v>
+        <v>3.86</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="DM9" t="n">
-        <v>36.1</v>
+        <v>35.91</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.47</v>
+        <v>12.5</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.67</v>
+        <v>12.82</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.619999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47.05</v>
+        <v>47.41</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.15</v>
+        <v>13.19</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.33</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.81</v>
+        <v>17.64</v>
       </c>
       <c r="EB9" t="n">
         <v>1.43</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="10">
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
@@ -4609,82 +4609,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="H10" t="n">
-        <v>80.73</v>
+        <v>79.83</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="L10" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="M10" t="n">
-        <v>37.45</v>
+        <v>36.67</v>
       </c>
       <c r="N10" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O10" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
-        <v>9.640000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.73</v>
+        <v>10.33</v>
       </c>
       <c r="R10" t="n">
-        <v>8.550000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="S10" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>40.82</v>
+        <v>40.25</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.27</v>
+        <v>12.08</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.550000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.73</v>
+        <v>3.92</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.36</v>
+        <v>17.42</v>
       </c>
       <c r="AD10" t="n">
         <v>1.31</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4768,58 +4768,58 @@
         <v>2.09</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="BH10" t="n">
-        <v>10</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.05</v>
+        <v>3.17</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM10" t="n">
         <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.95</v>
+        <v>5.91</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BT10" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BU10" t="n">
-        <v>31.82</v>
+        <v>34.78</v>
       </c>
       <c r="BV10" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BW10" t="n">
-        <v>4.55</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX10" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY10" t="n">
         <v>4.22</v>
@@ -4828,7 +4828,7 @@
         <v>4.75</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="CB10" t="n">
         <v>4.38</v>
@@ -4843,25 +4843,25 @@
         <v>1.29</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.66</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CM10" t="n">
         <v>2.42</v>
@@ -4873,25 +4873,25 @@
         <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CR10" t="n">
         <v>1.37</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CT10" t="n">
         <v>3.16</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CW10" t="n">
         <v>1.71</v>
@@ -4900,7 +4900,7 @@
         <v>1.57</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.39</v>
@@ -4912,85 +4912,85 @@
         <v>1.31</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="DG10" t="n">
         <v>3.04</v>
       </c>
       <c r="DH10" t="n">
-        <v>81.87</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DM10" t="n">
-        <v>38.32</v>
+        <v>37.87</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.36</v>
+        <v>10.48</v>
       </c>
       <c r="DQ10" t="n">
-        <v>10.46</v>
+        <v>10.26</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.82</v>
+        <v>8.65</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>42.32</v>
+        <v>41.96</v>
       </c>
       <c r="DW10" t="n">
         <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>12</v>
+        <v>11.91</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.5</v>
+        <v>3.61</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.72</v>
+        <v>18.7</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="11">
@@ -5000,13 +5000,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
         <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>0.18</v>
@@ -5090,139 +5090,139 @@
         <v>1.82</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.18</v>
+        <v>2.58</v>
       </c>
       <c r="AI11" t="n">
-        <v>103</v>
+        <v>103.58</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AN11" t="n">
-        <v>43.73</v>
+        <v>45.17</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.82</v>
+        <v>13.67</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.550000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.36</v>
+        <v>6.92</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>51.09</v>
+        <v>52.17</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA11" t="n">
-        <v>11.18</v>
+        <v>11.75</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.91</v>
+        <v>7.33</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.27</v>
+        <v>4.42</v>
       </c>
       <c r="BD11" t="n">
-        <v>20.27</v>
+        <v>20.33</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.64</v>
+        <v>10.74</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="BJ11" t="n">
         <v>1.09</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BM11" t="n">
         <v>0.91</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.68</v>
+        <v>5.74</v>
       </c>
       <c r="BR11" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS11" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BU11" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BV11" t="n">
-        <v>27.27</v>
+        <v>26.09</v>
       </c>
       <c r="BW11" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX11" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BY11" t="n">
         <v>2.53</v>
@@ -5231,25 +5231,25 @@
         <v>2.56</v>
       </c>
       <c r="CA11" t="n">
-        <v>4.01</v>
+        <v>3.99</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.5</v>
+        <v>3.39</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.64</v>
+        <v>3.51</v>
       </c>
       <c r="CE11" t="n">
         <v>1.25</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CH11" t="n">
         <v>1.67</v>
@@ -5258,7 +5258,7 @@
         <v>2.46</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CK11" t="n">
         <v>1.42</v>
@@ -5267,10 +5267,10 @@
         <v>1.79</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CO11" t="n">
         <v>1.15</v>
@@ -5294,7 +5294,7 @@
         <v>1.63</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CW11" t="n">
         <v>1.56</v>
@@ -5324,76 +5324,76 @@
         <v>0.13</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.22</v>
+        <v>2.43</v>
       </c>
       <c r="DH11" t="n">
-        <v>107.91</v>
+        <v>108</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="DK11" t="n">
-        <v>5</v>
+        <v>5.22</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="DM11" t="n">
-        <v>47.86</v>
+        <v>48.44</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.09</v>
+        <v>14</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.359999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.72</v>
+        <v>6.52</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.22</v>
+        <v>53.7</v>
       </c>
       <c r="DW11" t="n">
         <v>0.09</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.27</v>
+        <v>13.48</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.32</v>
+        <v>8.48</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.95</v>
+        <v>5</v>
       </c>
       <c r="EA11" t="n">
         <v>20.96</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="12">
@@ -5403,61 +5403,61 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="H12" t="n">
-        <v>97.81999999999999</v>
+        <v>96.17</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="J12" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>46.09</v>
+        <v>46.25</v>
       </c>
       <c r="N12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="O12" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="P12" t="n">
-        <v>7.82</v>
+        <v>7.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>11.64</v>
+        <v>11.67</v>
       </c>
       <c r="R12" t="n">
-        <v>7.73</v>
+        <v>8</v>
       </c>
       <c r="S12" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="T12" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5469,28 +5469,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>48.27</v>
+        <v>47.25</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.91</v>
+        <v>13.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.91</v>
+        <v>8.58</v>
       </c>
       <c r="AB12" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.73</v>
+        <v>21.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF12" t="n">
         <v>0.18</v>
@@ -5574,70 +5574,70 @@
         <v>1.91</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.949999999999999</v>
+        <v>10.09</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.09</v>
+        <v>3.13</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL12" t="n">
         <v>1</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.41</v>
+        <v>4.48</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.91</v>
+        <v>5</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU12" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BV12" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX12" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="CB12" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="CC12" t="n">
         <v>4.14</v>
@@ -5652,13 +5652,13 @@
         <v>2.36</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.48</v>
+        <v>3.47</v>
       </c>
       <c r="CH12" t="n">
         <v>1.59</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.57</v>
@@ -5667,22 +5667,22 @@
         <v>1.4</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CN12" t="n">
         <v>2.09</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
@@ -5724,46 +5724,46 @@
         <v>2.55</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="DH12" t="n">
-        <v>93.28</v>
+        <v>92.61</v>
       </c>
       <c r="DI12" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.18</v>
+        <v>4.13</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM12" t="n">
-        <v>43.22</v>
+        <v>43.43</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.369999999999999</v>
+        <v>8.26</v>
       </c>
       <c r="DQ12" t="n">
-        <v>10.82</v>
+        <v>10.87</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.039999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="DS12" t="n">
         <v>0.04</v>
@@ -5775,28 +5775,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>47.27</v>
+        <v>46.78</v>
       </c>
       <c r="DW12" t="n">
         <v>0.04</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.23</v>
+        <v>13.05</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.779999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.46</v>
+        <v>4.44</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.78</v>
+        <v>20.22</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="13">
@@ -5806,94 +5806,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F13" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="G13" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="H13" t="n">
-        <v>117.36</v>
+        <v>113.67</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J13" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="K13" t="n">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="L13" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="M13" t="n">
-        <v>56.36</v>
+        <v>56.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="O13" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="P13" t="n">
-        <v>11.82</v>
+        <v>12.17</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.91</v>
+        <v>10.17</v>
       </c>
       <c r="R13" t="n">
-        <v>6.82</v>
+        <v>7.08</v>
       </c>
       <c r="S13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="U13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>48.91</v>
+        <v>48.58</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>13</v>
+        <v>13.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.18</v>
+        <v>9.58</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>24.82</v>
+        <v>23.92</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5977,70 +5977,70 @@
         <v>2.82</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.41</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.64</v>
+        <v>5.65</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS13" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT13" t="n">
-        <v>54.55</v>
+        <v>52.17</v>
       </c>
       <c r="BU13" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV13" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX13" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="CC13" t="n">
         <v>5.18</v>
@@ -6058,10 +6058,10 @@
         <v>3.28</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.65</v>
@@ -6070,13 +6070,13 @@
         <v>1.47</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CO13" t="n">
         <v>1.22</v>
@@ -6088,13 +6088,13 @@
         <v>2.77</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS13" t="n">
         <v>2.56</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CU13" t="n">
         <v>1.58</v>
@@ -6109,13 +6109,13 @@
         <v>1.53</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB13" t="n">
         <v>1.3</v>
@@ -6124,82 +6124,82 @@
         <v>1.76</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="DE13" t="n">
         <v>0.04</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.41</v>
+        <v>3.48</v>
       </c>
       <c r="DH13" t="n">
-        <v>105.46</v>
+        <v>104.05</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.14</v>
+        <v>5.22</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="DM13" t="n">
-        <v>49.5</v>
+        <v>49.87</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.32</v>
+        <v>11.52</v>
       </c>
       <c r="DQ13" t="n">
-        <v>9.640000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.55</v>
+        <v>7.65</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.68</v>
+        <v>44.69</v>
       </c>
       <c r="DW13" t="n">
         <v>0.22</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.14</v>
+        <v>11.39</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.5</v>
+        <v>7.78</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.96</v>
+        <v>22.57</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="14">
@@ -6209,94 +6209,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F14" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="G14" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="H14" t="n">
-        <v>112.18</v>
+        <v>111</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="K14" t="n">
-        <v>5.73</v>
+        <v>5.75</v>
       </c>
       <c r="L14" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M14" t="n">
-        <v>53.18</v>
+        <v>52.33</v>
       </c>
       <c r="N14" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="O14" t="n">
-        <v>3.27</v>
+        <v>3.17</v>
       </c>
       <c r="P14" t="n">
-        <v>8.27</v>
+        <v>8.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>11.18</v>
+        <v>11.67</v>
       </c>
       <c r="R14" t="n">
-        <v>5.64</v>
+        <v>5.42</v>
       </c>
       <c r="S14" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T14" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>54</v>
+        <v>54.08</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>17.55</v>
+        <v>17.17</v>
       </c>
       <c r="AA14" t="n">
-        <v>10.45</v>
+        <v>10.42</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.09</v>
+        <v>6.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>21</v>
+        <v>20.42</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AE14" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AF14" t="n">
         <v>0.36</v>
@@ -6380,58 +6380,58 @@
         <v>1.73</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.82</v>
+        <v>9.74</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.41</v>
+        <v>4.35</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.41</v>
+        <v>5.39</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS14" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BU14" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BV14" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW14" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BX14" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY14" t="n">
         <v>2</v>
@@ -6440,10 +6440,10 @@
         <v>1.96</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="CC14" t="n">
         <v>3.1</v>
@@ -6455,7 +6455,7 @@
         <v>1.24</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CG14" t="n">
         <v>3.97</v>
@@ -6464,10 +6464,10 @@
         <v>1.7</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CK14" t="n">
         <v>1.41</v>
@@ -6485,25 +6485,25 @@
         <v>1.13</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CT14" t="n">
         <v>3.13</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CW14" t="n">
         <v>1.52</v>
@@ -6512,13 +6512,13 @@
         <v>1.52</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CZ14" t="n">
         <v>2.46</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DB14" t="n">
         <v>1.32</v>
@@ -6530,46 +6530,46 @@
         <v>2.18</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF14" t="n">
         <v>0.91</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="DH14" t="n">
-        <v>105.04</v>
+        <v>104.74</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.32</v>
+        <v>5.35</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="DM14" t="n">
-        <v>49.36</v>
+        <v>49.09</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.09</v>
+        <v>9.17</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.36</v>
+        <v>10.66</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.54</v>
+        <v>7.35</v>
       </c>
       <c r="DS14" t="n">
         <v>0.04</v>
@@ -6581,28 +6581,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>53.54</v>
+        <v>53.61</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>16.36</v>
+        <v>16.22</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.54</v>
+        <v>10.53</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.82</v>
+        <v>5.7</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.09</v>
+        <v>17.91</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="15">
@@ -6612,10 +6612,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
         <v>12</v>
@@ -6624,82 +6624,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4</v>
+        <v>3.09</v>
       </c>
       <c r="H15" t="n">
-        <v>102.8</v>
+        <v>101.73</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="K15" t="n">
-        <v>6.4</v>
+        <v>5.91</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M15" t="n">
-        <v>49.2</v>
+        <v>48.27</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="P15" t="n">
-        <v>10.3</v>
+        <v>9.91</v>
       </c>
       <c r="Q15" t="n">
-        <v>11</v>
+        <v>10.91</v>
       </c>
       <c r="R15" t="n">
-        <v>6.2</v>
+        <v>6.09</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>47.8</v>
+        <v>47.27</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z15" t="n">
-        <v>11.3</v>
+        <v>10.64</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.7</v>
+        <v>6.09</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AC15" t="n">
-        <v>21.7</v>
+        <v>22.18</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF15" t="n">
         <v>0.08</v>
@@ -6783,70 +6783,70 @@
         <v>1.42</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.859999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.09</v>
+        <v>4.04</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.23</v>
+        <v>5.13</v>
       </c>
       <c r="BR15" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS15" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT15" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU15" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV15" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX15" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY15" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="BZ15" t="n">
-        <v>3.24</v>
+        <v>3.19</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="CC15" t="n">
         <v>6.26</v>
@@ -6855,22 +6855,22 @@
         <v>6.38</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CK15" t="n">
         <v>1.61</v>
@@ -6888,34 +6888,34 @@
         <v>1.29</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.33</v>
+        <v>3.36</v>
       </c>
       <c r="CR15" t="n">
         <v>1.4</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="CT15" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV15" t="n">
         <v>2.05</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.23</v>
@@ -6939,73 +6939,73 @@
         <v>0.87</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="DH15" t="n">
-        <v>96.27</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.86</v>
+        <v>4.69</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM15" t="n">
-        <v>43.41</v>
+        <v>43.21</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.5</v>
+        <v>10.31</v>
       </c>
       <c r="DQ15" t="n">
-        <v>9.949999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.23</v>
+        <v>6.17</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.32</v>
+        <v>45.17</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.63</v>
+        <v>10.35</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.09</v>
+        <v>6.78</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.09</v>
+        <v>21.35</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="16">
@@ -7015,13 +7015,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7105,139 +7105,139 @@
         <v>2.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="AI16" t="n">
-        <v>127.09</v>
+        <v>127.33</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.82</v>
+        <v>5.67</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AN16" t="n">
-        <v>70.18000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.18</v>
+        <v>9.92</v>
       </c>
       <c r="AR16" t="n">
-        <v>11.91</v>
+        <v>11.92</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.55</v>
+        <v>5.67</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>59.27</v>
+        <v>59.83</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>14.55</v>
+        <v>14.33</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.82</v>
+        <v>8.42</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.73</v>
+        <v>5.92</v>
       </c>
       <c r="BD16" t="n">
-        <v>18.64</v>
+        <v>19.67</v>
       </c>
       <c r="BE16" t="n">
         <v>1.83</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.59</v>
+        <v>9.48</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.5</v>
+        <v>4.39</v>
       </c>
       <c r="BQ16" t="n">
         <v>5.09</v>
       </c>
       <c r="BR16" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS16" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT16" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BU16" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BV16" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.55</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX16" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY16" t="n">
         <v>1.98</v>
@@ -7246,16 +7246,16 @@
         <v>1.99</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.08</v>
+        <v>4.07</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.08</v>
+        <v>4.1</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.69</v>
+        <v>2.61</v>
       </c>
       <c r="CE16" t="n">
         <v>1.26</v>
@@ -7270,7 +7270,7 @@
         <v>1.65</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.54</v>
@@ -7309,7 +7309,7 @@
         <v>1.68</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CW16" t="n">
         <v>1.57</v>
@@ -7318,13 +7318,13 @@
         <v>1.57</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.36</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB16" t="n">
         <v>1.27</v>
@@ -7336,79 +7336,79 @@
         <v>2.46</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="DH16" t="n">
-        <v>112.09</v>
+        <v>112.87</v>
       </c>
       <c r="DI16" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.37</v>
+        <v>5.31</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DM16" t="n">
-        <v>56.09</v>
+        <v>56.35</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.960000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.23</v>
+        <v>12.22</v>
       </c>
       <c r="DR16" t="n">
-        <v>6</v>
+        <v>6.04</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>57.77</v>
+        <v>58.13</v>
       </c>
       <c r="DW16" t="n">
         <v>0.04</v>
       </c>
       <c r="DX16" t="n">
-        <v>15</v>
+        <v>14.87</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.279999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.73</v>
+        <v>5.83</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.32</v>
+        <v>18.87</v>
       </c>
       <c r="EB16" t="n">
         <v>1.76</v>
       </c>
       <c r="EC16" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="17">
@@ -7418,94 +7418,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
         <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="G17" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="H17" t="n">
-        <v>90.73</v>
+        <v>90.58</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="J17" t="n">
-        <v>2.91</v>
+        <v>3.08</v>
       </c>
       <c r="K17" t="n">
-        <v>5.36</v>
+        <v>5.25</v>
       </c>
       <c r="L17" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="M17" t="n">
-        <v>41.91</v>
+        <v>41.08</v>
       </c>
       <c r="N17" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="O17" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="P17" t="n">
-        <v>13.55</v>
+        <v>13.67</v>
       </c>
       <c r="Q17" t="n">
-        <v>11.73</v>
+        <v>11.33</v>
       </c>
       <c r="R17" t="n">
-        <v>6.36</v>
+        <v>6.75</v>
       </c>
       <c r="S17" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="T17" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="U17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>38.27</v>
+        <v>38</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z17" t="n">
-        <v>12.45</v>
+        <v>12.08</v>
       </c>
       <c r="AA17" t="n">
-        <v>8.73</v>
+        <v>8.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>20.36</v>
+        <v>20.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.73</v>
+        <v>2.92</v>
       </c>
       <c r="AF17" t="n">
         <v>0.09</v>
@@ -7589,70 +7589,70 @@
         <v>1.36</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.59</v>
+        <v>9.57</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.59</v>
+        <v>4.57</v>
       </c>
       <c r="BR17" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS17" t="n">
-        <v>77.27</v>
+        <v>73.91</v>
       </c>
       <c r="BT17" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU17" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV17" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW17" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX17" t="n">
-        <v>63.64</v>
+        <v>60.87</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CC17" t="n">
         <v>4.16</v>
@@ -7682,7 +7682,7 @@
         <v>1.5</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CM17" t="n">
         <v>2.43</v>
@@ -7697,7 +7697,7 @@
         <v>1.9</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CR17" t="n">
         <v>1.4</v>
@@ -7712,106 +7712,106 @@
         <v>1.48</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CW17" t="n">
         <v>1.82</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB17" t="n">
         <v>1.33</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="DE17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>90.43000000000001</v>
+      </c>
+      <c r="DI17" t="n">
         <v>0.09</v>
       </c>
-      <c r="DF17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="DG17" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="DH17" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="DI17" t="n">
-        <v>0</v>
-      </c>
       <c r="DJ17" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DM17" t="n">
-        <v>42.73</v>
+        <v>42.26</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.86</v>
+        <v>12.96</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.82</v>
+        <v>10.65</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.46</v>
+        <v>7.61</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>39.18</v>
+        <v>39</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.95</v>
+        <v>12.74</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.32</v>
+        <v>9.09</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.45</v>
+        <v>20.48</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="18">
@@ -7821,13 +7821,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
         <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
         <v>0.09</v>
@@ -7914,136 +7914,136 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>84.55</v>
+        <v>87.75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.27</v>
+        <v>2.58</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.55</v>
+        <v>4.58</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="AN18" t="n">
-        <v>37.27</v>
+        <v>39.67</v>
       </c>
       <c r="AO18" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.27</v>
+        <v>10.25</v>
       </c>
       <c r="AR18" t="n">
-        <v>9.91</v>
+        <v>9.58</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.73</v>
+        <v>8.33</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>49.36</v>
+        <v>50.08</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>11</v>
+        <v>11.17</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.18</v>
+        <v>7.33</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="BD18" t="n">
-        <v>19.55</v>
+        <v>20.25</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.27</v>
+        <v>2.58</v>
       </c>
       <c r="BG18" t="n">
         <v>2.91</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.73</v>
+        <v>9.57</v>
       </c>
       <c r="BI18" t="n">
         <v>2.91</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.82</v>
+        <v>4.74</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="BR18" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS18" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT18" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU18" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV18" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW18" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX18" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BY18" t="n">
         <v>3.14</v>
@@ -8052,40 +8052,40 @@
         <v>3.26</v>
       </c>
       <c r="CA18" t="n">
-        <v>4.35</v>
+        <v>4.3</v>
       </c>
       <c r="CB18" t="n">
-        <v>4.37</v>
+        <v>4.32</v>
       </c>
       <c r="CC18" t="n">
-        <v>5.58</v>
+        <v>5.34</v>
       </c>
       <c r="CD18" t="n">
-        <v>6.41</v>
+        <v>6.11</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CK18" t="n">
         <v>1.48</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM18" t="n">
         <v>2.48</v>
@@ -8094,49 +8094,49 @@
         <v>1.93</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX18" t="n">
         <v>1.55</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DD18" t="n">
         <v>2.46</v>
@@ -8145,31 +8145,31 @@
         <v>0.04</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="DH18" t="n">
-        <v>95.86</v>
+        <v>97.04000000000001</v>
       </c>
       <c r="DI18" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.41</v>
+        <v>2.57</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.6</v>
+        <v>4.61</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
       <c r="DM18" t="n">
-        <v>44.32</v>
+        <v>45.26</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="DO18" t="n">
         <v>1.95</v>
@@ -8178,43 +8178,43 @@
         <v>10.04</v>
       </c>
       <c r="DQ18" t="n">
-        <v>9.82</v>
+        <v>9.65</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.59</v>
+        <v>7.43</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>50.82</v>
+        <v>51.13</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.41</v>
+        <v>13.39</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.27</v>
+        <v>9.26</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.23</v>
+        <v>20.57</v>
       </c>
       <c r="EB18" t="n">
         <v>1.46</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="19">
@@ -8224,94 +8224,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
         <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F19" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="G19" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="H19" t="n">
-        <v>101.36</v>
+        <v>101.17</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>4.73</v>
+        <v>4.67</v>
       </c>
       <c r="L19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M19" t="n">
-        <v>56.18</v>
+        <v>53.75</v>
       </c>
       <c r="N19" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="O19" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="P19" t="n">
-        <v>12.09</v>
+        <v>11.92</v>
       </c>
       <c r="Q19" t="n">
-        <v>10.36</v>
+        <v>10.83</v>
       </c>
       <c r="R19" t="n">
-        <v>8.09</v>
+        <v>8</v>
       </c>
       <c r="S19" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="T19" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>49</v>
+        <v>49.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.27</v>
+        <v>13</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.550000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.73</v>
+        <v>4.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>18.73</v>
+        <v>18.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AF19" t="n">
         <v>0.18</v>
@@ -8395,70 +8395,70 @@
         <v>2.09</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.27</v>
+        <v>11.39</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BL19" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="BN19" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.77</v>
+        <v>4.87</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.77</v>
+        <v>5.83</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT19" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BU19" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BV19" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BW19" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX19" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.15</v>
+        <v>4.12</v>
       </c>
       <c r="CC19" t="n">
         <v>4.57</v>
@@ -8470,10 +8470,10 @@
         <v>1.28</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CH19" t="n">
         <v>1.59</v>
@@ -8485,7 +8485,7 @@
         <v>1.59</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="CL19" t="n">
         <v>1.8</v>
@@ -8494,7 +8494,7 @@
         <v>2.68</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CO19" t="n">
         <v>1.18</v>
@@ -8503,7 +8503,7 @@
         <v>1.63</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
@@ -8545,79 +8545,79 @@
         <v>2.7</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="DH19" t="n">
-        <v>91.86</v>
+        <v>92.17</v>
       </c>
       <c r="DI19" t="n">
         <v>0</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="DL19" t="n">
         <v>0.09</v>
       </c>
       <c r="DM19" t="n">
-        <v>44.22</v>
+        <v>43.48</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="DO19" t="n">
         <v>1.22</v>
       </c>
       <c r="DP19" t="n">
-        <v>11.22</v>
+        <v>11.17</v>
       </c>
       <c r="DQ19" t="n">
-        <v>9.4</v>
+        <v>9.69</v>
       </c>
       <c r="DR19" t="n">
-        <v>9.039999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>46.22</v>
+        <v>46.39</v>
       </c>
       <c r="DW19" t="n">
         <v>0.04</v>
       </c>
       <c r="DX19" t="n">
-        <v>11.68</v>
+        <v>11.61</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.73</v>
+        <v>7.65</v>
       </c>
       <c r="DZ19" t="n">
         <v>3.96</v>
       </c>
       <c r="EA19" t="n">
-        <v>17.69</v>
+        <v>17.48</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="EC19" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="G2" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="H2" t="n">
-        <v>99.42</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="K2" t="n">
-        <v>5.42</v>
+        <v>5.46</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="M2" t="n">
-        <v>42.08</v>
+        <v>42.69</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="P2" t="n">
-        <v>11.5</v>
+        <v>11.77</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.92</v>
+        <v>11.31</v>
       </c>
       <c r="R2" t="n">
-        <v>8.33</v>
+        <v>8.31</v>
       </c>
       <c r="S2" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="T2" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="U2" t="n">
         <v>0.08</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>47.17</v>
+        <v>47.08</v>
       </c>
       <c r="Y2" t="n">
         <v>0.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.33</v>
+        <v>12.46</v>
       </c>
       <c r="AA2" t="n">
-        <v>7.83</v>
+        <v>8</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="AC2" t="n">
-        <v>20.67</v>
+        <v>20.85</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="AF2" t="n">
         <v>0.09</v>
@@ -1550,70 +1550,70 @@
         <v>2.82</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.48</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4.57</v>
+        <v>4.79</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS2" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT2" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BU2" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BV2" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX2" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.01</v>
+        <v>3.98</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="CC2" t="n">
         <v>5.01</v>
@@ -1625,10 +1625,10 @@
         <v>1.33</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="CH2" t="n">
         <v>1.54</v>
@@ -1643,7 +1643,7 @@
         <v>1.51</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CM2" t="n">
         <v>2.44</v>
@@ -1664,13 +1664,13 @@
         <v>1.36</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CV2" t="n">
         <v>2.3</v>
@@ -1682,7 +1682,7 @@
         <v>1.57</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.37</v>
@@ -1697,49 +1697,49 @@
         <v>1.8</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="DH2" t="n">
-        <v>98</v>
+        <v>97.58</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.61</v>
+        <v>4.67</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="DM2" t="n">
-        <v>40.39</v>
+        <v>40.79</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DP2" t="n">
-        <v>11.91</v>
+        <v>12.04</v>
       </c>
       <c r="DQ2" t="n">
-        <v>12.31</v>
+        <v>11.96</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.34</v>
+        <v>8.33</v>
       </c>
       <c r="DS2" t="n">
         <v>0.13</v>
@@ -1757,22 +1757,22 @@
         <v>0.04</v>
       </c>
       <c r="DX2" t="n">
-        <v>12.82</v>
+        <v>12.87</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.43</v>
+        <v>8.5</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.39</v>
+        <v>4.37</v>
       </c>
       <c r="EA2" t="n">
-        <v>19</v>
+        <v>19.17</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.61</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="G3" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>118.36</v>
+        <v>119.83</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>49.82</v>
+        <v>51.83</v>
       </c>
       <c r="N3" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="O3" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>8.82</v>
+        <v>8.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.27</v>
+        <v>10.5</v>
       </c>
       <c r="R3" t="n">
-        <v>6.18</v>
+        <v>6.42</v>
       </c>
       <c r="S3" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="T3" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>61.55</v>
+        <v>61.92</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.82</v>
+        <v>15.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>10.27</v>
+        <v>10</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>16.27</v>
+        <v>17.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AF3" t="n">
         <v>0.18</v>
@@ -1953,70 +1953,70 @@
         <v>2.09</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="BH3" t="n">
-        <v>9.73</v>
+        <v>9.65</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="BP3" t="n">
-        <v>4.41</v>
+        <v>4.26</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.32</v>
+        <v>5.39</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU3" t="n">
-        <v>40.91</v>
+        <v>39.13</v>
       </c>
       <c r="BV3" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW3" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BX3" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CA3" t="n">
         <v>4.02</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.05</v>
+        <v>4.06</v>
       </c>
       <c r="CC3" t="n">
         <v>2.91</v>
@@ -2025,13 +2025,13 @@
         <v>3.17</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CH3" t="n">
         <v>1.61</v>
@@ -2043,10 +2043,10 @@
         <v>1.58</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CM3" t="n">
         <v>2.48</v>
@@ -2058,10 +2058,10 @@
         <v>1.17</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CR3" t="n">
         <v>1.35</v>
@@ -2076,22 +2076,22 @@
         <v>1.64</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CW3" t="n">
         <v>1.61</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DB3" t="n">
         <v>1.29</v>
@@ -2106,76 +2106,76 @@
         <v>0.22</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.95</v>
+        <v>3.09</v>
       </c>
       <c r="DH3" t="n">
-        <v>112.18</v>
+        <v>113.22</v>
       </c>
       <c r="DI3" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.09</v>
+        <v>5.13</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM3" t="n">
-        <v>48.18</v>
+        <v>49.3</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
       <c r="DP3" t="n">
-        <v>8.73</v>
+        <v>8.74</v>
       </c>
       <c r="DQ3" t="n">
-        <v>11.36</v>
+        <v>11.43</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.82</v>
+        <v>6.91</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>59.73</v>
+        <v>60</v>
       </c>
       <c r="DW3" t="n">
         <v>0.09</v>
       </c>
       <c r="DX3" t="n">
-        <v>13.78</v>
+        <v>13.7</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.220000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.55</v>
+        <v>4.57</v>
       </c>
       <c r="EA3" t="n">
-        <v>16.36</v>
+        <v>17</v>
       </c>
       <c r="EB3" t="n">
         <v>1.54</v>
       </c>
       <c r="EC3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0.25</v>
@@ -2275,58 +2275,58 @@
         <v>1.42</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>132.64</v>
+        <v>131.08</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.82</v>
+        <v>5.5</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>67.81999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.82</v>
+        <v>8.92</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.91</v>
+        <v>9.33</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.82</v>
+        <v>6.08</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
@@ -2338,55 +2338,55 @@
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>17.55</v>
+        <v>17.25</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.91</v>
+        <v>8.83</v>
       </c>
       <c r="BC4" t="n">
-        <v>8.640000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="BD4" t="n">
-        <v>19.45</v>
+        <v>19.42</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.61</v>
+        <v>4.62</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.74</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>4.61</v>
+        <v>4.62</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="BN4" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.04</v>
+        <v>4.96</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -2398,16 +2398,16 @@
         <v>100</v>
       </c>
       <c r="BU4" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BV4" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BW4" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BX4" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY4" t="n">
         <v>1.16</v>
@@ -2416,16 +2416,16 @@
         <v>1.17</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.62</v>
+        <v>7.49</v>
       </c>
       <c r="CB4" t="n">
-        <v>8.380000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="CC4" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="CD4" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="CE4" t="n">
         <v>1.15</v>
@@ -2434,37 +2434,37 @@
         <v>1.79</v>
       </c>
       <c r="CG4" t="n">
-        <v>4.97</v>
+        <v>4.93</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CK4" t="n">
         <v>1.5</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CN4" t="n">
         <v>1.91</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CQ4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CR4" t="inlineStr"/>
       <c r="CS4" t="n">
@@ -2472,107 +2472,107 @@
       </c>
       <c r="CT4" t="inlineStr"/>
       <c r="CU4" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.46</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="DB4" t="inlineStr"/>
       <c r="DC4" t="n">
         <v>1.36</v>
       </c>
       <c r="DD4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="DH4" t="n">
-        <v>133.91</v>
+        <v>133.08</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="DK4" t="n">
-        <v>6.35</v>
+        <v>6.16</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM4" t="n">
-        <v>68.22</v>
+        <v>67.62</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.17</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DQ4" t="n">
-        <v>8.57</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DR4" t="n">
-        <v>5.91</v>
+        <v>6.04</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>66.56999999999999</v>
+        <v>66.58</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>19.13</v>
+        <v>18.92</v>
       </c>
       <c r="DY4" t="n">
-        <v>10.22</v>
+        <v>10.12</v>
       </c>
       <c r="DZ4" t="n">
-        <v>8.92</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.22</v>
+        <v>19.21</v>
       </c>
       <c r="EB4" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="5">
@@ -2582,94 +2582,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G5" t="n">
-        <v>4.09</v>
+        <v>3.92</v>
       </c>
       <c r="H5" t="n">
-        <v>114.09</v>
+        <v>111.33</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>7.18</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>57.09</v>
+        <v>56.25</v>
       </c>
       <c r="N5" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="O5" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="P5" t="n">
-        <v>11.36</v>
+        <v>11.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.18</v>
+        <v>9.25</v>
       </c>
       <c r="R5" t="n">
-        <v>6.82</v>
+        <v>6.92</v>
       </c>
       <c r="S5" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="T5" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="U5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V5" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>56</v>
+        <v>54.08</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.36</v>
+        <v>14</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.640000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.73</v>
+        <v>5.42</v>
       </c>
       <c r="AC5" t="n">
-        <v>18</v>
+        <v>17.83</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AF5" t="n">
         <v>0.17</v>
@@ -2753,67 +2753,67 @@
         <v>2.25</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.91</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BL5" t="n">
         <v>1</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.78</v>
+        <v>0.88</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.65</v>
+        <v>5.54</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="BV5" t="n">
-        <v>21.74</v>
+        <v>25</v>
       </c>
       <c r="BW5" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX5" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.3</v>
+        <v>4.31</v>
       </c>
       <c r="CB5" t="n">
         <v>4.46</v>
@@ -2828,154 +2828,154 @@
         <v>1.26</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CK5" t="n">
         <v>1.48</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CN5" t="n">
         <v>1.94</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CR5" t="n">
         <v>1.34</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="CT5" t="n">
         <v>3.32</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CX5" t="n">
         <v>1.57</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.4</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="DB5" t="n">
         <v>1.29</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DE5" t="n">
         <v>0.17</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="DG5" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="DH5" t="n">
-        <v>107.13</v>
+        <v>106.04</v>
       </c>
       <c r="DI5" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.3</v>
+        <v>5.29</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM5" t="n">
-        <v>59.65</v>
+        <v>59.12</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO5" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.52</v>
+        <v>11.67</v>
       </c>
       <c r="DQ5" t="n">
-        <v>10.22</v>
+        <v>10.21</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.65</v>
+        <v>6.71</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>53.56</v>
+        <v>52.71</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.13</v>
+        <v>13</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.220000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.92</v>
+        <v>4.79</v>
       </c>
       <c r="EA5" t="n">
-        <v>20</v>
+        <v>19.83</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="6">
@@ -2985,94 +2985,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F6" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="G6" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="H6" t="n">
-        <v>87.27</v>
+        <v>90.08</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
       <c r="K6" t="n">
-        <v>3.91</v>
+        <v>4.08</v>
       </c>
       <c r="L6" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="M6" t="n">
-        <v>37.45</v>
+        <v>39.17</v>
       </c>
       <c r="N6" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>10.64</v>
+        <v>10.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.640000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="R6" t="n">
-        <v>8.449999999999999</v>
+        <v>8</v>
       </c>
       <c r="S6" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="T6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="U6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>45.09</v>
+        <v>46.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.91</v>
+        <v>11.67</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.91</v>
+        <v>7.42</v>
       </c>
       <c r="AB6" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>17.64</v>
+        <v>17.92</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.91</v>
+        <v>1.17</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3156,70 +3156,70 @@
         <v>1.58</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.09</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.96</v>
+        <v>4.88</v>
       </c>
       <c r="BR6" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BS6" t="n">
-        <v>73.91</v>
+        <v>70.83</v>
       </c>
       <c r="BT6" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BU6" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX6" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.24</v>
+        <v>3.17</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="CC6" t="n">
         <v>3.67</v>
@@ -3231,58 +3231,58 @@
         <v>1.29</v>
       </c>
       <c r="CF6" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CI6" t="n">
         <v>2.37</v>
       </c>
-      <c r="CG6" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="CH6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>2.39</v>
-      </c>
       <c r="CJ6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CL6" t="n">
         <v>1.87</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CX6" t="n">
         <v>1.56</v>
@@ -3300,85 +3300,85 @@
         <v>1.28</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="DG6" t="n">
         <v>2.08</v>
       </c>
       <c r="DH6" t="n">
-        <v>85.61</v>
+        <v>87.08</v>
       </c>
       <c r="DI6" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.35</v>
+        <v>4.42</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="DM6" t="n">
-        <v>35.82</v>
+        <v>36.75</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.47</v>
+        <v>0.54</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.22</v>
+        <v>10.96</v>
       </c>
       <c r="DQ6" t="n">
-        <v>10.65</v>
+        <v>10.92</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.43</v>
+        <v>7.25</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.96</v>
+        <v>46.54</v>
       </c>
       <c r="DW6" t="n">
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.26</v>
+        <v>11.62</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.26</v>
+        <v>7.5</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.44</v>
+        <v>17.58</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="EC6" t="n">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="7">
@@ -4597,13 +4597,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4690,49 +4690,49 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AH10" t="n">
-        <v>3.27</v>
+        <v>3.08</v>
       </c>
       <c r="AI10" t="n">
-        <v>83</v>
+        <v>82.67</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.82</v>
+        <v>4.58</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>39.18</v>
+        <v>38.33</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11.09</v>
+        <v>10.92</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.18</v>
+        <v>10.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.09</v>
+        <v>9.17</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4744,82 +4744,82 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>43.82</v>
+        <v>44.33</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.73</v>
+        <v>11.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.449999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="BD10" t="n">
-        <v>20.09</v>
+        <v>19.83</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.869999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="BM10" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BN10" t="n">
         <v>1.83</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.91</v>
+        <v>5.75</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU10" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX10" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BY10" t="n">
         <v>4.22</v>
@@ -4828,16 +4828,16 @@
         <v>4.75</v>
       </c>
       <c r="CA10" t="n">
-        <v>4.17</v>
+        <v>4.18</v>
       </c>
       <c r="CB10" t="n">
-        <v>4.38</v>
+        <v>4.37</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.72</v>
+        <v>5.62</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="CE10" t="n">
         <v>1.29</v>
@@ -4846,10 +4846,10 @@
         <v>2.4</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI10" t="n">
         <v>2.19</v>
@@ -4861,28 +4861,28 @@
         <v>1.51</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CM10" t="n">
         <v>2.42</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CO10" t="n">
         <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CQ10" t="n">
         <v>2.57</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CT10" t="n">
         <v>3.16</v>
@@ -4891,19 +4891,19 @@
         <v>1.6</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CW10" t="n">
         <v>1.71</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CY10" t="n">
         <v>1.92</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DA10" t="n">
         <v>1.91</v>
@@ -4921,43 +4921,43 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="DH10" t="n">
-        <v>81.34999999999999</v>
+        <v>81.25</v>
       </c>
       <c r="DI10" t="n">
         <v>0</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.83</v>
+        <v>4.7</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="DM10" t="n">
-        <v>37.87</v>
+        <v>37.5</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="DO10" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.48</v>
+        <v>10.42</v>
       </c>
       <c r="DQ10" t="n">
-        <v>10.26</v>
+        <v>10.42</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.65</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DS10" t="n">
         <v>0.04</v>
@@ -4969,28 +4969,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>41.96</v>
+        <v>42.29</v>
       </c>
       <c r="DW10" t="n">
         <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.91</v>
+        <v>11.79</v>
       </c>
       <c r="DY10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.61</v>
+        <v>3.46</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.7</v>
+        <v>18.62</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11">
@@ -5000,94 +5000,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F11" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="G11" t="n">
-        <v>2.27</v>
+        <v>2.58</v>
       </c>
       <c r="H11" t="n">
-        <v>112.82</v>
+        <v>116.17</v>
       </c>
       <c r="I11" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="J11" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="K11" t="n">
-        <v>5.45</v>
+        <v>5.83</v>
       </c>
       <c r="L11" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="M11" t="n">
-        <v>52</v>
+        <v>55.08</v>
       </c>
       <c r="N11" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="O11" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>14.36</v>
+        <v>14.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.18</v>
+        <v>9</v>
       </c>
       <c r="R11" t="n">
-        <v>6.09</v>
+        <v>6</v>
       </c>
       <c r="S11" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="U11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>55.36</v>
+        <v>56.17</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>15.36</v>
+        <v>15.83</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.73</v>
+        <v>9.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.64</v>
+        <v>6.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.64</v>
+        <v>22</v>
       </c>
       <c r="AD11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.82</v>
       </c>
       <c r="AF11" t="n">
         <v>0.08</v>
@@ -5171,70 +5171,70 @@
         <v>2.33</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.43</v>
+        <v>3.33</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.74</v>
+        <v>10.83</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.43</v>
+        <v>3.33</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BP11" t="n">
-        <v>5</v>
+        <v>5.08</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.74</v>
+        <v>5.75</v>
       </c>
       <c r="BR11" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS11" t="n">
-        <v>86.95999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT11" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU11" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BV11" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BW11" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.99</v>
+        <v>4.02</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="CC11" t="n">
         <v>3.39</v>
@@ -5246,46 +5246,46 @@
         <v>1.25</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CK11" t="n">
         <v>1.42</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO11" t="n">
         <v>1.15</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="CR11" t="n">
         <v>1.34</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CT11" t="n">
         <v>3.33</v>
@@ -5294,10 +5294,10 @@
         <v>1.63</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CX11" t="n">
         <v>1.52</v>
@@ -5306,61 +5306,61 @@
         <v>1.77</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="DA11" t="n">
         <v>2.07</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.51</v>
+        <v>2.55</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.43</v>
+        <v>2.58</v>
       </c>
       <c r="DH11" t="n">
-        <v>108</v>
+        <v>109.88</v>
       </c>
       <c r="DI11" t="n">
         <v>0.3</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.22</v>
+        <v>5.42</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="DM11" t="n">
-        <v>48.44</v>
+        <v>50.12</v>
       </c>
       <c r="DN11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="DP11" t="n">
-        <v>14</v>
+        <v>13.96</v>
       </c>
       <c r="DQ11" t="n">
-        <v>9.220000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.52</v>
+        <v>6.46</v>
       </c>
       <c r="DS11" t="n">
         <v>0.17</v>
@@ -5372,28 +5372,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>53.7</v>
+        <v>54.17</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.48</v>
+        <v>13.79</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.48</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.96</v>
+        <v>21.16</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="12">
@@ -5403,13 +5403,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
         <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>0.17</v>
@@ -5493,139 +5493,139 @@
         <v>1.33</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.09</v>
+        <v>2.42</v>
       </c>
       <c r="AI12" t="n">
-        <v>88.73</v>
+        <v>88.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.91</v>
+        <v>4.33</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="AN12" t="n">
-        <v>40.36</v>
+        <v>39.83</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.91</v>
+        <v>8.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>10</v>
+        <v>10.42</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.36</v>
+        <v>10.08</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>46.27</v>
+        <v>46.92</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.55</v>
+        <v>12.33</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.640000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.82</v>
+        <v>18.92</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.09</v>
+        <v>10.29</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.13</v>
+        <v>3.08</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL12" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BN12" t="n">
         <v>1.83</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5</v>
+        <v>5.21</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT12" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BU12" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BV12" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX12" t="n">
-        <v>73.91</v>
+        <v>70.83</v>
       </c>
       <c r="BY12" t="n">
         <v>2.98</v>
@@ -5634,16 +5634,16 @@
         <v>3.25</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.99</v>
+        <v>3.97</v>
       </c>
       <c r="CC12" t="n">
-        <v>4.14</v>
+        <v>4.07</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.22</v>
+        <v>4.15</v>
       </c>
       <c r="CE12" t="n">
         <v>1.29</v>
@@ -5652,43 +5652,43 @@
         <v>2.36</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="CH12" t="n">
         <v>1.59</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.57</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CT12" t="n">
         <v>3.24</v>
@@ -5709,61 +5709,61 @@
         <v>1.75</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DA12" t="n">
         <v>2.1</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="DE12" t="n">
         <v>0.17</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="DH12" t="n">
-        <v>92.61</v>
+        <v>92.34</v>
       </c>
       <c r="DI12" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.13</v>
+        <v>4.33</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DM12" t="n">
-        <v>43.43</v>
+        <v>43.04</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="DP12" t="n">
-        <v>8.26</v>
+        <v>8.08</v>
       </c>
       <c r="DQ12" t="n">
-        <v>10.87</v>
+        <v>11.04</v>
       </c>
       <c r="DR12" t="n">
-        <v>9.130000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DS12" t="n">
         <v>0.04</v>
@@ -5775,28 +5775,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>46.78</v>
+        <v>47.08</v>
       </c>
       <c r="DW12" t="n">
         <v>0.04</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.05</v>
+        <v>12.92</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.609999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.44</v>
+        <v>4.38</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.22</v>
+        <v>20.21</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="EC12" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="13">
@@ -5806,13 +5806,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>0.08</v>
@@ -5902,133 +5902,133 @@
         <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="AI13" t="n">
-        <v>93.55</v>
+        <v>94.25</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="AL13" t="n">
-        <v>3.82</v>
+        <v>3.67</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN13" t="n">
-        <v>42.64</v>
+        <v>42.75</v>
       </c>
       <c r="AO13" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.82</v>
+        <v>11</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.359999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.27</v>
+        <v>8.33</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>40.45</v>
+        <v>39.92</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.27</v>
+        <v>9.17</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.82</v>
+        <v>5.67</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>21.09</v>
+        <v>20.5</v>
       </c>
       <c r="BE13" t="n">
         <v>1.14</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.390000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.65</v>
+        <v>5.71</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS13" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT13" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV13" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW13" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX13" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BY13" t="n">
         <v>2.24</v>
@@ -6043,10 +6043,10 @@
         <v>4.07</v>
       </c>
       <c r="CC13" t="n">
-        <v>5.18</v>
+        <v>5.11</v>
       </c>
       <c r="CD13" t="n">
-        <v>5.48</v>
+        <v>5.43</v>
       </c>
       <c r="CE13" t="n">
         <v>1.32</v>
@@ -6070,7 +6070,7 @@
         <v>1.47</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM13" t="n">
         <v>2.5</v>
@@ -6079,7 +6079,7 @@
         <v>1.95</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP13" t="n">
         <v>1.72</v>
@@ -6091,7 +6091,7 @@
         <v>1.37</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CT13" t="n">
         <v>3.18</v>
@@ -6100,7 +6100,7 @@
         <v>1.58</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CW13" t="n">
         <v>1.66</v>
@@ -6112,7 +6112,7 @@
         <v>1.86</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DA13" t="n">
         <v>1.96</v>
@@ -6130,76 +6130,76 @@
         <v>0.04</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DG13" t="n">
-        <v>3.48</v>
+        <v>3.38</v>
       </c>
       <c r="DH13" t="n">
-        <v>104.05</v>
+        <v>103.96</v>
       </c>
       <c r="DI13" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.22</v>
+        <v>5.08</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM13" t="n">
-        <v>49.87</v>
+        <v>49.62</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.83</v>
+        <v>0.8</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.52</v>
+        <v>11.58</v>
       </c>
       <c r="DQ13" t="n">
-        <v>9.779999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.65</v>
+        <v>7.71</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>44.69</v>
+        <v>44.25</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.39</v>
+        <v>11.25</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.78</v>
+        <v>7.62</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.57</v>
+        <v>22.21</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="14">
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6708,46 +6708,46 @@
         <v>0.92</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AI15" t="n">
-        <v>90.83</v>
+        <v>88.54000000000001</v>
       </c>
       <c r="AJ15" t="n">
         <v>0.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AL15" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.58</v>
+        <v>37.85</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.67</v>
+        <v>10.38</v>
       </c>
       <c r="AR15" t="n">
-        <v>9.08</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.25</v>
+        <v>6.69</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AV15" t="n">
         <v>0.08</v>
@@ -6759,82 +6759,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>43.25</v>
+        <v>42.62</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.08</v>
+        <v>10.15</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.42</v>
+        <v>7.46</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="BD15" t="n">
-        <v>20.58</v>
+        <v>20.85</v>
       </c>
       <c r="BE15" t="n">
         <v>1.11</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.699999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="BO15" t="n">
         <v>1.04</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.04</v>
+        <v>4.17</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.13</v>
+        <v>5.17</v>
       </c>
       <c r="BR15" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS15" t="n">
-        <v>82.61</v>
+        <v>79.17</v>
       </c>
       <c r="BT15" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BU15" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV15" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW15" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX15" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BY15" t="n">
         <v>3.07</v>
@@ -6843,10 +6843,10 @@
         <v>3.19</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.96</v>
+        <v>3.97</v>
       </c>
       <c r="CC15" t="n">
         <v>6.26</v>
@@ -6858,13 +6858,13 @@
         <v>1.39</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI15" t="n">
         <v>1.93</v>
@@ -6873,25 +6873,25 @@
         <v>1.85</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CO15" t="n">
         <v>1.29</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="CR15" t="n">
         <v>1.4</v>
@@ -6906,22 +6906,22 @@
         <v>1.48</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DB15" t="n">
         <v>1.34</v>
@@ -6930,7 +6930,7 @@
         <v>1.99</v>
       </c>
       <c r="DD15" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="DE15" t="n">
         <v>0.04</v>
@@ -6939,40 +6939,40 @@
         <v>0.87</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="DH15" t="n">
-        <v>96.04000000000001</v>
+        <v>94.59</v>
       </c>
       <c r="DI15" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.69</v>
+        <v>4.63</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="DM15" t="n">
-        <v>43.21</v>
+        <v>42.63</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.31</v>
+        <v>10.16</v>
       </c>
       <c r="DQ15" t="n">
-        <v>9.960000000000001</v>
+        <v>10.08</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.17</v>
+        <v>6.41</v>
       </c>
       <c r="DS15" t="n">
         <v>0.17</v>
@@ -6984,28 +6984,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.17</v>
+        <v>44.75</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>10.35</v>
+        <v>10.37</v>
       </c>
       <c r="DY15" t="n">
-        <v>6.78</v>
+        <v>6.83</v>
       </c>
       <c r="DZ15" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.35</v>
+        <v>21.46</v>
       </c>
       <c r="EB15" t="n">
         <v>1.22</v>
       </c>
       <c r="EC15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="16">
@@ -7418,13 +7418,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
         <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
         <v>0.08</v>
@@ -7508,139 +7508,139 @@
         <v>2.92</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AI17" t="n">
-        <v>90.27</v>
+        <v>89.42</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.45</v>
+        <v>5.17</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AN17" t="n">
-        <v>43.55</v>
+        <v>42.75</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.18</v>
+        <v>12.67</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.91</v>
+        <v>9.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.550000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>40.09</v>
+        <v>40.08</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA17" t="n">
-        <v>13.45</v>
+        <v>12.83</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.91</v>
+        <v>9.42</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.55</v>
+        <v>20.75</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.87</v>
+        <v>2.79</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.57</v>
+        <v>9.5</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.87</v>
+        <v>2.79</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="BR17" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS17" t="n">
-        <v>73.91</v>
+        <v>70.83</v>
       </c>
       <c r="BT17" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BU17" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BV17" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX17" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BY17" t="n">
         <v>3.01</v>
@@ -7649,25 +7649,25 @@
         <v>3.58</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CC17" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="CD17" t="n">
         <v>4.16</v>
       </c>
-      <c r="CD17" t="n">
-        <v>4.25</v>
-      </c>
       <c r="CE17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CF17" t="n">
         <v>2.74</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CH17" t="n">
         <v>1.46</v>
@@ -7679,7 +7679,7 @@
         <v>1.76</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CL17" t="n">
         <v>1.95</v>
@@ -7688,28 +7688,28 @@
         <v>2.43</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CO17" t="n">
         <v>1.27</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CR17" t="n">
         <v>1.4</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CT17" t="n">
         <v>3.05</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV17" t="n">
         <v>2.08</v>
@@ -7733,52 +7733,52 @@
         <v>1.33</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DD17" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="DE17" t="n">
         <v>0.08</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="DH17" t="n">
-        <v>90.43000000000001</v>
+        <v>90</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.35</v>
+        <v>5.21</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DM17" t="n">
-        <v>42.26</v>
+        <v>41.92</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.96</v>
+        <v>13.17</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.65</v>
+        <v>10.42</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.61</v>
+        <v>7.71</v>
       </c>
       <c r="DS17" t="n">
         <v>0.08</v>
@@ -7790,28 +7790,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>39</v>
+        <v>39.04</v>
       </c>
       <c r="DW17" t="n">
         <v>0.08</v>
       </c>
       <c r="DX17" t="n">
-        <v>12.74</v>
+        <v>12.46</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.09</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.48</v>
+        <v>20.58</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -7821,94 +7821,94 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F18" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="G18" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="H18" t="n">
-        <v>107.18</v>
+        <v>107.25</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="K18" t="n">
-        <v>4.64</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="M18" t="n">
-        <v>51.36</v>
+        <v>50.83</v>
       </c>
       <c r="N18" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O18" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="P18" t="n">
-        <v>9.82</v>
+        <v>10.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>9.73</v>
+        <v>9.67</v>
       </c>
       <c r="R18" t="n">
-        <v>6.45</v>
+        <v>6.92</v>
       </c>
       <c r="S18" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="T18" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="U18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>52.27</v>
+        <v>52.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>15.82</v>
+        <v>15.92</v>
       </c>
       <c r="AA18" t="n">
-        <v>11.36</v>
+        <v>11.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.45</v>
+        <v>4.58</v>
       </c>
       <c r="AC18" t="n">
-        <v>20.91</v>
+        <v>21.58</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7992,64 +7992,64 @@
         <v>2.58</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.57</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BL18" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BN18" t="n">
         <v>1.83</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.74</v>
+        <v>4.67</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.83</v>
+        <v>4.71</v>
       </c>
       <c r="BR18" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS18" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT18" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BU18" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV18" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW18" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX18" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BY18" t="n">
-        <v>3.14</v>
+        <v>3.01</v>
       </c>
       <c r="BZ18" t="n">
-        <v>3.26</v>
+        <v>3.12</v>
       </c>
       <c r="CA18" t="n">
         <v>4.3</v>
@@ -8070,7 +8070,7 @@
         <v>2.31</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CH18" t="n">
         <v>1.62</v>
@@ -8085,7 +8085,7 @@
         <v>1.48</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CM18" t="n">
         <v>2.48</v>
@@ -8112,13 +8112,13 @@
         <v>3.18</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CX18" t="n">
         <v>1.55</v>
@@ -8127,7 +8127,7 @@
         <v>1.88</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="DA18" t="n">
         <v>1.95</v>
@@ -8145,43 +8145,43 @@
         <v>0.04</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="DH18" t="n">
-        <v>97.04000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="DI18" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ18" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.61</v>
+        <v>4.54</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="DM18" t="n">
-        <v>45.26</v>
+        <v>45.25</v>
       </c>
       <c r="DN18" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
       <c r="DO18" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DP18" t="n">
-        <v>10.04</v>
+        <v>10.21</v>
       </c>
       <c r="DQ18" t="n">
-        <v>9.65</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.43</v>
+        <v>7.62</v>
       </c>
       <c r="DS18" t="n">
         <v>0.08</v>
@@ -8193,28 +8193,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.13</v>
+        <v>51.08</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.39</v>
+        <v>13.54</v>
       </c>
       <c r="DY18" t="n">
-        <v>9.26</v>
+        <v>9.33</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.13</v>
+        <v>4.2</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.57</v>
+        <v>20.92</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2025-2026.xlsx
@@ -3057,10 +3057,10 @@
         <v>0.08</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.67</v>
+        <v>11.75</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.42</v>
+        <v>7.5</v>
       </c>
       <c r="AB6" t="n">
         <v>4.25</v>
@@ -3363,10 +3363,10 @@
         <v>0.04</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.62</v>
+        <v>11.66</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.5</v>
+        <v>7.54</v>
       </c>
       <c r="DZ6" t="n">
         <v>4.12</v>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
@@ -3400,82 +3400,82 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="G7" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="H7" t="n">
-        <v>93.27</v>
+        <v>93.08</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="M7" t="n">
-        <v>44.09</v>
+        <v>43.42</v>
       </c>
       <c r="N7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="O7" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="P7" t="n">
-        <v>10.36</v>
+        <v>10.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>10</v>
+        <v>10.08</v>
       </c>
       <c r="R7" t="n">
-        <v>7.45</v>
+        <v>7.17</v>
       </c>
       <c r="S7" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="V7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>50.55</v>
+        <v>51.58</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>12.45</v>
+        <v>12.67</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.45</v>
+        <v>7.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="AC7" t="n">
-        <v>20.09</v>
+        <v>19.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AF7" t="n">
         <v>0.17</v>
@@ -3559,70 +3559,70 @@
         <v>2.17</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.13</v>
+        <v>4.04</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.43</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="BI7" t="n">
-        <v>4.13</v>
+        <v>4.04</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BM7" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BN7" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.48</v>
+        <v>4.42</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.91</v>
+        <v>4.08</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BT7" t="n">
-        <v>69.56999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU7" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BX7" t="n">
-        <v>73.91</v>
+        <v>70.83</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.16</v>
+        <v>4.15</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
       <c r="CC7" t="n">
         <v>4.04</v>
@@ -3634,16 +3634,16 @@
         <v>1.25</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CH7" t="n">
         <v>1.65</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.53</v>
@@ -3652,7 +3652,7 @@
         <v>1.51</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CM7" t="n">
         <v>2.42</v>
@@ -3667,37 +3667,37 @@
         <v>1.56</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CU7" t="n">
         <v>1.66</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CW7" t="n">
         <v>1.58</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="DB7" t="n">
         <v>1.28</v>
@@ -3706,82 +3706,82 @@
         <v>1.64</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="DH7" t="n">
-        <v>97.95999999999999</v>
+        <v>97.66</v>
       </c>
       <c r="DI7" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="DK7" t="n">
-        <v>4.26</v>
+        <v>4.29</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM7" t="n">
-        <v>43.69</v>
+        <v>43.38</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.95</v>
+        <v>10.88</v>
       </c>
       <c r="DQ7" t="n">
-        <v>9.44</v>
+        <v>9.5</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.83</v>
+        <v>7.67</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>52.44</v>
+        <v>52.88</v>
       </c>
       <c r="DW7" t="n">
         <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>11.47</v>
+        <v>11.62</v>
       </c>
       <c r="DY7" t="n">
-        <v>7.08</v>
+        <v>7.12</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.39</v>
+        <v>4.5</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.26</v>
+        <v>20.08</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="8">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
         <v>0.18</v>
@@ -3884,136 +3884,136 @@
         <v>0.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>81.25</v>
+        <v>79.92</v>
       </c>
       <c r="AJ8" t="n">
         <v>0.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.92</v>
+        <v>4.08</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="AN8" t="n">
-        <v>38.83</v>
+        <v>38.15</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="AP8" t="n">
         <v>2.08</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.92</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.33</v>
+        <v>12.08</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>7.62</v>
       </c>
       <c r="AT8" t="n">
         <v>2.08</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>44.5</v>
+        <v>43.92</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.08</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.33</v>
+        <v>10.77</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.17</v>
+        <v>7.69</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="BD8" t="n">
-        <v>17.25</v>
+        <v>17.31</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.57</v>
+        <v>8.67</v>
       </c>
       <c r="BI8" t="n">
-        <v>3.09</v>
+        <v>3.04</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL8" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.26</v>
+        <v>4.42</v>
       </c>
       <c r="BR8" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS8" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>65.22</v>
+        <v>62.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV8" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX8" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BY8" t="n">
         <v>2.15</v>
@@ -4022,16 +4022,16 @@
         <v>2.29</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CC8" t="n">
-        <v>4.05</v>
+        <v>3.99</v>
       </c>
       <c r="CD8" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="CE8" t="n">
         <v>1.34</v>
@@ -4040,7 +4040,7 @@
         <v>2.62</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CH8" t="n">
         <v>1.49</v>
@@ -4055,10 +4055,10 @@
         <v>1.62</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CN8" t="n">
         <v>1.76</v>
@@ -4070,10 +4070,10 @@
         <v>1.81</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS8" t="n">
         <v>2.68</v>
@@ -4085,7 +4085,7 @@
         <v>1.5</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CW8" t="n">
         <v>1.73</v>
@@ -4115,76 +4115,76 @@
         <v>0.13</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="DH8" t="n">
-        <v>89.43000000000001</v>
+        <v>88.37</v>
       </c>
       <c r="DI8" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.39</v>
+        <v>4.46</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="DM8" t="n">
-        <v>42.3</v>
+        <v>41.79</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DP8" t="n">
-        <v>9.57</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.13</v>
+        <v>12</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.91</v>
+        <v>6.75</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47.96</v>
+        <v>47.5</v>
       </c>
       <c r="DW8" t="n">
         <v>0.13</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.43</v>
+        <v>12.09</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.35</v>
+        <v>8.08</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="EA8" t="n">
-        <v>18.87</v>
+        <v>18.84</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="EC8" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9">
@@ -4194,94 +4194,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="H9" t="n">
-        <v>86.18000000000001</v>
+        <v>84.92</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="K9" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="L9" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M9" t="n">
-        <v>39.82</v>
+        <v>39</v>
       </c>
       <c r="N9" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="P9" t="n">
-        <v>12.36</v>
+        <v>12</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.09</v>
+        <v>13</v>
       </c>
       <c r="R9" t="n">
-        <v>8.27</v>
+        <v>8.33</v>
       </c>
       <c r="S9" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="U9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>46.09</v>
+        <v>45.75</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.55</v>
+        <v>13.92</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.09</v>
+        <v>8.67</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.45</v>
+        <v>5.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.73</v>
+        <v>18</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4365,70 +4365,70 @@
         <v>2.27</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BH9" t="n">
-        <v>8.859999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BP9" t="n">
-        <v>3.64</v>
+        <v>3.78</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.55</v>
+        <v>4.61</v>
       </c>
       <c r="BR9" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BS9" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU9" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BV9" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.29</v>
+        <v>3.36</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="CC9" t="n">
         <v>5.44</v>
@@ -4443,16 +4443,16 @@
         <v>2.46</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="CH9" t="n">
         <v>1.57</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CK9" t="n">
         <v>1.49</v>
@@ -4461,7 +4461,7 @@
         <v>1.91</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CN9" t="n">
         <v>1.92</v>
@@ -4470,16 +4470,16 @@
         <v>1.2</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CR9" t="n">
         <v>1.37</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CT9" t="n">
         <v>3.16</v>
@@ -4488,19 +4488,19 @@
         <v>1.61</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY9" t="n">
         <v>1.93</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="DA9" t="n">
         <v>1.91</v>
@@ -4509,52 +4509,52 @@
         <v>1.31</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="DE9" t="n">
         <v>0.09</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DG9" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="DH9" t="n">
-        <v>83.77</v>
+        <v>83.22</v>
       </c>
       <c r="DI9" t="n">
         <v>0.13</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="DK9" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.91</v>
+        <v>35.65</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.5</v>
+        <v>12.31</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.82</v>
+        <v>12.78</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.59</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0.04</v>
@@ -4566,28 +4566,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>47.41</v>
+        <v>47.18</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.19</v>
+        <v>12.92</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.359999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.82</v>
+        <v>4.74</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.64</v>
+        <v>17.78</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="10">
@@ -4744,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>44.33</v>
+        <v>44.42</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>42.29</v>
+        <v>42.34</v>
       </c>
       <c r="DW10" t="n">
         <v>0.04</v>
@@ -5072,10 +5072,10 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>15.83</v>
+        <v>15.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>9.75</v>
+        <v>9.67</v>
       </c>
       <c r="AB11" t="n">
         <v>6.08</v>
@@ -5084,7 +5084,7 @@
         <v>22</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AE11" t="n">
         <v>1.75</v>
@@ -5378,10 +5378,10 @@
         <v>0.08</v>
       </c>
       <c r="DX11" t="n">
-        <v>13.79</v>
+        <v>13.75</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.539999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="DZ11" t="n">
         <v>5.25</v>
@@ -6209,13 +6209,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
         <v>0.08</v>
@@ -6299,52 +6299,52 @@
         <v>1.17</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH14" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="AI14" t="n">
-        <v>97.91</v>
+        <v>99</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL14" t="n">
-        <v>4.91</v>
+        <v>5.25</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AN14" t="n">
-        <v>45.55</v>
+        <v>46.25</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.91</v>
+        <v>10.08</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.550000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.449999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6356,82 +6356,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>53.09</v>
+        <v>53.5</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>15.18</v>
+        <v>15</v>
       </c>
       <c r="BB14" t="n">
-        <v>10.64</v>
+        <v>10.42</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.55</v>
+        <v>4.58</v>
       </c>
       <c r="BD14" t="n">
-        <v>15.18</v>
+        <v>15.33</v>
       </c>
       <c r="BE14" t="n">
         <v>1.61</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.74</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.35</v>
+        <v>4.46</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.39</v>
+        <v>5.42</v>
       </c>
       <c r="BR14" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS14" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BU14" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BV14" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW14" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BX14" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BY14" t="n">
         <v>2</v>
@@ -6440,25 +6440,25 @@
         <v>1.96</v>
       </c>
       <c r="CA14" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="CB14" t="n">
-        <v>4.32</v>
+        <v>4.31</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="CE14" t="n">
         <v>1.24</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.97</v>
+        <v>3.95</v>
       </c>
       <c r="CH14" t="n">
         <v>1.7</v>
@@ -6476,10 +6476,10 @@
         <v>1.79</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO14" t="n">
         <v>1.13</v>
@@ -6488,7 +6488,7 @@
         <v>1.5</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CR14" t="n">
         <v>1.38</v>
@@ -6512,13 +6512,13 @@
         <v>1.52</v>
       </c>
       <c r="CY14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DB14" t="n">
         <v>1.32</v>
@@ -6527,49 +6527,49 @@
         <v>1.49</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="DH14" t="n">
-        <v>104.74</v>
+        <v>105</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.35</v>
+        <v>5.5</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DM14" t="n">
-        <v>49.09</v>
+        <v>49.29</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.17</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.66</v>
+        <v>10.5</v>
       </c>
       <c r="DR14" t="n">
-        <v>7.35</v>
+        <v>7.29</v>
       </c>
       <c r="DS14" t="n">
         <v>0.04</v>
@@ -6581,28 +6581,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>53.61</v>
+        <v>53.79</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>16.22</v>
+        <v>16.08</v>
       </c>
       <c r="DY14" t="n">
-        <v>10.53</v>
+        <v>10.42</v>
       </c>
       <c r="DZ14" t="n">
-        <v>5.7</v>
+        <v>5.66</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.91</v>
+        <v>17.88</v>
       </c>
       <c r="EB14" t="n">
         <v>1.78</v>
       </c>
       <c r="EC14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="15">
@@ -7015,10 +7015,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
         <v>12</v>
@@ -7027,82 +7027,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="G16" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="H16" t="n">
-        <v>97.09</v>
+        <v>98.25</v>
       </c>
       <c r="I16" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="J16" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="K16" t="n">
-        <v>4.91</v>
+        <v>5.08</v>
       </c>
       <c r="L16" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="M16" t="n">
-        <v>42</v>
+        <v>44.08</v>
       </c>
       <c r="N16" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O16" t="n">
-        <v>2.64</v>
+        <v>2.83</v>
       </c>
       <c r="P16" t="n">
-        <v>9.73</v>
+        <v>9.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.55</v>
+        <v>12.92</v>
       </c>
       <c r="R16" t="n">
-        <v>6.45</v>
+        <v>6.58</v>
       </c>
       <c r="S16" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>56.27</v>
+        <v>56.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z16" t="n">
-        <v>15.45</v>
+        <v>16.17</v>
       </c>
       <c r="AA16" t="n">
-        <v>9.73</v>
+        <v>10</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.73</v>
+        <v>6.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
         <v>0.17</v>
@@ -7186,70 +7186,70 @@
         <v>1.75</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.48</v>
+        <v>9.5</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.39</v>
+        <v>4.46</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.09</v>
+        <v>5.04</v>
       </c>
       <c r="BR16" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS16" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT16" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BU16" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BV16" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BW16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX16" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="CA16" t="n">
-        <v>4.07</v>
+        <v>4.11</v>
       </c>
       <c r="CB16" t="n">
-        <v>4.1</v>
+        <v>4.16</v>
       </c>
       <c r="CC16" t="n">
         <v>2.5</v>
@@ -7258,19 +7258,19 @@
         <v>2.61</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="CH16" t="n">
         <v>1.65</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.54</v>
@@ -7279,37 +7279,37 @@
         <v>1.48</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CO16" t="n">
         <v>1.14</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CR16" t="n">
         <v>1.33</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CT16" t="n">
         <v>3.36</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CW16" t="n">
         <v>1.57</v>
@@ -7318,13 +7318,13 @@
         <v>1.57</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.36</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="DB16" t="n">
         <v>1.27</v>
@@ -7336,79 +7336,79 @@
         <v>2.46</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.78</v>
+        <v>2.75</v>
       </c>
       <c r="DH16" t="n">
-        <v>112.87</v>
+        <v>112.79</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.31</v>
+        <v>5.38</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="DM16" t="n">
-        <v>56.35</v>
+        <v>56.79</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.83</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="DQ16" t="n">
-        <v>12.22</v>
+        <v>12.42</v>
       </c>
       <c r="DR16" t="n">
-        <v>6.04</v>
+        <v>6.12</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>58.13</v>
+        <v>58.33</v>
       </c>
       <c r="DW16" t="n">
         <v>0.04</v>
       </c>
       <c r="DX16" t="n">
-        <v>14.87</v>
+        <v>15.25</v>
       </c>
       <c r="DY16" t="n">
-        <v>9.050000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5.83</v>
+        <v>6.04</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.87</v>
+        <v>19.08</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="EC16" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="17">
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>52.08</v>
+        <v>52</v>
       </c>
       <c r="Y18" t="n">
         <v>0.25</v>
@@ -8193,7 +8193,7 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>51.08</v>
+        <v>51.04</v>
       </c>
       <c r="DW18" t="n">
         <v>0.12</v>
@@ -8224,13 +8224,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" t="n">
         <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
         <v>0.17</v>
@@ -8314,139 +8314,139 @@
         <v>1.92</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AI19" t="n">
-        <v>82.36</v>
+        <v>83.25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AM19" t="n">
         <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>32.27</v>
+        <v>32.67</v>
       </c>
       <c r="AO19" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AP19" t="n">
         <v>1</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.36</v>
+        <v>10.92</v>
       </c>
       <c r="AR19" t="n">
-        <v>8.449999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="AS19" t="n">
-        <v>10</v>
+        <v>9.92</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>43.45</v>
+        <v>42.92</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.91</v>
+        <v>6.92</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="BD19" t="n">
-        <v>16.64</v>
+        <v>16.17</v>
       </c>
       <c r="BE19" t="n">
         <v>1.1</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="BH19" t="n">
-        <v>11.39</v>
+        <v>11.33</v>
       </c>
       <c r="BI19" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BL19" t="n">
         <v>1.17</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BN19" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="BO19" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.87</v>
+        <v>4.92</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.83</v>
+        <v>5.75</v>
       </c>
       <c r="BR19" t="n">
         <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT19" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BU19" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BV19" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW19" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BX19" t="n">
-        <v>78.26000000000001</v>
+        <v>75</v>
       </c>
       <c r="BY19" t="n">
         <v>2.53</v>
@@ -8455,25 +8455,25 @@
         <v>2.61</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="CB19" t="n">
-        <v>4.12</v>
+        <v>4.18</v>
       </c>
       <c r="CC19" t="n">
-        <v>4.57</v>
+        <v>4.72</v>
       </c>
       <c r="CD19" t="n">
-        <v>5.17</v>
+        <v>5.32</v>
       </c>
       <c r="CE19" t="n">
         <v>1.28</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="CH19" t="n">
         <v>1.59</v>
@@ -8482,7 +8482,7 @@
         <v>2.34</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CK19" t="n">
         <v>1.42</v>
@@ -8491,7 +8491,7 @@
         <v>1.8</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CN19" t="n">
         <v>2.04</v>
@@ -8500,25 +8500,25 @@
         <v>1.18</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="CT19" t="n">
         <v>3.16</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CW19" t="n">
         <v>1.61</v>
@@ -8533,7 +8533,7 @@
         <v>2.43</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DB19" t="n">
         <v>1.3</v>
@@ -8548,40 +8548,40 @@
         <v>0.17</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DH19" t="n">
-        <v>92.17</v>
+        <v>92.20999999999999</v>
       </c>
       <c r="DI19" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="DK19" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
      